--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>01-08-2026</t>
+          <t>02-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11903</v>
+        <v>1473.2</v>
       </c>
       <c r="D3" t="n">
-        <v>11446.68</v>
+        <v>1440.19</v>
       </c>
       <c r="E3" t="n">
-        <v>11281.17</v>
+        <v>1416.57</v>
       </c>
       <c r="F3" t="n">
-        <v>11569.56</v>
+        <v>1395.71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>5.55</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1135.3</v>
+        <v>1435.4</v>
       </c>
       <c r="D4" t="n">
-        <v>1109.24</v>
+        <v>1410.28</v>
       </c>
       <c r="E4" t="n">
-        <v>1105.8</v>
+        <v>1361.34</v>
       </c>
       <c r="F4" t="n">
-        <v>1100.59</v>
+        <v>1348.4</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>6.45</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5751.5</v>
+        <v>4646.5</v>
       </c>
       <c r="D5" t="n">
-        <v>5587.6</v>
+        <v>4479.85</v>
       </c>
       <c r="E5" t="n">
-        <v>5491.02</v>
+        <v>4409.79</v>
       </c>
       <c r="F5" t="n">
-        <v>5522.76</v>
+        <v>4345.73</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14</v>
+        <v>6.92</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1473.2</v>
+        <v>372.95</v>
       </c>
       <c r="D6" t="n">
-        <v>1440.19</v>
+        <v>357.93</v>
       </c>
       <c r="E6" t="n">
-        <v>1416.57</v>
+        <v>350.57</v>
       </c>
       <c r="F6" t="n">
-        <v>1395.71</v>
+        <v>347.65</v>
       </c>
       <c r="G6" t="n">
-        <v>5.55</v>
+        <v>7.28</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1435.4</v>
+        <v>738.55</v>
       </c>
       <c r="D7" t="n">
-        <v>1410.28</v>
+        <v>730.08</v>
       </c>
       <c r="E7" t="n">
-        <v>1361.34</v>
+        <v>705.51</v>
       </c>
       <c r="F7" t="n">
-        <v>1348.4</v>
+        <v>686.16</v>
       </c>
       <c r="G7" t="n">
-        <v>6.45</v>
+        <v>7.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2747.3</v>
+        <v>7833.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2689.12</v>
+        <v>7447.86</v>
       </c>
       <c r="E8" t="n">
-        <v>2681.37</v>
+        <v>7362.95</v>
       </c>
       <c r="F8" t="n">
-        <v>2572.85</v>
+        <v>7176.17</v>
       </c>
       <c r="G8" t="n">
-        <v>6.78</v>
+        <v>9.16</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4646.5</v>
+        <v>302.45</v>
       </c>
       <c r="D9" t="n">
-        <v>4479.85</v>
+        <v>282.98</v>
       </c>
       <c r="E9" t="n">
-        <v>4409.79</v>
+        <v>270.14</v>
       </c>
       <c r="F9" t="n">
-        <v>4345.73</v>
+        <v>273.78</v>
       </c>
       <c r="G9" t="n">
-        <v>6.92</v>
+        <v>10.47</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>372.95</v>
+        <v>613.35</v>
       </c>
       <c r="D10" t="n">
-        <v>357.93</v>
+        <v>579.77</v>
       </c>
       <c r="E10" t="n">
-        <v>350.57</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>347.65</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>7.28</v>
+        <v>10.78</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>738.55</v>
+        <v>1046.7</v>
       </c>
       <c r="D11" t="n">
-        <v>730.08</v>
+        <v>1034.29</v>
       </c>
       <c r="E11" t="n">
-        <v>705.51</v>
+        <v>997.16</v>
       </c>
       <c r="F11" t="n">
-        <v>686.16</v>
+        <v>944.85</v>
       </c>
       <c r="G11" t="n">
-        <v>7.63</v>
+        <v>10.78</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7833.5</v>
+        <v>2105.7</v>
       </c>
       <c r="D12" t="n">
-        <v>7447.86</v>
+        <v>2010.06</v>
       </c>
       <c r="E12" t="n">
-        <v>7362.95</v>
+        <v>1895.79</v>
       </c>
       <c r="F12" t="n">
-        <v>7176.17</v>
+        <v>1880.5</v>
       </c>
       <c r="G12" t="n">
-        <v>9.16</v>
+        <v>11.98</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>302.45</v>
+        <v>1651.3</v>
       </c>
       <c r="D13" t="n">
-        <v>282.98</v>
+        <v>1487.74</v>
       </c>
       <c r="E13" t="n">
-        <v>270.14</v>
+        <v>1465.74</v>
       </c>
       <c r="F13" t="n">
-        <v>273.78</v>
+        <v>1460.05</v>
       </c>
       <c r="G13" t="n">
-        <v>10.47</v>
+        <v>13.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1046.7</v>
+        <v>14049</v>
       </c>
       <c r="D14" t="n">
-        <v>1034.29</v>
+        <v>13241.63</v>
       </c>
       <c r="E14" t="n">
-        <v>997.16</v>
+        <v>12652.22</v>
       </c>
       <c r="F14" t="n">
-        <v>944.85</v>
+        <v>12318.22</v>
       </c>
       <c r="G14" t="n">
-        <v>10.78</v>
+        <v>14.05</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>613.35</v>
+        <v>1721</v>
       </c>
       <c r="D15" t="n">
-        <v>579.77</v>
+        <v>1514.7</v>
       </c>
       <c r="E15" t="n">
-        <v>544.3099999999999</v>
+        <v>1478.89</v>
       </c>
       <c r="F15" t="n">
-        <v>553.6900000000001</v>
+        <v>1508.07</v>
       </c>
       <c r="G15" t="n">
-        <v>10.78</v>
+        <v>14.12</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2105.7</v>
+        <v>2199.8</v>
       </c>
       <c r="D16" t="n">
-        <v>2010.06</v>
+        <v>2146.11</v>
       </c>
       <c r="E16" t="n">
-        <v>1895.79</v>
+        <v>2067.23</v>
       </c>
       <c r="F16" t="n">
-        <v>1880.5</v>
+        <v>1708.73</v>
       </c>
       <c r="G16" t="n">
-        <v>11.98</v>
+        <v>28.74</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1013,191 +1013,6 @@
         </is>
       </c>
       <c r="I16" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>02-08-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>3760</v>
-      </c>
-      <c r="D17" t="n">
-        <v>3594.93</v>
-      </c>
-      <c r="E17" t="n">
-        <v>3627.18</v>
-      </c>
-      <c r="F17" t="n">
-        <v>3333.67</v>
-      </c>
-      <c r="G17" t="n">
-        <v>12.79</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>02-08-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1651.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1487.74</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1465.74</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1460.05</v>
-      </c>
-      <c r="G18" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>02-08-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>14049</v>
-      </c>
-      <c r="D19" t="n">
-        <v>13241.63</v>
-      </c>
-      <c r="E19" t="n">
-        <v>12652.22</v>
-      </c>
-      <c r="F19" t="n">
-        <v>12318.22</v>
-      </c>
-      <c r="G19" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>02-08-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1721</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1514.7</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1478.89</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1508.07</v>
-      </c>
-      <c r="G20" t="n">
-        <v>14.12</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>02-08-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2199.8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2146.11</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2067.23</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1708.73</v>
-      </c>
-      <c r="G21" t="n">
-        <v>28.74</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1473.2</v>
+        <v>11903</v>
       </c>
       <c r="D3" t="n">
-        <v>1440.19</v>
+        <v>11446.68</v>
       </c>
       <c r="E3" t="n">
-        <v>1416.57</v>
+        <v>11281.17</v>
       </c>
       <c r="F3" t="n">
-        <v>1395.71</v>
+        <v>11569.56</v>
       </c>
       <c r="G3" t="n">
-        <v>5.55</v>
+        <v>2.88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1435.4</v>
+        <v>1135.3</v>
       </c>
       <c r="D4" t="n">
-        <v>1410.28</v>
+        <v>1109.24</v>
       </c>
       <c r="E4" t="n">
-        <v>1361.34</v>
+        <v>1105.8</v>
       </c>
       <c r="F4" t="n">
-        <v>1348.4</v>
+        <v>1100.59</v>
       </c>
       <c r="G4" t="n">
-        <v>6.45</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4646.5</v>
+        <v>5751.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4479.85</v>
+        <v>5587.6</v>
       </c>
       <c r="E5" t="n">
-        <v>4409.79</v>
+        <v>5491.02</v>
       </c>
       <c r="F5" t="n">
-        <v>4345.73</v>
+        <v>5522.76</v>
       </c>
       <c r="G5" t="n">
-        <v>6.92</v>
+        <v>4.14</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>372.95</v>
+        <v>1473.2</v>
       </c>
       <c r="D6" t="n">
-        <v>357.93</v>
+        <v>1440.19</v>
       </c>
       <c r="E6" t="n">
-        <v>350.57</v>
+        <v>1416.57</v>
       </c>
       <c r="F6" t="n">
-        <v>347.65</v>
+        <v>1395.71</v>
       </c>
       <c r="G6" t="n">
-        <v>7.28</v>
+        <v>5.55</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>738.55</v>
+        <v>1435.4</v>
       </c>
       <c r="D7" t="n">
-        <v>730.08</v>
+        <v>1410.28</v>
       </c>
       <c r="E7" t="n">
-        <v>705.51</v>
+        <v>1361.34</v>
       </c>
       <c r="F7" t="n">
-        <v>686.16</v>
+        <v>1348.4</v>
       </c>
       <c r="G7" t="n">
-        <v>7.63</v>
+        <v>6.45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>7833.5</v>
+        <v>2747.3</v>
       </c>
       <c r="D8" t="n">
-        <v>7447.86</v>
+        <v>2689.12</v>
       </c>
       <c r="E8" t="n">
-        <v>7362.95</v>
+        <v>2681.37</v>
       </c>
       <c r="F8" t="n">
-        <v>7176.17</v>
+        <v>2572.85</v>
       </c>
       <c r="G8" t="n">
-        <v>9.16</v>
+        <v>6.78</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>302.45</v>
+        <v>4646.5</v>
       </c>
       <c r="D9" t="n">
-        <v>282.98</v>
+        <v>4479.85</v>
       </c>
       <c r="E9" t="n">
-        <v>270.14</v>
+        <v>4409.79</v>
       </c>
       <c r="F9" t="n">
-        <v>273.78</v>
+        <v>4345.73</v>
       </c>
       <c r="G9" t="n">
-        <v>10.47</v>
+        <v>6.92</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>613.35</v>
+        <v>372.95</v>
       </c>
       <c r="D10" t="n">
-        <v>579.77</v>
+        <v>357.93</v>
       </c>
       <c r="E10" t="n">
-        <v>544.3099999999999</v>
+        <v>350.57</v>
       </c>
       <c r="F10" t="n">
-        <v>553.6900000000001</v>
+        <v>347.65</v>
       </c>
       <c r="G10" t="n">
-        <v>10.78</v>
+        <v>7.28</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1046.7</v>
+        <v>738.55</v>
       </c>
       <c r="D11" t="n">
-        <v>1034.29</v>
+        <v>730.08</v>
       </c>
       <c r="E11" t="n">
-        <v>997.16</v>
+        <v>705.51</v>
       </c>
       <c r="F11" t="n">
-        <v>944.85</v>
+        <v>686.16</v>
       </c>
       <c r="G11" t="n">
-        <v>10.78</v>
+        <v>7.63</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2105.7</v>
+        <v>7833.5</v>
       </c>
       <c r="D12" t="n">
-        <v>2010.06</v>
+        <v>7447.86</v>
       </c>
       <c r="E12" t="n">
-        <v>1895.79</v>
+        <v>7362.95</v>
       </c>
       <c r="F12" t="n">
-        <v>1880.5</v>
+        <v>7176.17</v>
       </c>
       <c r="G12" t="n">
-        <v>11.98</v>
+        <v>9.16</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1651.3</v>
+        <v>302.45</v>
       </c>
       <c r="D13" t="n">
-        <v>1487.74</v>
+        <v>282.98</v>
       </c>
       <c r="E13" t="n">
-        <v>1465.74</v>
+        <v>270.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1460.05</v>
+        <v>273.78</v>
       </c>
       <c r="G13" t="n">
-        <v>13.1</v>
+        <v>10.47</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14049</v>
+        <v>1046.7</v>
       </c>
       <c r="D14" t="n">
-        <v>13241.63</v>
+        <v>1034.29</v>
       </c>
       <c r="E14" t="n">
-        <v>12652.22</v>
+        <v>997.16</v>
       </c>
       <c r="F14" t="n">
-        <v>12318.22</v>
+        <v>944.85</v>
       </c>
       <c r="G14" t="n">
-        <v>14.05</v>
+        <v>10.78</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1721</v>
+        <v>613.35</v>
       </c>
       <c r="D15" t="n">
-        <v>1514.7</v>
+        <v>579.77</v>
       </c>
       <c r="E15" t="n">
-        <v>1478.89</v>
+        <v>544.3099999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1508.07</v>
+        <v>553.6900000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>14.12</v>
+        <v>10.78</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,30 +989,215 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2105.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2010.06</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1895.79</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1880.5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SIEMENS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3760</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3594.93</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3627.18</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3333.67</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.79</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1651.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1487.74</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1465.74</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1460.05</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>14049</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13241.63</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12652.22</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12318.22</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1721</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1514.7</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1478.89</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1508.07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>02-08-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>BHARATFORG</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C21" t="n">
         <v>2199.8</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D21" t="n">
         <v>2146.11</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E21" t="n">
         <v>2067.23</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F21" t="n">
         <v>1708.73</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G21" t="n">
         <v>28.74</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>112.71</v>
+        <v>113.61</v>
       </c>
       <c r="D2" t="n">
-        <v>107.8</v>
+        <v>107.92</v>
       </c>
       <c r="E2" t="n">
-        <v>106.57</v>
+        <v>106.77</v>
       </c>
       <c r="F2" t="n">
-        <v>112.63</v>
+        <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.87</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11903</v>
+        <v>11980</v>
       </c>
       <c r="D3" t="n">
-        <v>11446.68</v>
+        <v>11473.55</v>
       </c>
       <c r="E3" t="n">
-        <v>11281.17</v>
+        <v>11290.94</v>
       </c>
       <c r="F3" t="n">
-        <v>11569.56</v>
+        <v>11570.32</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>3.54</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1135.3</v>
+        <v>5774.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1109.24</v>
+        <v>5601.18</v>
       </c>
       <c r="E4" t="n">
-        <v>1105.8</v>
+        <v>5498.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1100.59</v>
+        <v>5524.39</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>4.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5751.5</v>
+        <v>1153.6</v>
       </c>
       <c r="D5" t="n">
-        <v>5587.6</v>
+        <v>1109.72</v>
       </c>
       <c r="E5" t="n">
-        <v>5491.02</v>
+        <v>1106.03</v>
       </c>
       <c r="F5" t="n">
-        <v>5522.76</v>
+        <v>1100.92</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14</v>
+        <v>4.79</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1473.2</v>
+        <v>1112.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1440.19</v>
+        <v>1108</v>
       </c>
       <c r="E6" t="n">
-        <v>1416.57</v>
+        <v>1066.97</v>
       </c>
       <c r="F6" t="n">
-        <v>1395.71</v>
+        <v>1056.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.55</v>
+        <v>5.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1435.4</v>
+        <v>1475</v>
       </c>
       <c r="D7" t="n">
-        <v>1410.28</v>
+        <v>1442.16</v>
       </c>
       <c r="E7" t="n">
-        <v>1361.34</v>
+        <v>1418.06</v>
       </c>
       <c r="F7" t="n">
-        <v>1348.4</v>
+        <v>1395.4</v>
       </c>
       <c r="G7" t="n">
-        <v>6.45</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2747.3</v>
+        <v>1434.2</v>
       </c>
       <c r="D8" t="n">
-        <v>2689.12</v>
+        <v>1401.6</v>
       </c>
       <c r="E8" t="n">
-        <v>2681.37</v>
+        <v>1353.03</v>
       </c>
       <c r="F8" t="n">
-        <v>2572.85</v>
+        <v>1337.43</v>
       </c>
       <c r="G8" t="n">
-        <v>6.78</v>
+        <v>7.24</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4646.5</v>
+        <v>4666</v>
       </c>
       <c r="D9" t="n">
-        <v>4479.85</v>
+        <v>4484.87</v>
       </c>
       <c r="E9" t="n">
-        <v>4409.79</v>
+        <v>4414.59</v>
       </c>
       <c r="F9" t="n">
-        <v>4345.73</v>
+        <v>4345.52</v>
       </c>
       <c r="G9" t="n">
-        <v>6.92</v>
+        <v>7.38</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>372.95</v>
+        <v>2770.9</v>
       </c>
       <c r="D10" t="n">
-        <v>357.93</v>
+        <v>2693.12</v>
       </c>
       <c r="E10" t="n">
-        <v>350.57</v>
+        <v>2684.09</v>
       </c>
       <c r="F10" t="n">
-        <v>347.65</v>
+        <v>2575.23</v>
       </c>
       <c r="G10" t="n">
-        <v>7.28</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>738.55</v>
+        <v>374.9</v>
       </c>
       <c r="D11" t="n">
-        <v>730.08</v>
+        <v>358.24</v>
       </c>
       <c r="E11" t="n">
-        <v>705.51</v>
+        <v>351.3</v>
       </c>
       <c r="F11" t="n">
-        <v>686.16</v>
+        <v>347.76</v>
       </c>
       <c r="G11" t="n">
-        <v>7.63</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7833.5</v>
+        <v>742.6</v>
       </c>
       <c r="D12" t="n">
-        <v>7447.86</v>
+        <v>730.5</v>
       </c>
       <c r="E12" t="n">
-        <v>7362.95</v>
+        <v>707.15</v>
       </c>
       <c r="F12" t="n">
-        <v>7176.17</v>
+        <v>686.29</v>
       </c>
       <c r="G12" t="n">
-        <v>9.16</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>302.45</v>
+        <v>7900</v>
       </c>
       <c r="D13" t="n">
-        <v>282.98</v>
+        <v>7459.18</v>
       </c>
       <c r="E13" t="n">
-        <v>270.14</v>
+        <v>7374.2</v>
       </c>
       <c r="F13" t="n">
-        <v>273.78</v>
+        <v>7181.6</v>
       </c>
       <c r="G13" t="n">
-        <v>10.47</v>
+        <v>10</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1046.7</v>
+        <v>613.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1034.29</v>
+        <v>581.3099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>997.16</v>
+        <v>547.16</v>
       </c>
       <c r="F14" t="n">
-        <v>944.85</v>
+        <v>553.91</v>
       </c>
       <c r="G14" t="n">
-        <v>10.78</v>
+        <v>10.81</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>613.35</v>
+        <v>303.5</v>
       </c>
       <c r="D15" t="n">
-        <v>579.77</v>
+        <v>284.3</v>
       </c>
       <c r="E15" t="n">
-        <v>544.3099999999999</v>
+        <v>271.26</v>
       </c>
       <c r="F15" t="n">
-        <v>553.6900000000001</v>
+        <v>273.56</v>
       </c>
       <c r="G15" t="n">
-        <v>10.78</v>
+        <v>10.94</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2105.7</v>
+        <v>3730</v>
       </c>
       <c r="D16" t="n">
-        <v>2010.06</v>
+        <v>3594.29</v>
       </c>
       <c r="E16" t="n">
-        <v>1895.79</v>
+        <v>3628.79</v>
       </c>
       <c r="F16" t="n">
-        <v>1880.5</v>
+        <v>3337.01</v>
       </c>
       <c r="G16" t="n">
-        <v>11.98</v>
+        <v>11.78</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3760</v>
+        <v>1059.9</v>
       </c>
       <c r="D17" t="n">
-        <v>3594.93</v>
+        <v>1036.71</v>
       </c>
       <c r="E17" t="n">
-        <v>3627.18</v>
+        <v>999.23</v>
       </c>
       <c r="F17" t="n">
-        <v>3333.67</v>
+        <v>946.8200000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>12.79</v>
+        <v>11.94</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1651.3</v>
+        <v>2105.7</v>
       </c>
       <c r="D18" t="n">
-        <v>1487.74</v>
+        <v>2010.06</v>
       </c>
       <c r="E18" t="n">
-        <v>1465.74</v>
+        <v>1895.79</v>
       </c>
       <c r="F18" t="n">
-        <v>1460.05</v>
+        <v>1880.5</v>
       </c>
       <c r="G18" t="n">
-        <v>13.1</v>
+        <v>11.98</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14049</v>
+        <v>13875</v>
       </c>
       <c r="D19" t="n">
-        <v>13241.63</v>
+        <v>13292.93</v>
       </c>
       <c r="E19" t="n">
-        <v>12652.22</v>
+        <v>12693.24</v>
       </c>
       <c r="F19" t="n">
-        <v>12318.22</v>
+        <v>12304.43</v>
       </c>
       <c r="G19" t="n">
-        <v>14.05</v>
+        <v>12.76</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1721</v>
+        <v>1661.7</v>
       </c>
       <c r="D20" t="n">
-        <v>1514.7</v>
+        <v>1496.5</v>
       </c>
       <c r="E20" t="n">
-        <v>1478.89</v>
+        <v>1470.99</v>
       </c>
       <c r="F20" t="n">
-        <v>1508.07</v>
+        <v>1461.27</v>
       </c>
       <c r="G20" t="n">
-        <v>14.12</v>
+        <v>13.72</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,35 +1169,72 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>02-08-2026</t>
+          <t>03-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1739</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1519.91</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1482.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1504.84</v>
+      </c>
+      <c r="G21" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>03-08-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>BHARATFORG</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>2199.8</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2146.11</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2067.23</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1708.73</v>
-      </c>
-      <c r="G21" t="n">
-        <v>28.74</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="C22" t="n">
+        <v>2218</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2150.13</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2073.34</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1713.71</v>
+      </c>
+      <c r="G22" t="n">
+        <v>29.43</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.61</v>
+        <v>113.98</v>
       </c>
       <c r="D2" t="n">
-        <v>107.92</v>
+        <v>107.93</v>
       </c>
       <c r="E2" t="n">
-        <v>106.77</v>
+        <v>106.78</v>
       </c>
       <c r="F2" t="n">
         <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>0.87</v>
+        <v>1.19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11980</v>
+        <v>5705.5</v>
       </c>
       <c r="D3" t="n">
-        <v>11473.55</v>
+        <v>5598.88</v>
       </c>
       <c r="E3" t="n">
-        <v>11290.94</v>
+        <v>5497.12</v>
       </c>
       <c r="F3" t="n">
-        <v>11570.32</v>
+        <v>5524.05</v>
       </c>
       <c r="G3" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5774.5</v>
+        <v>11963</v>
       </c>
       <c r="D4" t="n">
-        <v>5601.18</v>
+        <v>11472.98</v>
       </c>
       <c r="E4" t="n">
-        <v>5498.5</v>
+        <v>11290.6</v>
       </c>
       <c r="F4" t="n">
-        <v>5524.39</v>
+        <v>11570.23</v>
       </c>
       <c r="G4" t="n">
-        <v>4.53</v>
+        <v>3.39</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1153.6</v>
+        <v>1108.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1109.72</v>
+        <v>1107.88</v>
       </c>
       <c r="E5" t="n">
-        <v>1106.03</v>
+        <v>1066.9</v>
       </c>
       <c r="F5" t="n">
-        <v>1100.92</v>
+        <v>1056.09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.79</v>
+        <v>4.97</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1112.1</v>
+        <v>1156.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1108</v>
+        <v>1109.82</v>
       </c>
       <c r="E6" t="n">
-        <v>1066.97</v>
+        <v>1106.09</v>
       </c>
       <c r="F6" t="n">
-        <v>1056.1</v>
+        <v>1100.93</v>
       </c>
       <c r="G6" t="n">
-        <v>5.3</v>
+        <v>5.07</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1475</v>
+        <v>1472.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1442.16</v>
+        <v>1442.07</v>
       </c>
       <c r="E7" t="n">
-        <v>1418.06</v>
+        <v>1418</v>
       </c>
       <c r="F7" t="n">
-        <v>1395.4</v>
+        <v>1395.39</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1434.2</v>
+        <v>373.15</v>
       </c>
       <c r="D8" t="n">
-        <v>1401.6</v>
+        <v>358.18</v>
       </c>
       <c r="E8" t="n">
-        <v>1353.03</v>
+        <v>351.27</v>
       </c>
       <c r="F8" t="n">
-        <v>1337.43</v>
+        <v>347.75</v>
       </c>
       <c r="G8" t="n">
-        <v>7.24</v>
+        <v>7.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4666</v>
+        <v>4665</v>
       </c>
       <c r="D9" t="n">
-        <v>4484.87</v>
+        <v>4484.84</v>
       </c>
       <c r="E9" t="n">
-        <v>4414.59</v>
+        <v>4414.57</v>
       </c>
       <c r="F9" t="n">
-        <v>4345.52</v>
+        <v>4345.51</v>
       </c>
       <c r="G9" t="n">
-        <v>7.38</v>
+        <v>7.35</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2770.9</v>
+        <v>2771.8</v>
       </c>
       <c r="D10" t="n">
-        <v>2693.12</v>
+        <v>2693.15</v>
       </c>
       <c r="E10" t="n">
-        <v>2684.09</v>
+        <v>2684.1</v>
       </c>
       <c r="F10" t="n">
         <v>2575.23</v>
       </c>
       <c r="G10" t="n">
-        <v>7.6</v>
+        <v>7.63</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>374.9</v>
+        <v>1445</v>
       </c>
       <c r="D11" t="n">
-        <v>358.24</v>
+        <v>1401.96</v>
       </c>
       <c r="E11" t="n">
-        <v>351.3</v>
+        <v>1353.24</v>
       </c>
       <c r="F11" t="n">
-        <v>347.76</v>
+        <v>1337.49</v>
       </c>
       <c r="G11" t="n">
-        <v>7.8</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>742.6</v>
+        <v>744</v>
       </c>
       <c r="D12" t="n">
-        <v>730.5</v>
+        <v>730.55</v>
       </c>
       <c r="E12" t="n">
-        <v>707.15</v>
+        <v>707.1799999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>686.29</v>
+        <v>686.3</v>
       </c>
       <c r="G12" t="n">
-        <v>8.210000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7900</v>
+        <v>2091</v>
       </c>
       <c r="D13" t="n">
-        <v>7459.18</v>
+        <v>2020.09</v>
       </c>
       <c r="E13" t="n">
-        <v>7374.2</v>
+        <v>1902.44</v>
       </c>
       <c r="F13" t="n">
-        <v>7181.6</v>
+        <v>1880.72</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>11.18</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>613.8</v>
+        <v>618.85</v>
       </c>
       <c r="D14" t="n">
-        <v>581.3099999999999</v>
+        <v>581.48</v>
       </c>
       <c r="E14" t="n">
-        <v>547.16</v>
+        <v>547.26</v>
       </c>
       <c r="F14" t="n">
-        <v>553.91</v>
+        <v>553.9400000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>10.81</v>
+        <v>11.72</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>303.5</v>
+        <v>305.75</v>
       </c>
       <c r="D15" t="n">
-        <v>284.3</v>
+        <v>284.38</v>
       </c>
       <c r="E15" t="n">
-        <v>271.26</v>
+        <v>271.3</v>
       </c>
       <c r="F15" t="n">
-        <v>273.56</v>
+        <v>273.57</v>
       </c>
       <c r="G15" t="n">
-        <v>10.94</v>
+        <v>11.76</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3730</v>
+        <v>8043.5</v>
       </c>
       <c r="D16" t="n">
-        <v>3594.29</v>
+        <v>7463.96</v>
       </c>
       <c r="E16" t="n">
-        <v>3628.79</v>
+        <v>7377.07</v>
       </c>
       <c r="F16" t="n">
-        <v>3337.01</v>
+        <v>7182.31</v>
       </c>
       <c r="G16" t="n">
-        <v>11.78</v>
+        <v>11.99</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1059.9</v>
+        <v>1639.2</v>
       </c>
       <c r="D17" t="n">
-        <v>1036.71</v>
+        <v>1495.75</v>
       </c>
       <c r="E17" t="n">
-        <v>999.23</v>
+        <v>1470.54</v>
       </c>
       <c r="F17" t="n">
-        <v>946.8200000000001</v>
+        <v>1461.16</v>
       </c>
       <c r="G17" t="n">
-        <v>11.94</v>
+        <v>12.18</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2105.7</v>
+        <v>13935</v>
       </c>
       <c r="D18" t="n">
-        <v>2010.06</v>
+        <v>13294.93</v>
       </c>
       <c r="E18" t="n">
-        <v>1895.79</v>
+        <v>12694.44</v>
       </c>
       <c r="F18" t="n">
-        <v>1880.5</v>
+        <v>12304.73</v>
       </c>
       <c r="G18" t="n">
-        <v>11.98</v>
+        <v>13.25</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>13875</v>
+        <v>1729.2</v>
       </c>
       <c r="D19" t="n">
-        <v>13292.93</v>
+        <v>1519.58</v>
       </c>
       <c r="E19" t="n">
-        <v>12693.24</v>
+        <v>1482.21</v>
       </c>
       <c r="F19" t="n">
-        <v>12304.43</v>
+        <v>1504.79</v>
       </c>
       <c r="G19" t="n">
-        <v>12.76</v>
+        <v>14.91</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1661.7</v>
+        <v>1093.5</v>
       </c>
       <c r="D20" t="n">
-        <v>1496.5</v>
+        <v>1037.83</v>
       </c>
       <c r="E20" t="n">
-        <v>1470.99</v>
+        <v>999.9</v>
       </c>
       <c r="F20" t="n">
-        <v>1461.27</v>
+        <v>946.99</v>
       </c>
       <c r="G20" t="n">
-        <v>13.72</v>
+        <v>15.47</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1739</v>
+        <v>3877.1</v>
       </c>
       <c r="D21" t="n">
-        <v>1519.91</v>
+        <v>3598.84</v>
       </c>
       <c r="E21" t="n">
-        <v>1482.4</v>
+        <v>3629.53</v>
       </c>
       <c r="F21" t="n">
-        <v>1504.84</v>
+        <v>3334.26</v>
       </c>
       <c r="G21" t="n">
-        <v>15.56</v>
+        <v>16.28</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1198,43 +1198,6 @@
         </is>
       </c>
       <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>03-08-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>2218</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2150.13</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2073.34</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1713.71</v>
-      </c>
-      <c r="G22" t="n">
-        <v>29.43</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.98</v>
+        <v>113.36</v>
       </c>
       <c r="D2" t="n">
-        <v>107.93</v>
+        <v>107.91</v>
       </c>
       <c r="E2" t="n">
-        <v>106.78</v>
+        <v>106.77</v>
       </c>
       <c r="F2" t="n">
-        <v>112.64</v>
+        <v>112.63</v>
       </c>
       <c r="G2" t="n">
-        <v>1.19</v>
+        <v>0.64</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5705.5</v>
+        <v>5690.5</v>
       </c>
       <c r="D3" t="n">
-        <v>5598.88</v>
+        <v>5598.38</v>
       </c>
       <c r="E3" t="n">
-        <v>5497.12</v>
+        <v>5496.82</v>
       </c>
       <c r="F3" t="n">
-        <v>5524.05</v>
+        <v>5523.97</v>
       </c>
       <c r="G3" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11963</v>
+        <v>11957</v>
       </c>
       <c r="D4" t="n">
-        <v>11472.98</v>
+        <v>11472.78</v>
       </c>
       <c r="E4" t="n">
-        <v>11290.6</v>
+        <v>11290.48</v>
       </c>
       <c r="F4" t="n">
-        <v>11570.23</v>
+        <v>11570.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1108.6</v>
+        <v>1457.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1107.88</v>
+        <v>1441.59</v>
       </c>
       <c r="E5" t="n">
-        <v>1066.9</v>
+        <v>1417.71</v>
       </c>
       <c r="F5" t="n">
-        <v>1056.09</v>
+        <v>1395.31</v>
       </c>
       <c r="G5" t="n">
-        <v>4.97</v>
+        <v>4.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1156.8</v>
+        <v>1153.9</v>
       </c>
       <c r="D6" t="n">
-        <v>1109.82</v>
+        <v>1109.73</v>
       </c>
       <c r="E6" t="n">
-        <v>1106.09</v>
+        <v>1106.03</v>
       </c>
       <c r="F6" t="n">
-        <v>1100.93</v>
+        <v>1100.92</v>
       </c>
       <c r="G6" t="n">
-        <v>5.07</v>
+        <v>4.81</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1472.1</v>
+        <v>368</v>
       </c>
       <c r="D7" t="n">
-        <v>1442.07</v>
+        <v>358.01</v>
       </c>
       <c r="E7" t="n">
-        <v>1418</v>
+        <v>351.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1395.39</v>
+        <v>347.72</v>
       </c>
       <c r="G7" t="n">
-        <v>5.5</v>
+        <v>5.83</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>373.15</v>
+        <v>4668.6</v>
       </c>
       <c r="D8" t="n">
-        <v>358.18</v>
+        <v>4484.96</v>
       </c>
       <c r="E8" t="n">
-        <v>351.27</v>
+        <v>4414.65</v>
       </c>
       <c r="F8" t="n">
-        <v>347.75</v>
+        <v>4345.53</v>
       </c>
       <c r="G8" t="n">
-        <v>7.3</v>
+        <v>7.43</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4665</v>
+        <v>2786.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4484.84</v>
+        <v>2693.63</v>
       </c>
       <c r="E9" t="n">
-        <v>4414.57</v>
+        <v>2684.4</v>
       </c>
       <c r="F9" t="n">
-        <v>4345.51</v>
+        <v>2575.31</v>
       </c>
       <c r="G9" t="n">
-        <v>7.35</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2771.8</v>
+        <v>1448.9</v>
       </c>
       <c r="D10" t="n">
-        <v>2693.15</v>
+        <v>1402.09</v>
       </c>
       <c r="E10" t="n">
-        <v>2684.1</v>
+        <v>1353.32</v>
       </c>
       <c r="F10" t="n">
-        <v>2575.23</v>
+        <v>1337.51</v>
       </c>
       <c r="G10" t="n">
-        <v>7.63</v>
+        <v>8.33</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1445</v>
+        <v>747.6</v>
       </c>
       <c r="D11" t="n">
-        <v>1401.96</v>
+        <v>730.67</v>
       </c>
       <c r="E11" t="n">
-        <v>1353.24</v>
+        <v>707.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1337.49</v>
+        <v>686.3099999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>8.039999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>744</v>
+        <v>2070.4</v>
       </c>
       <c r="D12" t="n">
-        <v>730.55</v>
+        <v>2019.4</v>
       </c>
       <c r="E12" t="n">
-        <v>707.1799999999999</v>
+        <v>1902.02</v>
       </c>
       <c r="F12" t="n">
-        <v>686.3</v>
+        <v>1880.62</v>
       </c>
       <c r="G12" t="n">
-        <v>8.41</v>
+        <v>10.09</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2091</v>
+        <v>7990</v>
       </c>
       <c r="D13" t="n">
-        <v>2020.09</v>
+        <v>7462.18</v>
       </c>
       <c r="E13" t="n">
-        <v>1902.44</v>
+        <v>7376</v>
       </c>
       <c r="F13" t="n">
-        <v>1880.72</v>
+        <v>7182.05</v>
       </c>
       <c r="G13" t="n">
-        <v>11.18</v>
+        <v>11.25</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>618.85</v>
+        <v>621.2</v>
       </c>
       <c r="D14" t="n">
-        <v>581.48</v>
+        <v>581.5599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>547.26</v>
+        <v>547.3099999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>553.9400000000001</v>
+        <v>553.95</v>
       </c>
       <c r="G14" t="n">
-        <v>11.72</v>
+        <v>12.14</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>305.75</v>
+        <v>1647.9</v>
       </c>
       <c r="D15" t="n">
-        <v>284.38</v>
+        <v>1496.04</v>
       </c>
       <c r="E15" t="n">
-        <v>271.3</v>
+        <v>1470.72</v>
       </c>
       <c r="F15" t="n">
-        <v>273.57</v>
+        <v>1461.21</v>
       </c>
       <c r="G15" t="n">
-        <v>11.76</v>
+        <v>12.78</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8043.5</v>
+        <v>13886</v>
       </c>
       <c r="D16" t="n">
-        <v>7463.96</v>
+        <v>13293.3</v>
       </c>
       <c r="E16" t="n">
-        <v>7377.07</v>
+        <v>12693.46</v>
       </c>
       <c r="F16" t="n">
-        <v>7182.31</v>
+        <v>12304.48</v>
       </c>
       <c r="G16" t="n">
-        <v>11.99</v>
+        <v>12.85</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1639.2</v>
+        <v>311.45</v>
       </c>
       <c r="D17" t="n">
-        <v>1495.75</v>
+        <v>284.57</v>
       </c>
       <c r="E17" t="n">
-        <v>1470.54</v>
+        <v>271.42</v>
       </c>
       <c r="F17" t="n">
-        <v>1461.16</v>
+        <v>273.6</v>
       </c>
       <c r="G17" t="n">
-        <v>12.18</v>
+        <v>13.83</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>13935</v>
+        <v>1085.6</v>
       </c>
       <c r="D18" t="n">
-        <v>13294.93</v>
+        <v>1037.57</v>
       </c>
       <c r="E18" t="n">
-        <v>12694.44</v>
+        <v>999.74</v>
       </c>
       <c r="F18" t="n">
-        <v>12304.73</v>
+        <v>946.95</v>
       </c>
       <c r="G18" t="n">
-        <v>13.25</v>
+        <v>14.64</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1729.2</v>
+        <v>1743.8</v>
       </c>
       <c r="D19" t="n">
-        <v>1519.58</v>
+        <v>1520.07</v>
       </c>
       <c r="E19" t="n">
-        <v>1482.21</v>
+        <v>1482.5</v>
       </c>
       <c r="F19" t="n">
-        <v>1504.79</v>
+        <v>1504.86</v>
       </c>
       <c r="G19" t="n">
-        <v>14.91</v>
+        <v>15.88</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>03-08-2026</t>
+          <t>04-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1093.5</v>
+        <v>2201.8</v>
       </c>
       <c r="D20" t="n">
-        <v>1037.83</v>
+        <v>2149.59</v>
       </c>
       <c r="E20" t="n">
-        <v>999.9</v>
+        <v>2073.02</v>
       </c>
       <c r="F20" t="n">
-        <v>946.99</v>
+        <v>1713.63</v>
       </c>
       <c r="G20" t="n">
-        <v>15.47</v>
+        <v>28.49</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1161,43 +1161,6 @@
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>03-08-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SIEMENS</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3877.1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>3598.84</v>
-      </c>
-      <c r="E21" t="n">
-        <v>3629.53</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3334.26</v>
-      </c>
-      <c r="G21" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.36</v>
+        <v>113.55</v>
       </c>
       <c r="D2" t="n">
-        <v>107.91</v>
+        <v>107.92</v>
       </c>
       <c r="E2" t="n">
         <v>106.77</v>
       </c>
       <c r="F2" t="n">
-        <v>112.63</v>
+        <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5690.5</v>
+        <v>5687.5</v>
       </c>
       <c r="D3" t="n">
-        <v>5598.38</v>
+        <v>5598.28</v>
       </c>
       <c r="E3" t="n">
-        <v>5496.82</v>
+        <v>5496.76</v>
       </c>
       <c r="F3" t="n">
-        <v>5523.97</v>
+        <v>5523.96</v>
       </c>
       <c r="G3" t="n">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11957</v>
+        <v>11988</v>
       </c>
       <c r="D4" t="n">
-        <v>11472.78</v>
+        <v>11473.82</v>
       </c>
       <c r="E4" t="n">
-        <v>11290.48</v>
+        <v>11291.1</v>
       </c>
       <c r="F4" t="n">
-        <v>11570.2</v>
+        <v>11570.36</v>
       </c>
       <c r="G4" t="n">
-        <v>3.34</v>
+        <v>3.61</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1457.7</v>
+        <v>1455</v>
       </c>
       <c r="D5" t="n">
-        <v>1441.59</v>
+        <v>1441.5</v>
       </c>
       <c r="E5" t="n">
-        <v>1417.71</v>
+        <v>1417.66</v>
       </c>
       <c r="F5" t="n">
-        <v>1395.31</v>
+        <v>1395.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.47</v>
+        <v>4.28</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1153.9</v>
+        <v>1163</v>
       </c>
       <c r="D6" t="n">
-        <v>1109.73</v>
+        <v>1110.03</v>
       </c>
       <c r="E6" t="n">
-        <v>1106.03</v>
+        <v>1106.22</v>
       </c>
       <c r="F6" t="n">
-        <v>1100.92</v>
+        <v>1100.96</v>
       </c>
       <c r="G6" t="n">
-        <v>4.81</v>
+        <v>5.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>368</v>
+        <v>369.75</v>
       </c>
       <c r="D7" t="n">
-        <v>358.01</v>
+        <v>358.07</v>
       </c>
       <c r="E7" t="n">
-        <v>351.17</v>
+        <v>351.2</v>
       </c>
       <c r="F7" t="n">
-        <v>347.72</v>
+        <v>347.73</v>
       </c>
       <c r="G7" t="n">
-        <v>5.83</v>
+        <v>6.33</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4668.6</v>
+        <v>4678</v>
       </c>
       <c r="D8" t="n">
-        <v>4484.96</v>
+        <v>4485.27</v>
       </c>
       <c r="E8" t="n">
-        <v>4414.65</v>
+        <v>4414.83</v>
       </c>
       <c r="F8" t="n">
-        <v>4345.53</v>
+        <v>4345.58</v>
       </c>
       <c r="G8" t="n">
-        <v>7.43</v>
+        <v>7.65</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2786.4</v>
+        <v>1444.9</v>
       </c>
       <c r="D9" t="n">
-        <v>2693.63</v>
+        <v>1401.95</v>
       </c>
       <c r="E9" t="n">
-        <v>2684.4</v>
+        <v>1353.24</v>
       </c>
       <c r="F9" t="n">
-        <v>2575.31</v>
+        <v>1337.49</v>
       </c>
       <c r="G9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1448.9</v>
+        <v>2796.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1402.09</v>
+        <v>2693.98</v>
       </c>
       <c r="E10" t="n">
-        <v>1353.32</v>
+        <v>2684.6</v>
       </c>
       <c r="F10" t="n">
-        <v>1337.51</v>
+        <v>2575.36</v>
       </c>
       <c r="G10" t="n">
-        <v>8.33</v>
+        <v>8.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>747.6</v>
+        <v>745.65</v>
       </c>
       <c r="D11" t="n">
-        <v>730.67</v>
+        <v>730.61</v>
       </c>
       <c r="E11" t="n">
-        <v>707.25</v>
+        <v>707.21</v>
       </c>
       <c r="F11" t="n">
-        <v>686.3099999999999</v>
+        <v>686.3</v>
       </c>
       <c r="G11" t="n">
-        <v>8.93</v>
+        <v>8.65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2070.4</v>
+        <v>2058.2</v>
       </c>
       <c r="D12" t="n">
-        <v>2019.4</v>
+        <v>2019</v>
       </c>
       <c r="E12" t="n">
-        <v>1902.02</v>
+        <v>1901.78</v>
       </c>
       <c r="F12" t="n">
-        <v>1880.62</v>
+        <v>1880.56</v>
       </c>
       <c r="G12" t="n">
-        <v>10.09</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7990</v>
+        <v>7954.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7462.18</v>
+        <v>7461</v>
       </c>
       <c r="E13" t="n">
-        <v>7376</v>
+        <v>7375.29</v>
       </c>
       <c r="F13" t="n">
-        <v>7182.05</v>
+        <v>7181.87</v>
       </c>
       <c r="G13" t="n">
-        <v>11.25</v>
+        <v>10.76</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>621.2</v>
+        <v>620</v>
       </c>
       <c r="D14" t="n">
-        <v>581.5599999999999</v>
+        <v>581.52</v>
       </c>
       <c r="E14" t="n">
-        <v>547.3099999999999</v>
+        <v>547.29</v>
       </c>
       <c r="F14" t="n">
-        <v>553.95</v>
+        <v>553.9400000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>12.14</v>
+        <v>11.93</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1647.9</v>
+        <v>1649.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1496.04</v>
+        <v>1496.08</v>
       </c>
       <c r="E15" t="n">
-        <v>1470.72</v>
+        <v>1470.74</v>
       </c>
       <c r="F15" t="n">
         <v>1461.21</v>
       </c>
       <c r="G15" t="n">
-        <v>12.78</v>
+        <v>12.86</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13886</v>
+        <v>13942</v>
       </c>
       <c r="D16" t="n">
-        <v>13293.3</v>
+        <v>13295.17</v>
       </c>
       <c r="E16" t="n">
-        <v>12693.46</v>
+        <v>12694.58</v>
       </c>
       <c r="F16" t="n">
-        <v>12304.48</v>
+        <v>12304.76</v>
       </c>
       <c r="G16" t="n">
-        <v>12.85</v>
+        <v>13.31</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>311.45</v>
+        <v>310.75</v>
       </c>
       <c r="D17" t="n">
-        <v>284.57</v>
+        <v>284.55</v>
       </c>
       <c r="E17" t="n">
-        <v>271.42</v>
+        <v>271.4</v>
       </c>
       <c r="F17" t="n">
         <v>273.6</v>
       </c>
       <c r="G17" t="n">
-        <v>13.83</v>
+        <v>13.58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1085.6</v>
+        <v>1088.8</v>
       </c>
       <c r="D18" t="n">
-        <v>1037.57</v>
+        <v>1037.67</v>
       </c>
       <c r="E18" t="n">
-        <v>999.74</v>
+        <v>999.8</v>
       </c>
       <c r="F18" t="n">
-        <v>946.95</v>
+        <v>946.96</v>
       </c>
       <c r="G18" t="n">
-        <v>14.64</v>
+        <v>14.98</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1743.8</v>
+        <v>1747.3</v>
       </c>
       <c r="D19" t="n">
-        <v>1520.07</v>
+        <v>1520.18</v>
       </c>
       <c r="E19" t="n">
-        <v>1482.5</v>
+        <v>1482.57</v>
       </c>
       <c r="F19" t="n">
-        <v>1504.86</v>
+        <v>1504.88</v>
       </c>
       <c r="G19" t="n">
-        <v>15.88</v>
+        <v>16.11</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2201.8</v>
+        <v>2189.9</v>
       </c>
       <c r="D20" t="n">
-        <v>2149.59</v>
+        <v>2149.19</v>
       </c>
       <c r="E20" t="n">
-        <v>2073.02</v>
+        <v>2072.78</v>
       </c>
       <c r="F20" t="n">
-        <v>1713.63</v>
+        <v>1713.57</v>
       </c>
       <c r="G20" t="n">
-        <v>28.49</v>
+        <v>27.8</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.55</v>
+        <v>113.37</v>
       </c>
       <c r="D2" t="n">
-        <v>107.92</v>
+        <v>107.91</v>
       </c>
       <c r="E2" t="n">
         <v>106.77</v>
       </c>
       <c r="F2" t="n">
-        <v>112.64</v>
+        <v>112.63</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5687.5</v>
+        <v>5683</v>
       </c>
       <c r="D3" t="n">
-        <v>5598.28</v>
+        <v>5585.32</v>
       </c>
       <c r="E3" t="n">
-        <v>5496.76</v>
+        <v>5489.65</v>
       </c>
       <c r="F3" t="n">
-        <v>5523.96</v>
+        <v>5522.42</v>
       </c>
       <c r="G3" t="n">
-        <v>2.96</v>
+        <v>2.91</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11988</v>
+        <v>11949</v>
       </c>
       <c r="D4" t="n">
-        <v>11473.82</v>
+        <v>11448.21</v>
       </c>
       <c r="E4" t="n">
-        <v>11291.1</v>
+        <v>11282.09</v>
       </c>
       <c r="F4" t="n">
-        <v>11570.36</v>
+        <v>11569.79</v>
       </c>
       <c r="G4" t="n">
-        <v>3.61</v>
+        <v>3.28</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1455</v>
+        <v>1454.1</v>
       </c>
       <c r="D5" t="n">
-        <v>1441.5</v>
+        <v>1441.47</v>
       </c>
       <c r="E5" t="n">
-        <v>1417.66</v>
+        <v>1417.64</v>
       </c>
       <c r="F5" t="n">
         <v>1395.3</v>
       </c>
       <c r="G5" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1163</v>
+        <v>1164.4</v>
       </c>
       <c r="D6" t="n">
-        <v>1110.03</v>
+        <v>1110.21</v>
       </c>
       <c r="E6" t="n">
-        <v>1106.22</v>
+        <v>1106.39</v>
       </c>
       <c r="F6" t="n">
-        <v>1100.96</v>
+        <v>1100.74</v>
       </c>
       <c r="G6" t="n">
-        <v>5.63</v>
+        <v>5.78</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>369.75</v>
+        <v>369.25</v>
       </c>
       <c r="D7" t="n">
-        <v>358.07</v>
+        <v>358.05</v>
       </c>
       <c r="E7" t="n">
-        <v>351.2</v>
+        <v>351.19</v>
       </c>
       <c r="F7" t="n">
         <v>347.73</v>
       </c>
       <c r="G7" t="n">
-        <v>6.33</v>
+        <v>6.19</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4678</v>
+        <v>4657.2</v>
       </c>
       <c r="D8" t="n">
-        <v>4485.27</v>
+        <v>4484.58</v>
       </c>
       <c r="E8" t="n">
-        <v>4414.83</v>
+        <v>4414.42</v>
       </c>
       <c r="F8" t="n">
-        <v>4345.58</v>
+        <v>4345.47</v>
       </c>
       <c r="G8" t="n">
-        <v>7.65</v>
+        <v>7.17</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1444.9</v>
+        <v>1442.2</v>
       </c>
       <c r="D9" t="n">
-        <v>1401.95</v>
+        <v>1401.86</v>
       </c>
       <c r="E9" t="n">
-        <v>1353.24</v>
+        <v>1353.19</v>
       </c>
       <c r="F9" t="n">
-        <v>1337.49</v>
+        <v>1337.47</v>
       </c>
       <c r="G9" t="n">
-        <v>8.029999999999999</v>
+        <v>7.83</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2796.8</v>
+        <v>741.85</v>
       </c>
       <c r="D10" t="n">
-        <v>2693.98</v>
+        <v>730.48</v>
       </c>
       <c r="E10" t="n">
-        <v>2684.6</v>
+        <v>707.13</v>
       </c>
       <c r="F10" t="n">
-        <v>2575.36</v>
+        <v>686.28</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>745.65</v>
+        <v>2782.5</v>
       </c>
       <c r="D11" t="n">
-        <v>730.61</v>
+        <v>2690.29</v>
       </c>
       <c r="E11" t="n">
-        <v>707.21</v>
+        <v>2682.07</v>
       </c>
       <c r="F11" t="n">
-        <v>686.3</v>
+        <v>2573.02</v>
       </c>
       <c r="G11" t="n">
-        <v>8.65</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2058.2</v>
+        <v>2034.1</v>
       </c>
       <c r="D12" t="n">
-        <v>2019</v>
+        <v>2018.19</v>
       </c>
       <c r="E12" t="n">
-        <v>1901.78</v>
+        <v>1901.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1880.56</v>
+        <v>1880.44</v>
       </c>
       <c r="G12" t="n">
-        <v>9.449999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7954.5</v>
+        <v>7916.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7461</v>
+        <v>7459.73</v>
       </c>
       <c r="E13" t="n">
-        <v>7375.29</v>
+        <v>7374.53</v>
       </c>
       <c r="F13" t="n">
-        <v>7181.87</v>
+        <v>7181.68</v>
       </c>
       <c r="G13" t="n">
-        <v>10.76</v>
+        <v>10.23</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>620</v>
+        <v>615.25</v>
       </c>
       <c r="D14" t="n">
-        <v>581.52</v>
+        <v>581.36</v>
       </c>
       <c r="E14" t="n">
-        <v>547.29</v>
+        <v>547.1900000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>553.9400000000001</v>
+        <v>553.92</v>
       </c>
       <c r="G14" t="n">
-        <v>11.93</v>
+        <v>11.07</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1649.1</v>
+        <v>1647.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1496.08</v>
+        <v>1496.01</v>
       </c>
       <c r="E15" t="n">
-        <v>1470.74</v>
+        <v>1470.7</v>
       </c>
       <c r="F15" t="n">
-        <v>1461.21</v>
+        <v>1461.2</v>
       </c>
       <c r="G15" t="n">
-        <v>12.86</v>
+        <v>12.72</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13942</v>
+        <v>310.1</v>
       </c>
       <c r="D16" t="n">
-        <v>13295.17</v>
+        <v>284.52</v>
       </c>
       <c r="E16" t="n">
-        <v>12694.58</v>
+        <v>271.39</v>
       </c>
       <c r="F16" t="n">
-        <v>12304.76</v>
+        <v>273.6</v>
       </c>
       <c r="G16" t="n">
-        <v>13.31</v>
+        <v>13.34</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>310.75</v>
+        <v>13950</v>
       </c>
       <c r="D17" t="n">
-        <v>284.55</v>
+        <v>13295.43</v>
       </c>
       <c r="E17" t="n">
-        <v>271.4</v>
+        <v>12694.74</v>
       </c>
       <c r="F17" t="n">
-        <v>273.6</v>
+        <v>12304.8</v>
       </c>
       <c r="G17" t="n">
-        <v>13.58</v>
+        <v>13.37</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1088.8</v>
+        <v>1083.6</v>
       </c>
       <c r="D18" t="n">
-        <v>1037.67</v>
+        <v>1037.5</v>
       </c>
       <c r="E18" t="n">
-        <v>999.8</v>
+        <v>999.7</v>
       </c>
       <c r="F18" t="n">
-        <v>946.96</v>
+        <v>946.9400000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>14.98</v>
+        <v>14.43</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1747.3</v>
+        <v>1743.3</v>
       </c>
       <c r="D19" t="n">
-        <v>1520.18</v>
+        <v>1520.05</v>
       </c>
       <c r="E19" t="n">
-        <v>1482.57</v>
+        <v>1482.49</v>
       </c>
       <c r="F19" t="n">
-        <v>1504.88</v>
+        <v>1504.86</v>
       </c>
       <c r="G19" t="n">
-        <v>16.11</v>
+        <v>15.84</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2189.9</v>
+        <v>2181.2</v>
       </c>
       <c r="D20" t="n">
-        <v>2149.19</v>
+        <v>2148.9</v>
       </c>
       <c r="E20" t="n">
-        <v>2072.78</v>
+        <v>2072.61</v>
       </c>
       <c r="F20" t="n">
-        <v>1713.57</v>
+        <v>1713.53</v>
       </c>
       <c r="G20" t="n">
-        <v>27.8</v>
+        <v>27.29</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.37</v>
+        <v>113.99</v>
       </c>
       <c r="D2" t="n">
-        <v>107.91</v>
+        <v>108.12</v>
       </c>
       <c r="E2" t="n">
-        <v>106.77</v>
+        <v>106.98</v>
       </c>
       <c r="F2" t="n">
-        <v>112.63</v>
+        <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>0.65</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5683</v>
+        <v>12050</v>
       </c>
       <c r="D3" t="n">
-        <v>5585.32</v>
+        <v>11508.32</v>
       </c>
       <c r="E3" t="n">
-        <v>5489.65</v>
+        <v>11305.61</v>
       </c>
       <c r="F3" t="n">
-        <v>5522.42</v>
+        <v>11570.61</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91</v>
+        <v>4.14</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11949</v>
+        <v>1460</v>
       </c>
       <c r="D4" t="n">
-        <v>11448.21</v>
+        <v>1443.04</v>
       </c>
       <c r="E4" t="n">
-        <v>11282.09</v>
+        <v>1419.16</v>
       </c>
       <c r="F4" t="n">
-        <v>11569.79</v>
+        <v>1394.98</v>
       </c>
       <c r="G4" t="n">
-        <v>3.28</v>
+        <v>4.66</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1454.1</v>
+        <v>4635</v>
       </c>
       <c r="D5" t="n">
-        <v>1441.47</v>
+        <v>4490.17</v>
       </c>
       <c r="E5" t="n">
-        <v>1417.64</v>
+        <v>4419.22</v>
       </c>
       <c r="F5" t="n">
-        <v>1395.3</v>
+        <v>4344.79</v>
       </c>
       <c r="G5" t="n">
-        <v>4.21</v>
+        <v>6.68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1164.4</v>
+        <v>2775</v>
       </c>
       <c r="D6" t="n">
-        <v>1110.21</v>
+        <v>2698.21</v>
       </c>
       <c r="E6" t="n">
-        <v>1106.39</v>
+        <v>2687.88</v>
       </c>
       <c r="F6" t="n">
-        <v>1100.74</v>
+        <v>2577.55</v>
       </c>
       <c r="G6" t="n">
-        <v>5.78</v>
+        <v>7.66</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>369.25</v>
+        <v>2033.6</v>
       </c>
       <c r="D7" t="n">
-        <v>358.05</v>
+        <v>2028.46</v>
       </c>
       <c r="E7" t="n">
-        <v>351.19</v>
+        <v>1908.05</v>
       </c>
       <c r="F7" t="n">
-        <v>347.73</v>
+        <v>1880.26</v>
       </c>
       <c r="G7" t="n">
-        <v>6.19</v>
+        <v>8.16</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4657.2</v>
+        <v>1454.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4484.58</v>
+        <v>1406.71</v>
       </c>
       <c r="E8" t="n">
-        <v>4414.42</v>
+        <v>1357.26</v>
       </c>
       <c r="F8" t="n">
-        <v>4345.47</v>
+        <v>1337.9</v>
       </c>
       <c r="G8" t="n">
-        <v>7.17</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1442.2</v>
+        <v>750</v>
       </c>
       <c r="D9" t="n">
-        <v>1401.86</v>
+        <v>731.6799999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1353.19</v>
+        <v>709.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1337.47</v>
+        <v>686.46</v>
       </c>
       <c r="G9" t="n">
-        <v>7.83</v>
+        <v>9.26</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>741.85</v>
+        <v>7935</v>
       </c>
       <c r="D10" t="n">
-        <v>730.48</v>
+        <v>7478.7</v>
       </c>
       <c r="E10" t="n">
-        <v>707.13</v>
+        <v>7389.91</v>
       </c>
       <c r="F10" t="n">
-        <v>686.28</v>
+        <v>7187.9</v>
       </c>
       <c r="G10" t="n">
-        <v>8.1</v>
+        <v>10.39</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2782.5</v>
+        <v>612</v>
       </c>
       <c r="D11" t="n">
-        <v>2690.29</v>
+        <v>583.11</v>
       </c>
       <c r="E11" t="n">
-        <v>2682.07</v>
+        <v>550.15</v>
       </c>
       <c r="F11" t="n">
-        <v>2573.02</v>
+        <v>554.14</v>
       </c>
       <c r="G11" t="n">
-        <v>8.140000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2034.1</v>
+        <v>13988</v>
       </c>
       <c r="D12" t="n">
-        <v>2018.19</v>
+        <v>13362.03</v>
       </c>
       <c r="E12" t="n">
-        <v>1901.3</v>
+        <v>12739.88</v>
       </c>
       <c r="F12" t="n">
-        <v>1880.44</v>
+        <v>12290.57</v>
       </c>
       <c r="G12" t="n">
-        <v>8.17</v>
+        <v>13.81</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7916.5</v>
+        <v>312.4</v>
       </c>
       <c r="D13" t="n">
-        <v>7459.73</v>
+        <v>286.32</v>
       </c>
       <c r="E13" t="n">
-        <v>7374.53</v>
+        <v>272.64</v>
       </c>
       <c r="F13" t="n">
-        <v>7181.68</v>
+        <v>273.39</v>
       </c>
       <c r="G13" t="n">
-        <v>10.23</v>
+        <v>14.27</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>615.25</v>
+        <v>1087.3</v>
       </c>
       <c r="D14" t="n">
-        <v>581.36</v>
+        <v>1041.04</v>
       </c>
       <c r="E14" t="n">
-        <v>547.1900000000001</v>
+        <v>1002.64</v>
       </c>
       <c r="F14" t="n">
-        <v>553.92</v>
+        <v>949.0599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>11.07</v>
+        <v>14.57</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04-08-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1647.1</v>
+        <v>1749.9</v>
       </c>
       <c r="D15" t="n">
-        <v>1496.01</v>
+        <v>1530.06</v>
       </c>
       <c r="E15" t="n">
-        <v>1470.7</v>
+        <v>1489.66</v>
       </c>
       <c r="F15" t="n">
-        <v>1461.2</v>
+        <v>1504.99</v>
       </c>
       <c r="G15" t="n">
-        <v>12.72</v>
+        <v>16.27</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -976,191 +976,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>310.1</v>
-      </c>
-      <c r="D16" t="n">
-        <v>284.52</v>
-      </c>
-      <c r="E16" t="n">
-        <v>271.39</v>
-      </c>
-      <c r="F16" t="n">
-        <v>273.6</v>
-      </c>
-      <c r="G16" t="n">
-        <v>13.34</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>13950</v>
-      </c>
-      <c r="D17" t="n">
-        <v>13295.43</v>
-      </c>
-      <c r="E17" t="n">
-        <v>12694.74</v>
-      </c>
-      <c r="F17" t="n">
-        <v>12304.8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>13.37</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SHRIRAMFIN</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>1083.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1037.5</v>
-      </c>
-      <c r="E18" t="n">
-        <v>999.7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>946.9400000000001</v>
-      </c>
-      <c r="G18" t="n">
-        <v>14.43</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1743.3</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1520.05</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1482.49</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1504.86</v>
-      </c>
-      <c r="G19" t="n">
-        <v>15.84</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>04-08-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BHARATFORG</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>2181.2</v>
-      </c>
-      <c r="D20" t="n">
-        <v>2148.9</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2072.61</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1713.53</v>
-      </c>
-      <c r="G20" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.99</v>
+        <v>114.34</v>
       </c>
       <c r="D2" t="n">
-        <v>108.12</v>
+        <v>108.34</v>
       </c>
       <c r="E2" t="n">
-        <v>106.98</v>
+        <v>107.2</v>
       </c>
       <c r="F2" t="n">
         <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12050</v>
+        <v>130.59</v>
       </c>
       <c r="D3" t="n">
-        <v>11508.32</v>
+        <v>124.61</v>
       </c>
       <c r="E3" t="n">
-        <v>11305.61</v>
+        <v>124.04</v>
       </c>
       <c r="F3" t="n">
-        <v>11570.61</v>
+        <v>127.99</v>
       </c>
       <c r="G3" t="n">
-        <v>4.14</v>
+        <v>2.03</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1460</v>
+        <v>5651.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1443.04</v>
+        <v>5595.6</v>
       </c>
       <c r="E4" t="n">
-        <v>1419.16</v>
+        <v>5495.15</v>
       </c>
       <c r="F4" t="n">
-        <v>1394.98</v>
+        <v>5523.56</v>
       </c>
       <c r="G4" t="n">
-        <v>4.66</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4635</v>
+        <v>1452.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4490.17</v>
+        <v>1443.53</v>
       </c>
       <c r="E5" t="n">
-        <v>4419.22</v>
+        <v>1420.11</v>
       </c>
       <c r="F5" t="n">
-        <v>4344.79</v>
+        <v>1394.46</v>
       </c>
       <c r="G5" t="n">
-        <v>6.68</v>
+        <v>4.16</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2775</v>
+        <v>366.15</v>
       </c>
       <c r="D6" t="n">
-        <v>2698.21</v>
+        <v>358.29</v>
       </c>
       <c r="E6" t="n">
-        <v>2687.88</v>
+        <v>351.81</v>
       </c>
       <c r="F6" t="n">
-        <v>2577.55</v>
+        <v>347.76</v>
       </c>
       <c r="G6" t="n">
-        <v>7.66</v>
+        <v>5.29</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2033.6</v>
+        <v>12225</v>
       </c>
       <c r="D7" t="n">
-        <v>2028.46</v>
+        <v>11519.06</v>
       </c>
       <c r="E7" t="n">
-        <v>1908.05</v>
+        <v>11312.05</v>
       </c>
       <c r="F7" t="n">
-        <v>1880.26</v>
+        <v>11572.22</v>
       </c>
       <c r="G7" t="n">
-        <v>8.16</v>
+        <v>5.64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1454.6</v>
+        <v>4617.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1406.71</v>
+        <v>4498.46</v>
       </c>
       <c r="E8" t="n">
-        <v>1357.26</v>
+        <v>4423.31</v>
       </c>
       <c r="F8" t="n">
-        <v>1337.9</v>
+        <v>4343.77</v>
       </c>
       <c r="G8" t="n">
-        <v>8.720000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>2766.3</v>
       </c>
       <c r="D9" t="n">
-        <v>731.6799999999999</v>
+        <v>2698.85</v>
       </c>
       <c r="E9" t="n">
-        <v>709.25</v>
+        <v>2688.26</v>
       </c>
       <c r="F9" t="n">
-        <v>686.46</v>
+        <v>2577.64</v>
       </c>
       <c r="G9" t="n">
-        <v>9.26</v>
+        <v>7.32</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7935</v>
+        <v>1182.7</v>
       </c>
       <c r="D10" t="n">
-        <v>7478.7</v>
+        <v>1111.1</v>
       </c>
       <c r="E10" t="n">
-        <v>7389.91</v>
+        <v>1106.86</v>
       </c>
       <c r="F10" t="n">
-        <v>7187.9</v>
+        <v>1101.12</v>
       </c>
       <c r="G10" t="n">
-        <v>10.39</v>
+        <v>7.41</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>612</v>
+        <v>749.3</v>
       </c>
       <c r="D11" t="n">
-        <v>583.11</v>
+        <v>732.48</v>
       </c>
       <c r="E11" t="n">
-        <v>550.15</v>
+        <v>710.9400000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>554.14</v>
+        <v>686.54</v>
       </c>
       <c r="G11" t="n">
-        <v>10.44</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13988</v>
+        <v>7980</v>
       </c>
       <c r="D12" t="n">
-        <v>13362.03</v>
+        <v>7494.91</v>
       </c>
       <c r="E12" t="n">
-        <v>12739.88</v>
+        <v>7402.67</v>
       </c>
       <c r="F12" t="n">
-        <v>12290.57</v>
+        <v>7193.23</v>
       </c>
       <c r="G12" t="n">
-        <v>13.81</v>
+        <v>10.94</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>312.4</v>
+        <v>617</v>
       </c>
       <c r="D13" t="n">
-        <v>286.32</v>
+        <v>585.22</v>
       </c>
       <c r="E13" t="n">
-        <v>272.64</v>
+        <v>552.97</v>
       </c>
       <c r="F13" t="n">
-        <v>273.39</v>
+        <v>554.38</v>
       </c>
       <c r="G13" t="n">
-        <v>14.27</v>
+        <v>11.3</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1087.3</v>
+        <v>2126</v>
       </c>
       <c r="D14" t="n">
-        <v>1041.04</v>
+        <v>2038.94</v>
       </c>
       <c r="E14" t="n">
-        <v>1002.64</v>
+        <v>1914.97</v>
       </c>
       <c r="F14" t="n">
-        <v>949.0599999999999</v>
+        <v>1879.91</v>
       </c>
       <c r="G14" t="n">
-        <v>14.57</v>
+        <v>13.09</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,30 +952,141 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1662.3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1505.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1475.55</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1462.49</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13.66</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>313.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>288.23</v>
+      </c>
+      <c r="E16" t="n">
+        <v>273.78</v>
+      </c>
+      <c r="F16" t="n">
+        <v>273.22</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>14341</v>
+      </c>
+      <c r="D17" t="n">
+        <v>13437.2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12791.58</v>
+      </c>
+      <c r="F17" t="n">
+        <v>12278.06</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>05-08-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1749.9</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1530.06</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1489.66</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1504.99</v>
-      </c>
-      <c r="G15" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="C18" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1539.72</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1497.64</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1505.16</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18.33</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>114.34</v>
+        <v>113.75</v>
       </c>
       <c r="D2" t="n">
-        <v>108.34</v>
+        <v>108.32</v>
       </c>
       <c r="E2" t="n">
-        <v>107.2</v>
+        <v>107.18</v>
       </c>
       <c r="F2" t="n">
         <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.51</v>
+        <v>0.98</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>130.59</v>
+        <v>129.72</v>
       </c>
       <c r="D3" t="n">
-        <v>124.61</v>
+        <v>124.58</v>
       </c>
       <c r="E3" t="n">
-        <v>124.04</v>
+        <v>124.02</v>
       </c>
       <c r="F3" t="n">
-        <v>127.99</v>
+        <v>127.98</v>
       </c>
       <c r="G3" t="n">
-        <v>2.03</v>
+        <v>1.36</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5651.5</v>
+        <v>5640</v>
       </c>
       <c r="D4" t="n">
-        <v>5595.6</v>
+        <v>5606.42</v>
       </c>
       <c r="E4" t="n">
-        <v>5495.15</v>
+        <v>5502.35</v>
       </c>
       <c r="F4" t="n">
-        <v>5523.56</v>
+        <v>5525.01</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1452.5</v>
+        <v>1445.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1443.53</v>
+        <v>1443.3</v>
       </c>
       <c r="E5" t="n">
-        <v>1420.11</v>
+        <v>1419.98</v>
       </c>
       <c r="F5" t="n">
-        <v>1394.46</v>
+        <v>1394.43</v>
       </c>
       <c r="G5" t="n">
-        <v>4.16</v>
+        <v>3.68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>366.15</v>
+        <v>12166</v>
       </c>
       <c r="D6" t="n">
-        <v>358.29</v>
+        <v>11540.48</v>
       </c>
       <c r="E6" t="n">
-        <v>351.81</v>
+        <v>11319.83</v>
       </c>
       <c r="F6" t="n">
-        <v>347.76</v>
+        <v>11570.89</v>
       </c>
       <c r="G6" t="n">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12225</v>
+        <v>366.25</v>
       </c>
       <c r="D7" t="n">
-        <v>11519.06</v>
+        <v>358.3</v>
       </c>
       <c r="E7" t="n">
-        <v>11312.05</v>
+        <v>351.82</v>
       </c>
       <c r="F7" t="n">
-        <v>11572.22</v>
+        <v>347.76</v>
       </c>
       <c r="G7" t="n">
-        <v>5.64</v>
+        <v>5.32</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4617.6</v>
+        <v>4614.3</v>
       </c>
       <c r="D8" t="n">
-        <v>4498.46</v>
+        <v>4498.35</v>
       </c>
       <c r="E8" t="n">
-        <v>4423.31</v>
+        <v>4423.25</v>
       </c>
       <c r="F8" t="n">
-        <v>4343.77</v>
+        <v>4343.75</v>
       </c>
       <c r="G8" t="n">
-        <v>6.3</v>
+        <v>6.23</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2766.3</v>
+        <v>2762.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2698.85</v>
+        <v>2701.39</v>
       </c>
       <c r="E9" t="n">
-        <v>2688.26</v>
+        <v>2690.16</v>
       </c>
       <c r="F9" t="n">
-        <v>2577.64</v>
+        <v>2579.43</v>
       </c>
       <c r="G9" t="n">
-        <v>7.32</v>
+        <v>7.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1182.7</v>
+        <v>1187</v>
       </c>
       <c r="D10" t="n">
-        <v>1111.1</v>
+        <v>1111.86</v>
       </c>
       <c r="E10" t="n">
-        <v>1106.86</v>
+        <v>1107.15</v>
       </c>
       <c r="F10" t="n">
-        <v>1101.12</v>
+        <v>1101.25</v>
       </c>
       <c r="G10" t="n">
-        <v>7.41</v>
+        <v>7.79</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>749.3</v>
+        <v>741.25</v>
       </c>
       <c r="D11" t="n">
-        <v>732.48</v>
+        <v>732.21</v>
       </c>
       <c r="E11" t="n">
-        <v>710.9400000000001</v>
+        <v>710.78</v>
       </c>
       <c r="F11" t="n">
-        <v>686.54</v>
+        <v>686.49</v>
       </c>
       <c r="G11" t="n">
-        <v>9.140000000000001</v>
+        <v>7.98</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7980</v>
+        <v>609.05</v>
       </c>
       <c r="D12" t="n">
-        <v>7494.91</v>
+        <v>584.95</v>
       </c>
       <c r="E12" t="n">
-        <v>7402.67</v>
+        <v>552.8099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>7193.23</v>
+        <v>554.34</v>
       </c>
       <c r="G12" t="n">
-        <v>10.94</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>617</v>
+        <v>7964</v>
       </c>
       <c r="D13" t="n">
-        <v>585.22</v>
+        <v>7494.38</v>
       </c>
       <c r="E13" t="n">
-        <v>552.97</v>
+        <v>7402.35</v>
       </c>
       <c r="F13" t="n">
-        <v>554.38</v>
+        <v>7193.15</v>
       </c>
       <c r="G13" t="n">
-        <v>11.3</v>
+        <v>10.72</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2126</v>
+        <v>2115.4</v>
       </c>
       <c r="D14" t="n">
-        <v>2038.94</v>
+        <v>2038.58</v>
       </c>
       <c r="E14" t="n">
-        <v>1914.97</v>
+        <v>1914.76</v>
       </c>
       <c r="F14" t="n">
-        <v>1879.91</v>
+        <v>1879.86</v>
       </c>
       <c r="G14" t="n">
-        <v>13.09</v>
+        <v>12.53</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1662.3</v>
+        <v>1659.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1505.5</v>
+        <v>1505.41</v>
       </c>
       <c r="E15" t="n">
-        <v>1475.55</v>
+        <v>1475.5</v>
       </c>
       <c r="F15" t="n">
-        <v>1462.49</v>
+        <v>1462.47</v>
       </c>
       <c r="G15" t="n">
-        <v>13.66</v>
+        <v>13.49</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>313.7</v>
+        <v>312.1</v>
       </c>
       <c r="D16" t="n">
-        <v>288.23</v>
+        <v>288.18</v>
       </c>
       <c r="E16" t="n">
-        <v>273.78</v>
+        <v>273.75</v>
       </c>
       <c r="F16" t="n">
-        <v>273.22</v>
+        <v>273.21</v>
       </c>
       <c r="G16" t="n">
-        <v>14.82</v>
+        <v>14.24</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14341</v>
+        <v>14323</v>
       </c>
       <c r="D17" t="n">
-        <v>13437.2</v>
+        <v>13436.6</v>
       </c>
       <c r="E17" t="n">
-        <v>12791.58</v>
+        <v>12791.22</v>
       </c>
       <c r="F17" t="n">
-        <v>12278.06</v>
+        <v>12277.96</v>
       </c>
       <c r="G17" t="n">
-        <v>16.8</v>
+        <v>16.66</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1781</v>
+        <v>1779.9</v>
       </c>
       <c r="D18" t="n">
-        <v>1539.72</v>
+        <v>1539.69</v>
       </c>
       <c r="E18" t="n">
-        <v>1497.64</v>
+        <v>1497.61</v>
       </c>
       <c r="F18" t="n">
         <v>1505.16</v>
       </c>
       <c r="G18" t="n">
-        <v>18.33</v>
+        <v>18.25</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.75</v>
+        <v>113.85</v>
       </c>
       <c r="D2" t="n">
-        <v>108.32</v>
+        <v>108.33</v>
       </c>
       <c r="E2" t="n">
-        <v>107.18</v>
+        <v>107.19</v>
       </c>
       <c r="F2" t="n">
         <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>129.72</v>
+        <v>129.64</v>
       </c>
       <c r="D3" t="n">
         <v>124.58</v>
@@ -524,7 +524,7 @@
         <v>127.98</v>
       </c>
       <c r="G3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5640</v>
+        <v>5633</v>
       </c>
       <c r="D4" t="n">
-        <v>5606.42</v>
+        <v>5606.18</v>
       </c>
       <c r="E4" t="n">
-        <v>5502.35</v>
+        <v>5502.21</v>
       </c>
       <c r="F4" t="n">
-        <v>5525.01</v>
+        <v>5524.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1445.8</v>
+        <v>1453</v>
       </c>
       <c r="D5" t="n">
-        <v>1443.3</v>
+        <v>1443.54</v>
       </c>
       <c r="E5" t="n">
-        <v>1419.98</v>
+        <v>1420.12</v>
       </c>
       <c r="F5" t="n">
-        <v>1394.43</v>
+        <v>1394.47</v>
       </c>
       <c r="G5" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>12166</v>
+        <v>364.85</v>
       </c>
       <c r="D6" t="n">
-        <v>11540.48</v>
+        <v>358.25</v>
       </c>
       <c r="E6" t="n">
-        <v>11319.83</v>
+        <v>351.79</v>
       </c>
       <c r="F6" t="n">
-        <v>11570.89</v>
+        <v>347.75</v>
       </c>
       <c r="G6" t="n">
-        <v>5.14</v>
+        <v>4.92</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>366.25</v>
+        <v>12148</v>
       </c>
       <c r="D7" t="n">
-        <v>358.3</v>
+        <v>11539.88</v>
       </c>
       <c r="E7" t="n">
-        <v>351.82</v>
+        <v>11319.47</v>
       </c>
       <c r="F7" t="n">
-        <v>347.76</v>
+        <v>11570.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.32</v>
+        <v>4.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4614.3</v>
+        <v>4624.8</v>
       </c>
       <c r="D8" t="n">
-        <v>4498.35</v>
+        <v>4498.7</v>
       </c>
       <c r="E8" t="n">
-        <v>4423.25</v>
+        <v>4423.46</v>
       </c>
       <c r="F8" t="n">
-        <v>4343.75</v>
+        <v>4343.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.23</v>
+        <v>6.47</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2762.7</v>
+        <v>2757.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2701.39</v>
+        <v>2701.22</v>
       </c>
       <c r="E9" t="n">
-        <v>2690.16</v>
+        <v>2690.06</v>
       </c>
       <c r="F9" t="n">
-        <v>2579.43</v>
+        <v>2579.41</v>
       </c>
       <c r="G9" t="n">
-        <v>7.1</v>
+        <v>6.91</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1187</v>
+        <v>740.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1111.86</v>
+        <v>732.2</v>
       </c>
       <c r="E10" t="n">
-        <v>1107.15</v>
+        <v>710.77</v>
       </c>
       <c r="F10" t="n">
-        <v>1101.25</v>
+        <v>686.49</v>
       </c>
       <c r="G10" t="n">
-        <v>7.79</v>
+        <v>7.93</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>741.25</v>
+        <v>1191.6</v>
       </c>
       <c r="D11" t="n">
-        <v>732.21</v>
+        <v>1112.01</v>
       </c>
       <c r="E11" t="n">
-        <v>710.78</v>
+        <v>1107.24</v>
       </c>
       <c r="F11" t="n">
-        <v>686.49</v>
+        <v>1101.27</v>
       </c>
       <c r="G11" t="n">
-        <v>7.98</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>609.05</v>
+        <v>606.85</v>
       </c>
       <c r="D12" t="n">
-        <v>584.95</v>
+        <v>584.88</v>
       </c>
       <c r="E12" t="n">
-        <v>552.8099999999999</v>
+        <v>552.76</v>
       </c>
       <c r="F12" t="n">
-        <v>554.34</v>
+        <v>554.33</v>
       </c>
       <c r="G12" t="n">
-        <v>9.869999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7964</v>
+        <v>7992</v>
       </c>
       <c r="D13" t="n">
-        <v>7494.38</v>
+        <v>7495.31</v>
       </c>
       <c r="E13" t="n">
-        <v>7402.35</v>
+        <v>7402.91</v>
       </c>
       <c r="F13" t="n">
-        <v>7193.15</v>
+        <v>7193.29</v>
       </c>
       <c r="G13" t="n">
-        <v>10.72</v>
+        <v>11.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2115.4</v>
+        <v>2115.5</v>
       </c>
       <c r="D14" t="n">
-        <v>2038.58</v>
+        <v>2038.59</v>
       </c>
       <c r="E14" t="n">
         <v>1914.76</v>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1659.8</v>
+        <v>1656.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1505.41</v>
+        <v>1505.29</v>
       </c>
       <c r="E15" t="n">
-        <v>1475.5</v>
+        <v>1475.42</v>
       </c>
       <c r="F15" t="n">
-        <v>1462.47</v>
+        <v>1462.46</v>
       </c>
       <c r="G15" t="n">
-        <v>13.49</v>
+        <v>13.24</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>312.1</v>
+        <v>310.55</v>
       </c>
       <c r="D16" t="n">
-        <v>288.18</v>
+        <v>288.13</v>
       </c>
       <c r="E16" t="n">
-        <v>273.75</v>
+        <v>273.72</v>
       </c>
       <c r="F16" t="n">
-        <v>273.21</v>
+        <v>273.2</v>
       </c>
       <c r="G16" t="n">
-        <v>14.24</v>
+        <v>13.67</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14323</v>
+        <v>14297</v>
       </c>
       <c r="D17" t="n">
-        <v>13436.6</v>
+        <v>13435.73</v>
       </c>
       <c r="E17" t="n">
-        <v>12791.22</v>
+        <v>12790.7</v>
       </c>
       <c r="F17" t="n">
-        <v>12277.96</v>
+        <v>12277.84</v>
       </c>
       <c r="G17" t="n">
-        <v>16.66</v>
+        <v>16.45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1779.9</v>
+        <v>1781.3</v>
       </c>
       <c r="D18" t="n">
-        <v>1539.69</v>
+        <v>1539.73</v>
       </c>
       <c r="E18" t="n">
-        <v>1497.61</v>
+        <v>1497.64</v>
       </c>
       <c r="F18" t="n">
-        <v>1505.16</v>
+        <v>1505.17</v>
       </c>
       <c r="G18" t="n">
-        <v>18.25</v>
+        <v>18.35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.85</v>
+        <v>113.69</v>
       </c>
       <c r="D2" t="n">
-        <v>108.33</v>
+        <v>108.32</v>
       </c>
       <c r="E2" t="n">
-        <v>107.19</v>
+        <v>107.18</v>
       </c>
       <c r="F2" t="n">
         <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>129.64</v>
+        <v>129.81</v>
       </c>
       <c r="D3" t="n">
         <v>124.58</v>
@@ -524,7 +524,7 @@
         <v>127.98</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5633</v>
+        <v>5641</v>
       </c>
       <c r="D4" t="n">
-        <v>5606.18</v>
+        <v>5606.45</v>
       </c>
       <c r="E4" t="n">
-        <v>5502.21</v>
+        <v>5502.37</v>
       </c>
       <c r="F4" t="n">
-        <v>5524.98</v>
+        <v>5525.02</v>
       </c>
       <c r="G4" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D5" t="n">
-        <v>1443.54</v>
+        <v>1443.58</v>
       </c>
       <c r="E5" t="n">
-        <v>1420.12</v>
+        <v>1420.14</v>
       </c>
       <c r="F5" t="n">
         <v>1394.47</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>364.85</v>
+        <v>364.15</v>
       </c>
       <c r="D6" t="n">
-        <v>358.25</v>
+        <v>358.23</v>
       </c>
       <c r="E6" t="n">
-        <v>351.79</v>
+        <v>351.77</v>
       </c>
       <c r="F6" t="n">
         <v>347.75</v>
       </c>
       <c r="G6" t="n">
-        <v>4.92</v>
+        <v>4.72</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12148</v>
+        <v>12160</v>
       </c>
       <c r="D7" t="n">
-        <v>11539.88</v>
+        <v>11540.28</v>
       </c>
       <c r="E7" t="n">
-        <v>11319.47</v>
+        <v>11319.71</v>
       </c>
       <c r="F7" t="n">
-        <v>11570.8</v>
+        <v>11570.86</v>
       </c>
       <c r="G7" t="n">
-        <v>4.99</v>
+        <v>5.09</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4624.8</v>
+        <v>4626.7</v>
       </c>
       <c r="D8" t="n">
-        <v>4498.7</v>
+        <v>4498.76</v>
       </c>
       <c r="E8" t="n">
-        <v>4423.46</v>
+        <v>4423.49</v>
       </c>
       <c r="F8" t="n">
-        <v>4343.8</v>
+        <v>4343.81</v>
       </c>
       <c r="G8" t="n">
-        <v>6.47</v>
+        <v>6.51</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2757.7</v>
+        <v>2758.1</v>
       </c>
       <c r="D9" t="n">
-        <v>2701.22</v>
+        <v>2701.23</v>
       </c>
       <c r="E9" t="n">
-        <v>2690.06</v>
+        <v>2690.07</v>
       </c>
       <c r="F9" t="n">
         <v>2579.41</v>
       </c>
       <c r="G9" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>740.9</v>
+        <v>737</v>
       </c>
       <c r="D10" t="n">
-        <v>732.2</v>
+        <v>732.0700000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>710.77</v>
+        <v>710.7</v>
       </c>
       <c r="F10" t="n">
-        <v>686.49</v>
+        <v>686.47</v>
       </c>
       <c r="G10" t="n">
-        <v>7.93</v>
+        <v>7.36</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1191.6</v>
+        <v>1191</v>
       </c>
       <c r="D11" t="n">
-        <v>1112.01</v>
+        <v>1111.99</v>
       </c>
       <c r="E11" t="n">
-        <v>1107.24</v>
+        <v>1107.23</v>
       </c>
       <c r="F11" t="n">
         <v>1101.27</v>
       </c>
       <c r="G11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.15</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>606.85</v>
+        <v>612.4</v>
       </c>
       <c r="D12" t="n">
-        <v>584.88</v>
+        <v>585.0599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>552.76</v>
+        <v>552.87</v>
       </c>
       <c r="F12" t="n">
-        <v>554.33</v>
+        <v>554.35</v>
       </c>
       <c r="G12" t="n">
-        <v>9.48</v>
+        <v>10.47</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7992</v>
+        <v>8008.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7495.31</v>
+        <v>7495.86</v>
       </c>
       <c r="E13" t="n">
-        <v>7402.91</v>
+        <v>7403.24</v>
       </c>
       <c r="F13" t="n">
-        <v>7193.29</v>
+        <v>7193.37</v>
       </c>
       <c r="G13" t="n">
-        <v>11.1</v>
+        <v>11.33</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2115.5</v>
+        <v>2121.3</v>
       </c>
       <c r="D14" t="n">
-        <v>2038.59</v>
+        <v>2038.78</v>
       </c>
       <c r="E14" t="n">
-        <v>1914.76</v>
+        <v>1914.87</v>
       </c>
       <c r="F14" t="n">
-        <v>1879.86</v>
+        <v>1879.89</v>
       </c>
       <c r="G14" t="n">
-        <v>12.53</v>
+        <v>12.84</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1656.1</v>
+        <v>1660.9</v>
       </c>
       <c r="D15" t="n">
-        <v>1505.29</v>
+        <v>1505.45</v>
       </c>
       <c r="E15" t="n">
-        <v>1475.42</v>
+        <v>1475.52</v>
       </c>
       <c r="F15" t="n">
-        <v>1462.46</v>
+        <v>1462.48</v>
       </c>
       <c r="G15" t="n">
-        <v>13.24</v>
+        <v>13.57</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>310.55</v>
+        <v>311.25</v>
       </c>
       <c r="D16" t="n">
-        <v>288.13</v>
+        <v>288.15</v>
       </c>
       <c r="E16" t="n">
-        <v>273.72</v>
+        <v>273.74</v>
       </c>
       <c r="F16" t="n">
         <v>273.2</v>
       </c>
       <c r="G16" t="n">
-        <v>13.67</v>
+        <v>13.93</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14297</v>
+        <v>14341</v>
       </c>
       <c r="D17" t="n">
-        <v>13435.73</v>
+        <v>13437.2</v>
       </c>
       <c r="E17" t="n">
-        <v>12790.7</v>
+        <v>12791.58</v>
       </c>
       <c r="F17" t="n">
-        <v>12277.84</v>
+        <v>12278.06</v>
       </c>
       <c r="G17" t="n">
-        <v>16.45</v>
+        <v>16.8</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1781.3</v>
+        <v>1780.6</v>
       </c>
       <c r="D18" t="n">
-        <v>1539.73</v>
+        <v>1539.71</v>
       </c>
       <c r="E18" t="n">
-        <v>1497.64</v>
+        <v>1497.63</v>
       </c>
       <c r="F18" t="n">
-        <v>1505.17</v>
+        <v>1505.16</v>
       </c>
       <c r="G18" t="n">
-        <v>18.35</v>
+        <v>18.3</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.69</v>
+        <v>113.55</v>
       </c>
       <c r="D2" t="n">
         <v>108.32</v>
@@ -487,7 +487,7 @@
         <v>112.64</v>
       </c>
       <c r="G2" t="n">
-        <v>0.93</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>129.81</v>
+        <v>129.59</v>
       </c>
       <c r="D3" t="n">
         <v>124.58</v>
@@ -524,7 +524,7 @@
         <v>127.98</v>
       </c>
       <c r="G3" t="n">
-        <v>1.43</v>
+        <v>1.26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5641</v>
+        <v>5696.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5606.45</v>
+        <v>5614.28</v>
       </c>
       <c r="E4" t="n">
-        <v>5502.37</v>
+        <v>5506.61</v>
       </c>
       <c r="F4" t="n">
-        <v>5525.02</v>
+        <v>5525.72</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1</v>
+        <v>3.09</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1454</v>
+        <v>1458.8</v>
       </c>
       <c r="D5" t="n">
-        <v>1443.58</v>
+        <v>1443.74</v>
       </c>
       <c r="E5" t="n">
-        <v>1420.14</v>
+        <v>1420.24</v>
       </c>
       <c r="F5" t="n">
-        <v>1394.47</v>
+        <v>1394.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.27</v>
+        <v>4.61</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>364.15</v>
+        <v>366</v>
       </c>
       <c r="D6" t="n">
-        <v>358.23</v>
+        <v>358.57</v>
       </c>
       <c r="E6" t="n">
-        <v>351.77</v>
+        <v>352.45</v>
       </c>
       <c r="F6" t="n">
-        <v>347.75</v>
+        <v>347.8</v>
       </c>
       <c r="G6" t="n">
-        <v>4.72</v>
+        <v>5.23</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12160</v>
+        <v>12190</v>
       </c>
       <c r="D7" t="n">
-        <v>11540.28</v>
+        <v>11541.28</v>
       </c>
       <c r="E7" t="n">
-        <v>11319.71</v>
+        <v>11320.31</v>
       </c>
       <c r="F7" t="n">
-        <v>11570.86</v>
+        <v>11571.01</v>
       </c>
       <c r="G7" t="n">
-        <v>5.09</v>
+        <v>5.35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4626.7</v>
+        <v>4645</v>
       </c>
       <c r="D8" t="n">
-        <v>4498.76</v>
+        <v>4499.37</v>
       </c>
       <c r="E8" t="n">
-        <v>4423.49</v>
+        <v>4423.86</v>
       </c>
       <c r="F8" t="n">
-        <v>4343.81</v>
+        <v>4343.91</v>
       </c>
       <c r="G8" t="n">
-        <v>6.51</v>
+        <v>6.93</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2758.1</v>
+        <v>2760</v>
       </c>
       <c r="D9" t="n">
-        <v>2701.23</v>
+        <v>2701.3</v>
       </c>
       <c r="E9" t="n">
-        <v>2690.07</v>
+        <v>2690.11</v>
       </c>
       <c r="F9" t="n">
-        <v>2579.41</v>
+        <v>2579.42</v>
       </c>
       <c r="G9" t="n">
-        <v>6.93</v>
+        <v>7</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>737</v>
+        <v>741.05</v>
       </c>
       <c r="D10" t="n">
-        <v>732.0700000000001</v>
+        <v>732.2</v>
       </c>
       <c r="E10" t="n">
-        <v>710.7</v>
+        <v>710.78</v>
       </c>
       <c r="F10" t="n">
-        <v>686.47</v>
+        <v>686.49</v>
       </c>
       <c r="G10" t="n">
-        <v>7.36</v>
+        <v>7.95</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D11" t="n">
-        <v>1111.99</v>
+        <v>1113.86</v>
       </c>
       <c r="E11" t="n">
-        <v>1107.23</v>
+        <v>1108.1</v>
       </c>
       <c r="F11" t="n">
-        <v>1101.27</v>
+        <v>1101.31</v>
       </c>
       <c r="G11" t="n">
-        <v>8.15</v>
+        <v>8.23</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>612.4</v>
+        <v>603</v>
       </c>
       <c r="D12" t="n">
-        <v>585.0599999999999</v>
+        <v>584.75</v>
       </c>
       <c r="E12" t="n">
-        <v>552.87</v>
+        <v>552.6900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>554.35</v>
+        <v>554.3099999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>10.47</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8008.5</v>
+        <v>7986.5</v>
       </c>
       <c r="D13" t="n">
-        <v>7495.86</v>
+        <v>7495.13</v>
       </c>
       <c r="E13" t="n">
-        <v>7403.24</v>
+        <v>7402.8</v>
       </c>
       <c r="F13" t="n">
-        <v>7193.37</v>
+        <v>7193.26</v>
       </c>
       <c r="G13" t="n">
-        <v>11.33</v>
+        <v>11.03</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2121.3</v>
+        <v>2099</v>
       </c>
       <c r="D14" t="n">
-        <v>2038.78</v>
+        <v>2038.04</v>
       </c>
       <c r="E14" t="n">
-        <v>1914.87</v>
+        <v>1914.43</v>
       </c>
       <c r="F14" t="n">
-        <v>1879.89</v>
+        <v>1879.78</v>
       </c>
       <c r="G14" t="n">
-        <v>12.84</v>
+        <v>11.66</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1660.9</v>
+        <v>1650</v>
       </c>
       <c r="D15" t="n">
-        <v>1505.45</v>
+        <v>1512.55</v>
       </c>
       <c r="E15" t="n">
-        <v>1475.52</v>
+        <v>1479.9</v>
       </c>
       <c r="F15" t="n">
-        <v>1462.48</v>
+        <v>1463.61</v>
       </c>
       <c r="G15" t="n">
-        <v>13.57</v>
+        <v>12.74</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>311.25</v>
+        <v>310.35</v>
       </c>
       <c r="D16" t="n">
-        <v>288.15</v>
+        <v>288.12</v>
       </c>
       <c r="E16" t="n">
-        <v>273.74</v>
+        <v>273.72</v>
       </c>
       <c r="F16" t="n">
         <v>273.2</v>
       </c>
       <c r="G16" t="n">
-        <v>13.93</v>
+        <v>13.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14341</v>
+        <v>14310</v>
       </c>
       <c r="D17" t="n">
-        <v>13437.2</v>
+        <v>13436.17</v>
       </c>
       <c r="E17" t="n">
-        <v>12791.58</v>
+        <v>12790.96</v>
       </c>
       <c r="F17" t="n">
-        <v>12278.06</v>
+        <v>12277.9</v>
       </c>
       <c r="G17" t="n">
-        <v>16.8</v>
+        <v>16.55</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1780.6</v>
+        <v>1777</v>
       </c>
       <c r="D18" t="n">
-        <v>1539.71</v>
+        <v>1539.59</v>
       </c>
       <c r="E18" t="n">
-        <v>1497.63</v>
+        <v>1497.56</v>
       </c>
       <c r="F18" t="n">
-        <v>1505.16</v>
+        <v>1505.14</v>
       </c>
       <c r="G18" t="n">
-        <v>18.3</v>
+        <v>18.06</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.55</v>
+        <v>113.6</v>
       </c>
       <c r="D2" t="n">
-        <v>108.32</v>
+        <v>108</v>
       </c>
       <c r="E2" t="n">
-        <v>107.18</v>
+        <v>106.82</v>
       </c>
       <c r="F2" t="n">
-        <v>112.64</v>
+        <v>112.65</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>129.59</v>
+        <v>5546</v>
       </c>
       <c r="D3" t="n">
-        <v>124.58</v>
+        <v>5056.39</v>
       </c>
       <c r="E3" t="n">
-        <v>124.02</v>
+        <v>5031.07</v>
       </c>
       <c r="F3" t="n">
-        <v>127.98</v>
+        <v>5452.67</v>
       </c>
       <c r="G3" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5696.5</v>
+        <v>5685</v>
       </c>
       <c r="D4" t="n">
-        <v>5614.28</v>
+        <v>5587.17</v>
       </c>
       <c r="E4" t="n">
-        <v>5506.61</v>
+        <v>5490.76</v>
       </c>
       <c r="F4" t="n">
-        <v>5525.72</v>
+        <v>5522.7</v>
       </c>
       <c r="G4" t="n">
-        <v>3.09</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1458.8</v>
+        <v>3437.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1443.74</v>
+        <v>3202.47</v>
       </c>
       <c r="E5" t="n">
-        <v>1420.24</v>
+        <v>3128.76</v>
       </c>
       <c r="F5" t="n">
-        <v>1394.5</v>
+        <v>3328.45</v>
       </c>
       <c r="G5" t="n">
-        <v>4.61</v>
+        <v>3.28</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>366</v>
+        <v>517.75</v>
       </c>
       <c r="D6" t="n">
-        <v>358.57</v>
+        <v>489.63</v>
       </c>
       <c r="E6" t="n">
-        <v>352.45</v>
+        <v>477.29</v>
       </c>
       <c r="F6" t="n">
-        <v>347.8</v>
+        <v>494.04</v>
       </c>
       <c r="G6" t="n">
-        <v>5.23</v>
+        <v>4.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12190</v>
+        <v>364.7</v>
       </c>
       <c r="D7" t="n">
-        <v>11541.28</v>
+        <v>358.71</v>
       </c>
       <c r="E7" t="n">
-        <v>11320.31</v>
+        <v>353.03</v>
       </c>
       <c r="F7" t="n">
-        <v>11571.01</v>
+        <v>347.83</v>
       </c>
       <c r="G7" t="n">
-        <v>5.35</v>
+        <v>4.85</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4645</v>
+        <v>12146</v>
       </c>
       <c r="D8" t="n">
-        <v>4499.37</v>
+        <v>11484.12</v>
       </c>
       <c r="E8" t="n">
-        <v>4423.86</v>
+        <v>11297.28</v>
       </c>
       <c r="F8" t="n">
-        <v>4343.91</v>
+        <v>11571.9</v>
       </c>
       <c r="G8" t="n">
-        <v>6.93</v>
+        <v>4.96</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2760</v>
+        <v>1469.6</v>
       </c>
       <c r="D9" t="n">
-        <v>2701.3</v>
+        <v>1444.72</v>
       </c>
       <c r="E9" t="n">
-        <v>2690.11</v>
+        <v>1421.53</v>
       </c>
       <c r="F9" t="n">
-        <v>2579.42</v>
+        <v>1394.03</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>5.42</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>741.05</v>
+        <v>1182.6</v>
       </c>
       <c r="D10" t="n">
-        <v>732.2</v>
+        <v>1117.1</v>
       </c>
       <c r="E10" t="n">
-        <v>710.78</v>
+        <v>1109.51</v>
       </c>
       <c r="F10" t="n">
-        <v>686.49</v>
+        <v>1101.43</v>
       </c>
       <c r="G10" t="n">
-        <v>7.95</v>
+        <v>7.37</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1192</v>
+        <v>739.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1113.86</v>
+        <v>731.33</v>
       </c>
       <c r="E11" t="n">
-        <v>1108.1</v>
+        <v>709.04</v>
       </c>
       <c r="F11" t="n">
-        <v>1101.31</v>
+        <v>686.41</v>
       </c>
       <c r="G11" t="n">
-        <v>8.23</v>
+        <v>7.72</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>603</v>
+        <v>2779</v>
       </c>
       <c r="D12" t="n">
-        <v>584.75</v>
+        <v>2694.68</v>
       </c>
       <c r="E12" t="n">
-        <v>552.6900000000001</v>
+        <v>2682.86</v>
       </c>
       <c r="F12" t="n">
-        <v>554.3099999999999</v>
+        <v>2571.73</v>
       </c>
       <c r="G12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7986.5</v>
+        <v>601.75</v>
       </c>
       <c r="D13" t="n">
-        <v>7495.13</v>
+        <v>586.61</v>
       </c>
       <c r="E13" t="n">
-        <v>7402.8</v>
+        <v>555.2</v>
       </c>
       <c r="F13" t="n">
-        <v>7193.26</v>
+        <v>554.37</v>
       </c>
       <c r="G13" t="n">
-        <v>11.03</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2099</v>
+        <v>807.6</v>
       </c>
       <c r="D14" t="n">
-        <v>2038.04</v>
+        <v>781.67</v>
       </c>
       <c r="E14" t="n">
-        <v>1914.43</v>
+        <v>778.92</v>
       </c>
       <c r="F14" t="n">
-        <v>1879.78</v>
+        <v>743.1</v>
       </c>
       <c r="G14" t="n">
-        <v>11.66</v>
+        <v>8.68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1650</v>
+        <v>2080.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1512.55</v>
+        <v>1902.24</v>
       </c>
       <c r="E15" t="n">
-        <v>1479.9</v>
+        <v>1835.41</v>
       </c>
       <c r="F15" t="n">
-        <v>1463.61</v>
+        <v>1912.05</v>
       </c>
       <c r="G15" t="n">
-        <v>12.74</v>
+        <v>8.81</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>310.35</v>
+        <v>4738.6</v>
       </c>
       <c r="D16" t="n">
-        <v>288.12</v>
+        <v>4511.7</v>
       </c>
       <c r="E16" t="n">
-        <v>273.72</v>
+        <v>4430.37</v>
       </c>
       <c r="F16" t="n">
-        <v>273.2</v>
+        <v>4343.41</v>
       </c>
       <c r="G16" t="n">
-        <v>13.6</v>
+        <v>9.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14310</v>
+        <v>5407</v>
       </c>
       <c r="D17" t="n">
-        <v>13436.17</v>
+        <v>5276.59</v>
       </c>
       <c r="E17" t="n">
-        <v>12790.96</v>
+        <v>5060.61</v>
       </c>
       <c r="F17" t="n">
-        <v>12277.9</v>
+        <v>4938.55</v>
       </c>
       <c r="G17" t="n">
-        <v>16.55</v>
+        <v>9.49</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,35 +1058,220 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>8013</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7496.01</v>
+      </c>
+      <c r="E18" t="n">
+        <v>7403.33</v>
+      </c>
+      <c r="F18" t="n">
+        <v>7193.39</v>
+      </c>
+      <c r="G18" t="n">
+        <v>11.39</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>GODREJPROP</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2095</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2010.24</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1895.89</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1880.53</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1669.2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1521.5</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1484.91</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1464.97</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>313.8</v>
+      </c>
+      <c r="D21" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>274.86</v>
+      </c>
+      <c r="F21" t="n">
+        <v>273.06</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>14419</v>
+      </c>
+      <c r="D22" t="n">
+        <v>13311.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>12704.32</v>
+      </c>
+      <c r="F22" t="n">
+        <v>12307.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>17.16</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1777</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1539.59</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1497.56</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1505.14</v>
-      </c>
-      <c r="G18" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1795.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1531.12</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1487.42</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1507.56</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113.6</v>
+        <v>129.39</v>
       </c>
       <c r="D2" t="n">
-        <v>108</v>
+        <v>124.72</v>
       </c>
       <c r="E2" t="n">
-        <v>106.82</v>
+        <v>124.08</v>
       </c>
       <c r="F2" t="n">
-        <v>112.65</v>
+        <v>127.98</v>
       </c>
       <c r="G2" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5546</v>
+        <v>5524</v>
       </c>
       <c r="D3" t="n">
-        <v>5056.39</v>
+        <v>5055.65</v>
       </c>
       <c r="E3" t="n">
-        <v>5031.07</v>
+        <v>5030.63</v>
       </c>
       <c r="F3" t="n">
-        <v>5452.67</v>
+        <v>5452.56</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.31</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5685</v>
+        <v>114.42</v>
       </c>
       <c r="D4" t="n">
-        <v>5587.17</v>
+        <v>108.53</v>
       </c>
       <c r="E4" t="n">
-        <v>5490.76</v>
+        <v>107.4</v>
       </c>
       <c r="F4" t="n">
-        <v>5522.7</v>
+        <v>112.66</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>1.56</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3437.5</v>
+        <v>5668</v>
       </c>
       <c r="D5" t="n">
-        <v>3202.47</v>
+        <v>5613.33</v>
       </c>
       <c r="E5" t="n">
-        <v>3128.76</v>
+        <v>5506.04</v>
       </c>
       <c r="F5" t="n">
-        <v>3328.45</v>
+        <v>5525.58</v>
       </c>
       <c r="G5" t="n">
-        <v>3.28</v>
+        <v>2.58</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>517.75</v>
+        <v>3427.3</v>
       </c>
       <c r="D6" t="n">
-        <v>489.63</v>
+        <v>3202.13</v>
       </c>
       <c r="E6" t="n">
-        <v>477.29</v>
+        <v>3128.56</v>
       </c>
       <c r="F6" t="n">
-        <v>494.04</v>
+        <v>3328.4</v>
       </c>
       <c r="G6" t="n">
-        <v>4.8</v>
+        <v>2.97</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>364.7</v>
+        <v>516.35</v>
       </c>
       <c r="D7" t="n">
-        <v>358.71</v>
+        <v>489.58</v>
       </c>
       <c r="E7" t="n">
-        <v>353.03</v>
+        <v>477.27</v>
       </c>
       <c r="F7" t="n">
-        <v>347.83</v>
+        <v>494.03</v>
       </c>
       <c r="G7" t="n">
-        <v>4.85</v>
+        <v>4.52</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12146</v>
+        <v>364.7</v>
       </c>
       <c r="D8" t="n">
-        <v>11484.12</v>
+        <v>358.71</v>
       </c>
       <c r="E8" t="n">
-        <v>11297.28</v>
+        <v>353.03</v>
       </c>
       <c r="F8" t="n">
-        <v>11571.9</v>
+        <v>347.83</v>
       </c>
       <c r="G8" t="n">
-        <v>4.96</v>
+        <v>4.85</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1469.6</v>
+        <v>12147</v>
       </c>
       <c r="D9" t="n">
-        <v>1444.72</v>
+        <v>11570.87</v>
       </c>
       <c r="E9" t="n">
-        <v>1421.53</v>
+        <v>11334.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1394.03</v>
+        <v>11571.13</v>
       </c>
       <c r="G9" t="n">
-        <v>5.42</v>
+        <v>4.98</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1182.6</v>
+        <v>1478.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1117.1</v>
+        <v>1445.02</v>
       </c>
       <c r="E10" t="n">
-        <v>1109.51</v>
+        <v>1421.71</v>
       </c>
       <c r="F10" t="n">
-        <v>1101.43</v>
+        <v>1394.07</v>
       </c>
       <c r="G10" t="n">
-        <v>7.37</v>
+        <v>6.06</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>739.4</v>
+        <v>2765.7</v>
       </c>
       <c r="D11" t="n">
-        <v>731.33</v>
+        <v>2705.31</v>
       </c>
       <c r="E11" t="n">
-        <v>709.04</v>
+        <v>2692.44</v>
       </c>
       <c r="F11" t="n">
-        <v>686.41</v>
+        <v>2580.84</v>
       </c>
       <c r="G11" t="n">
-        <v>7.72</v>
+        <v>7.16</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2779</v>
+        <v>741.5</v>
       </c>
       <c r="D12" t="n">
-        <v>2694.68</v>
+        <v>732.9</v>
       </c>
       <c r="E12" t="n">
-        <v>2682.86</v>
+        <v>712.3099999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>2571.73</v>
+        <v>686.54</v>
       </c>
       <c r="G12" t="n">
-        <v>8.06</v>
+        <v>8.01</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>601.75</v>
+        <v>1193.1</v>
       </c>
       <c r="D13" t="n">
-        <v>586.61</v>
+        <v>1117.45</v>
       </c>
       <c r="E13" t="n">
-        <v>555.2</v>
+        <v>1109.72</v>
       </c>
       <c r="F13" t="n">
-        <v>554.37</v>
+        <v>1101.48</v>
       </c>
       <c r="G13" t="n">
-        <v>8.550000000000001</v>
+        <v>8.32</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>807.6</v>
+        <v>806.95</v>
       </c>
       <c r="D14" t="n">
-        <v>781.67</v>
+        <v>781.64</v>
       </c>
       <c r="E14" t="n">
-        <v>778.92</v>
+        <v>778.91</v>
       </c>
       <c r="F14" t="n">
         <v>743.1</v>
       </c>
       <c r="G14" t="n">
-        <v>8.68</v>
+        <v>8.59</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2080.5</v>
+        <v>2087.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1902.24</v>
+        <v>1902.48</v>
       </c>
       <c r="E15" t="n">
-        <v>1835.41</v>
+        <v>1835.55</v>
       </c>
       <c r="F15" t="n">
-        <v>1912.05</v>
+        <v>1912.09</v>
       </c>
       <c r="G15" t="n">
-        <v>8.81</v>
+        <v>9.17</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4738.6</v>
+        <v>5396.5</v>
       </c>
       <c r="D16" t="n">
-        <v>4511.7</v>
+        <v>5276.24</v>
       </c>
       <c r="E16" t="n">
-        <v>4430.37</v>
+        <v>5060.4</v>
       </c>
       <c r="F16" t="n">
-        <v>4343.41</v>
+        <v>4938.5</v>
       </c>
       <c r="G16" t="n">
-        <v>9.1</v>
+        <v>9.27</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5407</v>
+        <v>611.4</v>
       </c>
       <c r="D17" t="n">
-        <v>5276.59</v>
+        <v>586.9299999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>5060.61</v>
+        <v>555.39</v>
       </c>
       <c r="F17" t="n">
-        <v>4938.55</v>
+        <v>554.42</v>
       </c>
       <c r="G17" t="n">
-        <v>9.49</v>
+        <v>10.28</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8013</v>
+        <v>2082.5</v>
       </c>
       <c r="D18" t="n">
-        <v>7496.01</v>
+        <v>2046.06</v>
       </c>
       <c r="E18" t="n">
-        <v>7403.33</v>
+        <v>1920.48</v>
       </c>
       <c r="F18" t="n">
-        <v>7193.39</v>
+        <v>1879.06</v>
       </c>
       <c r="G18" t="n">
-        <v>11.39</v>
+        <v>10.83</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2095</v>
+        <v>8036.5</v>
       </c>
       <c r="D19" t="n">
-        <v>2010.24</v>
+        <v>7496.8</v>
       </c>
       <c r="E19" t="n">
-        <v>1895.89</v>
+        <v>7403.8</v>
       </c>
       <c r="F19" t="n">
-        <v>1880.53</v>
+        <v>7193.51</v>
       </c>
       <c r="G19" t="n">
-        <v>11.4</v>
+        <v>11.72</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1669.2</v>
+        <v>4859.3</v>
       </c>
       <c r="D20" t="n">
-        <v>1521.5</v>
+        <v>4515.72</v>
       </c>
       <c r="E20" t="n">
-        <v>1484.91</v>
+        <v>4432.79</v>
       </c>
       <c r="F20" t="n">
-        <v>1464.97</v>
+        <v>4344.01</v>
       </c>
       <c r="G20" t="n">
-        <v>13.94</v>
+        <v>11.86</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>313.8</v>
+        <v>1655.6</v>
       </c>
       <c r="D21" t="n">
-        <v>290.07</v>
+        <v>1521.05</v>
       </c>
       <c r="E21" t="n">
-        <v>274.86</v>
+        <v>1484.64</v>
       </c>
       <c r="F21" t="n">
-        <v>273.06</v>
+        <v>1464.9</v>
       </c>
       <c r="G21" t="n">
-        <v>14.92</v>
+        <v>13.02</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14419</v>
+        <v>316.45</v>
       </c>
       <c r="D22" t="n">
-        <v>13311.4</v>
+        <v>290.16</v>
       </c>
       <c r="E22" t="n">
-        <v>12704.32</v>
+        <v>274.92</v>
       </c>
       <c r="F22" t="n">
-        <v>12307.2</v>
+        <v>273.07</v>
       </c>
       <c r="G22" t="n">
-        <v>17.16</v>
+        <v>15.89</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,30 +1248,67 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>14317</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13512.97</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12842.18</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12265.98</v>
+      </c>
+      <c r="G23" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1795.4</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1531.12</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1487.42</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1507.56</v>
-      </c>
-      <c r="G23" t="n">
-        <v>19.09</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1782.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1539.76</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1497.66</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1505.17</v>
+      </c>
+      <c r="G24" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>129.39</v>
+        <v>128</v>
       </c>
       <c r="D2" t="n">
-        <v>124.72</v>
+        <v>124.68</v>
       </c>
       <c r="E2" t="n">
-        <v>124.08</v>
+        <v>124.05</v>
       </c>
       <c r="F2" t="n">
-        <v>127.98</v>
+        <v>127.97</v>
       </c>
       <c r="G2" t="n">
-        <v>1.1</v>
+        <v>0.02</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5524</v>
+        <v>5474</v>
       </c>
       <c r="D3" t="n">
-        <v>5055.65</v>
+        <v>5053.99</v>
       </c>
       <c r="E3" t="n">
-        <v>5030.63</v>
+        <v>5029.63</v>
       </c>
       <c r="F3" t="n">
-        <v>5452.56</v>
+        <v>5452.31</v>
       </c>
       <c r="G3" t="n">
-        <v>1.31</v>
+        <v>0.4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>114.42</v>
+        <v>114.44</v>
       </c>
       <c r="D4" t="n">
         <v>108.53</v>
@@ -561,7 +561,7 @@
         <v>112.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5668</v>
+        <v>3414</v>
       </c>
       <c r="D5" t="n">
-        <v>5613.33</v>
+        <v>3201.69</v>
       </c>
       <c r="E5" t="n">
-        <v>5506.04</v>
+        <v>3128.29</v>
       </c>
       <c r="F5" t="n">
-        <v>5525.58</v>
+        <v>3328.33</v>
       </c>
       <c r="G5" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3427.3</v>
+        <v>511.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3202.13</v>
+        <v>489.42</v>
       </c>
       <c r="E6" t="n">
-        <v>3128.56</v>
+        <v>477.17</v>
       </c>
       <c r="F6" t="n">
-        <v>3328.4</v>
+        <v>494.01</v>
       </c>
       <c r="G6" t="n">
-        <v>2.97</v>
+        <v>3.54</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>516.35</v>
+        <v>363.3</v>
       </c>
       <c r="D7" t="n">
-        <v>489.58</v>
+        <v>358.66</v>
       </c>
       <c r="E7" t="n">
-        <v>477.27</v>
+        <v>353</v>
       </c>
       <c r="F7" t="n">
-        <v>494.03</v>
+        <v>347.82</v>
       </c>
       <c r="G7" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>364.7</v>
+        <v>12099</v>
       </c>
       <c r="D8" t="n">
-        <v>358.71</v>
+        <v>11569.27</v>
       </c>
       <c r="E8" t="n">
-        <v>353.03</v>
+        <v>11333.18</v>
       </c>
       <c r="F8" t="n">
-        <v>347.83</v>
+        <v>11570.89</v>
       </c>
       <c r="G8" t="n">
-        <v>4.85</v>
+        <v>4.56</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12147</v>
+        <v>1474</v>
       </c>
       <c r="D9" t="n">
-        <v>11570.87</v>
+        <v>1444.87</v>
       </c>
       <c r="E9" t="n">
-        <v>11334.14</v>
+        <v>1421.62</v>
       </c>
       <c r="F9" t="n">
-        <v>11571.13</v>
+        <v>1394.05</v>
       </c>
       <c r="G9" t="n">
-        <v>4.98</v>
+        <v>5.73</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1478.5</v>
+        <v>2754.8</v>
       </c>
       <c r="D10" t="n">
-        <v>1445.02</v>
+        <v>2704.95</v>
       </c>
       <c r="E10" t="n">
-        <v>1421.71</v>
+        <v>2692.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1394.07</v>
+        <v>2580.78</v>
       </c>
       <c r="G10" t="n">
-        <v>6.06</v>
+        <v>6.74</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2765.7</v>
+        <v>733.9</v>
       </c>
       <c r="D11" t="n">
-        <v>2705.31</v>
+        <v>732.64</v>
       </c>
       <c r="E11" t="n">
-        <v>2692.44</v>
+        <v>712.16</v>
       </c>
       <c r="F11" t="n">
-        <v>2580.84</v>
+        <v>686.5</v>
       </c>
       <c r="G11" t="n">
-        <v>7.16</v>
+        <v>6.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>741.5</v>
+        <v>1232.1</v>
       </c>
       <c r="D12" t="n">
-        <v>732.9</v>
+        <v>1157.77</v>
       </c>
       <c r="E12" t="n">
-        <v>712.3099999999999</v>
+        <v>1091.04</v>
       </c>
       <c r="F12" t="n">
-        <v>686.54</v>
+        <v>1148.56</v>
       </c>
       <c r="G12" t="n">
-        <v>8.01</v>
+        <v>7.27</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1193.1</v>
+        <v>799.45</v>
       </c>
       <c r="D13" t="n">
-        <v>1117.45</v>
+        <v>781.39</v>
       </c>
       <c r="E13" t="n">
-        <v>1109.72</v>
+        <v>778.76</v>
       </c>
       <c r="F13" t="n">
-        <v>1101.48</v>
+        <v>743.0599999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>8.32</v>
+        <v>7.59</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>806.95</v>
+        <v>1186</v>
       </c>
       <c r="D14" t="n">
-        <v>781.64</v>
+        <v>1117.22</v>
       </c>
       <c r="E14" t="n">
-        <v>778.91</v>
+        <v>1109.58</v>
       </c>
       <c r="F14" t="n">
-        <v>743.1</v>
+        <v>1101.44</v>
       </c>
       <c r="G14" t="n">
-        <v>8.59</v>
+        <v>7.68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2087.5</v>
+        <v>5330</v>
       </c>
       <c r="D15" t="n">
-        <v>1902.48</v>
+        <v>5274.02</v>
       </c>
       <c r="E15" t="n">
-        <v>1835.55</v>
+        <v>5059.07</v>
       </c>
       <c r="F15" t="n">
-        <v>1912.09</v>
+        <v>4938.17</v>
       </c>
       <c r="G15" t="n">
-        <v>9.17</v>
+        <v>7.93</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5396.5</v>
+        <v>2084.5</v>
       </c>
       <c r="D16" t="n">
-        <v>5276.24</v>
+        <v>1902.38</v>
       </c>
       <c r="E16" t="n">
-        <v>5060.4</v>
+        <v>1835.49</v>
       </c>
       <c r="F16" t="n">
-        <v>4938.5</v>
+        <v>1912.07</v>
       </c>
       <c r="G16" t="n">
-        <v>9.27</v>
+        <v>9.02</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>611.4</v>
+        <v>609</v>
       </c>
       <c r="D17" t="n">
-        <v>586.9299999999999</v>
+        <v>586.85</v>
       </c>
       <c r="E17" t="n">
-        <v>555.39</v>
+        <v>555.34</v>
       </c>
       <c r="F17" t="n">
-        <v>554.42</v>
+        <v>554.41</v>
       </c>
       <c r="G17" t="n">
-        <v>10.28</v>
+        <v>9.85</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2082.5</v>
+        <v>7935</v>
       </c>
       <c r="D18" t="n">
-        <v>2046.06</v>
+        <v>7508.99</v>
       </c>
       <c r="E18" t="n">
-        <v>1920.48</v>
+        <v>7414.66</v>
       </c>
       <c r="F18" t="n">
-        <v>1879.06</v>
+        <v>7198.09</v>
       </c>
       <c r="G18" t="n">
-        <v>10.83</v>
+        <v>10.24</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>8036.5</v>
+        <v>2095</v>
       </c>
       <c r="D19" t="n">
-        <v>7496.8</v>
+        <v>2046.48</v>
       </c>
       <c r="E19" t="n">
-        <v>7403.8</v>
+        <v>1920.73</v>
       </c>
       <c r="F19" t="n">
-        <v>7193.51</v>
+        <v>1879.13</v>
       </c>
       <c r="G19" t="n">
-        <v>11.72</v>
+        <v>11.49</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4859.3</v>
+        <v>1635</v>
       </c>
       <c r="D20" t="n">
-        <v>4515.72</v>
+        <v>1520.36</v>
       </c>
       <c r="E20" t="n">
-        <v>4432.79</v>
+        <v>1484.22</v>
       </c>
       <c r="F20" t="n">
-        <v>4344.01</v>
+        <v>1464.8</v>
       </c>
       <c r="G20" t="n">
-        <v>11.86</v>
+        <v>11.62</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1655.6</v>
+        <v>14200</v>
       </c>
       <c r="D21" t="n">
-        <v>1521.05</v>
+        <v>13509.07</v>
       </c>
       <c r="E21" t="n">
-        <v>1484.64</v>
+        <v>12839.84</v>
       </c>
       <c r="F21" t="n">
-        <v>1464.9</v>
+        <v>12265.4</v>
       </c>
       <c r="G21" t="n">
-        <v>13.02</v>
+        <v>15.77</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>316.45</v>
+        <v>316.5</v>
       </c>
       <c r="D22" t="n">
         <v>290.16</v>
@@ -1227,7 +1227,7 @@
         <v>273.07</v>
       </c>
       <c r="G22" t="n">
-        <v>15.89</v>
+        <v>15.9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>14317</v>
+        <v>1778</v>
       </c>
       <c r="D23" t="n">
-        <v>13512.97</v>
+        <v>1549.32</v>
       </c>
       <c r="E23" t="n">
-        <v>12842.18</v>
+        <v>1505.48</v>
       </c>
       <c r="F23" t="n">
-        <v>12265.98</v>
+        <v>1505.44</v>
       </c>
       <c r="G23" t="n">
-        <v>16.72</v>
+        <v>18.11</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1272,43 +1272,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1782.2</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1539.76</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1497.66</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1505.17</v>
-      </c>
-      <c r="G24" t="n">
-        <v>18.41</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128</v>
+        <v>128.31</v>
       </c>
       <c r="D2" t="n">
-        <v>124.68</v>
+        <v>124.81</v>
       </c>
       <c r="E2" t="n">
-        <v>124.05</v>
+        <v>124.06</v>
       </c>
       <c r="F2" t="n">
-        <v>127.97</v>
+        <v>127.94</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02</v>
+        <v>0.29</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5474</v>
+        <v>114.07</v>
       </c>
       <c r="D3" t="n">
-        <v>5053.99</v>
+        <v>108.74</v>
       </c>
       <c r="E3" t="n">
-        <v>5029.63</v>
+        <v>107.61</v>
       </c>
       <c r="F3" t="n">
-        <v>5452.31</v>
+        <v>112.66</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4</v>
+        <v>1.26</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>114.44</v>
+        <v>5549.5</v>
       </c>
       <c r="D4" t="n">
-        <v>108.53</v>
+        <v>5077.66</v>
       </c>
       <c r="E4" t="n">
-        <v>107.4</v>
+        <v>5036.8</v>
       </c>
       <c r="F4" t="n">
-        <v>112.66</v>
+        <v>5450.97</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3414</v>
+        <v>3444</v>
       </c>
       <c r="D5" t="n">
-        <v>3201.69</v>
+        <v>3211.25</v>
       </c>
       <c r="E5" t="n">
-        <v>3128.29</v>
+        <v>3136.73</v>
       </c>
       <c r="F5" t="n">
-        <v>3328.33</v>
+        <v>3327.7</v>
       </c>
       <c r="G5" t="n">
-        <v>2.57</v>
+        <v>3.49</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>511.5</v>
+        <v>513.4</v>
       </c>
       <c r="D6" t="n">
-        <v>489.42</v>
+        <v>490.94</v>
       </c>
       <c r="E6" t="n">
-        <v>477.17</v>
+        <v>478.2</v>
       </c>
       <c r="F6" t="n">
-        <v>494.01</v>
+        <v>493.95</v>
       </c>
       <c r="G6" t="n">
-        <v>3.54</v>
+        <v>3.94</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>363.3</v>
+        <v>12033</v>
       </c>
       <c r="D7" t="n">
-        <v>358.66</v>
+        <v>11567.07</v>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>11331.86</v>
       </c>
       <c r="F7" t="n">
-        <v>347.82</v>
+        <v>11570.56</v>
       </c>
       <c r="G7" t="n">
-        <v>4.45</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12099</v>
+        <v>363.75</v>
       </c>
       <c r="D8" t="n">
-        <v>11569.27</v>
+        <v>358.71</v>
       </c>
       <c r="E8" t="n">
-        <v>11333.18</v>
+        <v>353.57</v>
       </c>
       <c r="F8" t="n">
-        <v>11570.89</v>
+        <v>347.84</v>
       </c>
       <c r="G8" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1474</v>
+        <v>2017</v>
       </c>
       <c r="D9" t="n">
-        <v>1444.87</v>
+        <v>1900.13</v>
       </c>
       <c r="E9" t="n">
-        <v>1421.62</v>
+        <v>1834.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1394.05</v>
+        <v>1911.73</v>
       </c>
       <c r="G9" t="n">
-        <v>5.73</v>
+        <v>5.51</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2754.8</v>
+        <v>1470.2</v>
       </c>
       <c r="D10" t="n">
-        <v>2704.95</v>
+        <v>1445.97</v>
       </c>
       <c r="E10" t="n">
-        <v>2692.22</v>
+        <v>1423.32</v>
       </c>
       <c r="F10" t="n">
-        <v>2580.78</v>
+        <v>1393.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.74</v>
+        <v>5.52</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>733.9</v>
+        <v>2739.9</v>
       </c>
       <c r="D11" t="n">
-        <v>732.64</v>
+        <v>2708.11</v>
       </c>
       <c r="E11" t="n">
-        <v>712.16</v>
+        <v>2694.05</v>
       </c>
       <c r="F11" t="n">
-        <v>686.5</v>
+        <v>2582.03</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>6.11</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1232.1</v>
+        <v>733.15</v>
       </c>
       <c r="D12" t="n">
-        <v>1157.77</v>
+        <v>733.13</v>
       </c>
       <c r="E12" t="n">
-        <v>1091.04</v>
+        <v>713.84</v>
       </c>
       <c r="F12" t="n">
-        <v>1148.56</v>
+        <v>686.48</v>
       </c>
       <c r="G12" t="n">
-        <v>7.27</v>
+        <v>6.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>799.45</v>
+        <v>794.2</v>
       </c>
       <c r="D13" t="n">
         <v>781.39</v>
       </c>
       <c r="E13" t="n">
-        <v>778.76</v>
+        <v>778.89</v>
       </c>
       <c r="F13" t="n">
-        <v>743.0599999999999</v>
+        <v>743.25</v>
       </c>
       <c r="G13" t="n">
-        <v>7.59</v>
+        <v>6.85</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1186</v>
+        <v>1238.2</v>
       </c>
       <c r="D14" t="n">
-        <v>1117.22</v>
+        <v>1166.77</v>
       </c>
       <c r="E14" t="n">
-        <v>1109.58</v>
+        <v>1096.12</v>
       </c>
       <c r="F14" t="n">
-        <v>1101.44</v>
+        <v>1148.28</v>
       </c>
       <c r="G14" t="n">
-        <v>7.68</v>
+        <v>7.83</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,7 +947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5330</v>
+        <v>5325</v>
       </c>
       <c r="D15" t="n">
-        <v>5274.02</v>
+        <v>5269.47</v>
       </c>
       <c r="E15" t="n">
-        <v>5059.07</v>
+        <v>5077.24</v>
       </c>
       <c r="F15" t="n">
-        <v>4938.17</v>
+        <v>4935.49</v>
       </c>
       <c r="G15" t="n">
-        <v>7.93</v>
+        <v>7.89</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2084.5</v>
+        <v>1191</v>
       </c>
       <c r="D16" t="n">
-        <v>1902.38</v>
+        <v>1120.74</v>
       </c>
       <c r="E16" t="n">
-        <v>1835.49</v>
+        <v>1111.31</v>
       </c>
       <c r="F16" t="n">
-        <v>1912.07</v>
+        <v>1101.64</v>
       </c>
       <c r="G16" t="n">
-        <v>9.02</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>609</v>
+        <v>8015.5</v>
       </c>
       <c r="D17" t="n">
-        <v>586.85</v>
+        <v>7511.67</v>
       </c>
       <c r="E17" t="n">
-        <v>555.34</v>
+        <v>7416.27</v>
       </c>
       <c r="F17" t="n">
-        <v>554.41</v>
+        <v>7198.49</v>
       </c>
       <c r="G17" t="n">
-        <v>9.85</v>
+        <v>11.35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7935</v>
+        <v>2097.7</v>
       </c>
       <c r="D18" t="n">
-        <v>7508.99</v>
+        <v>2054.58</v>
       </c>
       <c r="E18" t="n">
-        <v>7414.66</v>
+        <v>1927.34</v>
       </c>
       <c r="F18" t="n">
-        <v>7198.09</v>
+        <v>1878.15</v>
       </c>
       <c r="G18" t="n">
-        <v>10.24</v>
+        <v>11.69</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2095</v>
+        <v>624.35</v>
       </c>
       <c r="D19" t="n">
-        <v>2046.48</v>
+        <v>589.49</v>
       </c>
       <c r="E19" t="n">
-        <v>1920.73</v>
+        <v>558.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1879.13</v>
+        <v>554.62</v>
       </c>
       <c r="G19" t="n">
-        <v>11.49</v>
+        <v>12.57</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1635</v>
+        <v>1663.6</v>
       </c>
       <c r="D20" t="n">
-        <v>1520.36</v>
+        <v>1521.31</v>
       </c>
       <c r="E20" t="n">
-        <v>1484.22</v>
+        <v>1484.8</v>
       </c>
       <c r="F20" t="n">
-        <v>1464.8</v>
+        <v>1464.94</v>
       </c>
       <c r="G20" t="n">
-        <v>11.62</v>
+        <v>13.56</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14200</v>
+        <v>316.6</v>
       </c>
       <c r="D21" t="n">
-        <v>13509.07</v>
+        <v>292.2</v>
       </c>
       <c r="E21" t="n">
-        <v>12839.84</v>
+        <v>276.23</v>
       </c>
       <c r="F21" t="n">
-        <v>12265.4</v>
+        <v>272.96</v>
       </c>
       <c r="G21" t="n">
-        <v>15.77</v>
+        <v>15.99</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>316.5</v>
+        <v>14263</v>
       </c>
       <c r="D22" t="n">
-        <v>290.16</v>
+        <v>13511.17</v>
       </c>
       <c r="E22" t="n">
-        <v>274.92</v>
+        <v>12841.1</v>
       </c>
       <c r="F22" t="n">
-        <v>273.07</v>
+        <v>12265.72</v>
       </c>
       <c r="G22" t="n">
-        <v>15.9</v>
+        <v>16.28</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1778</v>
+        <v>1795.9</v>
       </c>
       <c r="D23" t="n">
-        <v>1549.32</v>
+        <v>1559.48</v>
       </c>
       <c r="E23" t="n">
-        <v>1505.48</v>
+        <v>1512.98</v>
       </c>
       <c r="F23" t="n">
-        <v>1505.44</v>
+        <v>1505.74</v>
       </c>
       <c r="G23" t="n">
-        <v>18.11</v>
+        <v>19.27</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>128.31</v>
+        <v>5475</v>
       </c>
       <c r="D2" t="n">
-        <v>124.81</v>
+        <v>5075.18</v>
       </c>
       <c r="E2" t="n">
-        <v>124.06</v>
+        <v>5035.31</v>
       </c>
       <c r="F2" t="n">
-        <v>127.94</v>
+        <v>5450.59</v>
       </c>
       <c r="G2" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>114.07</v>
+        <v>280.6</v>
       </c>
       <c r="D3" t="n">
-        <v>108.74</v>
+        <v>277.65</v>
       </c>
       <c r="E3" t="n">
-        <v>107.61</v>
+        <v>277.22</v>
       </c>
       <c r="F3" t="n">
-        <v>112.66</v>
+        <v>276.16</v>
       </c>
       <c r="G3" t="n">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5549.5</v>
+        <v>5620</v>
       </c>
       <c r="D4" t="n">
-        <v>5077.66</v>
+        <v>5616.82</v>
       </c>
       <c r="E4" t="n">
-        <v>5036.8</v>
+        <v>5502.32</v>
       </c>
       <c r="F4" t="n">
-        <v>5450.97</v>
+        <v>5516.9</v>
       </c>
       <c r="G4" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3444</v>
+        <v>114.81</v>
       </c>
       <c r="D5" t="n">
-        <v>3211.25</v>
+        <v>108.76</v>
       </c>
       <c r="E5" t="n">
-        <v>3136.73</v>
+        <v>107.63</v>
       </c>
       <c r="F5" t="n">
-        <v>3327.7</v>
+        <v>112.66</v>
       </c>
       <c r="G5" t="n">
-        <v>3.49</v>
+        <v>1.91</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>513.4</v>
+        <v>505.2</v>
       </c>
       <c r="D6" t="n">
-        <v>490.94</v>
+        <v>490.67</v>
       </c>
       <c r="E6" t="n">
-        <v>478.2</v>
+        <v>478.04</v>
       </c>
       <c r="F6" t="n">
-        <v>493.95</v>
+        <v>493.91</v>
       </c>
       <c r="G6" t="n">
-        <v>3.94</v>
+        <v>2.29</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12033</v>
+        <v>12105</v>
       </c>
       <c r="D7" t="n">
-        <v>11567.07</v>
+        <v>11596.66</v>
       </c>
       <c r="E7" t="n">
-        <v>11331.86</v>
+        <v>11349.76</v>
       </c>
       <c r="F7" t="n">
-        <v>11570.56</v>
+        <v>11570.8</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>363.75</v>
+        <v>1463.8</v>
       </c>
       <c r="D8" t="n">
-        <v>358.71</v>
+        <v>1445.76</v>
       </c>
       <c r="E8" t="n">
-        <v>353.57</v>
+        <v>1423.19</v>
       </c>
       <c r="F8" t="n">
-        <v>347.84</v>
+        <v>1393.27</v>
       </c>
       <c r="G8" t="n">
-        <v>4.57</v>
+        <v>5.06</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2017</v>
+        <v>2008.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1900.13</v>
+        <v>1910.62</v>
       </c>
       <c r="E9" t="n">
-        <v>1834.14</v>
+        <v>1840.06</v>
       </c>
       <c r="F9" t="n">
-        <v>1911.73</v>
+        <v>1911.43</v>
       </c>
       <c r="G9" t="n">
-        <v>5.51</v>
+        <v>5.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1470.2</v>
+        <v>3502</v>
       </c>
       <c r="D10" t="n">
-        <v>1445.97</v>
+        <v>3213.18</v>
       </c>
       <c r="E10" t="n">
-        <v>1423.32</v>
+        <v>3137.89</v>
       </c>
       <c r="F10" t="n">
-        <v>1393.3</v>
+        <v>3327.99</v>
       </c>
       <c r="G10" t="n">
-        <v>5.52</v>
+        <v>5.23</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2739.9</v>
+        <v>367</v>
       </c>
       <c r="D11" t="n">
-        <v>2708.11</v>
+        <v>358.82</v>
       </c>
       <c r="E11" t="n">
-        <v>2694.05</v>
+        <v>353.63</v>
       </c>
       <c r="F11" t="n">
-        <v>2582.03</v>
+        <v>347.86</v>
       </c>
       <c r="G11" t="n">
-        <v>6.11</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>733.15</v>
+        <v>2735</v>
       </c>
       <c r="D12" t="n">
-        <v>733.13</v>
+        <v>2707.95</v>
       </c>
       <c r="E12" t="n">
-        <v>713.84</v>
+        <v>2693.95</v>
       </c>
       <c r="F12" t="n">
-        <v>686.48</v>
+        <v>2582.01</v>
       </c>
       <c r="G12" t="n">
-        <v>6.8</v>
+        <v>5.93</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>794.2</v>
+        <v>787.5</v>
       </c>
       <c r="D13" t="n">
-        <v>781.39</v>
+        <v>781.17</v>
       </c>
       <c r="E13" t="n">
-        <v>778.89</v>
+        <v>778.76</v>
       </c>
       <c r="F13" t="n">
-        <v>743.25</v>
+        <v>743.22</v>
       </c>
       <c r="G13" t="n">
-        <v>6.85</v>
+        <v>5.96</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1238.2</v>
+        <v>1168.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1166.77</v>
+        <v>1119.97</v>
       </c>
       <c r="E14" t="n">
-        <v>1096.12</v>
+        <v>1110.85</v>
       </c>
       <c r="F14" t="n">
-        <v>1148.28</v>
+        <v>1101.52</v>
       </c>
       <c r="G14" t="n">
-        <v>7.83</v>
+        <v>6.04</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5325</v>
+        <v>1225.3</v>
       </c>
       <c r="D15" t="n">
-        <v>5269.47</v>
+        <v>1166.34</v>
       </c>
       <c r="E15" t="n">
-        <v>5077.24</v>
+        <v>1095.86</v>
       </c>
       <c r="F15" t="n">
-        <v>4935.49</v>
+        <v>1148.21</v>
       </c>
       <c r="G15" t="n">
-        <v>7.89</v>
+        <v>6.71</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1191</v>
+        <v>5333</v>
       </c>
       <c r="D16" t="n">
-        <v>1120.74</v>
+        <v>5269.74</v>
       </c>
       <c r="E16" t="n">
-        <v>1111.31</v>
+        <v>5077.4</v>
       </c>
       <c r="F16" t="n">
-        <v>1101.64</v>
+        <v>4935.53</v>
       </c>
       <c r="G16" t="n">
-        <v>8.109999999999999</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>8015.5</v>
+        <v>2070</v>
       </c>
       <c r="D17" t="n">
-        <v>7511.67</v>
+        <v>2053.65</v>
       </c>
       <c r="E17" t="n">
-        <v>7416.27</v>
+        <v>1926.78</v>
       </c>
       <c r="F17" t="n">
-        <v>7198.49</v>
+        <v>1878.01</v>
       </c>
       <c r="G17" t="n">
-        <v>11.35</v>
+        <v>10.22</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2097.7</v>
+        <v>8020</v>
       </c>
       <c r="D18" t="n">
-        <v>2054.58</v>
+        <v>7526.76</v>
       </c>
       <c r="E18" t="n">
-        <v>1927.34</v>
+        <v>7433.66</v>
       </c>
       <c r="F18" t="n">
-        <v>1878.15</v>
+        <v>7203.64</v>
       </c>
       <c r="G18" t="n">
-        <v>11.69</v>
+        <v>11.33</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>624.35</v>
+        <v>1635</v>
       </c>
       <c r="D19" t="n">
-        <v>589.49</v>
+        <v>1528.08</v>
       </c>
       <c r="E19" t="n">
-        <v>558.2</v>
+        <v>1487.94</v>
       </c>
       <c r="F19" t="n">
-        <v>554.62</v>
+        <v>1465.92</v>
       </c>
       <c r="G19" t="n">
-        <v>12.57</v>
+        <v>11.53</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1663.6</v>
+        <v>630.65</v>
       </c>
       <c r="D20" t="n">
-        <v>1521.31</v>
+        <v>589.7</v>
       </c>
       <c r="E20" t="n">
-        <v>1484.8</v>
+        <v>558.3200000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1464.94</v>
+        <v>554.65</v>
       </c>
       <c r="G20" t="n">
-        <v>13.56</v>
+        <v>13.7</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1178,19 +1178,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>316.6</v>
+        <v>315</v>
       </c>
       <c r="D21" t="n">
-        <v>292.2</v>
+        <v>292.15</v>
       </c>
       <c r="E21" t="n">
-        <v>276.23</v>
+        <v>276.2</v>
       </c>
       <c r="F21" t="n">
-        <v>272.96</v>
+        <v>272.95</v>
       </c>
       <c r="G21" t="n">
-        <v>15.99</v>
+        <v>15.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14263</v>
+        <v>14200</v>
       </c>
       <c r="D22" t="n">
-        <v>13511.17</v>
+        <v>13581.97</v>
       </c>
       <c r="E22" t="n">
-        <v>12841.1</v>
+        <v>12893.36</v>
       </c>
       <c r="F22" t="n">
-        <v>12265.72</v>
+        <v>12256.02</v>
       </c>
       <c r="G22" t="n">
-        <v>16.28</v>
+        <v>15.86</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1795.9</v>
+        <v>1776</v>
       </c>
       <c r="D23" t="n">
-        <v>1559.48</v>
+        <v>1558.82</v>
       </c>
       <c r="E23" t="n">
-        <v>1512.98</v>
+        <v>1512.59</v>
       </c>
       <c r="F23" t="n">
-        <v>1505.74</v>
+        <v>1505.64</v>
       </c>
       <c r="G23" t="n">
-        <v>19.27</v>
+        <v>17.96</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5475</v>
+        <v>5491.5</v>
       </c>
       <c r="D2" t="n">
-        <v>5075.18</v>
+        <v>5115.44</v>
       </c>
       <c r="E2" t="n">
-        <v>5035.31</v>
+        <v>5037.48</v>
       </c>
       <c r="F2" t="n">
-        <v>5450.59</v>
+        <v>5449.26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.45</v>
+        <v>0.78</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>280.6</v>
+        <v>1946.1</v>
       </c>
       <c r="D3" t="n">
-        <v>277.65</v>
+        <v>1912.8</v>
       </c>
       <c r="E3" t="n">
-        <v>277.22</v>
+        <v>1875.35</v>
       </c>
       <c r="F3" t="n">
-        <v>276.16</v>
+        <v>1927.29</v>
       </c>
       <c r="G3" t="n">
-        <v>1.61</v>
+        <v>0.98</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5620</v>
+        <v>114.44</v>
       </c>
       <c r="D4" t="n">
-        <v>5616.82</v>
+        <v>109.01</v>
       </c>
       <c r="E4" t="n">
-        <v>5502.32</v>
+        <v>107.9</v>
       </c>
       <c r="F4" t="n">
-        <v>5516.9</v>
+        <v>112.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>114.81</v>
+        <v>4034</v>
       </c>
       <c r="D5" t="n">
-        <v>108.76</v>
+        <v>3932.69</v>
       </c>
       <c r="E5" t="n">
-        <v>107.63</v>
+        <v>3991.17</v>
       </c>
       <c r="F5" t="n">
-        <v>112.66</v>
+        <v>3948.76</v>
       </c>
       <c r="G5" t="n">
-        <v>1.91</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>505.2</v>
+        <v>5647</v>
       </c>
       <c r="D6" t="n">
-        <v>490.67</v>
+        <v>5624.82</v>
       </c>
       <c r="E6" t="n">
-        <v>478.04</v>
+        <v>5509.16</v>
       </c>
       <c r="F6" t="n">
-        <v>493.91</v>
+        <v>5517.62</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12105</v>
+        <v>505.8</v>
       </c>
       <c r="D7" t="n">
-        <v>11596.66</v>
+        <v>491.87</v>
       </c>
       <c r="E7" t="n">
-        <v>11349.76</v>
+        <v>478.9</v>
       </c>
       <c r="F7" t="n">
-        <v>11570.8</v>
+        <v>493.81</v>
       </c>
       <c r="G7" t="n">
-        <v>4.62</v>
+        <v>2.43</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1463.8</v>
+        <v>360.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1445.76</v>
+        <v>358.8</v>
       </c>
       <c r="E8" t="n">
-        <v>1423.19</v>
+        <v>354.28</v>
       </c>
       <c r="F8" t="n">
-        <v>1393.27</v>
+        <v>347.86</v>
       </c>
       <c r="G8" t="n">
-        <v>5.06</v>
+        <v>3.55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2008.9</v>
+        <v>12037</v>
       </c>
       <c r="D9" t="n">
-        <v>1910.62</v>
+        <v>11627.59</v>
       </c>
       <c r="E9" t="n">
-        <v>1840.06</v>
+        <v>11370.35</v>
       </c>
       <c r="F9" t="n">
-        <v>1911.43</v>
+        <v>11570.51</v>
       </c>
       <c r="G9" t="n">
-        <v>5.1</v>
+        <v>4.03</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3502</v>
+        <v>2000.6</v>
       </c>
       <c r="D10" t="n">
-        <v>3213.18</v>
+        <v>1918.71</v>
       </c>
       <c r="E10" t="n">
-        <v>3137.89</v>
+        <v>1844.92</v>
       </c>
       <c r="F10" t="n">
-        <v>3327.99</v>
+        <v>1910.6</v>
       </c>
       <c r="G10" t="n">
-        <v>5.23</v>
+        <v>4.71</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>367</v>
+        <v>785.5</v>
       </c>
       <c r="D11" t="n">
-        <v>358.82</v>
+        <v>781.2</v>
       </c>
       <c r="E11" t="n">
-        <v>353.63</v>
+        <v>779.16</v>
       </c>
       <c r="F11" t="n">
-        <v>347.86</v>
+        <v>743.36</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2735</v>
+        <v>2730.8</v>
       </c>
       <c r="D12" t="n">
-        <v>2707.95</v>
+        <v>2710.41</v>
       </c>
       <c r="E12" t="n">
-        <v>2693.95</v>
+        <v>2696.38</v>
       </c>
       <c r="F12" t="n">
-        <v>2582.01</v>
+        <v>2583.26</v>
       </c>
       <c r="G12" t="n">
-        <v>5.93</v>
+        <v>5.71</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>787.5</v>
+        <v>3527</v>
       </c>
       <c r="D13" t="n">
-        <v>781.17</v>
+        <v>3228.72</v>
       </c>
       <c r="E13" t="n">
-        <v>778.76</v>
+        <v>3149.65</v>
       </c>
       <c r="F13" t="n">
-        <v>743.22</v>
+        <v>3327.71</v>
       </c>
       <c r="G13" t="n">
-        <v>5.96</v>
+        <v>5.99</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1168.1</v>
+        <v>1476.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1119.97</v>
+        <v>1446.51</v>
       </c>
       <c r="E14" t="n">
-        <v>1110.85</v>
+        <v>1425.18</v>
       </c>
       <c r="F14" t="n">
-        <v>1101.52</v>
+        <v>1392.41</v>
       </c>
       <c r="G14" t="n">
-        <v>6.04</v>
+        <v>6.05</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1225.3</v>
+        <v>1170.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1166.34</v>
+        <v>1122.66</v>
       </c>
       <c r="E15" t="n">
-        <v>1095.86</v>
+        <v>1112.68</v>
       </c>
       <c r="F15" t="n">
-        <v>1148.21</v>
+        <v>1101.52</v>
       </c>
       <c r="G15" t="n">
-        <v>6.71</v>
+        <v>6.24</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5333</v>
+        <v>5305</v>
       </c>
       <c r="D16" t="n">
-        <v>5269.74</v>
+        <v>5269.4</v>
       </c>
       <c r="E16" t="n">
-        <v>5077.4</v>
+        <v>5094.43</v>
       </c>
       <c r="F16" t="n">
-        <v>4935.53</v>
+        <v>4932.39</v>
       </c>
       <c r="G16" t="n">
-        <v>8.050000000000001</v>
+        <v>7.55</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2070</v>
+        <v>1260.1</v>
       </c>
       <c r="D17" t="n">
-        <v>2053.65</v>
+        <v>1175.56</v>
       </c>
       <c r="E17" t="n">
-        <v>1926.78</v>
+        <v>1101.05</v>
       </c>
       <c r="F17" t="n">
-        <v>1878.01</v>
+        <v>1147.97</v>
       </c>
       <c r="G17" t="n">
-        <v>10.22</v>
+        <v>9.77</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8020</v>
+        <v>7972.5</v>
       </c>
       <c r="D18" t="n">
-        <v>7526.76</v>
+        <v>7547.55</v>
       </c>
       <c r="E18" t="n">
-        <v>7433.66</v>
+        <v>7452.57</v>
       </c>
       <c r="F18" t="n">
-        <v>7203.64</v>
+        <v>7208.78</v>
       </c>
       <c r="G18" t="n">
-        <v>11.33</v>
+        <v>10.59</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1635</v>
+        <v>2078.4</v>
       </c>
       <c r="D19" t="n">
-        <v>1528.08</v>
+        <v>2062.22</v>
       </c>
       <c r="E19" t="n">
-        <v>1487.94</v>
+        <v>1934.23</v>
       </c>
       <c r="F19" t="n">
-        <v>1465.92</v>
+        <v>1876.99</v>
       </c>
       <c r="G19" t="n">
-        <v>11.53</v>
+        <v>10.73</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>630.65</v>
+        <v>184.17</v>
       </c>
       <c r="D20" t="n">
-        <v>589.7</v>
+        <v>170.18</v>
       </c>
       <c r="E20" t="n">
-        <v>558.3200000000001</v>
+        <v>168.5</v>
       </c>
       <c r="F20" t="n">
-        <v>554.65</v>
+        <v>164.58</v>
       </c>
       <c r="G20" t="n">
-        <v>13.7</v>
+        <v>11.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>315</v>
+        <v>622.5</v>
       </c>
       <c r="D21" t="n">
-        <v>292.15</v>
+        <v>592.5700000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>276.2</v>
+        <v>561.36</v>
       </c>
       <c r="F21" t="n">
-        <v>272.95</v>
+        <v>554.84</v>
       </c>
       <c r="G21" t="n">
-        <v>15.4</v>
+        <v>12.19</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14200</v>
+        <v>1656.7</v>
       </c>
       <c r="D22" t="n">
-        <v>13581.97</v>
+        <v>1536.72</v>
       </c>
       <c r="E22" t="n">
-        <v>12893.36</v>
+        <v>1490.99</v>
       </c>
       <c r="F22" t="n">
-        <v>12256.02</v>
+        <v>1467.15</v>
       </c>
       <c r="G22" t="n">
-        <v>15.86</v>
+        <v>12.92</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,30 +1248,104 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>313.65</v>
+      </c>
+      <c r="D23" t="n">
+        <v>293.96</v>
+      </c>
+      <c r="E23" t="n">
+        <v>277.51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>272.83</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>14138</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13659.73</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12946.86</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12246.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15.45</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1776</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1558.82</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1512.59</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1505.64</v>
-      </c>
-      <c r="G23" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="C25" t="n">
+        <v>1809</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1569.63</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1519.68</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1506.05</v>
+      </c>
+      <c r="G25" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5491.5</v>
+        <v>278.1</v>
       </c>
       <c r="D2" t="n">
-        <v>5115.44</v>
+        <v>277.54</v>
       </c>
       <c r="E2" t="n">
-        <v>5037.48</v>
+        <v>277.44</v>
       </c>
       <c r="F2" t="n">
-        <v>5449.26</v>
+        <v>276.21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1946.1</v>
+        <v>1943.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1912.8</v>
+        <v>1912.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1875.35</v>
+        <v>1875.29</v>
       </c>
       <c r="F3" t="n">
-        <v>1927.29</v>
+        <v>1927.28</v>
       </c>
       <c r="G3" t="n">
-        <v>0.98</v>
+        <v>0.83</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>114.44</v>
+        <v>114.03</v>
       </c>
       <c r="D4" t="n">
-        <v>109.01</v>
+        <v>109</v>
       </c>
       <c r="E4" t="n">
-        <v>107.9</v>
+        <v>107.89</v>
       </c>
       <c r="F4" t="n">
         <v>112.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4034</v>
+        <v>5521</v>
       </c>
       <c r="D5" t="n">
-        <v>3932.69</v>
+        <v>5074.24</v>
       </c>
       <c r="E5" t="n">
-        <v>3991.17</v>
+        <v>5034.75</v>
       </c>
       <c r="F5" t="n">
-        <v>3948.76</v>
+        <v>5450.45</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>1.29</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5647</v>
+        <v>5617</v>
       </c>
       <c r="D6" t="n">
-        <v>5624.82</v>
+        <v>5612.68</v>
       </c>
       <c r="E6" t="n">
-        <v>5509.16</v>
+        <v>5499.84</v>
       </c>
       <c r="F6" t="n">
-        <v>5517.62</v>
+        <v>5516.28</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>1.83</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>505.8</v>
+        <v>504.75</v>
       </c>
       <c r="D7" t="n">
-        <v>491.87</v>
+        <v>490.03</v>
       </c>
       <c r="E7" t="n">
-        <v>478.9</v>
+        <v>477.66</v>
       </c>
       <c r="F7" t="n">
         <v>493.81</v>
       </c>
       <c r="G7" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>360.2</v>
+        <v>4061.9</v>
       </c>
       <c r="D8" t="n">
-        <v>358.8</v>
+        <v>3933.62</v>
       </c>
       <c r="E8" t="n">
-        <v>354.28</v>
+        <v>3991.73</v>
       </c>
       <c r="F8" t="n">
-        <v>347.86</v>
+        <v>3948.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12037</v>
+        <v>12042</v>
       </c>
       <c r="D9" t="n">
-        <v>11627.59</v>
+        <v>11601.3</v>
       </c>
       <c r="E9" t="n">
-        <v>11370.35</v>
+        <v>11352.54</v>
       </c>
       <c r="F9" t="n">
-        <v>11570.51</v>
+        <v>11571.5</v>
       </c>
       <c r="G9" t="n">
-        <v>4.03</v>
+        <v>4.07</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2000.6</v>
+        <v>2008.1</v>
       </c>
       <c r="D10" t="n">
-        <v>1918.71</v>
+        <v>1918.96</v>
       </c>
       <c r="E10" t="n">
-        <v>1844.92</v>
+        <v>1845.07</v>
       </c>
       <c r="F10" t="n">
-        <v>1910.6</v>
+        <v>1910.64</v>
       </c>
       <c r="G10" t="n">
-        <v>4.71</v>
+        <v>5.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>785.5</v>
+        <v>2728.5</v>
       </c>
       <c r="D11" t="n">
-        <v>781.2</v>
+        <v>2707.32</v>
       </c>
       <c r="E11" t="n">
-        <v>779.16</v>
+        <v>2693.58</v>
       </c>
       <c r="F11" t="n">
-        <v>743.36</v>
+        <v>2581.91</v>
       </c>
       <c r="G11" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2730.8</v>
+        <v>1472</v>
       </c>
       <c r="D12" t="n">
-        <v>2710.41</v>
+        <v>1446.35</v>
       </c>
       <c r="E12" t="n">
-        <v>2696.38</v>
+        <v>1425.08</v>
       </c>
       <c r="F12" t="n">
-        <v>2583.26</v>
+        <v>1392.39</v>
       </c>
       <c r="G12" t="n">
-        <v>5.71</v>
+        <v>5.72</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3527</v>
+        <v>3520.9</v>
       </c>
       <c r="D13" t="n">
-        <v>3228.72</v>
+        <v>3228.52</v>
       </c>
       <c r="E13" t="n">
-        <v>3149.65</v>
+        <v>3149.53</v>
       </c>
       <c r="F13" t="n">
-        <v>3327.71</v>
+        <v>3327.68</v>
       </c>
       <c r="G13" t="n">
-        <v>5.99</v>
+        <v>5.81</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1476.6</v>
+        <v>790</v>
       </c>
       <c r="D14" t="n">
-        <v>1446.51</v>
+        <v>781.35</v>
       </c>
       <c r="E14" t="n">
-        <v>1425.18</v>
+        <v>779.25</v>
       </c>
       <c r="F14" t="n">
-        <v>1392.41</v>
+        <v>743.39</v>
       </c>
       <c r="G14" t="n">
-        <v>6.05</v>
+        <v>6.27</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1170.3</v>
+        <v>1172.4</v>
       </c>
       <c r="D15" t="n">
-        <v>1122.66</v>
+        <v>1121.21</v>
       </c>
       <c r="E15" t="n">
-        <v>1112.68</v>
+        <v>1111.6</v>
       </c>
       <c r="F15" t="n">
-        <v>1101.52</v>
+        <v>1101.71</v>
       </c>
       <c r="G15" t="n">
-        <v>6.24</v>
+        <v>6.42</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5305</v>
+        <v>5345</v>
       </c>
       <c r="D16" t="n">
-        <v>5269.4</v>
+        <v>5270.73</v>
       </c>
       <c r="E16" t="n">
-        <v>5094.43</v>
+        <v>5095.23</v>
       </c>
       <c r="F16" t="n">
-        <v>4932.39</v>
+        <v>4932.59</v>
       </c>
       <c r="G16" t="n">
-        <v>7.55</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1260.1</v>
+        <v>1262</v>
       </c>
       <c r="D17" t="n">
-        <v>1175.56</v>
+        <v>1167.54</v>
       </c>
       <c r="E17" t="n">
-        <v>1101.05</v>
+        <v>1096.58</v>
       </c>
       <c r="F17" t="n">
-        <v>1147.97</v>
+        <v>1148.39</v>
       </c>
       <c r="G17" t="n">
-        <v>9.77</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7972.5</v>
+        <v>7983.5</v>
       </c>
       <c r="D18" t="n">
-        <v>7547.55</v>
+        <v>7547.91</v>
       </c>
       <c r="E18" t="n">
-        <v>7452.57</v>
+        <v>7452.79</v>
       </c>
       <c r="F18" t="n">
-        <v>7208.78</v>
+        <v>7208.83</v>
       </c>
       <c r="G18" t="n">
-        <v>10.59</v>
+        <v>10.75</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2078.4</v>
+        <v>620.55</v>
       </c>
       <c r="D19" t="n">
-        <v>2062.22</v>
+        <v>592.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1934.23</v>
+        <v>561.3200000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1876.99</v>
+        <v>554.83</v>
       </c>
       <c r="G19" t="n">
-        <v>10.73</v>
+        <v>11.84</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>184.17</v>
+        <v>2101.9</v>
       </c>
       <c r="D20" t="n">
-        <v>170.18</v>
+        <v>2063.01</v>
       </c>
       <c r="E20" t="n">
-        <v>168.5</v>
+        <v>1934.7</v>
       </c>
       <c r="F20" t="n">
-        <v>164.58</v>
+        <v>1877.1</v>
       </c>
       <c r="G20" t="n">
-        <v>11.9</v>
+        <v>11.98</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>622.5</v>
+        <v>1655.6</v>
       </c>
       <c r="D21" t="n">
-        <v>592.5700000000001</v>
+        <v>1536.68</v>
       </c>
       <c r="E21" t="n">
-        <v>561.36</v>
+        <v>1490.97</v>
       </c>
       <c r="F21" t="n">
-        <v>554.84</v>
+        <v>1467.14</v>
       </c>
       <c r="G21" t="n">
-        <v>12.19</v>
+        <v>12.85</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1656.7</v>
+        <v>14068</v>
       </c>
       <c r="D22" t="n">
-        <v>1536.72</v>
+        <v>13657.4</v>
       </c>
       <c r="E22" t="n">
-        <v>1490.99</v>
+        <v>12945.46</v>
       </c>
       <c r="F22" t="n">
-        <v>1467.15</v>
+        <v>12245.76</v>
       </c>
       <c r="G22" t="n">
-        <v>12.92</v>
+        <v>14.88</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>313.65</v>
+        <v>315.1</v>
       </c>
       <c r="D23" t="n">
-        <v>293.96</v>
+        <v>294.01</v>
       </c>
       <c r="E23" t="n">
-        <v>277.51</v>
+        <v>277.54</v>
       </c>
       <c r="F23" t="n">
-        <v>272.83</v>
+        <v>272.84</v>
       </c>
       <c r="G23" t="n">
-        <v>14.96</v>
+        <v>15.49</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14138</v>
+        <v>1814.1</v>
       </c>
       <c r="D24" t="n">
-        <v>13659.73</v>
+        <v>1569.8</v>
       </c>
       <c r="E24" t="n">
-        <v>12946.86</v>
+        <v>1519.78</v>
       </c>
       <c r="F24" t="n">
-        <v>12246.1</v>
+        <v>1506.08</v>
       </c>
       <c r="G24" t="n">
-        <v>15.45</v>
+        <v>20.45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1309,43 +1309,6 @@
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1809</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1569.63</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1519.68</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1506.05</v>
-      </c>
-      <c r="G25" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>278.1</v>
+        <v>277.65</v>
       </c>
       <c r="D2" t="n">
-        <v>277.54</v>
+        <v>277.52</v>
       </c>
       <c r="E2" t="n">
-        <v>277.44</v>
+        <v>277.43</v>
       </c>
       <c r="F2" t="n">
         <v>276.21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1943.3</v>
+        <v>1945.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1912.7</v>
+        <v>1912.76</v>
       </c>
       <c r="E3" t="n">
-        <v>1875.29</v>
+        <v>1875.33</v>
       </c>
       <c r="F3" t="n">
-        <v>1927.28</v>
+        <v>1927.29</v>
       </c>
       <c r="G3" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,10 +549,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>114.03</v>
+        <v>113.75</v>
       </c>
       <c r="D4" t="n">
-        <v>109</v>
+        <v>108.99</v>
       </c>
       <c r="E4" t="n">
         <v>107.89</v>
@@ -561,7 +561,7 @@
         <v>112.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5521</v>
+        <v>5519.5</v>
       </c>
       <c r="D5" t="n">
-        <v>5074.24</v>
+        <v>5074.19</v>
       </c>
       <c r="E5" t="n">
-        <v>5034.75</v>
+        <v>5034.72</v>
       </c>
       <c r="F5" t="n">
         <v>5450.45</v>
       </c>
       <c r="G5" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5617</v>
+        <v>503.15</v>
       </c>
       <c r="D6" t="n">
-        <v>5612.68</v>
+        <v>489.97</v>
       </c>
       <c r="E6" t="n">
-        <v>5499.84</v>
+        <v>477.62</v>
       </c>
       <c r="F6" t="n">
-        <v>5516.28</v>
+        <v>493.81</v>
       </c>
       <c r="G6" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>504.75</v>
+        <v>4054.9</v>
       </c>
       <c r="D7" t="n">
-        <v>490.03</v>
+        <v>3933.38</v>
       </c>
       <c r="E7" t="n">
-        <v>477.66</v>
+        <v>3991.59</v>
       </c>
       <c r="F7" t="n">
-        <v>493.81</v>
+        <v>3948.86</v>
       </c>
       <c r="G7" t="n">
-        <v>2.21</v>
+        <v>2.69</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4061.9</v>
+        <v>12074</v>
       </c>
       <c r="D8" t="n">
-        <v>3933.62</v>
+        <v>11602.36</v>
       </c>
       <c r="E8" t="n">
-        <v>3991.73</v>
+        <v>11353.18</v>
       </c>
       <c r="F8" t="n">
-        <v>3948.9</v>
+        <v>11571.66</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>4.34</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12042</v>
+        <v>1465.3</v>
       </c>
       <c r="D9" t="n">
-        <v>11601.3</v>
+        <v>1446.13</v>
       </c>
       <c r="E9" t="n">
-        <v>11352.54</v>
+        <v>1424.95</v>
       </c>
       <c r="F9" t="n">
-        <v>11571.5</v>
+        <v>1392.35</v>
       </c>
       <c r="G9" t="n">
-        <v>4.07</v>
+        <v>5.24</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2008.1</v>
+        <v>2018.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1918.96</v>
+        <v>1919.3</v>
       </c>
       <c r="E10" t="n">
-        <v>1845.07</v>
+        <v>1845.28</v>
       </c>
       <c r="F10" t="n">
-        <v>1910.64</v>
+        <v>1910.69</v>
       </c>
       <c r="G10" t="n">
-        <v>5.1</v>
+        <v>5.63</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2728.5</v>
+        <v>2733.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2707.32</v>
+        <v>2707.48</v>
       </c>
       <c r="E11" t="n">
-        <v>2693.58</v>
+        <v>2693.67</v>
       </c>
       <c r="F11" t="n">
-        <v>2581.91</v>
+        <v>2581.93</v>
       </c>
       <c r="G11" t="n">
-        <v>5.68</v>
+        <v>5.85</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1472</v>
+        <v>3533.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1446.35</v>
+        <v>3228.93</v>
       </c>
       <c r="E12" t="n">
-        <v>1425.08</v>
+        <v>3149.78</v>
       </c>
       <c r="F12" t="n">
-        <v>1392.39</v>
+        <v>3327.74</v>
       </c>
       <c r="G12" t="n">
-        <v>5.72</v>
+        <v>6.18</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3520.9</v>
+        <v>795.65</v>
       </c>
       <c r="D13" t="n">
-        <v>3228.52</v>
+        <v>781.54</v>
       </c>
       <c r="E13" t="n">
-        <v>3149.53</v>
+        <v>779.36</v>
       </c>
       <c r="F13" t="n">
-        <v>3327.68</v>
+        <v>743.41</v>
       </c>
       <c r="G13" t="n">
-        <v>5.81</v>
+        <v>7.03</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>790</v>
+        <v>1184</v>
       </c>
       <c r="D14" t="n">
-        <v>781.35</v>
+        <v>1121.6</v>
       </c>
       <c r="E14" t="n">
-        <v>779.25</v>
+        <v>1111.83</v>
       </c>
       <c r="F14" t="n">
-        <v>743.39</v>
+        <v>1101.77</v>
       </c>
       <c r="G14" t="n">
-        <v>6.27</v>
+        <v>7.46</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1172.4</v>
+        <v>5345</v>
       </c>
       <c r="D15" t="n">
-        <v>1121.21</v>
+        <v>5270.73</v>
       </c>
       <c r="E15" t="n">
-        <v>1111.6</v>
+        <v>5095.23</v>
       </c>
       <c r="F15" t="n">
-        <v>1101.71</v>
+        <v>4932.59</v>
       </c>
       <c r="G15" t="n">
-        <v>6.42</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5345</v>
+        <v>7982.5</v>
       </c>
       <c r="D16" t="n">
-        <v>5270.73</v>
+        <v>7547.88</v>
       </c>
       <c r="E16" t="n">
-        <v>5095.23</v>
+        <v>7452.77</v>
       </c>
       <c r="F16" t="n">
-        <v>4932.59</v>
+        <v>7208.83</v>
       </c>
       <c r="G16" t="n">
-        <v>8.359999999999999</v>
+        <v>10.73</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1030,19 +1030,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1262</v>
+        <v>1276</v>
       </c>
       <c r="D17" t="n">
-        <v>1167.54</v>
+        <v>1168</v>
       </c>
       <c r="E17" t="n">
-        <v>1096.58</v>
+        <v>1096.86</v>
       </c>
       <c r="F17" t="n">
-        <v>1148.39</v>
+        <v>1148.46</v>
       </c>
       <c r="G17" t="n">
-        <v>9.890000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7983.5</v>
+        <v>2114.8</v>
       </c>
       <c r="D18" t="n">
-        <v>7547.91</v>
+        <v>2063.44</v>
       </c>
       <c r="E18" t="n">
-        <v>7452.79</v>
+        <v>1934.96</v>
       </c>
       <c r="F18" t="n">
-        <v>7208.83</v>
+        <v>1877.17</v>
       </c>
       <c r="G18" t="n">
-        <v>10.75</v>
+        <v>12.66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>620.55</v>
+        <v>1658.4</v>
       </c>
       <c r="D19" t="n">
-        <v>592.5</v>
+        <v>1536.77</v>
       </c>
       <c r="E19" t="n">
-        <v>561.3200000000001</v>
+        <v>1491.03</v>
       </c>
       <c r="F19" t="n">
-        <v>554.83</v>
+        <v>1467.15</v>
       </c>
       <c r="G19" t="n">
-        <v>11.84</v>
+        <v>13.04</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2101.9</v>
+        <v>628</v>
       </c>
       <c r="D20" t="n">
-        <v>2063.01</v>
+        <v>592.75</v>
       </c>
       <c r="E20" t="n">
-        <v>1934.7</v>
+        <v>561.47</v>
       </c>
       <c r="F20" t="n">
-        <v>1877.1</v>
+        <v>554.87</v>
       </c>
       <c r="G20" t="n">
-        <v>11.98</v>
+        <v>13.18</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1655.6</v>
+        <v>14105</v>
       </c>
       <c r="D21" t="n">
-        <v>1536.68</v>
+        <v>13658.63</v>
       </c>
       <c r="E21" t="n">
-        <v>1490.97</v>
+        <v>12946.2</v>
       </c>
       <c r="F21" t="n">
-        <v>1467.14</v>
+        <v>12245.94</v>
       </c>
       <c r="G21" t="n">
-        <v>12.85</v>
+        <v>15.18</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14068</v>
+        <v>315.95</v>
       </c>
       <c r="D22" t="n">
-        <v>13657.4</v>
+        <v>294.04</v>
       </c>
       <c r="E22" t="n">
-        <v>12945.46</v>
+        <v>277.56</v>
       </c>
       <c r="F22" t="n">
-        <v>12245.76</v>
+        <v>272.84</v>
       </c>
       <c r="G22" t="n">
-        <v>14.88</v>
+        <v>15.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>315.1</v>
+        <v>1813.6</v>
       </c>
       <c r="D23" t="n">
-        <v>294.01</v>
+        <v>1569.78</v>
       </c>
       <c r="E23" t="n">
-        <v>277.54</v>
+        <v>1519.77</v>
       </c>
       <c r="F23" t="n">
-        <v>272.84</v>
+        <v>1506.08</v>
       </c>
       <c r="G23" t="n">
-        <v>15.49</v>
+        <v>20.42</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1272,43 +1272,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1814.1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1569.8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1519.78</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1506.08</v>
-      </c>
-      <c r="G24" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>277.65</v>
+        <v>5474</v>
       </c>
       <c r="D2" t="n">
-        <v>277.52</v>
+        <v>5114.86</v>
       </c>
       <c r="E2" t="n">
-        <v>277.43</v>
+        <v>5037.13</v>
       </c>
       <c r="F2" t="n">
-        <v>276.21</v>
+        <v>5449.17</v>
       </c>
       <c r="G2" t="n">
-        <v>0.52</v>
+        <v>0.46</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1945.1</v>
+        <v>113.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1912.76</v>
+        <v>108.98</v>
       </c>
       <c r="E3" t="n">
-        <v>1875.33</v>
+        <v>107.88</v>
       </c>
       <c r="F3" t="n">
-        <v>1927.29</v>
+        <v>112.66</v>
       </c>
       <c r="G3" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>113.75</v>
+        <v>1943</v>
       </c>
       <c r="D4" t="n">
-        <v>108.99</v>
+        <v>1912.69</v>
       </c>
       <c r="E4" t="n">
-        <v>107.89</v>
+        <v>1875.29</v>
       </c>
       <c r="F4" t="n">
-        <v>112.66</v>
+        <v>1927.28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5519.5</v>
+        <v>280</v>
       </c>
       <c r="D5" t="n">
-        <v>5074.19</v>
+        <v>277.6</v>
       </c>
       <c r="E5" t="n">
-        <v>5034.72</v>
+        <v>277.48</v>
       </c>
       <c r="F5" t="n">
-        <v>5450.45</v>
+        <v>276.22</v>
       </c>
       <c r="G5" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>503.15</v>
+        <v>501.9</v>
       </c>
       <c r="D6" t="n">
-        <v>489.97</v>
+        <v>491.74</v>
       </c>
       <c r="E6" t="n">
-        <v>477.62</v>
+        <v>478.82</v>
       </c>
       <c r="F6" t="n">
-        <v>493.81</v>
+        <v>493.79</v>
       </c>
       <c r="G6" t="n">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4054.9</v>
+        <v>4080</v>
       </c>
       <c r="D7" t="n">
-        <v>3933.38</v>
+        <v>3934.22</v>
       </c>
       <c r="E7" t="n">
-        <v>3991.59</v>
+        <v>3992.09</v>
       </c>
       <c r="F7" t="n">
-        <v>3948.86</v>
+        <v>3948.99</v>
       </c>
       <c r="G7" t="n">
-        <v>2.69</v>
+        <v>3.32</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12074</v>
+        <v>12038</v>
       </c>
       <c r="D8" t="n">
-        <v>11602.36</v>
+        <v>11627.62</v>
       </c>
       <c r="E8" t="n">
-        <v>11353.18</v>
+        <v>11370.37</v>
       </c>
       <c r="F8" t="n">
-        <v>11571.66</v>
+        <v>11570.52</v>
       </c>
       <c r="G8" t="n">
-        <v>4.34</v>
+        <v>4.04</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1465.3</v>
+        <v>1467.7</v>
       </c>
       <c r="D9" t="n">
-        <v>1446.13</v>
+        <v>1446.21</v>
       </c>
       <c r="E9" t="n">
-        <v>1424.95</v>
+        <v>1425</v>
       </c>
       <c r="F9" t="n">
-        <v>1392.35</v>
+        <v>1392.36</v>
       </c>
       <c r="G9" t="n">
-        <v>5.24</v>
+        <v>5.41</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2018.3</v>
+        <v>3517</v>
       </c>
       <c r="D10" t="n">
-        <v>1919.3</v>
+        <v>3228.39</v>
       </c>
       <c r="E10" t="n">
-        <v>1845.28</v>
+        <v>3149.45</v>
       </c>
       <c r="F10" t="n">
-        <v>1910.69</v>
+        <v>3327.66</v>
       </c>
       <c r="G10" t="n">
-        <v>5.63</v>
+        <v>5.69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2733.1</v>
+        <v>2021.3</v>
       </c>
       <c r="D11" t="n">
-        <v>2707.48</v>
+        <v>1919.4</v>
       </c>
       <c r="E11" t="n">
-        <v>2693.67</v>
+        <v>1845.34</v>
       </c>
       <c r="F11" t="n">
-        <v>2581.93</v>
+        <v>1910.7</v>
       </c>
       <c r="G11" t="n">
-        <v>5.85</v>
+        <v>5.79</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3533.4</v>
+        <v>789.45</v>
       </c>
       <c r="D12" t="n">
-        <v>3228.93</v>
+        <v>781.33</v>
       </c>
       <c r="E12" t="n">
-        <v>3149.78</v>
+        <v>779.24</v>
       </c>
       <c r="F12" t="n">
-        <v>3327.74</v>
+        <v>743.38</v>
       </c>
       <c r="G12" t="n">
-        <v>6.18</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>795.65</v>
+        <v>2750</v>
       </c>
       <c r="D13" t="n">
-        <v>781.54</v>
+        <v>2711.05</v>
       </c>
       <c r="E13" t="n">
-        <v>779.36</v>
+        <v>2696.76</v>
       </c>
       <c r="F13" t="n">
-        <v>743.41</v>
+        <v>2583.36</v>
       </c>
       <c r="G13" t="n">
-        <v>7.03</v>
+        <v>6.45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1184</v>
+        <v>1175.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1121.6</v>
+        <v>1122.83</v>
       </c>
       <c r="E14" t="n">
-        <v>1111.83</v>
+        <v>1112.79</v>
       </c>
       <c r="F14" t="n">
-        <v>1101.77</v>
+        <v>1101.55</v>
       </c>
       <c r="G14" t="n">
-        <v>7.46</v>
+        <v>6.72</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5345</v>
+        <v>5333.5</v>
       </c>
       <c r="D15" t="n">
-        <v>5270.73</v>
+        <v>5270.35</v>
       </c>
       <c r="E15" t="n">
-        <v>5095.23</v>
+        <v>5095</v>
       </c>
       <c r="F15" t="n">
-        <v>4932.59</v>
+        <v>4932.53</v>
       </c>
       <c r="G15" t="n">
-        <v>8.359999999999999</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>7982.5</v>
+        <v>181.14</v>
       </c>
       <c r="D16" t="n">
-        <v>7547.88</v>
+        <v>170.08</v>
       </c>
       <c r="E16" t="n">
-        <v>7452.77</v>
+        <v>168.44</v>
       </c>
       <c r="F16" t="n">
-        <v>7208.83</v>
+        <v>164.57</v>
       </c>
       <c r="G16" t="n">
-        <v>10.73</v>
+        <v>10.07</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1276</v>
+        <v>7975</v>
       </c>
       <c r="D17" t="n">
-        <v>1168</v>
+        <v>7547.63</v>
       </c>
       <c r="E17" t="n">
-        <v>1096.86</v>
+        <v>7452.62</v>
       </c>
       <c r="F17" t="n">
-        <v>1148.46</v>
+        <v>7208.79</v>
       </c>
       <c r="G17" t="n">
-        <v>11.11</v>
+        <v>10.63</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2114.8</v>
+        <v>1282</v>
       </c>
       <c r="D18" t="n">
-        <v>2063.44</v>
+        <v>1176.29</v>
       </c>
       <c r="E18" t="n">
-        <v>1934.96</v>
+        <v>1101.48</v>
       </c>
       <c r="F18" t="n">
-        <v>1877.17</v>
+        <v>1148.08</v>
       </c>
       <c r="G18" t="n">
-        <v>12.66</v>
+        <v>11.66</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1658.4</v>
+        <v>1640</v>
       </c>
       <c r="D19" t="n">
-        <v>1536.77</v>
+        <v>1536.16</v>
       </c>
       <c r="E19" t="n">
-        <v>1491.03</v>
+        <v>1490.66</v>
       </c>
       <c r="F19" t="n">
-        <v>1467.15</v>
+        <v>1467.06</v>
       </c>
       <c r="G19" t="n">
-        <v>13.04</v>
+        <v>11.79</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>628</v>
+        <v>621.8</v>
       </c>
       <c r="D20" t="n">
-        <v>592.75</v>
+        <v>592.55</v>
       </c>
       <c r="E20" t="n">
-        <v>561.47</v>
+        <v>561.35</v>
       </c>
       <c r="F20" t="n">
-        <v>554.87</v>
+        <v>554.84</v>
       </c>
       <c r="G20" t="n">
-        <v>13.18</v>
+        <v>12.07</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14105</v>
+        <v>2108.4</v>
       </c>
       <c r="D21" t="n">
-        <v>13658.63</v>
+        <v>2063.22</v>
       </c>
       <c r="E21" t="n">
-        <v>12946.2</v>
+        <v>1934.83</v>
       </c>
       <c r="F21" t="n">
-        <v>12245.94</v>
+        <v>1877.14</v>
       </c>
       <c r="G21" t="n">
-        <v>15.18</v>
+        <v>12.32</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>315.95</v>
+        <v>310.25</v>
       </c>
       <c r="D22" t="n">
-        <v>294.04</v>
+        <v>293.85</v>
       </c>
       <c r="E22" t="n">
-        <v>277.56</v>
+        <v>277.44</v>
       </c>
       <c r="F22" t="n">
-        <v>272.84</v>
+        <v>272.81</v>
       </c>
       <c r="G22" t="n">
-        <v>15.8</v>
+        <v>13.72</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,30 +1248,67 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>14115</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13658.97</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12946.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12245.99</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1813.6</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1569.78</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1519.77</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1506.08</v>
-      </c>
-      <c r="G23" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1810</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1569.66</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1519.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1506.06</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>501.9</v>
+        <v>4080</v>
       </c>
       <c r="D6" t="n">
-        <v>491.74</v>
+        <v>3934.22</v>
       </c>
       <c r="E6" t="n">
-        <v>478.82</v>
+        <v>3992.09</v>
       </c>
       <c r="F6" t="n">
-        <v>493.79</v>
+        <v>3948.99</v>
       </c>
       <c r="G6" t="n">
-        <v>1.64</v>
+        <v>3.32</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4080</v>
+        <v>12038</v>
       </c>
       <c r="D7" t="n">
-        <v>3934.22</v>
+        <v>11627.62</v>
       </c>
       <c r="E7" t="n">
-        <v>3992.09</v>
+        <v>11370.37</v>
       </c>
       <c r="F7" t="n">
-        <v>3948.99</v>
+        <v>11570.52</v>
       </c>
       <c r="G7" t="n">
-        <v>3.32</v>
+        <v>4.04</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12038</v>
+        <v>3517</v>
       </c>
       <c r="D8" t="n">
-        <v>11627.62</v>
+        <v>3228.39</v>
       </c>
       <c r="E8" t="n">
-        <v>11370.37</v>
+        <v>3149.45</v>
       </c>
       <c r="F8" t="n">
-        <v>11570.52</v>
+        <v>3327.66</v>
       </c>
       <c r="G8" t="n">
-        <v>4.04</v>
+        <v>5.69</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1467.7</v>
+        <v>2021.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1446.21</v>
+        <v>1919.4</v>
       </c>
       <c r="E9" t="n">
-        <v>1425</v>
+        <v>1845.34</v>
       </c>
       <c r="F9" t="n">
-        <v>1392.36</v>
+        <v>1910.7</v>
       </c>
       <c r="G9" t="n">
-        <v>5.41</v>
+        <v>5.79</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3517</v>
+        <v>2750</v>
       </c>
       <c r="D10" t="n">
-        <v>3228.39</v>
+        <v>2711.05</v>
       </c>
       <c r="E10" t="n">
-        <v>3149.45</v>
+        <v>2696.76</v>
       </c>
       <c r="F10" t="n">
-        <v>3327.66</v>
+        <v>2583.36</v>
       </c>
       <c r="G10" t="n">
-        <v>5.69</v>
+        <v>6.45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2021.3</v>
+        <v>1175.6</v>
       </c>
       <c r="D11" t="n">
-        <v>1919.4</v>
+        <v>1122.83</v>
       </c>
       <c r="E11" t="n">
-        <v>1845.34</v>
+        <v>1112.79</v>
       </c>
       <c r="F11" t="n">
-        <v>1910.7</v>
+        <v>1101.55</v>
       </c>
       <c r="G11" t="n">
-        <v>5.79</v>
+        <v>6.72</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>789.45</v>
+        <v>181.14</v>
       </c>
       <c r="D12" t="n">
-        <v>781.33</v>
+        <v>170.08</v>
       </c>
       <c r="E12" t="n">
-        <v>779.24</v>
+        <v>168.44</v>
       </c>
       <c r="F12" t="n">
-        <v>743.38</v>
+        <v>164.57</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>10.07</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2750</v>
+        <v>1282</v>
       </c>
       <c r="D13" t="n">
-        <v>2711.05</v>
+        <v>1176.29</v>
       </c>
       <c r="E13" t="n">
-        <v>2696.76</v>
+        <v>1101.48</v>
       </c>
       <c r="F13" t="n">
-        <v>2583.36</v>
+        <v>1148.08</v>
       </c>
       <c r="G13" t="n">
-        <v>6.45</v>
+        <v>11.66</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1175.6</v>
+        <v>621.8</v>
       </c>
       <c r="D14" t="n">
-        <v>1122.83</v>
+        <v>592.55</v>
       </c>
       <c r="E14" t="n">
-        <v>1112.79</v>
+        <v>561.35</v>
       </c>
       <c r="F14" t="n">
-        <v>1101.55</v>
+        <v>554.84</v>
       </c>
       <c r="G14" t="n">
-        <v>6.72</v>
+        <v>12.07</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5333.5</v>
+        <v>2108.4</v>
       </c>
       <c r="D15" t="n">
-        <v>5270.35</v>
+        <v>2063.22</v>
       </c>
       <c r="E15" t="n">
-        <v>5095</v>
+        <v>1934.83</v>
       </c>
       <c r="F15" t="n">
-        <v>4932.53</v>
+        <v>1877.14</v>
       </c>
       <c r="G15" t="n">
-        <v>8.130000000000001</v>
+        <v>12.32</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>181.14</v>
+        <v>310.25</v>
       </c>
       <c r="D16" t="n">
-        <v>170.08</v>
+        <v>293.85</v>
       </c>
       <c r="E16" t="n">
-        <v>168.44</v>
+        <v>277.44</v>
       </c>
       <c r="F16" t="n">
-        <v>164.57</v>
+        <v>272.81</v>
       </c>
       <c r="G16" t="n">
-        <v>10.07</v>
+        <v>13.72</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>7975</v>
+        <v>14115</v>
       </c>
       <c r="D17" t="n">
-        <v>7547.63</v>
+        <v>13658.97</v>
       </c>
       <c r="E17" t="n">
-        <v>7452.62</v>
+        <v>12946.4</v>
       </c>
       <c r="F17" t="n">
-        <v>7208.79</v>
+        <v>12245.99</v>
       </c>
       <c r="G17" t="n">
-        <v>10.63</v>
+        <v>15.26</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1282</v>
+        <v>1810</v>
       </c>
       <c r="D18" t="n">
-        <v>1176.29</v>
+        <v>1569.66</v>
       </c>
       <c r="E18" t="n">
-        <v>1101.48</v>
+        <v>1519.7</v>
       </c>
       <c r="F18" t="n">
-        <v>1148.08</v>
+        <v>1506.06</v>
       </c>
       <c r="G18" t="n">
-        <v>11.66</v>
+        <v>20.18</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1087,228 +1087,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1640</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1536.16</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1490.66</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1467.06</v>
-      </c>
-      <c r="G19" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>621.8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>592.55</v>
-      </c>
-      <c r="E20" t="n">
-        <v>561.35</v>
-      </c>
-      <c r="F20" t="n">
-        <v>554.84</v>
-      </c>
-      <c r="G20" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>GODREJPROP</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>2108.4</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2063.22</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1934.83</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1877.14</v>
-      </c>
-      <c r="G21" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>310.25</v>
-      </c>
-      <c r="D22" t="n">
-        <v>293.85</v>
-      </c>
-      <c r="E22" t="n">
-        <v>277.44</v>
-      </c>
-      <c r="F22" t="n">
-        <v>272.81</v>
-      </c>
-      <c r="G22" t="n">
-        <v>13.72</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>14115</v>
-      </c>
-      <c r="D23" t="n">
-        <v>13658.97</v>
-      </c>
-      <c r="E23" t="n">
-        <v>12946.4</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12245.99</v>
-      </c>
-      <c r="G23" t="n">
-        <v>15.26</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>10-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1810</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1569.66</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1519.7</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1506.06</v>
-      </c>
-      <c r="G24" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5474</v>
+        <v>114.03</v>
       </c>
       <c r="D2" t="n">
-        <v>5114.86</v>
+        <v>109.22</v>
       </c>
       <c r="E2" t="n">
-        <v>5037.13</v>
+        <v>108.14</v>
       </c>
       <c r="F2" t="n">
-        <v>5449.17</v>
+        <v>112.65</v>
       </c>
       <c r="G2" t="n">
-        <v>0.46</v>
+        <v>1.22</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>113.5</v>
+        <v>5536</v>
       </c>
       <c r="D3" t="n">
-        <v>108.98</v>
+        <v>5155.67</v>
       </c>
       <c r="E3" t="n">
-        <v>107.88</v>
+        <v>5038.82</v>
       </c>
       <c r="F3" t="n">
-        <v>112.66</v>
+        <v>5447.87</v>
       </c>
       <c r="G3" t="n">
-        <v>0.75</v>
+        <v>1.62</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1943</v>
+        <v>11780</v>
       </c>
       <c r="D4" t="n">
-        <v>1912.69</v>
+        <v>11652.69</v>
       </c>
       <c r="E4" t="n">
-        <v>1875.29</v>
+        <v>11387.14</v>
       </c>
       <c r="F4" t="n">
-        <v>1927.28</v>
+        <v>11569.91</v>
       </c>
       <c r="G4" t="n">
-        <v>0.82</v>
+        <v>1.82</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>280</v>
+        <v>4037.4</v>
       </c>
       <c r="D5" t="n">
-        <v>277.6</v>
+        <v>3930.69</v>
       </c>
       <c r="E5" t="n">
-        <v>277.48</v>
+        <v>3992.82</v>
       </c>
       <c r="F5" t="n">
-        <v>276.22</v>
+        <v>3949.77</v>
       </c>
       <c r="G5" t="n">
-        <v>1.37</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4080</v>
+        <v>512</v>
       </c>
       <c r="D6" t="n">
-        <v>3934.22</v>
+        <v>493.02</v>
       </c>
       <c r="E6" t="n">
-        <v>3992.09</v>
+        <v>479.9</v>
       </c>
       <c r="F6" t="n">
-        <v>3948.99</v>
+        <v>493.71</v>
       </c>
       <c r="G6" t="n">
-        <v>3.32</v>
+        <v>3.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12038</v>
+        <v>3460.1</v>
       </c>
       <c r="D7" t="n">
-        <v>11627.62</v>
+        <v>3242.49</v>
       </c>
       <c r="E7" t="n">
-        <v>11370.37</v>
+        <v>3159.31</v>
       </c>
       <c r="F7" t="n">
-        <v>11570.52</v>
+        <v>3327.03</v>
       </c>
       <c r="G7" t="n">
-        <v>4.04</v>
+        <v>4</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3517</v>
+        <v>1463</v>
       </c>
       <c r="D8" t="n">
-        <v>3228.39</v>
+        <v>1446.13</v>
       </c>
       <c r="E8" t="n">
-        <v>3149.45</v>
+        <v>1426.93</v>
       </c>
       <c r="F8" t="n">
-        <v>3327.66</v>
+        <v>1391.53</v>
       </c>
       <c r="G8" t="n">
-        <v>5.69</v>
+        <v>5.14</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2021.3</v>
+        <v>2735.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1919.4</v>
+        <v>2714.38</v>
       </c>
       <c r="E9" t="n">
-        <v>1845.34</v>
+        <v>2698.71</v>
       </c>
       <c r="F9" t="n">
-        <v>1910.7</v>
+        <v>2584.65</v>
       </c>
       <c r="G9" t="n">
-        <v>5.79</v>
+        <v>5.84</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2750</v>
+        <v>788</v>
       </c>
       <c r="D10" t="n">
-        <v>2711.05</v>
+        <v>781.17</v>
       </c>
       <c r="E10" t="n">
-        <v>2696.76</v>
+        <v>779.62</v>
       </c>
       <c r="F10" t="n">
-        <v>2583.36</v>
+        <v>743.5</v>
       </c>
       <c r="G10" t="n">
-        <v>6.45</v>
+        <v>5.98</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1175.6</v>
+        <v>1168</v>
       </c>
       <c r="D11" t="n">
-        <v>1122.83</v>
+        <v>1125.95</v>
       </c>
       <c r="E11" t="n">
-        <v>1112.79</v>
+        <v>1114.37</v>
       </c>
       <c r="F11" t="n">
-        <v>1101.55</v>
+        <v>1101.57</v>
       </c>
       <c r="G11" t="n">
-        <v>6.72</v>
+        <v>6.03</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>181.14</v>
+        <v>2032</v>
       </c>
       <c r="D12" t="n">
-        <v>170.08</v>
+        <v>1927.8</v>
       </c>
       <c r="E12" t="n">
-        <v>168.44</v>
+        <v>1851.18</v>
       </c>
       <c r="F12" t="n">
-        <v>164.57</v>
+        <v>1909.99</v>
       </c>
       <c r="G12" t="n">
-        <v>10.07</v>
+        <v>6.39</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1282</v>
+        <v>5284</v>
       </c>
       <c r="D13" t="n">
-        <v>1176.29</v>
+        <v>5267.53</v>
       </c>
       <c r="E13" t="n">
-        <v>1101.48</v>
+        <v>5111.36</v>
       </c>
       <c r="F13" t="n">
-        <v>1148.08</v>
+        <v>4929.39</v>
       </c>
       <c r="G13" t="n">
-        <v>11.66</v>
+        <v>7.19</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>621.8</v>
+        <v>1275</v>
       </c>
       <c r="D14" t="n">
-        <v>592.55</v>
+        <v>1171.94</v>
       </c>
       <c r="E14" t="n">
-        <v>561.35</v>
+        <v>1141.47</v>
       </c>
       <c r="F14" t="n">
-        <v>554.84</v>
+        <v>1169.23</v>
       </c>
       <c r="G14" t="n">
-        <v>12.07</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2108.4</v>
+        <v>182.5</v>
       </c>
       <c r="D15" t="n">
-        <v>2063.22</v>
+        <v>170.58</v>
       </c>
       <c r="E15" t="n">
-        <v>1934.83</v>
+        <v>168.93</v>
       </c>
       <c r="F15" t="n">
-        <v>1877.14</v>
+        <v>164.78</v>
       </c>
       <c r="G15" t="n">
-        <v>12.32</v>
+        <v>10.75</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>310.25</v>
+        <v>8000</v>
       </c>
       <c r="D16" t="n">
-        <v>293.85</v>
+        <v>7580.96</v>
       </c>
       <c r="E16" t="n">
-        <v>277.44</v>
+        <v>7471.27</v>
       </c>
       <c r="F16" t="n">
-        <v>272.81</v>
+        <v>7214.72</v>
       </c>
       <c r="G16" t="n">
-        <v>13.72</v>
+        <v>10.88</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14115</v>
+        <v>616</v>
       </c>
       <c r="D17" t="n">
-        <v>13658.97</v>
+        <v>595.3</v>
       </c>
       <c r="E17" t="n">
-        <v>12946.4</v>
+        <v>564.0599999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>12245.99</v>
+        <v>555.04</v>
       </c>
       <c r="G17" t="n">
-        <v>15.26</v>
+        <v>10.98</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,30 +1063,215 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5865.5</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5118.13</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5005.78</v>
+      </c>
+      <c r="F18" t="n">
+        <v>5284.67</v>
+      </c>
+      <c r="G18" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>11-08-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1545.29</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1492.89</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1468.15</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>11-08-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>14023</v>
+      </c>
+      <c r="D20" t="n">
+        <v>13729.07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12994.78</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12238.05</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11-08-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>318</v>
+      </c>
+      <c r="D21" t="n">
+        <v>295.63</v>
+      </c>
+      <c r="E21" t="n">
+        <v>278.79</v>
+      </c>
+      <c r="F21" t="n">
+        <v>272.76</v>
+      </c>
+      <c r="G21" t="n">
+        <v>16.59</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11-08-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1189.12</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1108.43</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1148.03</v>
+      </c>
+      <c r="G22" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>11-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1810</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1569.66</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1519.7</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1506.06</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1819</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1581.67</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1525.83</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1506.46</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,16 +515,16 @@
         <v>5536</v>
       </c>
       <c r="D3" t="n">
-        <v>5155.67</v>
+        <v>5114.42</v>
       </c>
       <c r="E3" t="n">
-        <v>5038.82</v>
+        <v>5036.87</v>
       </c>
       <c r="F3" t="n">
-        <v>5447.87</v>
+        <v>5449.1</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,13 +552,13 @@
         <v>11780</v>
       </c>
       <c r="D4" t="n">
-        <v>11652.69</v>
+        <v>11623.52</v>
       </c>
       <c r="E4" t="n">
-        <v>11387.14</v>
+        <v>11367.91</v>
       </c>
       <c r="F4" t="n">
-        <v>11569.91</v>
+        <v>11569.9</v>
       </c>
       <c r="G4" t="n">
         <v>1.82</v>
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -626,13 +626,13 @@
         <v>512</v>
       </c>
       <c r="D6" t="n">
-        <v>493.02</v>
+        <v>491.35</v>
       </c>
       <c r="E6" t="n">
-        <v>479.9</v>
+        <v>478.59</v>
       </c>
       <c r="F6" t="n">
-        <v>493.71</v>
+        <v>493.73</v>
       </c>
       <c r="G6" t="n">
         <v>3.7</v>
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2735.5</v>
+        <v>1168</v>
       </c>
       <c r="D9" t="n">
-        <v>2714.38</v>
+        <v>1123.92</v>
       </c>
       <c r="E9" t="n">
-        <v>2698.71</v>
+        <v>1113.44</v>
       </c>
       <c r="F9" t="n">
-        <v>2584.65</v>
+        <v>1101.71</v>
       </c>
       <c r="G9" t="n">
-        <v>5.84</v>
+        <v>6.02</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>788</v>
+        <v>182.5</v>
       </c>
       <c r="D10" t="n">
-        <v>781.17</v>
+        <v>170.46</v>
       </c>
       <c r="E10" t="n">
-        <v>779.62</v>
+        <v>168.67</v>
       </c>
       <c r="F10" t="n">
-        <v>743.5</v>
+        <v>164.62</v>
       </c>
       <c r="G10" t="n">
-        <v>5.98</v>
+        <v>10.86</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1168</v>
+        <v>8000</v>
       </c>
       <c r="D11" t="n">
-        <v>1125.95</v>
+        <v>7580.96</v>
       </c>
       <c r="E11" t="n">
-        <v>1114.37</v>
+        <v>7471.27</v>
       </c>
       <c r="F11" t="n">
-        <v>1101.57</v>
+        <v>7214.72</v>
       </c>
       <c r="G11" t="n">
-        <v>6.03</v>
+        <v>10.88</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2032</v>
+        <v>616</v>
       </c>
       <c r="D12" t="n">
-        <v>1927.8</v>
+        <v>595.3</v>
       </c>
       <c r="E12" t="n">
-        <v>1851.18</v>
+        <v>564.0599999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1909.99</v>
+        <v>555.04</v>
       </c>
       <c r="G12" t="n">
-        <v>6.39</v>
+        <v>10.98</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5284</v>
+        <v>5865.5</v>
       </c>
       <c r="D13" t="n">
-        <v>5267.53</v>
+        <v>5118.13</v>
       </c>
       <c r="E13" t="n">
-        <v>5111.36</v>
+        <v>5005.78</v>
       </c>
       <c r="F13" t="n">
-        <v>4929.39</v>
+        <v>5284.67</v>
       </c>
       <c r="G13" t="n">
-        <v>7.19</v>
+        <v>10.99</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1275</v>
+        <v>1643</v>
       </c>
       <c r="D14" t="n">
-        <v>1171.94</v>
+        <v>1545.29</v>
       </c>
       <c r="E14" t="n">
-        <v>1141.47</v>
+        <v>1492.89</v>
       </c>
       <c r="F14" t="n">
-        <v>1169.23</v>
+        <v>1468.15</v>
       </c>
       <c r="G14" t="n">
-        <v>9.050000000000001</v>
+        <v>11.91</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>182.5</v>
+        <v>14023</v>
       </c>
       <c r="D15" t="n">
-        <v>170.58</v>
+        <v>13729.07</v>
       </c>
       <c r="E15" t="n">
-        <v>168.93</v>
+        <v>12994.78</v>
       </c>
       <c r="F15" t="n">
-        <v>164.78</v>
+        <v>12238.05</v>
       </c>
       <c r="G15" t="n">
-        <v>10.75</v>
+        <v>14.59</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>8000</v>
+        <v>318</v>
       </c>
       <c r="D16" t="n">
-        <v>7580.96</v>
+        <v>295.63</v>
       </c>
       <c r="E16" t="n">
-        <v>7471.27</v>
+        <v>278.79</v>
       </c>
       <c r="F16" t="n">
-        <v>7214.72</v>
+        <v>272.76</v>
       </c>
       <c r="G16" t="n">
-        <v>10.88</v>
+        <v>16.59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>616</v>
+        <v>1360</v>
       </c>
       <c r="D17" t="n">
-        <v>595.3</v>
+        <v>1180.74</v>
       </c>
       <c r="E17" t="n">
-        <v>564.0599999999999</v>
+        <v>1104.16</v>
       </c>
       <c r="F17" t="n">
-        <v>555.04</v>
+        <v>1148.75</v>
       </c>
       <c r="G17" t="n">
-        <v>10.98</v>
+        <v>18.39</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5865.5</v>
+        <v>1819</v>
       </c>
       <c r="D18" t="n">
-        <v>5118.13</v>
+        <v>1581.67</v>
       </c>
       <c r="E18" t="n">
-        <v>5005.78</v>
+        <v>1525.83</v>
       </c>
       <c r="F18" t="n">
-        <v>5284.67</v>
+        <v>1506.46</v>
       </c>
       <c r="G18" t="n">
-        <v>10.99</v>
+        <v>20.75</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1087,191 +1087,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>1643</v>
-      </c>
-      <c r="D19" t="n">
-        <v>1545.29</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1492.89</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1468.15</v>
-      </c>
-      <c r="G19" t="n">
-        <v>11.91</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>14023</v>
-      </c>
-      <c r="D20" t="n">
-        <v>13729.07</v>
-      </c>
-      <c r="E20" t="n">
-        <v>12994.78</v>
-      </c>
-      <c r="F20" t="n">
-        <v>12238.05</v>
-      </c>
-      <c r="G20" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>318</v>
-      </c>
-      <c r="D21" t="n">
-        <v>295.63</v>
-      </c>
-      <c r="E21" t="n">
-        <v>278.79</v>
-      </c>
-      <c r="F21" t="n">
-        <v>272.76</v>
-      </c>
-      <c r="G21" t="n">
-        <v>16.59</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1360</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1189.12</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1108.43</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1148.03</v>
-      </c>
-      <c r="G22" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1819</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1581.67</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1525.83</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1506.46</v>
-      </c>
-      <c r="G23" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>114.03</v>
+        <v>5474</v>
       </c>
       <c r="D2" t="n">
-        <v>109.22</v>
+        <v>5194.3</v>
       </c>
       <c r="E2" t="n">
-        <v>108.14</v>
+        <v>5046.7</v>
       </c>
       <c r="F2" t="n">
-        <v>112.65</v>
+        <v>5446.32</v>
       </c>
       <c r="G2" t="n">
-        <v>1.22</v>
+        <v>0.51</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5536</v>
+        <v>1945</v>
       </c>
       <c r="D3" t="n">
-        <v>5114.42</v>
+        <v>1918.81</v>
       </c>
       <c r="E3" t="n">
-        <v>5036.87</v>
+        <v>1880.63</v>
       </c>
       <c r="F3" t="n">
-        <v>5449.1</v>
+        <v>1926.64</v>
       </c>
       <c r="G3" t="n">
-        <v>1.59</v>
+        <v>0.95</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11780</v>
+        <v>279.85</v>
       </c>
       <c r="D4" t="n">
-        <v>11623.52</v>
+        <v>277.5</v>
       </c>
       <c r="E4" t="n">
-        <v>11367.91</v>
+        <v>277.96</v>
       </c>
       <c r="F4" t="n">
-        <v>11569.9</v>
+        <v>276.31</v>
       </c>
       <c r="G4" t="n">
-        <v>1.82</v>
+        <v>1.28</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4037.4</v>
+        <v>4020</v>
       </c>
       <c r="D5" t="n">
-        <v>3930.69</v>
+        <v>3928.27</v>
       </c>
       <c r="E5" t="n">
-        <v>3992.82</v>
+        <v>3994.16</v>
       </c>
       <c r="F5" t="n">
-        <v>3949.77</v>
+        <v>3950.54</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>1.76</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>512</v>
+        <v>3403.6</v>
       </c>
       <c r="D6" t="n">
-        <v>491.35</v>
+        <v>3252.7</v>
       </c>
       <c r="E6" t="n">
-        <v>478.59</v>
+        <v>3167.78</v>
       </c>
       <c r="F6" t="n">
-        <v>493.73</v>
+        <v>3326.11</v>
       </c>
       <c r="G6" t="n">
-        <v>3.7</v>
+        <v>2.33</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3460.1</v>
+        <v>11891</v>
       </c>
       <c r="D7" t="n">
-        <v>3242.49</v>
+        <v>11674.83</v>
       </c>
       <c r="E7" t="n">
-        <v>3159.31</v>
+        <v>11407.38</v>
       </c>
       <c r="F7" t="n">
-        <v>3327.03</v>
+        <v>11570.96</v>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>2.77</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1463</v>
+        <v>512.05</v>
       </c>
       <c r="D8" t="n">
-        <v>1446.13</v>
+        <v>494.13</v>
       </c>
       <c r="E8" t="n">
-        <v>1426.93</v>
+        <v>481.13</v>
       </c>
       <c r="F8" t="n">
-        <v>1391.53</v>
+        <v>493.63</v>
       </c>
       <c r="G8" t="n">
-        <v>5.14</v>
+        <v>3.73</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1168</v>
+        <v>1463</v>
       </c>
       <c r="D9" t="n">
-        <v>1123.92</v>
+        <v>1446.34</v>
       </c>
       <c r="E9" t="n">
-        <v>1113.44</v>
+        <v>1428.94</v>
       </c>
       <c r="F9" t="n">
-        <v>1101.71</v>
+        <v>1391</v>
       </c>
       <c r="G9" t="n">
-        <v>6.02</v>
+        <v>5.18</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>182.5</v>
+        <v>1232.4</v>
       </c>
       <c r="D10" t="n">
-        <v>170.46</v>
+        <v>1176.75</v>
       </c>
       <c r="E10" t="n">
-        <v>168.67</v>
+        <v>1144.47</v>
       </c>
       <c r="F10" t="n">
-        <v>164.62</v>
+        <v>1169.44</v>
       </c>
       <c r="G10" t="n">
-        <v>10.86</v>
+        <v>5.38</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>8000</v>
+        <v>1161</v>
       </c>
       <c r="D11" t="n">
-        <v>7580.96</v>
+        <v>1129.12</v>
       </c>
       <c r="E11" t="n">
-        <v>7471.27</v>
+        <v>1116.14</v>
       </c>
       <c r="F11" t="n">
-        <v>7214.72</v>
+        <v>1101.55</v>
       </c>
       <c r="G11" t="n">
-        <v>10.88</v>
+        <v>5.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>616</v>
+        <v>118.98</v>
       </c>
       <c r="D12" t="n">
-        <v>595.3</v>
+        <v>109.6</v>
       </c>
       <c r="E12" t="n">
-        <v>564.0599999999999</v>
+        <v>108.46</v>
       </c>
       <c r="F12" t="n">
-        <v>555.04</v>
+        <v>112.68</v>
       </c>
       <c r="G12" t="n">
-        <v>10.98</v>
+        <v>5.59</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5865.5</v>
+        <v>2020.5</v>
       </c>
       <c r="D13" t="n">
-        <v>5118.13</v>
+        <v>1935.23</v>
       </c>
       <c r="E13" t="n">
-        <v>5005.78</v>
+        <v>1856.93</v>
       </c>
       <c r="F13" t="n">
-        <v>5284.67</v>
+        <v>1909.3</v>
       </c>
       <c r="G13" t="n">
-        <v>10.99</v>
+        <v>5.82</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1643</v>
+        <v>2740</v>
       </c>
       <c r="D14" t="n">
-        <v>1545.29</v>
+        <v>2715.17</v>
       </c>
       <c r="E14" t="n">
-        <v>1492.89</v>
+        <v>2700.72</v>
       </c>
       <c r="F14" t="n">
-        <v>1468.15</v>
+        <v>2585.97</v>
       </c>
       <c r="G14" t="n">
-        <v>11.91</v>
+        <v>5.96</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14023</v>
+        <v>176.7</v>
       </c>
       <c r="D15" t="n">
-        <v>13729.07</v>
+        <v>162.37</v>
       </c>
       <c r="E15" t="n">
-        <v>12994.78</v>
+        <v>158.63</v>
       </c>
       <c r="F15" t="n">
-        <v>12238.05</v>
+        <v>166.43</v>
       </c>
       <c r="G15" t="n">
-        <v>14.59</v>
+        <v>6.17</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>318</v>
+        <v>2240</v>
       </c>
       <c r="D16" t="n">
-        <v>295.63</v>
+        <v>2032</v>
       </c>
       <c r="E16" t="n">
-        <v>278.79</v>
+        <v>1990.77</v>
       </c>
       <c r="F16" t="n">
-        <v>272.76</v>
+        <v>2070.85</v>
       </c>
       <c r="G16" t="n">
-        <v>16.59</v>
+        <v>8.17</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1360</v>
+        <v>5333</v>
       </c>
       <c r="D17" t="n">
-        <v>1180.74</v>
+        <v>5265.33</v>
       </c>
       <c r="E17" t="n">
-        <v>1104.16</v>
+        <v>5127.78</v>
       </c>
       <c r="F17" t="n">
-        <v>1148.75</v>
+        <v>4927.11</v>
       </c>
       <c r="G17" t="n">
-        <v>18.39</v>
+        <v>8.24</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,30 +1063,400 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>BAJAJHLDNG</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>11579</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10895.93</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10657.94</v>
+      </c>
+      <c r="F18" t="n">
+        <v>10672.27</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1625</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1555.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1496.69</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1469.19</v>
+      </c>
+      <c r="G19" t="n">
+        <v>10.61</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>614.65</v>
+      </c>
+      <c r="D20" t="n">
+        <v>597.4299999999999</v>
+      </c>
+      <c r="E20" t="n">
+        <v>566.9299999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>555.24</v>
+      </c>
+      <c r="G20" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8049</v>
+      </c>
+      <c r="D21" t="n">
+        <v>7613.75</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7491.12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>7221.12</v>
+      </c>
+      <c r="G21" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5895</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5155.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5028.26</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5287.37</v>
+      </c>
+      <c r="G22" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>13800</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13790.53</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13046.24</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12229.6</v>
+      </c>
+      <c r="G23" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>187</v>
+      </c>
+      <c r="D24" t="n">
+        <v>171.15</v>
+      </c>
+      <c r="E24" t="n">
+        <v>169.43</v>
+      </c>
+      <c r="F24" t="n">
+        <v>165.03</v>
+      </c>
+      <c r="G24" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>314.05</v>
+      </c>
+      <c r="D25" t="n">
+        <v>296.77</v>
+      </c>
+      <c r="E25" t="n">
+        <v>280.13</v>
+      </c>
+      <c r="F25" t="n">
+        <v>272.7</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15.16</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1339</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1200.74</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1115.15</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1147.89</v>
+      </c>
+      <c r="G26" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>1819</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1581.67</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1525.83</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1506.46</v>
-      </c>
-      <c r="G18" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="C27" t="n">
+        <v>1801.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1596.24</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1533.57</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1506.75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>11679</v>
+      </c>
+      <c r="D28" t="n">
+        <v>11404.13</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10829.95</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8538.25</v>
+      </c>
+      <c r="G28" t="n">
+        <v>36.78</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5474</v>
+        <v>1945</v>
       </c>
       <c r="D2" t="n">
-        <v>5194.3</v>
+        <v>1918.81</v>
       </c>
       <c r="E2" t="n">
-        <v>5046.7</v>
+        <v>1880.63</v>
       </c>
       <c r="F2" t="n">
-        <v>5446.32</v>
+        <v>1926.64</v>
       </c>
       <c r="G2" t="n">
-        <v>0.51</v>
+        <v>0.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1945</v>
+        <v>279.85</v>
       </c>
       <c r="D3" t="n">
-        <v>1918.81</v>
+        <v>277.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1880.63</v>
+        <v>277.96</v>
       </c>
       <c r="F3" t="n">
-        <v>1926.64</v>
+        <v>276.31</v>
       </c>
       <c r="G3" t="n">
-        <v>0.95</v>
+        <v>1.28</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>279.85</v>
+        <v>4020</v>
       </c>
       <c r="D4" t="n">
-        <v>277.5</v>
+        <v>3928.27</v>
       </c>
       <c r="E4" t="n">
-        <v>277.96</v>
+        <v>3994.16</v>
       </c>
       <c r="F4" t="n">
-        <v>276.31</v>
+        <v>3950.54</v>
       </c>
       <c r="G4" t="n">
-        <v>1.28</v>
+        <v>1.76</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4020</v>
+        <v>3403.6</v>
       </c>
       <c r="D5" t="n">
-        <v>3928.27</v>
+        <v>3252.7</v>
       </c>
       <c r="E5" t="n">
-        <v>3994.16</v>
+        <v>3167.78</v>
       </c>
       <c r="F5" t="n">
-        <v>3950.54</v>
+        <v>3326.11</v>
       </c>
       <c r="G5" t="n">
-        <v>1.76</v>
+        <v>2.33</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3403.6</v>
+        <v>512.05</v>
       </c>
       <c r="D6" t="n">
-        <v>3252.7</v>
+        <v>492.62</v>
       </c>
       <c r="E6" t="n">
-        <v>3167.78</v>
+        <v>479.67</v>
       </c>
       <c r="F6" t="n">
-        <v>3326.11</v>
+        <v>493.65</v>
       </c>
       <c r="G6" t="n">
-        <v>2.33</v>
+        <v>3.73</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11891</v>
+        <v>1463</v>
       </c>
       <c r="D7" t="n">
-        <v>11674.83</v>
+        <v>1446.34</v>
       </c>
       <c r="E7" t="n">
-        <v>11407.38</v>
+        <v>1428.94</v>
       </c>
       <c r="F7" t="n">
-        <v>11570.96</v>
+        <v>1391</v>
       </c>
       <c r="G7" t="n">
-        <v>2.77</v>
+        <v>5.18</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>512.05</v>
+        <v>118.98</v>
       </c>
       <c r="D8" t="n">
-        <v>494.13</v>
+        <v>109.6</v>
       </c>
       <c r="E8" t="n">
-        <v>481.13</v>
+        <v>108.46</v>
       </c>
       <c r="F8" t="n">
-        <v>493.63</v>
+        <v>112.68</v>
       </c>
       <c r="G8" t="n">
-        <v>3.73</v>
+        <v>5.59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1463</v>
+        <v>176.7</v>
       </c>
       <c r="D9" t="n">
-        <v>1446.34</v>
+        <v>162.37</v>
       </c>
       <c r="E9" t="n">
-        <v>1428.94</v>
+        <v>158.63</v>
       </c>
       <c r="F9" t="n">
-        <v>1391</v>
+        <v>166.43</v>
       </c>
       <c r="G9" t="n">
-        <v>5.18</v>
+        <v>6.17</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1232.4</v>
+        <v>2240</v>
       </c>
       <c r="D10" t="n">
-        <v>1176.75</v>
+        <v>2032</v>
       </c>
       <c r="E10" t="n">
-        <v>1144.47</v>
+        <v>1990.77</v>
       </c>
       <c r="F10" t="n">
-        <v>1169.44</v>
+        <v>2070.85</v>
       </c>
       <c r="G10" t="n">
-        <v>5.38</v>
+        <v>8.17</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1161</v>
+        <v>1625</v>
       </c>
       <c r="D11" t="n">
-        <v>1129.12</v>
+        <v>1555.2</v>
       </c>
       <c r="E11" t="n">
-        <v>1116.14</v>
+        <v>1496.69</v>
       </c>
       <c r="F11" t="n">
-        <v>1101.55</v>
+        <v>1469.19</v>
       </c>
       <c r="G11" t="n">
-        <v>5.4</v>
+        <v>10.61</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>118.98</v>
+        <v>614.65</v>
       </c>
       <c r="D12" t="n">
-        <v>109.6</v>
+        <v>597.4299999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>108.46</v>
+        <v>566.9299999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>112.68</v>
+        <v>555.24</v>
       </c>
       <c r="G12" t="n">
-        <v>5.59</v>
+        <v>10.7</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2020.5</v>
+        <v>8049</v>
       </c>
       <c r="D13" t="n">
-        <v>1935.23</v>
+        <v>7613.75</v>
       </c>
       <c r="E13" t="n">
-        <v>1856.93</v>
+        <v>7491.12</v>
       </c>
       <c r="F13" t="n">
-        <v>1909.3</v>
+        <v>7221.12</v>
       </c>
       <c r="G13" t="n">
-        <v>5.82</v>
+        <v>11.46</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2740</v>
+        <v>5895</v>
       </c>
       <c r="D14" t="n">
-        <v>2715.17</v>
+        <v>5155.8</v>
       </c>
       <c r="E14" t="n">
-        <v>2700.72</v>
+        <v>5028.26</v>
       </c>
       <c r="F14" t="n">
-        <v>2585.97</v>
+        <v>5287.37</v>
       </c>
       <c r="G14" t="n">
-        <v>5.96</v>
+        <v>11.49</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>176.7</v>
+        <v>13800</v>
       </c>
       <c r="D15" t="n">
-        <v>162.37</v>
+        <v>13790.53</v>
       </c>
       <c r="E15" t="n">
-        <v>158.63</v>
+        <v>13046.24</v>
       </c>
       <c r="F15" t="n">
-        <v>166.43</v>
+        <v>12229.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.17</v>
+        <v>12.84</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2240</v>
+        <v>187</v>
       </c>
       <c r="D16" t="n">
-        <v>2032</v>
+        <v>171.11</v>
       </c>
       <c r="E16" t="n">
-        <v>1990.77</v>
+        <v>169.25</v>
       </c>
       <c r="F16" t="n">
-        <v>2070.85</v>
+        <v>164.86</v>
       </c>
       <c r="G16" t="n">
-        <v>8.17</v>
+        <v>13.43</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5333</v>
+        <v>314.05</v>
       </c>
       <c r="D17" t="n">
-        <v>5265.33</v>
+        <v>296.77</v>
       </c>
       <c r="E17" t="n">
-        <v>5127.78</v>
+        <v>280.13</v>
       </c>
       <c r="F17" t="n">
-        <v>4927.11</v>
+        <v>272.7</v>
       </c>
       <c r="G17" t="n">
-        <v>8.24</v>
+        <v>15.16</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11579</v>
+        <v>1339</v>
       </c>
       <c r="D18" t="n">
-        <v>10895.93</v>
+        <v>1192.88</v>
       </c>
       <c r="E18" t="n">
-        <v>10657.94</v>
+        <v>1110.69</v>
       </c>
       <c r="F18" t="n">
-        <v>10672.27</v>
+        <v>1148.6</v>
       </c>
       <c r="G18" t="n">
-        <v>8.5</v>
+        <v>16.58</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1625</v>
+        <v>1801.5</v>
       </c>
       <c r="D19" t="n">
-        <v>1555.2</v>
+        <v>1596.24</v>
       </c>
       <c r="E19" t="n">
-        <v>1496.69</v>
+        <v>1533.57</v>
       </c>
       <c r="F19" t="n">
-        <v>1469.19</v>
+        <v>1506.75</v>
       </c>
       <c r="G19" t="n">
-        <v>10.61</v>
+        <v>19.56</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>13-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>614.65</v>
+        <v>11679</v>
       </c>
       <c r="D20" t="n">
-        <v>597.4299999999999</v>
+        <v>11404.13</v>
       </c>
       <c r="E20" t="n">
-        <v>566.9299999999999</v>
+        <v>10829.95</v>
       </c>
       <c r="F20" t="n">
-        <v>555.24</v>
+        <v>8538.25</v>
       </c>
       <c r="G20" t="n">
-        <v>10.7</v>
+        <v>36.78</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1161,302 +1161,6 @@
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>8049</v>
-      </c>
-      <c r="D21" t="n">
-        <v>7613.75</v>
-      </c>
-      <c r="E21" t="n">
-        <v>7491.12</v>
-      </c>
-      <c r="F21" t="n">
-        <v>7221.12</v>
-      </c>
-      <c r="G21" t="n">
-        <v>11.46</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>5895</v>
-      </c>
-      <c r="D22" t="n">
-        <v>5155.8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5028.26</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5287.37</v>
-      </c>
-      <c r="G22" t="n">
-        <v>11.49</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>13800</v>
-      </c>
-      <c r="D23" t="n">
-        <v>13790.53</v>
-      </c>
-      <c r="E23" t="n">
-        <v>13046.24</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12229.6</v>
-      </c>
-      <c r="G23" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>187</v>
-      </c>
-      <c r="D24" t="n">
-        <v>171.15</v>
-      </c>
-      <c r="E24" t="n">
-        <v>169.43</v>
-      </c>
-      <c r="F24" t="n">
-        <v>165.03</v>
-      </c>
-      <c r="G24" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>314.05</v>
-      </c>
-      <c r="D25" t="n">
-        <v>296.77</v>
-      </c>
-      <c r="E25" t="n">
-        <v>280.13</v>
-      </c>
-      <c r="F25" t="n">
-        <v>272.7</v>
-      </c>
-      <c r="G25" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1339</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1200.74</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1115.15</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1147.89</v>
-      </c>
-      <c r="G26" t="n">
-        <v>16.65</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1801.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1596.24</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1533.57</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1506.75</v>
-      </c>
-      <c r="G27" t="n">
-        <v>19.56</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>11679</v>
-      </c>
-      <c r="D28" t="n">
-        <v>11404.13</v>
-      </c>
-      <c r="E28" t="n">
-        <v>10829.95</v>
-      </c>
-      <c r="F28" t="n">
-        <v>8538.25</v>
-      </c>
-      <c r="G28" t="n">
-        <v>36.78</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -478,16 +478,16 @@
         <v>1945</v>
       </c>
       <c r="D2" t="n">
-        <v>1918.81</v>
+        <v>1913.34</v>
       </c>
       <c r="E2" t="n">
-        <v>1880.63</v>
+        <v>1875.68</v>
       </c>
       <c r="F2" t="n">
-        <v>1926.64</v>
+        <v>1927.38</v>
       </c>
       <c r="G2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>4020</v>
       </c>
       <c r="D4" t="n">
-        <v>3928.27</v>
+        <v>3937.44</v>
       </c>
       <c r="E4" t="n">
-        <v>3994.16</v>
+        <v>3996.87</v>
       </c>
       <c r="F4" t="n">
-        <v>3950.54</v>
+        <v>3950.79</v>
       </c>
       <c r="G4" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -626,13 +626,13 @@
         <v>512.05</v>
       </c>
       <c r="D6" t="n">
-        <v>492.62</v>
+        <v>494.13</v>
       </c>
       <c r="E6" t="n">
-        <v>479.67</v>
+        <v>481.13</v>
       </c>
       <c r="F6" t="n">
-        <v>493.65</v>
+        <v>493.63</v>
       </c>
       <c r="G6" t="n">
         <v>3.73</v>
@@ -737,16 +737,16 @@
         <v>176.7</v>
       </c>
       <c r="D9" t="n">
-        <v>162.37</v>
+        <v>162.7</v>
       </c>
       <c r="E9" t="n">
-        <v>158.63</v>
+        <v>158.5</v>
       </c>
       <c r="F9" t="n">
-        <v>166.43</v>
+        <v>166.33</v>
       </c>
       <c r="G9" t="n">
-        <v>6.17</v>
+        <v>6.23</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1625</v>
+        <v>614.65</v>
       </c>
       <c r="D11" t="n">
-        <v>1555.2</v>
+        <v>596.61</v>
       </c>
       <c r="E11" t="n">
-        <v>1496.69</v>
+        <v>564.85</v>
       </c>
       <c r="F11" t="n">
-        <v>1469.19</v>
+        <v>555.24</v>
       </c>
       <c r="G11" t="n">
-        <v>10.61</v>
+        <v>10.7</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>614.65</v>
+        <v>1625</v>
       </c>
       <c r="D12" t="n">
-        <v>597.4299999999999</v>
+        <v>1540.53</v>
       </c>
       <c r="E12" t="n">
-        <v>566.9299999999999</v>
+        <v>1493.28</v>
       </c>
       <c r="F12" t="n">
-        <v>555.24</v>
+        <v>1467.72</v>
       </c>
       <c r="G12" t="n">
-        <v>10.7</v>
+        <v>10.72</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>8049</v>
+        <v>5895</v>
       </c>
       <c r="D13" t="n">
-        <v>7613.75</v>
+        <v>5150.8</v>
       </c>
       <c r="E13" t="n">
-        <v>7491.12</v>
+        <v>5025.38</v>
       </c>
       <c r="F13" t="n">
-        <v>7221.12</v>
+        <v>5289.57</v>
       </c>
       <c r="G13" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5895</v>
+        <v>8049</v>
       </c>
       <c r="D14" t="n">
-        <v>5155.8</v>
+        <v>7599.75</v>
       </c>
       <c r="E14" t="n">
-        <v>5028.26</v>
+        <v>7482.54</v>
       </c>
       <c r="F14" t="n">
-        <v>5287.37</v>
+        <v>7217.54</v>
       </c>
       <c r="G14" t="n">
-        <v>11.49</v>
+        <v>11.52</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         <v>13800</v>
       </c>
       <c r="D15" t="n">
-        <v>13790.53</v>
+        <v>13726.33</v>
       </c>
       <c r="E15" t="n">
-        <v>13046.24</v>
+        <v>12993.14</v>
       </c>
       <c r="F15" t="n">
-        <v>12229.6</v>
+        <v>12237.64</v>
       </c>
       <c r="G15" t="n">
-        <v>12.84</v>
+        <v>12.77</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         <v>187</v>
       </c>
       <c r="D16" t="n">
-        <v>171.11</v>
+        <v>171.15</v>
       </c>
       <c r="E16" t="n">
-        <v>169.25</v>
+        <v>169.43</v>
       </c>
       <c r="F16" t="n">
-        <v>164.86</v>
+        <v>165.03</v>
       </c>
       <c r="G16" t="n">
-        <v>13.43</v>
+        <v>13.31</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>314.05</v>
       </c>
       <c r="D17" t="n">
-        <v>296.77</v>
+        <v>295.87</v>
       </c>
       <c r="E17" t="n">
-        <v>280.13</v>
+        <v>278.66</v>
       </c>
       <c r="F17" t="n">
-        <v>272.7</v>
+        <v>273.12</v>
       </c>
       <c r="G17" t="n">
-        <v>15.16</v>
+        <v>14.99</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1070,16 +1070,16 @@
         <v>1339</v>
       </c>
       <c r="D18" t="n">
-        <v>1192.88</v>
+        <v>1200.74</v>
       </c>
       <c r="E18" t="n">
-        <v>1110.69</v>
+        <v>1115.15</v>
       </c>
       <c r="F18" t="n">
-        <v>1148.6</v>
+        <v>1147.89</v>
       </c>
       <c r="G18" t="n">
-        <v>16.58</v>
+        <v>16.65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1107,16 +1107,16 @@
         <v>1801.5</v>
       </c>
       <c r="D19" t="n">
-        <v>1596.24</v>
+        <v>1591.51</v>
       </c>
       <c r="E19" t="n">
-        <v>1533.57</v>
+        <v>1532.81</v>
       </c>
       <c r="F19" t="n">
-        <v>1506.75</v>
+        <v>1509.34</v>
       </c>
       <c r="G19" t="n">
-        <v>19.56</v>
+        <v>19.36</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1945</v>
+        <v>1939.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1913.34</v>
+        <v>1917.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1875.68</v>
+        <v>1878.63</v>
       </c>
       <c r="F2" t="n">
-        <v>1927.38</v>
+        <v>1927.16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.91</v>
+        <v>0.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>279.85</v>
+        <v>279.3</v>
       </c>
       <c r="D3" t="n">
-        <v>277.5</v>
+        <v>277.64</v>
       </c>
       <c r="E3" t="n">
-        <v>277.96</v>
+        <v>278.22</v>
       </c>
       <c r="F3" t="n">
-        <v>276.31</v>
+        <v>276.35</v>
       </c>
       <c r="G3" t="n">
-        <v>1.28</v>
+        <v>1.07</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4020</v>
+        <v>11706</v>
       </c>
       <c r="D4" t="n">
-        <v>3937.44</v>
+        <v>11688.19</v>
       </c>
       <c r="E4" t="n">
-        <v>3996.87</v>
+        <v>11425.96</v>
       </c>
       <c r="F4" t="n">
-        <v>3950.79</v>
+        <v>11570.62</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3403.6</v>
+        <v>5523</v>
       </c>
       <c r="D5" t="n">
-        <v>3252.7</v>
+        <v>5226.24</v>
       </c>
       <c r="E5" t="n">
-        <v>3167.78</v>
+        <v>5055.08</v>
       </c>
       <c r="F5" t="n">
-        <v>3326.11</v>
+        <v>5444.75</v>
       </c>
       <c r="G5" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>512.05</v>
+        <v>4070.7</v>
       </c>
       <c r="D6" t="n">
-        <v>494.13</v>
+        <v>3928.64</v>
       </c>
       <c r="E6" t="n">
-        <v>481.13</v>
+        <v>3996.73</v>
       </c>
       <c r="F6" t="n">
-        <v>493.63</v>
+        <v>3951.46</v>
       </c>
       <c r="G6" t="n">
-        <v>3.73</v>
+        <v>3.02</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1463</v>
+        <v>3428.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1446.34</v>
+        <v>3262.22</v>
       </c>
       <c r="E7" t="n">
-        <v>1428.94</v>
+        <v>3176.65</v>
       </c>
       <c r="F7" t="n">
-        <v>1391</v>
+        <v>3325.38</v>
       </c>
       <c r="G7" t="n">
-        <v>5.18</v>
+        <v>3.09</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>118.98</v>
+        <v>117.59</v>
       </c>
       <c r="D8" t="n">
-        <v>109.6</v>
+        <v>109.96</v>
       </c>
       <c r="E8" t="n">
-        <v>108.46</v>
+        <v>108.76</v>
       </c>
       <c r="F8" t="n">
         <v>112.68</v>
       </c>
       <c r="G8" t="n">
-        <v>5.59</v>
+        <v>4.35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>176.7</v>
+        <v>1458.8</v>
       </c>
       <c r="D9" t="n">
-        <v>162.7</v>
+        <v>1446.43</v>
       </c>
       <c r="E9" t="n">
-        <v>158.5</v>
+        <v>1430.4</v>
       </c>
       <c r="F9" t="n">
-        <v>166.33</v>
+        <v>1390.44</v>
       </c>
       <c r="G9" t="n">
-        <v>6.23</v>
+        <v>4.92</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2240</v>
+        <v>176.23</v>
       </c>
       <c r="D10" t="n">
-        <v>2032</v>
+        <v>163.16</v>
       </c>
       <c r="E10" t="n">
-        <v>1990.77</v>
+        <v>159.1</v>
       </c>
       <c r="F10" t="n">
-        <v>2070.85</v>
+        <v>166.55</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17</v>
+        <v>5.81</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>614.65</v>
+        <v>897</v>
       </c>
       <c r="D11" t="n">
-        <v>596.61</v>
+        <v>839.46</v>
       </c>
       <c r="E11" t="n">
-        <v>564.85</v>
+        <v>840.08</v>
       </c>
       <c r="F11" t="n">
-        <v>555.24</v>
+        <v>847.41</v>
       </c>
       <c r="G11" t="n">
-        <v>10.7</v>
+        <v>5.85</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1625</v>
+        <v>1240</v>
       </c>
       <c r="D12" t="n">
-        <v>1540.53</v>
+        <v>1178.18</v>
       </c>
       <c r="E12" t="n">
-        <v>1493.28</v>
+        <v>1145.21</v>
       </c>
       <c r="F12" t="n">
-        <v>1467.72</v>
+        <v>1170.16</v>
       </c>
       <c r="G12" t="n">
-        <v>10.72</v>
+        <v>5.97</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5895</v>
+        <v>2025</v>
       </c>
       <c r="D13" t="n">
-        <v>5150.8</v>
+        <v>1940.87</v>
       </c>
       <c r="E13" t="n">
-        <v>5025.38</v>
+        <v>1863.26</v>
       </c>
       <c r="F13" t="n">
-        <v>5289.57</v>
+        <v>1908.59</v>
       </c>
       <c r="G13" t="n">
-        <v>11.45</v>
+        <v>6.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8049</v>
+        <v>1083</v>
       </c>
       <c r="D14" t="n">
-        <v>7599.75</v>
+        <v>1041.98</v>
       </c>
       <c r="E14" t="n">
-        <v>7482.54</v>
+        <v>1033.27</v>
       </c>
       <c r="F14" t="n">
-        <v>7217.54</v>
+        <v>1020.3</v>
       </c>
       <c r="G14" t="n">
-        <v>11.52</v>
+        <v>6.15</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13800</v>
+        <v>2755.5</v>
       </c>
       <c r="D15" t="n">
-        <v>13726.33</v>
+        <v>2715.53</v>
       </c>
       <c r="E15" t="n">
-        <v>12993.14</v>
+        <v>2703.06</v>
       </c>
       <c r="F15" t="n">
-        <v>12237.64</v>
+        <v>2587.28</v>
       </c>
       <c r="G15" t="n">
-        <v>12.77</v>
+        <v>6.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>187</v>
+        <v>1183</v>
       </c>
       <c r="D16" t="n">
-        <v>171.15</v>
+        <v>1132.88</v>
       </c>
       <c r="E16" t="n">
-        <v>169.43</v>
+        <v>1118.36</v>
       </c>
       <c r="F16" t="n">
-        <v>165.03</v>
+        <v>1101.6</v>
       </c>
       <c r="G16" t="n">
-        <v>13.31</v>
+        <v>7.39</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>314.05</v>
+        <v>11500</v>
       </c>
       <c r="D17" t="n">
-        <v>295.87</v>
+        <v>10915.17</v>
       </c>
       <c r="E17" t="n">
-        <v>278.66</v>
+        <v>10656.4</v>
       </c>
       <c r="F17" t="n">
-        <v>273.12</v>
+        <v>10686.47</v>
       </c>
       <c r="G17" t="n">
-        <v>14.99</v>
+        <v>7.61</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1339</v>
+        <v>2237.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1200.74</v>
+        <v>2042.16</v>
       </c>
       <c r="E18" t="n">
-        <v>1115.15</v>
+        <v>1997.23</v>
       </c>
       <c r="F18" t="n">
-        <v>1147.89</v>
+        <v>2070.78</v>
       </c>
       <c r="G18" t="n">
-        <v>16.65</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1801.5</v>
+        <v>533.65</v>
       </c>
       <c r="D19" t="n">
-        <v>1591.51</v>
+        <v>494.41</v>
       </c>
       <c r="E19" t="n">
-        <v>1532.81</v>
+        <v>480.74</v>
       </c>
       <c r="F19" t="n">
-        <v>1509.34</v>
+        <v>493.92</v>
       </c>
       <c r="G19" t="n">
-        <v>19.36</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11679</v>
+        <v>5370</v>
       </c>
       <c r="D20" t="n">
-        <v>11404.13</v>
+        <v>5279.43</v>
       </c>
       <c r="E20" t="n">
-        <v>10829.95</v>
+        <v>5118.5</v>
       </c>
       <c r="F20" t="n">
-        <v>8538.25</v>
+        <v>4931.17</v>
       </c>
       <c r="G20" t="n">
-        <v>36.78</v>
+        <v>8.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1161,6 +1161,450 @@
         </is>
       </c>
       <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>5850</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5190.91</v>
+      </c>
+      <c r="E21" t="n">
+        <v>5049.03</v>
+      </c>
+      <c r="F21" t="n">
+        <v>5289.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>615</v>
+      </c>
+      <c r="D22" t="n">
+        <v>599.22</v>
+      </c>
+      <c r="E22" t="n">
+        <v>569.37</v>
+      </c>
+      <c r="F22" t="n">
+        <v>555.45</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1046.25</v>
+      </c>
+      <c r="D23" t="n">
+        <v>982.9</v>
+      </c>
+      <c r="E23" t="n">
+        <v>988.3200000000001</v>
+      </c>
+      <c r="F23" t="n">
+        <v>944.92</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1639</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1563.66</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1500.47</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1470.25</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D25" t="n">
+        <v>7644.59</v>
+      </c>
+      <c r="E25" t="n">
+        <v>7512.4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>7227.45</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="D26" t="n">
+        <v>171.73</v>
+      </c>
+      <c r="E26" t="n">
+        <v>169.93</v>
+      </c>
+      <c r="F26" t="n">
+        <v>165.26</v>
+      </c>
+      <c r="G26" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>400.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>359.53</v>
+      </c>
+      <c r="E27" t="n">
+        <v>360.6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>350.79</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14.17</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>14035</v>
+      </c>
+      <c r="D28" t="n">
+        <v>13795.63</v>
+      </c>
+      <c r="E28" t="n">
+        <v>13049.3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>12230.36</v>
+      </c>
+      <c r="G28" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>318</v>
+      </c>
+      <c r="D29" t="n">
+        <v>298.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>281.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>272.62</v>
+      </c>
+      <c r="G29" t="n">
+        <v>16.65</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1357.3</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1211.88</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1122.19</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1147.9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>18.24</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1609.36</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1541.55</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1506.83</v>
+      </c>
+      <c r="G31" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>13-08-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7710</v>
+      </c>
+      <c r="D32" t="n">
+        <v>7277</v>
+      </c>
+      <c r="E32" t="n">
+        <v>7138.73</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6124.4</v>
+      </c>
+      <c r="G32" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,16 +478,16 @@
         <v>1939.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1917.01</v>
+        <v>1921.72</v>
       </c>
       <c r="E2" t="n">
-        <v>1878.63</v>
+        <v>1883.49</v>
       </c>
       <c r="F2" t="n">
-        <v>1927.16</v>
+        <v>1926.07</v>
       </c>
       <c r="G2" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11706</v>
+        <v>4070.7</v>
       </c>
       <c r="D4" t="n">
-        <v>11688.19</v>
+        <v>3928.64</v>
       </c>
       <c r="E4" t="n">
-        <v>11425.96</v>
+        <v>3996.73</v>
       </c>
       <c r="F4" t="n">
-        <v>11570.62</v>
+        <v>3951.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.17</v>
+        <v>3.02</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5523</v>
+        <v>3428.2</v>
       </c>
       <c r="D5" t="n">
-        <v>5226.24</v>
+        <v>3262.22</v>
       </c>
       <c r="E5" t="n">
-        <v>5055.08</v>
+        <v>3176.65</v>
       </c>
       <c r="F5" t="n">
-        <v>5444.75</v>
+        <v>3325.38</v>
       </c>
       <c r="G5" t="n">
-        <v>1.44</v>
+        <v>3.09</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4070.7</v>
+        <v>117.59</v>
       </c>
       <c r="D6" t="n">
-        <v>3928.64</v>
+        <v>109.96</v>
       </c>
       <c r="E6" t="n">
-        <v>3996.73</v>
+        <v>108.76</v>
       </c>
       <c r="F6" t="n">
-        <v>3951.46</v>
+        <v>112.68</v>
       </c>
       <c r="G6" t="n">
-        <v>3.02</v>
+        <v>4.35</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3428.2</v>
+        <v>176.23</v>
       </c>
       <c r="D7" t="n">
-        <v>3262.22</v>
+        <v>162.76</v>
       </c>
       <c r="E7" t="n">
-        <v>3176.65</v>
+        <v>159.27</v>
       </c>
       <c r="F7" t="n">
-        <v>3325.38</v>
+        <v>166.62</v>
       </c>
       <c r="G7" t="n">
-        <v>3.09</v>
+        <v>5.77</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>117.59</v>
+        <v>1083</v>
       </c>
       <c r="D8" t="n">
-        <v>109.96</v>
+        <v>1041.1</v>
       </c>
       <c r="E8" t="n">
-        <v>108.76</v>
+        <v>1034.18</v>
       </c>
       <c r="F8" t="n">
-        <v>112.68</v>
+        <v>1020.89</v>
       </c>
       <c r="G8" t="n">
-        <v>4.35</v>
+        <v>6.08</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1458.8</v>
+        <v>2755.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1446.43</v>
+        <v>2715.44</v>
       </c>
       <c r="E9" t="n">
-        <v>1430.4</v>
+        <v>2700.89</v>
       </c>
       <c r="F9" t="n">
-        <v>1390.44</v>
+        <v>2586.01</v>
       </c>
       <c r="G9" t="n">
-        <v>4.92</v>
+        <v>6.55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>176.23</v>
+        <v>2237.1</v>
       </c>
       <c r="D10" t="n">
-        <v>163.16</v>
+        <v>2042.16</v>
       </c>
       <c r="E10" t="n">
-        <v>159.1</v>
+        <v>1997.23</v>
       </c>
       <c r="F10" t="n">
-        <v>166.55</v>
+        <v>2070.78</v>
       </c>
       <c r="G10" t="n">
-        <v>5.81</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>897</v>
+        <v>533.65</v>
       </c>
       <c r="D11" t="n">
-        <v>839.46</v>
+        <v>494.45</v>
       </c>
       <c r="E11" t="n">
-        <v>840.08</v>
+        <v>481.33</v>
       </c>
       <c r="F11" t="n">
-        <v>847.41</v>
+        <v>493.68</v>
       </c>
       <c r="G11" t="n">
-        <v>5.85</v>
+        <v>8.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1240</v>
+        <v>5370</v>
       </c>
       <c r="D12" t="n">
-        <v>1178.18</v>
+        <v>5262.87</v>
       </c>
       <c r="E12" t="n">
-        <v>1145.21</v>
+        <v>5145</v>
       </c>
       <c r="F12" t="n">
-        <v>1170.16</v>
+        <v>4925.06</v>
       </c>
       <c r="G12" t="n">
-        <v>5.97</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2025</v>
+        <v>5850</v>
       </c>
       <c r="D13" t="n">
-        <v>1940.87</v>
+        <v>5190.91</v>
       </c>
       <c r="E13" t="n">
-        <v>1863.26</v>
+        <v>5049.03</v>
       </c>
       <c r="F13" t="n">
-        <v>1908.59</v>
+        <v>5289.32</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>10.6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1083</v>
+        <v>615</v>
       </c>
       <c r="D14" t="n">
-        <v>1041.98</v>
+        <v>599.22</v>
       </c>
       <c r="E14" t="n">
-        <v>1033.27</v>
+        <v>569.37</v>
       </c>
       <c r="F14" t="n">
-        <v>1020.3</v>
+        <v>555.45</v>
       </c>
       <c r="G14" t="n">
-        <v>6.15</v>
+        <v>10.72</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2755.5</v>
+        <v>1046.25</v>
       </c>
       <c r="D15" t="n">
-        <v>2715.53</v>
+        <v>981.89</v>
       </c>
       <c r="E15" t="n">
-        <v>2703.06</v>
+        <v>991.22</v>
       </c>
       <c r="F15" t="n">
-        <v>2587.28</v>
+        <v>944.23</v>
       </c>
       <c r="G15" t="n">
-        <v>6.5</v>
+        <v>10.8</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1183</v>
+        <v>1639</v>
       </c>
       <c r="D16" t="n">
-        <v>1132.88</v>
+        <v>1563.66</v>
       </c>
       <c r="E16" t="n">
-        <v>1118.36</v>
+        <v>1500.47</v>
       </c>
       <c r="F16" t="n">
-        <v>1101.6</v>
+        <v>1470.25</v>
       </c>
       <c r="G16" t="n">
-        <v>7.39</v>
+        <v>11.48</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>11500</v>
+        <v>186.5</v>
       </c>
       <c r="D17" t="n">
-        <v>10915.17</v>
+        <v>171.66</v>
       </c>
       <c r="E17" t="n">
-        <v>10656.4</v>
+        <v>169.74</v>
       </c>
       <c r="F17" t="n">
-        <v>10686.47</v>
+        <v>165.11</v>
       </c>
       <c r="G17" t="n">
-        <v>7.61</v>
+        <v>12.96</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2237.1</v>
+        <v>400.5</v>
       </c>
       <c r="D18" t="n">
-        <v>2042.16</v>
+        <v>359.53</v>
       </c>
       <c r="E18" t="n">
-        <v>1997.23</v>
+        <v>360.6</v>
       </c>
       <c r="F18" t="n">
-        <v>2070.78</v>
+        <v>350.79</v>
       </c>
       <c r="G18" t="n">
-        <v>8.029999999999999</v>
+        <v>14.17</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>533.65</v>
+        <v>14035</v>
       </c>
       <c r="D19" t="n">
-        <v>494.41</v>
+        <v>13845.93</v>
       </c>
       <c r="E19" t="n">
-        <v>480.74</v>
+        <v>13097.18</v>
       </c>
       <c r="F19" t="n">
-        <v>493.92</v>
+        <v>12222.25</v>
       </c>
       <c r="G19" t="n">
-        <v>8.039999999999999</v>
+        <v>14.83</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5370</v>
+        <v>318</v>
       </c>
       <c r="D20" t="n">
-        <v>5279.43</v>
+        <v>298.05</v>
       </c>
       <c r="E20" t="n">
-        <v>5118.5</v>
+        <v>281.4</v>
       </c>
       <c r="F20" t="n">
-        <v>4931.17</v>
+        <v>272.62</v>
       </c>
       <c r="G20" t="n">
-        <v>8.9</v>
+        <v>16.65</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>5850</v>
+        <v>1357.3</v>
       </c>
       <c r="D21" t="n">
-        <v>5190.91</v>
+        <v>1205.1</v>
       </c>
       <c r="E21" t="n">
-        <v>5049.03</v>
+        <v>1117.78</v>
       </c>
       <c r="F21" t="n">
-        <v>5289.32</v>
+        <v>1148.54</v>
       </c>
       <c r="G21" t="n">
-        <v>10.6</v>
+        <v>18.18</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13-08-2026</t>
+          <t>14-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>615</v>
+        <v>1829</v>
       </c>
       <c r="D22" t="n">
-        <v>599.22</v>
+        <v>1609.36</v>
       </c>
       <c r="E22" t="n">
-        <v>569.37</v>
+        <v>1541.55</v>
       </c>
       <c r="F22" t="n">
-        <v>555.45</v>
+        <v>1506.83</v>
       </c>
       <c r="G22" t="n">
-        <v>10.72</v>
+        <v>21.38</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1235,376 +1235,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1046.25</v>
-      </c>
-      <c r="D23" t="n">
-        <v>982.9</v>
-      </c>
-      <c r="E23" t="n">
-        <v>988.3200000000001</v>
-      </c>
-      <c r="F23" t="n">
-        <v>944.92</v>
-      </c>
-      <c r="G23" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1639</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1563.66</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1500.47</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1470.25</v>
-      </c>
-      <c r="G24" t="n">
-        <v>11.48</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>EICHERMOT</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>8100</v>
-      </c>
-      <c r="D25" t="n">
-        <v>7644.59</v>
-      </c>
-      <c r="E25" t="n">
-        <v>7512.4</v>
-      </c>
-      <c r="F25" t="n">
-        <v>7227.45</v>
-      </c>
-      <c r="G25" t="n">
-        <v>12.07</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>186.5</v>
-      </c>
-      <c r="D26" t="n">
-        <v>171.73</v>
-      </c>
-      <c r="E26" t="n">
-        <v>169.93</v>
-      </c>
-      <c r="F26" t="n">
-        <v>165.26</v>
-      </c>
-      <c r="G26" t="n">
-        <v>12.85</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>400.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>359.53</v>
-      </c>
-      <c r="E27" t="n">
-        <v>360.6</v>
-      </c>
-      <c r="F27" t="n">
-        <v>350.79</v>
-      </c>
-      <c r="G27" t="n">
-        <v>14.17</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>14035</v>
-      </c>
-      <c r="D28" t="n">
-        <v>13795.63</v>
-      </c>
-      <c r="E28" t="n">
-        <v>13049.3</v>
-      </c>
-      <c r="F28" t="n">
-        <v>12230.36</v>
-      </c>
-      <c r="G28" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>318</v>
-      </c>
-      <c r="D29" t="n">
-        <v>298.05</v>
-      </c>
-      <c r="E29" t="n">
-        <v>281.4</v>
-      </c>
-      <c r="F29" t="n">
-        <v>272.62</v>
-      </c>
-      <c r="G29" t="n">
-        <v>16.65</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1357.3</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1211.88</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1122.19</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1147.9</v>
-      </c>
-      <c r="G30" t="n">
-        <v>18.24</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>1829</v>
-      </c>
-      <c r="D31" t="n">
-        <v>1609.36</v>
-      </c>
-      <c r="E31" t="n">
-        <v>1541.55</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1506.83</v>
-      </c>
-      <c r="G31" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>13-08-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>7710</v>
-      </c>
-      <c r="D32" t="n">
-        <v>7277</v>
-      </c>
-      <c r="E32" t="n">
-        <v>7138.73</v>
-      </c>
-      <c r="F32" t="n">
-        <v>6124.4</v>
-      </c>
-      <c r="G32" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -478,16 +478,16 @@
         <v>1939.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1921.72</v>
+        <v>1917.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1883.49</v>
+        <v>1878.63</v>
       </c>
       <c r="F2" t="n">
-        <v>1926.07</v>
+        <v>1927.16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.68</v>
+        <v>0.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -518,13 +518,13 @@
         <v>277.64</v>
       </c>
       <c r="E3" t="n">
-        <v>278.22</v>
+        <v>278.04</v>
       </c>
       <c r="F3" t="n">
-        <v>276.35</v>
+        <v>276.33</v>
       </c>
       <c r="G3" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -552,16 +552,16 @@
         <v>4070.7</v>
       </c>
       <c r="D4" t="n">
-        <v>3928.64</v>
+        <v>3936.71</v>
       </c>
       <c r="E4" t="n">
-        <v>3996.73</v>
+        <v>3999.22</v>
       </c>
       <c r="F4" t="n">
-        <v>3951.46</v>
+        <v>3951.8</v>
       </c>
       <c r="G4" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>117.59</v>
       </c>
       <c r="D6" t="n">
-        <v>109.96</v>
+        <v>109.83</v>
       </c>
       <c r="E6" t="n">
-        <v>108.76</v>
+        <v>108.6</v>
       </c>
       <c r="F6" t="n">
-        <v>112.68</v>
+        <v>112.71</v>
       </c>
       <c r="G6" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -737,16 +737,16 @@
         <v>2755.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2715.44</v>
+        <v>2714.37</v>
       </c>
       <c r="E9" t="n">
-        <v>2700.89</v>
+        <v>2698.75</v>
       </c>
       <c r="F9" t="n">
-        <v>2586.01</v>
+        <v>2583.86</v>
       </c>
       <c r="G9" t="n">
-        <v>6.55</v>
+        <v>6.64</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -811,16 +811,16 @@
         <v>533.65</v>
       </c>
       <c r="D11" t="n">
-        <v>494.45</v>
+        <v>494.41</v>
       </c>
       <c r="E11" t="n">
-        <v>481.33</v>
+        <v>480.74</v>
       </c>
       <c r="F11" t="n">
-        <v>493.68</v>
+        <v>493.92</v>
       </c>
       <c r="G11" t="n">
-        <v>8.1</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -848,16 +848,16 @@
         <v>5370</v>
       </c>
       <c r="D12" t="n">
-        <v>5262.87</v>
+        <v>5279.43</v>
       </c>
       <c r="E12" t="n">
-        <v>5145</v>
+        <v>5118.5</v>
       </c>
       <c r="F12" t="n">
-        <v>4925.06</v>
+        <v>4931.17</v>
       </c>
       <c r="G12" t="n">
-        <v>9.029999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -915,20 +915,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>615</v>
+        <v>1046.25</v>
       </c>
       <c r="D14" t="n">
-        <v>599.22</v>
+        <v>982.9</v>
       </c>
       <c r="E14" t="n">
-        <v>569.37</v>
+        <v>988.3200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>555.45</v>
+        <v>944.92</v>
       </c>
       <c r="G14" t="n">
         <v>10.72</v>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1046.25</v>
+        <v>615</v>
       </c>
       <c r="D15" t="n">
-        <v>981.89</v>
+        <v>599.22</v>
       </c>
       <c r="E15" t="n">
-        <v>991.22</v>
+        <v>569.37</v>
       </c>
       <c r="F15" t="n">
-        <v>944.23</v>
+        <v>555.45</v>
       </c>
       <c r="G15" t="n">
-        <v>10.8</v>
+        <v>10.72</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         <v>1639</v>
       </c>
       <c r="D16" t="n">
-        <v>1563.66</v>
+        <v>1549.52</v>
       </c>
       <c r="E16" t="n">
-        <v>1500.47</v>
+        <v>1495.43</v>
       </c>
       <c r="F16" t="n">
-        <v>1470.25</v>
+        <v>1468.78</v>
       </c>
       <c r="G16" t="n">
-        <v>11.48</v>
+        <v>11.59</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>186.5</v>
       </c>
       <c r="D17" t="n">
-        <v>171.66</v>
+        <v>171.73</v>
       </c>
       <c r="E17" t="n">
-        <v>169.74</v>
+        <v>169.93</v>
       </c>
       <c r="F17" t="n">
-        <v>165.11</v>
+        <v>165.26</v>
       </c>
       <c r="G17" t="n">
-        <v>12.96</v>
+        <v>12.85</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1070,16 +1070,16 @@
         <v>400.5</v>
       </c>
       <c r="D18" t="n">
-        <v>359.53</v>
+        <v>359.17</v>
       </c>
       <c r="E18" t="n">
-        <v>360.6</v>
+        <v>362.02</v>
       </c>
       <c r="F18" t="n">
-        <v>350.79</v>
+        <v>350.23</v>
       </c>
       <c r="G18" t="n">
-        <v>14.17</v>
+        <v>14.35</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1107,16 +1107,16 @@
         <v>14035</v>
       </c>
       <c r="D19" t="n">
-        <v>13845.93</v>
+        <v>13795.63</v>
       </c>
       <c r="E19" t="n">
-        <v>13097.18</v>
+        <v>13049.3</v>
       </c>
       <c r="F19" t="n">
-        <v>12222.25</v>
+        <v>12230.36</v>
       </c>
       <c r="G19" t="n">
-        <v>14.83</v>
+        <v>14.76</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1144,16 +1144,16 @@
         <v>318</v>
       </c>
       <c r="D20" t="n">
-        <v>298.05</v>
+        <v>297.65</v>
       </c>
       <c r="E20" t="n">
-        <v>281.4</v>
+        <v>280</v>
       </c>
       <c r="F20" t="n">
-        <v>272.62</v>
+        <v>273.06</v>
       </c>
       <c r="G20" t="n">
-        <v>16.65</v>
+        <v>16.46</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
         <v>1357.3</v>
       </c>
       <c r="D21" t="n">
-        <v>1205.1</v>
+        <v>1198.6</v>
       </c>
       <c r="E21" t="n">
-        <v>1117.78</v>
+        <v>1114.12</v>
       </c>
       <c r="F21" t="n">
-        <v>1148.54</v>
+        <v>1149.46</v>
       </c>
       <c r="G21" t="n">
-        <v>18.18</v>
+        <v>18.08</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1218,16 +1218,16 @@
         <v>1829</v>
       </c>
       <c r="D22" t="n">
-        <v>1609.36</v>
+        <v>1603.85</v>
       </c>
       <c r="E22" t="n">
-        <v>1541.55</v>
+        <v>1539.14</v>
       </c>
       <c r="F22" t="n">
-        <v>1506.83</v>
+        <v>1509.79</v>
       </c>
       <c r="G22" t="n">
-        <v>21.38</v>
+        <v>21.14</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1939.1</v>
+        <v>282.6</v>
       </c>
       <c r="D2" t="n">
-        <v>1917.01</v>
+        <v>277.89</v>
       </c>
       <c r="E2" t="n">
-        <v>1878.63</v>
+        <v>278.37</v>
       </c>
       <c r="F2" t="n">
-        <v>1927.16</v>
+        <v>276.39</v>
       </c>
       <c r="G2" t="n">
-        <v>0.62</v>
+        <v>2.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>279.3</v>
+        <v>5580</v>
       </c>
       <c r="D3" t="n">
-        <v>277.64</v>
+        <v>5256.69</v>
       </c>
       <c r="E3" t="n">
-        <v>278.04</v>
+        <v>5066.26</v>
       </c>
       <c r="F3" t="n">
-        <v>276.33</v>
+        <v>5443.72</v>
       </c>
       <c r="G3" t="n">
-        <v>1.08</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4070.7</v>
+        <v>4057</v>
       </c>
       <c r="D4" t="n">
-        <v>3936.71</v>
+        <v>3936.63</v>
       </c>
       <c r="E4" t="n">
-        <v>3999.22</v>
+        <v>4001.52</v>
       </c>
       <c r="F4" t="n">
-        <v>3951.8</v>
+        <v>3952.66</v>
       </c>
       <c r="G4" t="n">
-        <v>3.01</v>
+        <v>2.64</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3428.2</v>
+        <v>171.64</v>
       </c>
       <c r="D5" t="n">
-        <v>3262.22</v>
+        <v>163.39</v>
       </c>
       <c r="E5" t="n">
-        <v>3176.65</v>
+        <v>159.65</v>
       </c>
       <c r="F5" t="n">
-        <v>3325.38</v>
+        <v>166.72</v>
       </c>
       <c r="G5" t="n">
-        <v>3.09</v>
+        <v>2.95</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>117.59</v>
+        <v>3428.3</v>
       </c>
       <c r="D6" t="n">
-        <v>109.83</v>
+        <v>3271.94</v>
       </c>
       <c r="E6" t="n">
-        <v>108.6</v>
+        <v>3185.04</v>
       </c>
       <c r="F6" t="n">
-        <v>112.71</v>
+        <v>3324.82</v>
       </c>
       <c r="G6" t="n">
-        <v>4.33</v>
+        <v>3.11</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>176.23</v>
+        <v>1992.1</v>
       </c>
       <c r="D7" t="n">
-        <v>162.76</v>
+        <v>1925.24</v>
       </c>
       <c r="E7" t="n">
-        <v>159.27</v>
+        <v>1887.81</v>
       </c>
       <c r="F7" t="n">
-        <v>166.62</v>
+        <v>1925.71</v>
       </c>
       <c r="G7" t="n">
-        <v>5.77</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1083</v>
+        <v>1450</v>
       </c>
       <c r="D8" t="n">
-        <v>1041.1</v>
+        <v>1446.16</v>
       </c>
       <c r="E8" t="n">
-        <v>1034.18</v>
+        <v>1431.38</v>
       </c>
       <c r="F8" t="n">
-        <v>1020.89</v>
+        <v>1389.93</v>
       </c>
       <c r="G8" t="n">
-        <v>6.08</v>
+        <v>4.32</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2755.5</v>
+        <v>1067.7</v>
       </c>
       <c r="D9" t="n">
-        <v>2714.37</v>
+        <v>1042.02</v>
       </c>
       <c r="E9" t="n">
-        <v>2698.75</v>
+        <v>1035.98</v>
       </c>
       <c r="F9" t="n">
-        <v>2583.86</v>
+        <v>1021.66</v>
       </c>
       <c r="G9" t="n">
-        <v>6.64</v>
+        <v>4.51</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2237.1</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>2042.16</v>
+        <v>110.2</v>
       </c>
       <c r="E10" t="n">
-        <v>1997.23</v>
+        <v>108.91</v>
       </c>
       <c r="F10" t="n">
-        <v>2070.78</v>
+        <v>112.72</v>
       </c>
       <c r="G10" t="n">
-        <v>8.029999999999999</v>
+        <v>4.68</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>533.65</v>
+        <v>2008.3</v>
       </c>
       <c r="D11" t="n">
-        <v>494.41</v>
+        <v>1944.63</v>
       </c>
       <c r="E11" t="n">
-        <v>480.74</v>
+        <v>1869.39</v>
       </c>
       <c r="F11" t="n">
-        <v>493.92</v>
+        <v>1907.94</v>
       </c>
       <c r="G11" t="n">
-        <v>8.039999999999999</v>
+        <v>5.26</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5370</v>
+        <v>894.95</v>
       </c>
       <c r="D12" t="n">
-        <v>5279.43</v>
+        <v>842.66</v>
       </c>
       <c r="E12" t="n">
-        <v>5118.5</v>
+        <v>841.49</v>
       </c>
       <c r="F12" t="n">
-        <v>4931.17</v>
+        <v>847.71</v>
       </c>
       <c r="G12" t="n">
-        <v>8.9</v>
+        <v>5.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5850</v>
+        <v>1240</v>
       </c>
       <c r="D13" t="n">
-        <v>5190.91</v>
+        <v>1184.51</v>
       </c>
       <c r="E13" t="n">
-        <v>5049.03</v>
+        <v>1150.61</v>
       </c>
       <c r="F13" t="n">
-        <v>5289.32</v>
+        <v>1169.86</v>
       </c>
       <c r="G13" t="n">
-        <v>10.6</v>
+        <v>6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1046.25</v>
+        <v>2199</v>
       </c>
       <c r="D14" t="n">
-        <v>982.9</v>
+        <v>2049.64</v>
       </c>
       <c r="E14" t="n">
-        <v>988.3200000000001</v>
+        <v>2003.3</v>
       </c>
       <c r="F14" t="n">
-        <v>944.92</v>
+        <v>2070.39</v>
       </c>
       <c r="G14" t="n">
-        <v>10.72</v>
+        <v>6.21</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>615</v>
+        <v>527</v>
       </c>
       <c r="D15" t="n">
-        <v>599.22</v>
+        <v>496.02</v>
       </c>
       <c r="E15" t="n">
-        <v>569.37</v>
+        <v>482.27</v>
       </c>
       <c r="F15" t="n">
-        <v>555.45</v>
+        <v>493.91</v>
       </c>
       <c r="G15" t="n">
-        <v>10.72</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1639</v>
+        <v>1180</v>
       </c>
       <c r="D16" t="n">
-        <v>1549.52</v>
+        <v>1135.23</v>
       </c>
       <c r="E16" t="n">
-        <v>1495.43</v>
+        <v>1120.48</v>
       </c>
       <c r="F16" t="n">
-        <v>1468.78</v>
+        <v>1101.67</v>
       </c>
       <c r="G16" t="n">
-        <v>11.59</v>
+        <v>7.11</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>186.5</v>
+        <v>376</v>
       </c>
       <c r="D17" t="n">
-        <v>171.73</v>
+        <v>360.63</v>
       </c>
       <c r="E17" t="n">
-        <v>169.93</v>
+        <v>361.26</v>
       </c>
       <c r="F17" t="n">
-        <v>165.26</v>
+        <v>350.96</v>
       </c>
       <c r="G17" t="n">
-        <v>12.85</v>
+        <v>7.13</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>400.5</v>
+        <v>11475</v>
       </c>
       <c r="D18" t="n">
-        <v>359.17</v>
+        <v>10914.33</v>
       </c>
       <c r="E18" t="n">
-        <v>362.02</v>
+        <v>10655.9</v>
       </c>
       <c r="F18" t="n">
-        <v>350.23</v>
+        <v>10686.34</v>
       </c>
       <c r="G18" t="n">
-        <v>14.35</v>
+        <v>7.38</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14035</v>
+        <v>5310</v>
       </c>
       <c r="D19" t="n">
-        <v>13795.63</v>
+        <v>5258.98</v>
       </c>
       <c r="E19" t="n">
-        <v>13049.3</v>
+        <v>5161.57</v>
       </c>
       <c r="F19" t="n">
-        <v>12230.36</v>
+        <v>4922.44</v>
       </c>
       <c r="G19" t="n">
-        <v>14.76</v>
+        <v>7.87</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>318</v>
+        <v>601</v>
       </c>
       <c r="D20" t="n">
-        <v>297.65</v>
+        <v>600.08</v>
       </c>
       <c r="E20" t="n">
-        <v>280</v>
+        <v>569.88</v>
       </c>
       <c r="F20" t="n">
-        <v>273.06</v>
+        <v>555.58</v>
       </c>
       <c r="G20" t="n">
-        <v>16.46</v>
+        <v>8.18</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1357.3</v>
+        <v>1029.5</v>
       </c>
       <c r="D21" t="n">
-        <v>1198.6</v>
+        <v>985.61</v>
       </c>
       <c r="E21" t="n">
-        <v>1114.12</v>
+        <v>987.17</v>
       </c>
       <c r="F21" t="n">
-        <v>1149.46</v>
+        <v>945.85</v>
       </c>
       <c r="G21" t="n">
-        <v>18.08</v>
+        <v>8.84</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,30 +1211,363 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>5790</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5220.09</v>
+      </c>
+      <c r="E22" t="n">
+        <v>5066.53</v>
+      </c>
+      <c r="F22" t="n">
+        <v>5293.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1632.8</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1571.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1504.21</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1471.36</v>
+      </c>
+      <c r="G23" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8066.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7633.13</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7502.75</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7224.03</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.66</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>187.38</v>
+      </c>
+      <c r="D25" t="n">
+        <v>172.54</v>
+      </c>
+      <c r="E25" t="n">
+        <v>170.43</v>
+      </c>
+      <c r="F25" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14130</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13854.2</v>
+      </c>
+      <c r="E26" t="n">
+        <v>13102.14</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12223.49</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>298.94</v>
+      </c>
+      <c r="E27" t="n">
+        <v>281.43</v>
+      </c>
+      <c r="F27" t="n">
+        <v>273.02</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16.66</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1210.35</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1120.92</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1149.33</v>
+      </c>
+      <c r="G28" t="n">
+        <v>16.85</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1829</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1603.85</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1539.14</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1509.79</v>
-      </c>
-      <c r="G22" t="n">
-        <v>21.14</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="C29" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1618.77</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1547.09</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1510.13</v>
+      </c>
+      <c r="G29" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7241.91</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7128.63</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6102.23</v>
+      </c>
+      <c r="G30" t="n">
+        <v>25.35</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>11828</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11437.93</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10894.22</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8571.700000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -478,16 +478,16 @@
         <v>282.6</v>
       </c>
       <c r="D2" t="n">
-        <v>277.89</v>
+        <v>277.86</v>
       </c>
       <c r="E2" t="n">
-        <v>278.37</v>
+        <v>278.55</v>
       </c>
       <c r="F2" t="n">
-        <v>276.39</v>
+        <v>276.43</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,16 +515,16 @@
         <v>5580</v>
       </c>
       <c r="D3" t="n">
-        <v>5256.69</v>
+        <v>5227.27</v>
       </c>
       <c r="E3" t="n">
-        <v>5066.26</v>
+        <v>5055.7</v>
       </c>
       <c r="F3" t="n">
-        <v>5443.72</v>
+        <v>5444.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,16 +552,16 @@
         <v>4057</v>
       </c>
       <c r="D4" t="n">
-        <v>3936.63</v>
+        <v>3929.66</v>
       </c>
       <c r="E4" t="n">
-        <v>4001.52</v>
+        <v>3998.81</v>
       </c>
       <c r="F4" t="n">
-        <v>3952.66</v>
+        <v>3952.07</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -589,16 +589,16 @@
         <v>171.64</v>
       </c>
       <c r="D5" t="n">
-        <v>163.39</v>
+        <v>163</v>
       </c>
       <c r="E5" t="n">
-        <v>159.65</v>
+        <v>159.79</v>
       </c>
       <c r="F5" t="n">
-        <v>166.72</v>
+        <v>166.8</v>
       </c>
       <c r="G5" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3428.3</v>
+        <v>1992.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3271.94</v>
+        <v>1925.24</v>
       </c>
       <c r="E6" t="n">
-        <v>3185.04</v>
+        <v>1887.81</v>
       </c>
       <c r="F6" t="n">
-        <v>3324.82</v>
+        <v>1925.71</v>
       </c>
       <c r="G6" t="n">
-        <v>3.11</v>
+        <v>3.45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1992.1</v>
+        <v>1450</v>
       </c>
       <c r="D7" t="n">
-        <v>1925.24</v>
+        <v>1446.16</v>
       </c>
       <c r="E7" t="n">
-        <v>1887.81</v>
+        <v>1431.38</v>
       </c>
       <c r="F7" t="n">
-        <v>1925.71</v>
+        <v>1389.93</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>4.32</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1450</v>
+        <v>1067.7</v>
       </c>
       <c r="D8" t="n">
-        <v>1446.16</v>
+        <v>1042.02</v>
       </c>
       <c r="E8" t="n">
-        <v>1431.38</v>
+        <v>1035.98</v>
       </c>
       <c r="F8" t="n">
-        <v>1389.93</v>
+        <v>1021.66</v>
       </c>
       <c r="G8" t="n">
-        <v>4.32</v>
+        <v>4.51</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1067.7</v>
+        <v>118</v>
       </c>
       <c r="D9" t="n">
-        <v>1042.02</v>
+        <v>110.38</v>
       </c>
       <c r="E9" t="n">
-        <v>1035.98</v>
+        <v>109.04</v>
       </c>
       <c r="F9" t="n">
-        <v>1021.66</v>
+        <v>112.69</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51</v>
+        <v>4.72</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>118</v>
+        <v>2199</v>
       </c>
       <c r="D10" t="n">
-        <v>110.2</v>
+        <v>2049.64</v>
       </c>
       <c r="E10" t="n">
-        <v>108.91</v>
+        <v>2003.3</v>
       </c>
       <c r="F10" t="n">
-        <v>112.72</v>
+        <v>2070.39</v>
       </c>
       <c r="G10" t="n">
-        <v>4.68</v>
+        <v>6.21</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2008.3</v>
+        <v>527</v>
       </c>
       <c r="D11" t="n">
-        <v>1944.63</v>
+        <v>496.15</v>
       </c>
       <c r="E11" t="n">
-        <v>1869.39</v>
+        <v>482.81</v>
       </c>
       <c r="F11" t="n">
-        <v>1907.94</v>
+        <v>493.65</v>
       </c>
       <c r="G11" t="n">
-        <v>5.26</v>
+        <v>6.76</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>894.95</v>
+        <v>376</v>
       </c>
       <c r="D12" t="n">
-        <v>842.66</v>
+        <v>360.47</v>
       </c>
       <c r="E12" t="n">
-        <v>841.49</v>
+        <v>360.21</v>
       </c>
       <c r="F12" t="n">
-        <v>847.71</v>
+        <v>351.53</v>
       </c>
       <c r="G12" t="n">
-        <v>5.57</v>
+        <v>6.96</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1240</v>
+        <v>5310</v>
       </c>
       <c r="D13" t="n">
-        <v>1184.51</v>
+        <v>5258.98</v>
       </c>
       <c r="E13" t="n">
-        <v>1150.61</v>
+        <v>5161.57</v>
       </c>
       <c r="F13" t="n">
-        <v>1169.86</v>
+        <v>4922.44</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>7.87</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2199</v>
+        <v>601</v>
       </c>
       <c r="D14" t="n">
-        <v>2049.64</v>
+        <v>600.51</v>
       </c>
       <c r="E14" t="n">
-        <v>2003.3</v>
+        <v>571.6799999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2070.39</v>
+        <v>555.63</v>
       </c>
       <c r="G14" t="n">
-        <v>6.21</v>
+        <v>8.17</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>527</v>
+        <v>1029.5</v>
       </c>
       <c r="D15" t="n">
-        <v>496.02</v>
+        <v>984.73</v>
       </c>
       <c r="E15" t="n">
-        <v>482.27</v>
+        <v>989.42</v>
       </c>
       <c r="F15" t="n">
-        <v>493.91</v>
+        <v>945.2</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>8.92</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1180</v>
+        <v>5790</v>
       </c>
       <c r="D16" t="n">
-        <v>1135.23</v>
+        <v>5224.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1120.48</v>
+        <v>5069.53</v>
       </c>
       <c r="F16" t="n">
-        <v>1101.67</v>
+        <v>5291.16</v>
       </c>
       <c r="G16" t="n">
-        <v>7.11</v>
+        <v>9.43</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>376</v>
+        <v>1632.8</v>
       </c>
       <c r="D17" t="n">
-        <v>360.63</v>
+        <v>1571.08</v>
       </c>
       <c r="E17" t="n">
-        <v>361.26</v>
+        <v>1504.21</v>
       </c>
       <c r="F17" t="n">
-        <v>350.96</v>
+        <v>1471.36</v>
       </c>
       <c r="G17" t="n">
-        <v>7.13</v>
+        <v>10.97</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11475</v>
+        <v>187.38</v>
       </c>
       <c r="D18" t="n">
-        <v>10914.33</v>
+        <v>172.26</v>
       </c>
       <c r="E18" t="n">
-        <v>10655.9</v>
+        <v>170.25</v>
       </c>
       <c r="F18" t="n">
-        <v>10686.34</v>
+        <v>165.34</v>
       </c>
       <c r="G18" t="n">
-        <v>7.38</v>
+        <v>13.33</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5310</v>
+        <v>14130</v>
       </c>
       <c r="D19" t="n">
-        <v>5258.98</v>
+        <v>13901.73</v>
       </c>
       <c r="E19" t="n">
-        <v>5161.57</v>
+        <v>13151.14</v>
       </c>
       <c r="F19" t="n">
-        <v>4922.44</v>
+        <v>12216.04</v>
       </c>
       <c r="G19" t="n">
-        <v>7.87</v>
+        <v>15.67</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>601</v>
+        <v>318.5</v>
       </c>
       <c r="D20" t="n">
-        <v>600.08</v>
+        <v>299.28</v>
       </c>
       <c r="E20" t="n">
-        <v>569.88</v>
+        <v>282.64</v>
       </c>
       <c r="F20" t="n">
-        <v>555.58</v>
+        <v>272.54</v>
       </c>
       <c r="G20" t="n">
-        <v>8.18</v>
+        <v>16.86</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1029.5</v>
+        <v>1343</v>
       </c>
       <c r="D21" t="n">
-        <v>985.61</v>
+        <v>1215.77</v>
       </c>
       <c r="E21" t="n">
-        <v>987.17</v>
+        <v>1124.52</v>
       </c>
       <c r="F21" t="n">
-        <v>945.85</v>
+        <v>1148.48</v>
       </c>
       <c r="G21" t="n">
-        <v>8.84</v>
+        <v>16.94</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5790</v>
+        <v>1812</v>
       </c>
       <c r="D22" t="n">
-        <v>5220.09</v>
+        <v>1621.19</v>
       </c>
       <c r="E22" t="n">
-        <v>5066.53</v>
+        <v>1549.22</v>
       </c>
       <c r="F22" t="n">
-        <v>5293.7</v>
+        <v>1506.92</v>
       </c>
       <c r="G22" t="n">
-        <v>9.380000000000001</v>
+        <v>20.25</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,28 +1243,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1632.8</v>
+        <v>7649</v>
       </c>
       <c r="D23" t="n">
-        <v>1571.08</v>
+        <v>7291.98</v>
       </c>
       <c r="E23" t="n">
-        <v>1504.21</v>
+        <v>7147.72</v>
       </c>
       <c r="F23" t="n">
-        <v>1471.36</v>
+        <v>6126.65</v>
       </c>
       <c r="G23" t="n">
-        <v>10.97</v>
+        <v>24.85</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1280,28 +1280,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>14-08-2026</t>
+          <t>15-08-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8066.5</v>
+        <v>11828</v>
       </c>
       <c r="D24" t="n">
-        <v>7633.13</v>
+        <v>11437.93</v>
       </c>
       <c r="E24" t="n">
-        <v>7502.75</v>
+        <v>10894.22</v>
       </c>
       <c r="F24" t="n">
-        <v>7224.03</v>
+        <v>8571.700000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>11.66</v>
+        <v>37.99</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1309,265 +1309,6 @@
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>187.38</v>
-      </c>
-      <c r="D25" t="n">
-        <v>172.54</v>
-      </c>
-      <c r="E25" t="n">
-        <v>170.43</v>
-      </c>
-      <c r="F25" t="n">
-        <v>165.48</v>
-      </c>
-      <c r="G25" t="n">
-        <v>13.23</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>14130</v>
-      </c>
-      <c r="D26" t="n">
-        <v>13854.2</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13102.14</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12223.49</v>
-      </c>
-      <c r="G26" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>318.5</v>
-      </c>
-      <c r="D27" t="n">
-        <v>298.94</v>
-      </c>
-      <c r="E27" t="n">
-        <v>281.43</v>
-      </c>
-      <c r="F27" t="n">
-        <v>273.02</v>
-      </c>
-      <c r="G27" t="n">
-        <v>16.66</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1343</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1210.35</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1120.92</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1149.33</v>
-      </c>
-      <c r="G28" t="n">
-        <v>16.85</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1812</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1618.77</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1547.09</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1510.13</v>
-      </c>
-      <c r="G29" t="n">
-        <v>19.99</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>7649</v>
-      </c>
-      <c r="D30" t="n">
-        <v>7241.91</v>
-      </c>
-      <c r="E30" t="n">
-        <v>7128.63</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6102.23</v>
-      </c>
-      <c r="G30" t="n">
-        <v>25.35</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>14-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>11828</v>
-      </c>
-      <c r="D31" t="n">
-        <v>11437.93</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10894.22</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8571.700000000001</v>
-      </c>
-      <c r="G31" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,16 +478,16 @@
         <v>282.6</v>
       </c>
       <c r="D2" t="n">
-        <v>277.86</v>
+        <v>277.89</v>
       </c>
       <c r="E2" t="n">
-        <v>278.55</v>
+        <v>278.37</v>
       </c>
       <c r="F2" t="n">
-        <v>276.43</v>
+        <v>276.39</v>
       </c>
       <c r="G2" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -515,16 +515,16 @@
         <v>5580</v>
       </c>
       <c r="D3" t="n">
-        <v>5227.27</v>
+        <v>5256.69</v>
       </c>
       <c r="E3" t="n">
-        <v>5055.7</v>
+        <v>5066.26</v>
       </c>
       <c r="F3" t="n">
-        <v>5444.9</v>
+        <v>5443.72</v>
       </c>
       <c r="G3" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1992.1</v>
+        <v>3428.3</v>
       </c>
       <c r="D6" t="n">
-        <v>1925.24</v>
+        <v>3271.94</v>
       </c>
       <c r="E6" t="n">
-        <v>1887.81</v>
+        <v>3185.04</v>
       </c>
       <c r="F6" t="n">
-        <v>1925.71</v>
+        <v>3324.82</v>
       </c>
       <c r="G6" t="n">
-        <v>3.45</v>
+        <v>3.11</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1450</v>
+        <v>1992.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1446.16</v>
+        <v>1921.82</v>
       </c>
       <c r="E7" t="n">
-        <v>1431.38</v>
+        <v>1882.44</v>
       </c>
       <c r="F7" t="n">
-        <v>1389.93</v>
+        <v>1927.1</v>
       </c>
       <c r="G7" t="n">
-        <v>4.32</v>
+        <v>3.37</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1067.7</v>
+        <v>1450</v>
       </c>
       <c r="D8" t="n">
-        <v>1042.02</v>
+        <v>1446.16</v>
       </c>
       <c r="E8" t="n">
-        <v>1035.98</v>
+        <v>1431.38</v>
       </c>
       <c r="F8" t="n">
-        <v>1021.66</v>
+        <v>1389.93</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51</v>
+        <v>4.32</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>118</v>
+        <v>1067.7</v>
       </c>
       <c r="D9" t="n">
-        <v>110.38</v>
+        <v>1042.02</v>
       </c>
       <c r="E9" t="n">
-        <v>109.04</v>
+        <v>1035.98</v>
       </c>
       <c r="F9" t="n">
-        <v>112.69</v>
+        <v>1021.66</v>
       </c>
       <c r="G9" t="n">
-        <v>4.72</v>
+        <v>4.51</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2199</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>2049.64</v>
+        <v>110.38</v>
       </c>
       <c r="E10" t="n">
-        <v>2003.3</v>
+        <v>109.04</v>
       </c>
       <c r="F10" t="n">
-        <v>2070.39</v>
+        <v>112.69</v>
       </c>
       <c r="G10" t="n">
-        <v>6.21</v>
+        <v>4.72</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>527</v>
+        <v>2008.3</v>
       </c>
       <c r="D11" t="n">
-        <v>496.15</v>
+        <v>1944.63</v>
       </c>
       <c r="E11" t="n">
-        <v>482.81</v>
+        <v>1869.39</v>
       </c>
       <c r="F11" t="n">
-        <v>493.65</v>
+        <v>1907.94</v>
       </c>
       <c r="G11" t="n">
-        <v>6.76</v>
+        <v>5.26</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>376</v>
+        <v>894.95</v>
       </c>
       <c r="D12" t="n">
-        <v>360.47</v>
+        <v>842.66</v>
       </c>
       <c r="E12" t="n">
-        <v>360.21</v>
+        <v>841.49</v>
       </c>
       <c r="F12" t="n">
-        <v>351.53</v>
+        <v>847.71</v>
       </c>
       <c r="G12" t="n">
-        <v>6.96</v>
+        <v>5.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5310</v>
+        <v>1240</v>
       </c>
       <c r="D13" t="n">
-        <v>5258.98</v>
+        <v>1184.51</v>
       </c>
       <c r="E13" t="n">
-        <v>5161.57</v>
+        <v>1150.61</v>
       </c>
       <c r="F13" t="n">
-        <v>4922.44</v>
+        <v>1169.86</v>
       </c>
       <c r="G13" t="n">
-        <v>7.87</v>
+        <v>6</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>601</v>
+        <v>2199</v>
       </c>
       <c r="D14" t="n">
-        <v>600.51</v>
+        <v>2049.64</v>
       </c>
       <c r="E14" t="n">
-        <v>571.6799999999999</v>
+        <v>2003.3</v>
       </c>
       <c r="F14" t="n">
-        <v>555.63</v>
+        <v>2070.39</v>
       </c>
       <c r="G14" t="n">
-        <v>8.17</v>
+        <v>6.21</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1029.5</v>
+        <v>527</v>
       </c>
       <c r="D15" t="n">
-        <v>984.73</v>
+        <v>497.39</v>
       </c>
       <c r="E15" t="n">
-        <v>989.42</v>
+        <v>484.29</v>
       </c>
       <c r="F15" t="n">
-        <v>945.2</v>
+        <v>493.6</v>
       </c>
       <c r="G15" t="n">
-        <v>8.92</v>
+        <v>6.77</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5790</v>
+        <v>376</v>
       </c>
       <c r="D16" t="n">
-        <v>5224.5</v>
+        <v>360.47</v>
       </c>
       <c r="E16" t="n">
-        <v>5069.53</v>
+        <v>360.21</v>
       </c>
       <c r="F16" t="n">
-        <v>5291.16</v>
+        <v>351.53</v>
       </c>
       <c r="G16" t="n">
-        <v>9.43</v>
+        <v>6.96</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1632.8</v>
+        <v>1180</v>
       </c>
       <c r="D17" t="n">
-        <v>1571.08</v>
+        <v>1135.23</v>
       </c>
       <c r="E17" t="n">
-        <v>1504.21</v>
+        <v>1120.48</v>
       </c>
       <c r="F17" t="n">
-        <v>1471.36</v>
+        <v>1101.67</v>
       </c>
       <c r="G17" t="n">
-        <v>10.97</v>
+        <v>7.11</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>187.38</v>
+        <v>11475</v>
       </c>
       <c r="D18" t="n">
-        <v>172.26</v>
+        <v>10930.53</v>
       </c>
       <c r="E18" t="n">
-        <v>170.25</v>
+        <v>10715.91</v>
       </c>
       <c r="F18" t="n">
-        <v>165.34</v>
+        <v>10660.02</v>
       </c>
       <c r="G18" t="n">
-        <v>13.33</v>
+        <v>7.65</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14130</v>
+        <v>5310</v>
       </c>
       <c r="D19" t="n">
-        <v>13901.73</v>
+        <v>5258.98</v>
       </c>
       <c r="E19" t="n">
-        <v>13151.14</v>
+        <v>5161.57</v>
       </c>
       <c r="F19" t="n">
-        <v>12216.04</v>
+        <v>4922.44</v>
       </c>
       <c r="G19" t="n">
-        <v>15.67</v>
+        <v>7.87</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>318.5</v>
+        <v>601</v>
       </c>
       <c r="D20" t="n">
-        <v>299.28</v>
+        <v>600.51</v>
       </c>
       <c r="E20" t="n">
-        <v>282.64</v>
+        <v>571.6799999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>272.54</v>
+        <v>555.63</v>
       </c>
       <c r="G20" t="n">
-        <v>16.86</v>
+        <v>8.17</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1343</v>
+        <v>1029.5</v>
       </c>
       <c r="D21" t="n">
-        <v>1215.77</v>
+        <v>985.61</v>
       </c>
       <c r="E21" t="n">
-        <v>1124.52</v>
+        <v>987.17</v>
       </c>
       <c r="F21" t="n">
-        <v>1148.48</v>
+        <v>945.85</v>
       </c>
       <c r="G21" t="n">
-        <v>16.94</v>
+        <v>8.84</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1812</v>
+        <v>5790</v>
       </c>
       <c r="D22" t="n">
-        <v>1621.19</v>
+        <v>5224.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1549.22</v>
+        <v>5069.53</v>
       </c>
       <c r="F22" t="n">
-        <v>1506.92</v>
+        <v>5291.16</v>
       </c>
       <c r="G22" t="n">
-        <v>20.25</v>
+        <v>9.43</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7649</v>
+        <v>1632.8</v>
       </c>
       <c r="D23" t="n">
-        <v>7291.98</v>
+        <v>1571.08</v>
       </c>
       <c r="E23" t="n">
-        <v>7147.72</v>
+        <v>1504.21</v>
       </c>
       <c r="F23" t="n">
-        <v>6126.65</v>
+        <v>1471.36</v>
       </c>
       <c r="G23" t="n">
-        <v>24.85</v>
+        <v>10.97</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,30 +1285,289 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>EICHERMOT</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>8066.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>7671.36</v>
+      </c>
+      <c r="E24" t="n">
+        <v>7533.79</v>
+      </c>
+      <c r="F24" t="n">
+        <v>7233.13</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.52</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>187.38</v>
+      </c>
+      <c r="D25" t="n">
+        <v>172.54</v>
+      </c>
+      <c r="E25" t="n">
+        <v>170.43</v>
+      </c>
+      <c r="F25" t="n">
+        <v>165.48</v>
+      </c>
+      <c r="G25" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14130</v>
+      </c>
+      <c r="D26" t="n">
+        <v>13901.73</v>
+      </c>
+      <c r="E26" t="n">
+        <v>13151.14</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12216.04</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.67</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>318.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>299.28</v>
+      </c>
+      <c r="E27" t="n">
+        <v>282.64</v>
+      </c>
+      <c r="F27" t="n">
+        <v>272.54</v>
+      </c>
+      <c r="G27" t="n">
+        <v>16.86</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1343</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1222.26</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1129.34</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1147.73</v>
+      </c>
+      <c r="G28" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1621.19</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1549.22</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1506.92</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7649</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7302.98</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7150.03</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6137.17</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24.63</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C31" t="n">
         <v>11828</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D31" t="n">
         <v>11437.93</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E31" t="n">
         <v>10894.22</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F31" t="n">
         <v>8571.700000000001</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G31" t="n">
         <v>37.99</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -515,16 +515,16 @@
         <v>5580</v>
       </c>
       <c r="D3" t="n">
-        <v>5256.69</v>
+        <v>5181.54</v>
       </c>
       <c r="E3" t="n">
-        <v>5066.26</v>
+        <v>5054.34</v>
       </c>
       <c r="F3" t="n">
-        <v>5443.72</v>
+        <v>5451.75</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -552,16 +552,16 @@
         <v>4057</v>
       </c>
       <c r="D4" t="n">
-        <v>3929.66</v>
+        <v>3936.63</v>
       </c>
       <c r="E4" t="n">
-        <v>3998.81</v>
+        <v>4001.52</v>
       </c>
       <c r="F4" t="n">
-        <v>3952.07</v>
+        <v>3952.66</v>
       </c>
       <c r="G4" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,16 +663,16 @@
         <v>1992.1</v>
       </c>
       <c r="D7" t="n">
-        <v>1921.82</v>
+        <v>1925.24</v>
       </c>
       <c r="E7" t="n">
-        <v>1882.44</v>
+        <v>1887.81</v>
       </c>
       <c r="F7" t="n">
-        <v>1927.1</v>
+        <v>1925.71</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -848,13 +848,13 @@
         <v>894.95</v>
       </c>
       <c r="D12" t="n">
-        <v>842.66</v>
+        <v>841.41</v>
       </c>
       <c r="E12" t="n">
-        <v>841.49</v>
+        <v>841.25</v>
       </c>
       <c r="F12" t="n">
-        <v>847.71</v>
+        <v>847.7</v>
       </c>
       <c r="G12" t="n">
         <v>5.57</v>
@@ -873,7 +873,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1107,16 +1107,16 @@
         <v>5310</v>
       </c>
       <c r="D19" t="n">
-        <v>5258.98</v>
+        <v>5276.47</v>
       </c>
       <c r="E19" t="n">
-        <v>5161.57</v>
+        <v>5134.46</v>
       </c>
       <c r="F19" t="n">
-        <v>4922.44</v>
+        <v>4928.78</v>
       </c>
       <c r="G19" t="n">
-        <v>7.87</v>
+        <v>7.73</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5790</v>
+        <v>1632.8</v>
       </c>
       <c r="D22" t="n">
-        <v>5224.5</v>
+        <v>1559.69</v>
       </c>
       <c r="E22" t="n">
-        <v>5069.53</v>
+        <v>1499.38</v>
       </c>
       <c r="F22" t="n">
-        <v>5291.16</v>
+        <v>1469.86</v>
       </c>
       <c r="G22" t="n">
-        <v>9.43</v>
+        <v>11.09</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,28 +1243,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1632.8</v>
+        <v>8066.5</v>
       </c>
       <c r="D23" t="n">
-        <v>1571.08</v>
+        <v>7663.97</v>
       </c>
       <c r="E23" t="n">
-        <v>1504.21</v>
+        <v>7524.03</v>
       </c>
       <c r="F23" t="n">
-        <v>1471.36</v>
+        <v>7230.36</v>
       </c>
       <c r="G23" t="n">
-        <v>10.97</v>
+        <v>11.56</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1280,28 +1280,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>8066.5</v>
+        <v>187.38</v>
       </c>
       <c r="D24" t="n">
-        <v>7671.36</v>
+        <v>172.54</v>
       </c>
       <c r="E24" t="n">
-        <v>7533.79</v>
+        <v>170.43</v>
       </c>
       <c r="F24" t="n">
-        <v>7233.13</v>
+        <v>165.48</v>
       </c>
       <c r="G24" t="n">
-        <v>11.52</v>
+        <v>13.23</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1317,28 +1317,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>187.38</v>
+        <v>14130</v>
       </c>
       <c r="D25" t="n">
-        <v>172.54</v>
+        <v>13901.73</v>
       </c>
       <c r="E25" t="n">
-        <v>170.43</v>
+        <v>13151.14</v>
       </c>
       <c r="F25" t="n">
-        <v>165.48</v>
+        <v>12216.04</v>
       </c>
       <c r="G25" t="n">
-        <v>13.23</v>
+        <v>15.67</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1354,28 +1354,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14130</v>
+        <v>318.5</v>
       </c>
       <c r="D26" t="n">
-        <v>13901.73</v>
+        <v>299.28</v>
       </c>
       <c r="E26" t="n">
-        <v>13151.14</v>
+        <v>282.64</v>
       </c>
       <c r="F26" t="n">
-        <v>12216.04</v>
+        <v>272.54</v>
       </c>
       <c r="G26" t="n">
-        <v>15.67</v>
+        <v>16.86</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1391,28 +1391,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>318.5</v>
+        <v>1343</v>
       </c>
       <c r="D27" t="n">
-        <v>299.28</v>
+        <v>1222.26</v>
       </c>
       <c r="E27" t="n">
-        <v>282.64</v>
+        <v>1129.34</v>
       </c>
       <c r="F27" t="n">
-        <v>272.54</v>
+        <v>1147.73</v>
       </c>
       <c r="G27" t="n">
-        <v>16.86</v>
+        <v>17.01</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1428,28 +1428,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1343</v>
+        <v>1812</v>
       </c>
       <c r="D28" t="n">
-        <v>1222.26</v>
+        <v>1621.19</v>
       </c>
       <c r="E28" t="n">
-        <v>1129.34</v>
+        <v>1549.22</v>
       </c>
       <c r="F28" t="n">
-        <v>1147.73</v>
+        <v>1506.92</v>
       </c>
       <c r="G28" t="n">
-        <v>17.01</v>
+        <v>20.25</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1465,28 +1465,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1812</v>
+        <v>7649</v>
       </c>
       <c r="D29" t="n">
-        <v>1621.19</v>
+        <v>7302.98</v>
       </c>
       <c r="E29" t="n">
-        <v>1549.22</v>
+        <v>7150.03</v>
       </c>
       <c r="F29" t="n">
-        <v>1506.92</v>
+        <v>6137.17</v>
       </c>
       <c r="G29" t="n">
-        <v>20.25</v>
+        <v>24.63</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1502,28 +1502,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>15-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7649</v>
+        <v>11828</v>
       </c>
       <c r="D30" t="n">
-        <v>7302.98</v>
+        <v>11437.93</v>
       </c>
       <c r="E30" t="n">
-        <v>7150.03</v>
+        <v>10894.22</v>
       </c>
       <c r="F30" t="n">
-        <v>6137.17</v>
+        <v>8571.700000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>24.63</v>
+        <v>37.99</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1531,43 +1531,6 @@
         </is>
       </c>
       <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>15-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>11828</v>
-      </c>
-      <c r="D31" t="n">
-        <v>11437.93</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10894.22</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8571.700000000001</v>
-      </c>
-      <c r="G31" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>282.6</v>
+        <v>281.8</v>
       </c>
       <c r="D2" t="n">
-        <v>277.89</v>
+        <v>278.07</v>
       </c>
       <c r="E2" t="n">
-        <v>278.37</v>
+        <v>278.9</v>
       </c>
       <c r="F2" t="n">
-        <v>276.39</v>
+        <v>276.47</v>
       </c>
       <c r="G2" t="n">
-        <v>2.25</v>
+        <v>1.93</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5580</v>
+        <v>3390.4</v>
       </c>
       <c r="D3" t="n">
-        <v>5181.54</v>
+        <v>3278.24</v>
       </c>
       <c r="E3" t="n">
-        <v>5054.34</v>
+        <v>3194.14</v>
       </c>
       <c r="F3" t="n">
-        <v>5451.75</v>
+        <v>3324.28</v>
       </c>
       <c r="G3" t="n">
-        <v>2.35</v>
+        <v>1.99</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4057</v>
+        <v>1969.3</v>
       </c>
       <c r="D4" t="n">
-        <v>3936.63</v>
+        <v>1927.49</v>
       </c>
       <c r="E4" t="n">
-        <v>4001.52</v>
+        <v>1891.38</v>
       </c>
       <c r="F4" t="n">
-        <v>3952.66</v>
+        <v>1925.18</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64</v>
+        <v>2.29</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>171.64</v>
+        <v>5570</v>
       </c>
       <c r="D5" t="n">
-        <v>163</v>
+        <v>5285.71</v>
       </c>
       <c r="E5" t="n">
-        <v>159.79</v>
+        <v>5076.71</v>
       </c>
       <c r="F5" t="n">
-        <v>166.8</v>
+        <v>5442.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3428.3</v>
+        <v>4086.7</v>
       </c>
       <c r="D6" t="n">
-        <v>3271.94</v>
+        <v>3931.18</v>
       </c>
       <c r="E6" t="n">
-        <v>3185.04</v>
+        <v>4003.03</v>
       </c>
       <c r="F6" t="n">
-        <v>3324.82</v>
+        <v>3952.91</v>
       </c>
       <c r="G6" t="n">
-        <v>3.11</v>
+        <v>3.38</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1992.1</v>
+        <v>1061.2</v>
       </c>
       <c r="D7" t="n">
-        <v>1925.24</v>
+        <v>1042.8</v>
       </c>
       <c r="E7" t="n">
-        <v>1887.81</v>
+        <v>1037.57</v>
       </c>
       <c r="F7" t="n">
-        <v>1925.71</v>
+        <v>1022.35</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1450</v>
+        <v>881.2</v>
       </c>
       <c r="D8" t="n">
-        <v>1446.16</v>
+        <v>845.8</v>
       </c>
       <c r="E8" t="n">
-        <v>1431.38</v>
+        <v>842.6</v>
       </c>
       <c r="F8" t="n">
-        <v>1389.93</v>
+        <v>847.9299999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>4.32</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1067.7</v>
+        <v>117.32</v>
       </c>
       <c r="D9" t="n">
-        <v>1042.02</v>
+        <v>110.82</v>
       </c>
       <c r="E9" t="n">
-        <v>1035.98</v>
+        <v>109.34</v>
       </c>
       <c r="F9" t="n">
-        <v>1021.66</v>
+        <v>112.68</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51</v>
+        <v>4.11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>118</v>
+        <v>2005</v>
       </c>
       <c r="D10" t="n">
-        <v>110.38</v>
+        <v>1949.1</v>
       </c>
       <c r="E10" t="n">
-        <v>109.04</v>
+        <v>1876.03</v>
       </c>
       <c r="F10" t="n">
-        <v>112.69</v>
+        <v>1907.29</v>
       </c>
       <c r="G10" t="n">
-        <v>4.72</v>
+        <v>5.12</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2008.3</v>
+        <v>2190</v>
       </c>
       <c r="D11" t="n">
-        <v>1944.63</v>
+        <v>2056.46</v>
       </c>
       <c r="E11" t="n">
-        <v>1869.39</v>
+        <v>2009.56</v>
       </c>
       <c r="F11" t="n">
-        <v>1907.94</v>
+        <v>2069.66</v>
       </c>
       <c r="G11" t="n">
-        <v>5.26</v>
+        <v>5.81</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>894.95</v>
+        <v>177.1</v>
       </c>
       <c r="D12" t="n">
-        <v>841.41</v>
+        <v>163.37</v>
       </c>
       <c r="E12" t="n">
-        <v>841.25</v>
+        <v>160.51</v>
       </c>
       <c r="F12" t="n">
-        <v>847.7</v>
+        <v>167</v>
       </c>
       <c r="G12" t="n">
-        <v>5.57</v>
+        <v>6.05</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1240</v>
+        <v>524.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1184.51</v>
+        <v>497.64</v>
       </c>
       <c r="E13" t="n">
-        <v>1150.61</v>
+        <v>483.7</v>
       </c>
       <c r="F13" t="n">
-        <v>1169.86</v>
+        <v>493.87</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2199</v>
+        <v>1173</v>
       </c>
       <c r="D14" t="n">
-        <v>2049.64</v>
+        <v>1136.56</v>
       </c>
       <c r="E14" t="n">
-        <v>2003.3</v>
+        <v>1122.84</v>
       </c>
       <c r="F14" t="n">
-        <v>2070.39</v>
+        <v>1101.71</v>
       </c>
       <c r="G14" t="n">
-        <v>6.21</v>
+        <v>6.47</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>527</v>
+        <v>11379</v>
       </c>
       <c r="D15" t="n">
-        <v>497.39</v>
+        <v>10957.73</v>
       </c>
       <c r="E15" t="n">
-        <v>484.29</v>
+        <v>10712.13</v>
       </c>
       <c r="F15" t="n">
-        <v>493.6</v>
+        <v>10671.86</v>
       </c>
       <c r="G15" t="n">
-        <v>6.77</v>
+        <v>6.63</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>376</v>
+        <v>5275.5</v>
       </c>
       <c r="D16" t="n">
-        <v>360.47</v>
+        <v>5270.85</v>
       </c>
       <c r="E16" t="n">
-        <v>360.21</v>
+        <v>5149.79</v>
       </c>
       <c r="F16" t="n">
-        <v>351.53</v>
+        <v>4926.26</v>
       </c>
       <c r="G16" t="n">
-        <v>6.96</v>
+        <v>7.09</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1180</v>
+        <v>2081.3</v>
       </c>
       <c r="D17" t="n">
-        <v>1135.23</v>
+        <v>1888.57</v>
       </c>
       <c r="E17" t="n">
-        <v>1120.48</v>
+        <v>1858.31</v>
       </c>
       <c r="F17" t="n">
-        <v>1101.67</v>
+        <v>1918.55</v>
       </c>
       <c r="G17" t="n">
-        <v>7.11</v>
+        <v>8.48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11475</v>
+        <v>1269.9</v>
       </c>
       <c r="D18" t="n">
-        <v>10930.53</v>
+        <v>1188.91</v>
       </c>
       <c r="E18" t="n">
-        <v>10715.91</v>
+        <v>1154.95</v>
       </c>
       <c r="F18" t="n">
-        <v>10660.02</v>
+        <v>1170.15</v>
       </c>
       <c r="G18" t="n">
-        <v>7.65</v>
+        <v>8.52</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5310</v>
+        <v>5745</v>
       </c>
       <c r="D19" t="n">
-        <v>5276.47</v>
+        <v>5218.59</v>
       </c>
       <c r="E19" t="n">
-        <v>5134.46</v>
+        <v>5065.63</v>
       </c>
       <c r="F19" t="n">
-        <v>4928.78</v>
+        <v>5293.48</v>
       </c>
       <c r="G19" t="n">
-        <v>7.73</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>601</v>
+        <v>1610</v>
       </c>
       <c r="D20" t="n">
-        <v>600.51</v>
+        <v>1577.86</v>
       </c>
       <c r="E20" t="n">
-        <v>571.6799999999999</v>
+        <v>1507.11</v>
       </c>
       <c r="F20" t="n">
-        <v>555.63</v>
+        <v>1472.34</v>
       </c>
       <c r="G20" t="n">
-        <v>8.17</v>
+        <v>9.35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1029.5</v>
+        <v>387.55</v>
       </c>
       <c r="D21" t="n">
-        <v>985.61</v>
+        <v>361.69</v>
       </c>
       <c r="E21" t="n">
-        <v>987.17</v>
+        <v>360.39</v>
       </c>
       <c r="F21" t="n">
-        <v>945.85</v>
+        <v>352.31</v>
       </c>
       <c r="G21" t="n">
-        <v>8.84</v>
+        <v>10</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1632.8</v>
+        <v>614</v>
       </c>
       <c r="D22" t="n">
-        <v>1559.69</v>
+        <v>601.79</v>
       </c>
       <c r="E22" t="n">
-        <v>1499.38</v>
+        <v>572.45</v>
       </c>
       <c r="F22" t="n">
-        <v>1469.86</v>
+        <v>555.8200000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>11.09</v>
+        <v>10.47</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8066.5</v>
+        <v>1049.9</v>
       </c>
       <c r="D23" t="n">
-        <v>7663.97</v>
+        <v>987.95</v>
       </c>
       <c r="E23" t="n">
-        <v>7524.03</v>
+        <v>994.86</v>
       </c>
       <c r="F23" t="n">
-        <v>7230.36</v>
+        <v>945.14</v>
       </c>
       <c r="G23" t="n">
-        <v>11.56</v>
+        <v>11.08</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>187.38</v>
+        <v>955</v>
       </c>
       <c r="D24" t="n">
-        <v>172.54</v>
+        <v>911.48</v>
       </c>
       <c r="E24" t="n">
-        <v>170.43</v>
+        <v>916.23</v>
       </c>
       <c r="F24" t="n">
-        <v>165.48</v>
+        <v>846.33</v>
       </c>
       <c r="G24" t="n">
-        <v>13.23</v>
+        <v>12.84</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>14130</v>
+        <v>188.9</v>
       </c>
       <c r="D25" t="n">
-        <v>13901.73</v>
+        <v>172.27</v>
       </c>
       <c r="E25" t="n">
-        <v>13151.14</v>
+        <v>170.1</v>
       </c>
       <c r="F25" t="n">
-        <v>12216.04</v>
+        <v>165.2</v>
       </c>
       <c r="G25" t="n">
-        <v>15.67</v>
+        <v>14.35</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>318.5</v>
+        <v>14025</v>
       </c>
       <c r="D26" t="n">
-        <v>299.28</v>
+        <v>13925.77</v>
       </c>
       <c r="E26" t="n">
-        <v>282.64</v>
+        <v>13203.8</v>
       </c>
       <c r="F26" t="n">
-        <v>272.54</v>
+        <v>12208.6</v>
       </c>
       <c r="G26" t="n">
-        <v>16.86</v>
+        <v>14.88</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1396,23 +1396,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1343</v>
+        <v>318</v>
       </c>
       <c r="D27" t="n">
-        <v>1222.26</v>
+        <v>300.43</v>
       </c>
       <c r="E27" t="n">
-        <v>1129.34</v>
+        <v>284.04</v>
       </c>
       <c r="F27" t="n">
-        <v>1147.73</v>
+        <v>272.48</v>
       </c>
       <c r="G27" t="n">
-        <v>17.01</v>
+        <v>16.71</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1433,23 +1433,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1812</v>
+        <v>1355.8</v>
       </c>
       <c r="D28" t="n">
-        <v>1621.19</v>
+        <v>1233.39</v>
       </c>
       <c r="E28" t="n">
-        <v>1549.22</v>
+        <v>1136.53</v>
       </c>
       <c r="F28" t="n">
-        <v>1506.92</v>
+        <v>1147.62</v>
       </c>
       <c r="G28" t="n">
-        <v>20.25</v>
+        <v>18.14</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1470,23 +1470,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7649</v>
+        <v>1806</v>
       </c>
       <c r="D29" t="n">
-        <v>7302.98</v>
+        <v>1632.22</v>
       </c>
       <c r="E29" t="n">
-        <v>7150.03</v>
+        <v>1557.04</v>
       </c>
       <c r="F29" t="n">
-        <v>6137.17</v>
+        <v>1507.04</v>
       </c>
       <c r="G29" t="n">
-        <v>24.63</v>
+        <v>19.84</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1507,30 +1507,67 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>7660</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7325.29</v>
+      </c>
+      <c r="E30" t="n">
+        <v>7165.69</v>
+      </c>
+      <c r="F30" t="n">
+        <v>6149.44</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24.56</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>11828</v>
-      </c>
-      <c r="D30" t="n">
-        <v>11437.93</v>
-      </c>
-      <c r="E30" t="n">
-        <v>10894.22</v>
-      </c>
-      <c r="F30" t="n">
-        <v>8571.700000000001</v>
-      </c>
-      <c r="G30" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="C31" t="n">
+        <v>11789</v>
+      </c>
+      <c r="D31" t="n">
+        <v>11461.87</v>
+      </c>
+      <c r="E31" t="n">
+        <v>10934.88</v>
+      </c>
+      <c r="F31" t="n">
+        <v>8589.190000000001</v>
+      </c>
+      <c r="G31" t="n">
+        <v>37.25</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>281.8</v>
+        <v>3390.4</v>
       </c>
       <c r="D2" t="n">
-        <v>278.07</v>
+        <v>3278.24</v>
       </c>
       <c r="E2" t="n">
-        <v>278.9</v>
+        <v>3194.14</v>
       </c>
       <c r="F2" t="n">
-        <v>276.47</v>
+        <v>3324.28</v>
       </c>
       <c r="G2" t="n">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3390.4</v>
+        <v>1969.3</v>
       </c>
       <c r="D3" t="n">
-        <v>3278.24</v>
+        <v>1927.49</v>
       </c>
       <c r="E3" t="n">
-        <v>3194.14</v>
+        <v>1891.38</v>
       </c>
       <c r="F3" t="n">
-        <v>3324.28</v>
+        <v>1925.18</v>
       </c>
       <c r="G3" t="n">
-        <v>1.99</v>
+        <v>2.29</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1969.3</v>
+        <v>5570</v>
       </c>
       <c r="D4" t="n">
-        <v>1927.49</v>
+        <v>5257.39</v>
       </c>
       <c r="E4" t="n">
-        <v>1891.38</v>
+        <v>5066.68</v>
       </c>
       <c r="F4" t="n">
-        <v>1925.18</v>
+        <v>5443.82</v>
       </c>
       <c r="G4" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5570</v>
+        <v>4086.7</v>
       </c>
       <c r="D5" t="n">
-        <v>5285.71</v>
+        <v>3931.18</v>
       </c>
       <c r="E5" t="n">
-        <v>5076.71</v>
+        <v>4003.03</v>
       </c>
       <c r="F5" t="n">
-        <v>5442.32</v>
+        <v>3952.91</v>
       </c>
       <c r="G5" t="n">
-        <v>2.35</v>
+        <v>3.38</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4086.7</v>
+        <v>1061.2</v>
       </c>
       <c r="D6" t="n">
-        <v>3931.18</v>
+        <v>1042.8</v>
       </c>
       <c r="E6" t="n">
-        <v>4003.03</v>
+        <v>1037.57</v>
       </c>
       <c r="F6" t="n">
-        <v>3952.91</v>
+        <v>1022.35</v>
       </c>
       <c r="G6" t="n">
-        <v>3.38</v>
+        <v>3.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1061.2</v>
+        <v>117.32</v>
       </c>
       <c r="D7" t="n">
-        <v>1042.8</v>
+        <v>110.82</v>
       </c>
       <c r="E7" t="n">
-        <v>1037.57</v>
+        <v>109.34</v>
       </c>
       <c r="F7" t="n">
-        <v>1022.35</v>
+        <v>112.68</v>
       </c>
       <c r="G7" t="n">
-        <v>3.8</v>
+        <v>4.11</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>881.2</v>
+        <v>2005</v>
       </c>
       <c r="D8" t="n">
-        <v>845.8</v>
+        <v>1949.1</v>
       </c>
       <c r="E8" t="n">
-        <v>842.6</v>
+        <v>1876.03</v>
       </c>
       <c r="F8" t="n">
-        <v>847.9299999999999</v>
+        <v>1907.29</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>5.12</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>117.32</v>
+        <v>2190</v>
       </c>
       <c r="D9" t="n">
-        <v>110.82</v>
+        <v>2056.46</v>
       </c>
       <c r="E9" t="n">
-        <v>109.34</v>
+        <v>2009.56</v>
       </c>
       <c r="F9" t="n">
-        <v>112.68</v>
+        <v>2069.66</v>
       </c>
       <c r="G9" t="n">
-        <v>4.11</v>
+        <v>5.81</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2005</v>
+        <v>177.1</v>
       </c>
       <c r="D10" t="n">
-        <v>1949.1</v>
+        <v>163.37</v>
       </c>
       <c r="E10" t="n">
-        <v>1876.03</v>
+        <v>160.51</v>
       </c>
       <c r="F10" t="n">
-        <v>1907.29</v>
+        <v>167</v>
       </c>
       <c r="G10" t="n">
-        <v>5.12</v>
+        <v>6.05</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2190</v>
+        <v>1173</v>
       </c>
       <c r="D11" t="n">
-        <v>2056.46</v>
+        <v>1136.49</v>
       </c>
       <c r="E11" t="n">
-        <v>2009.56</v>
+        <v>1121.24</v>
       </c>
       <c r="F11" t="n">
-        <v>2069.66</v>
+        <v>1101.86</v>
       </c>
       <c r="G11" t="n">
-        <v>5.81</v>
+        <v>6.46</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>177.1</v>
+        <v>5275.5</v>
       </c>
       <c r="D12" t="n">
-        <v>163.37</v>
+        <v>5254.55</v>
       </c>
       <c r="E12" t="n">
-        <v>160.51</v>
+        <v>5179.89</v>
       </c>
       <c r="F12" t="n">
-        <v>167</v>
+        <v>4919.77</v>
       </c>
       <c r="G12" t="n">
-        <v>6.05</v>
+        <v>7.23</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>524.5</v>
+        <v>2081.3</v>
       </c>
       <c r="D13" t="n">
-        <v>497.64</v>
+        <v>1888.57</v>
       </c>
       <c r="E13" t="n">
-        <v>483.7</v>
+        <v>1858.31</v>
       </c>
       <c r="F13" t="n">
-        <v>493.87</v>
+        <v>1918.55</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>8.48</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1173</v>
+        <v>1610</v>
       </c>
       <c r="D14" t="n">
-        <v>1136.56</v>
+        <v>1577.86</v>
       </c>
       <c r="E14" t="n">
-        <v>1122.84</v>
+        <v>1507.11</v>
       </c>
       <c r="F14" t="n">
-        <v>1101.71</v>
+        <v>1472.34</v>
       </c>
       <c r="G14" t="n">
-        <v>6.47</v>
+        <v>9.35</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11379</v>
+        <v>387.55</v>
       </c>
       <c r="D15" t="n">
-        <v>10957.73</v>
+        <v>361.69</v>
       </c>
       <c r="E15" t="n">
-        <v>10712.13</v>
+        <v>360.39</v>
       </c>
       <c r="F15" t="n">
-        <v>10671.86</v>
+        <v>352.31</v>
       </c>
       <c r="G15" t="n">
-        <v>6.63</v>
+        <v>10</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5275.5</v>
+        <v>614</v>
       </c>
       <c r="D16" t="n">
-        <v>5270.85</v>
+        <v>601.96</v>
       </c>
       <c r="E16" t="n">
-        <v>5149.79</v>
+        <v>574.55</v>
       </c>
       <c r="F16" t="n">
-        <v>4926.26</v>
+        <v>555.83</v>
       </c>
       <c r="G16" t="n">
-        <v>7.09</v>
+        <v>10.47</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2081.3</v>
+        <v>1049.9</v>
       </c>
       <c r="D17" t="n">
-        <v>1888.57</v>
+        <v>988.12</v>
       </c>
       <c r="E17" t="n">
-        <v>1858.31</v>
+        <v>988.6799999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1918.55</v>
+        <v>946.22</v>
       </c>
       <c r="G17" t="n">
-        <v>8.48</v>
+        <v>10.96</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1269.9</v>
+        <v>955</v>
       </c>
       <c r="D18" t="n">
-        <v>1188.91</v>
+        <v>912.15</v>
       </c>
       <c r="E18" t="n">
-        <v>1154.95</v>
+        <v>919.27</v>
       </c>
       <c r="F18" t="n">
-        <v>1170.15</v>
+        <v>846.2</v>
       </c>
       <c r="G18" t="n">
-        <v>8.52</v>
+        <v>12.86</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5745</v>
+        <v>14025</v>
       </c>
       <c r="D19" t="n">
-        <v>5218.59</v>
+        <v>13925.77</v>
       </c>
       <c r="E19" t="n">
-        <v>5065.63</v>
+        <v>13203.8</v>
       </c>
       <c r="F19" t="n">
-        <v>5293.48</v>
+        <v>12208.6</v>
       </c>
       <c r="G19" t="n">
-        <v>8.529999999999999</v>
+        <v>14.88</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1610</v>
+        <v>318</v>
       </c>
       <c r="D20" t="n">
-        <v>1577.86</v>
+        <v>300.43</v>
       </c>
       <c r="E20" t="n">
-        <v>1507.11</v>
+        <v>284.04</v>
       </c>
       <c r="F20" t="n">
-        <v>1472.34</v>
+        <v>272.48</v>
       </c>
       <c r="G20" t="n">
-        <v>9.35</v>
+        <v>16.71</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>387.55</v>
+        <v>1806</v>
       </c>
       <c r="D21" t="n">
-        <v>361.69</v>
+        <v>1632.22</v>
       </c>
       <c r="E21" t="n">
-        <v>360.39</v>
+        <v>1557.04</v>
       </c>
       <c r="F21" t="n">
-        <v>352.31</v>
+        <v>1507.04</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>19.84</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>18-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>614</v>
+        <v>7660</v>
       </c>
       <c r="D22" t="n">
-        <v>601.79</v>
+        <v>7318.33</v>
       </c>
       <c r="E22" t="n">
-        <v>572.45</v>
+        <v>7159.24</v>
       </c>
       <c r="F22" t="n">
-        <v>555.8200000000001</v>
+        <v>6139.47</v>
       </c>
       <c r="G22" t="n">
-        <v>10.47</v>
+        <v>24.77</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1235,339 +1235,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>HINDALCO</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1049.9</v>
-      </c>
-      <c r="D23" t="n">
-        <v>987.95</v>
-      </c>
-      <c r="E23" t="n">
-        <v>994.86</v>
-      </c>
-      <c r="F23" t="n">
-        <v>945.14</v>
-      </c>
-      <c r="G23" t="n">
-        <v>11.08</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>955</v>
-      </c>
-      <c r="D24" t="n">
-        <v>911.48</v>
-      </c>
-      <c r="E24" t="n">
-        <v>916.23</v>
-      </c>
-      <c r="F24" t="n">
-        <v>846.33</v>
-      </c>
-      <c r="G24" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>188.9</v>
-      </c>
-      <c r="D25" t="n">
-        <v>172.27</v>
-      </c>
-      <c r="E25" t="n">
-        <v>170.1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>165.2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>14.35</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>14025</v>
-      </c>
-      <c r="D26" t="n">
-        <v>13925.77</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13203.8</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12208.6</v>
-      </c>
-      <c r="G26" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>318</v>
-      </c>
-      <c r="D27" t="n">
-        <v>300.43</v>
-      </c>
-      <c r="E27" t="n">
-        <v>284.04</v>
-      </c>
-      <c r="F27" t="n">
-        <v>272.48</v>
-      </c>
-      <c r="G27" t="n">
-        <v>16.71</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1355.8</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1233.39</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1136.53</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1147.62</v>
-      </c>
-      <c r="G28" t="n">
-        <v>18.14</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>1806</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1632.22</v>
-      </c>
-      <c r="E29" t="n">
-        <v>1557.04</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1507.04</v>
-      </c>
-      <c r="G29" t="n">
-        <v>19.84</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>7660</v>
-      </c>
-      <c r="D30" t="n">
-        <v>7325.29</v>
-      </c>
-      <c r="E30" t="n">
-        <v>7165.69</v>
-      </c>
-      <c r="F30" t="n">
-        <v>6149.44</v>
-      </c>
-      <c r="G30" t="n">
-        <v>24.56</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>11789</v>
-      </c>
-      <c r="D31" t="n">
-        <v>11461.87</v>
-      </c>
-      <c r="E31" t="n">
-        <v>10934.88</v>
-      </c>
-      <c r="F31" t="n">
-        <v>8589.190000000001</v>
-      </c>
-      <c r="G31" t="n">
-        <v>37.25</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3390.4</v>
+        <v>1934.2</v>
       </c>
       <c r="D2" t="n">
-        <v>3278.24</v>
+        <v>1927.33</v>
       </c>
       <c r="E2" t="n">
-        <v>3194.14</v>
+        <v>1889.07</v>
       </c>
       <c r="F2" t="n">
-        <v>3324.28</v>
+        <v>1926.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.99</v>
+        <v>0.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1969.3</v>
+        <v>4064.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1927.49</v>
+        <v>3939.41</v>
       </c>
       <c r="E3" t="n">
-        <v>1891.38</v>
+        <v>4007.97</v>
       </c>
       <c r="F3" t="n">
-        <v>1925.18</v>
+        <v>3954.14</v>
       </c>
       <c r="G3" t="n">
-        <v>2.29</v>
+        <v>2.79</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5570</v>
+        <v>3421.5</v>
       </c>
       <c r="D4" t="n">
-        <v>5257.39</v>
+        <v>3285.75</v>
       </c>
       <c r="E4" t="n">
-        <v>5066.68</v>
+        <v>3203.39</v>
       </c>
       <c r="F4" t="n">
-        <v>5443.82</v>
+        <v>3324.06</v>
       </c>
       <c r="G4" t="n">
-        <v>2.32</v>
+        <v>2.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4086.7</v>
+        <v>1053</v>
       </c>
       <c r="D5" t="n">
-        <v>3931.18</v>
+        <v>1043.74</v>
       </c>
       <c r="E5" t="n">
-        <v>4003.03</v>
+        <v>1038.13</v>
       </c>
       <c r="F5" t="n">
-        <v>3952.91</v>
+        <v>1022.49</v>
       </c>
       <c r="G5" t="n">
-        <v>3.38</v>
+        <v>2.98</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1061.2</v>
+        <v>875</v>
       </c>
       <c r="D6" t="n">
-        <v>1042.8</v>
+        <v>847.09</v>
       </c>
       <c r="E6" t="n">
-        <v>1037.57</v>
+        <v>843.37</v>
       </c>
       <c r="F6" t="n">
-        <v>1022.35</v>
+        <v>848.12</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>117.32</v>
+        <v>116.5</v>
       </c>
       <c r="D7" t="n">
-        <v>110.82</v>
+        <v>111.01</v>
       </c>
       <c r="E7" t="n">
-        <v>109.34</v>
+        <v>109.45</v>
       </c>
       <c r="F7" t="n">
-        <v>112.68</v>
+        <v>112.71</v>
       </c>
       <c r="G7" t="n">
-        <v>4.11</v>
+        <v>3.36</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2005</v>
+        <v>286.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1949.1</v>
+        <v>278.44</v>
       </c>
       <c r="E8" t="n">
-        <v>1876.03</v>
+        <v>279.12</v>
       </c>
       <c r="F8" t="n">
-        <v>1907.29</v>
+        <v>276.52</v>
       </c>
       <c r="G8" t="n">
-        <v>5.12</v>
+        <v>3.52</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2190</v>
+        <v>518.25</v>
       </c>
       <c r="D9" t="n">
-        <v>2056.46</v>
+        <v>500.44</v>
       </c>
       <c r="E9" t="n">
-        <v>2009.56</v>
+        <v>487.24</v>
       </c>
       <c r="F9" t="n">
-        <v>2069.66</v>
+        <v>493.38</v>
       </c>
       <c r="G9" t="n">
-        <v>5.81</v>
+        <v>5.04</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>177.1</v>
+        <v>2011.2</v>
       </c>
       <c r="D10" t="n">
-        <v>163.37</v>
+        <v>1953.3</v>
       </c>
       <c r="E10" t="n">
-        <v>160.51</v>
+        <v>1882.42</v>
       </c>
       <c r="F10" t="n">
-        <v>167</v>
+        <v>1906.78</v>
       </c>
       <c r="G10" t="n">
-        <v>6.05</v>
+        <v>5.48</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1173</v>
+        <v>176.35</v>
       </c>
       <c r="D11" t="n">
-        <v>1136.49</v>
+        <v>164.16</v>
       </c>
       <c r="E11" t="n">
-        <v>1121.24</v>
+        <v>160.99</v>
       </c>
       <c r="F11" t="n">
-        <v>1101.86</v>
+        <v>167.12</v>
       </c>
       <c r="G11" t="n">
-        <v>6.46</v>
+        <v>5.52</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5275.5</v>
+        <v>1163.6</v>
       </c>
       <c r="D12" t="n">
-        <v>5254.55</v>
+        <v>1138.82</v>
       </c>
       <c r="E12" t="n">
-        <v>5179.89</v>
+        <v>1122.64</v>
       </c>
       <c r="F12" t="n">
-        <v>4919.77</v>
+        <v>1102.21</v>
       </c>
       <c r="G12" t="n">
-        <v>7.23</v>
+        <v>5.57</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2081.3</v>
+        <v>2186</v>
       </c>
       <c r="D13" t="n">
-        <v>1888.57</v>
+        <v>2063.93</v>
       </c>
       <c r="E13" t="n">
-        <v>1858.31</v>
+        <v>2015.67</v>
       </c>
       <c r="F13" t="n">
-        <v>1918.55</v>
+        <v>2068.63</v>
       </c>
       <c r="G13" t="n">
-        <v>8.48</v>
+        <v>5.67</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1610</v>
+        <v>11254</v>
       </c>
       <c r="D14" t="n">
-        <v>1577.86</v>
+        <v>10965.7</v>
       </c>
       <c r="E14" t="n">
-        <v>1507.11</v>
+        <v>10771.09</v>
       </c>
       <c r="F14" t="n">
-        <v>1472.34</v>
+        <v>10649.4</v>
       </c>
       <c r="G14" t="n">
-        <v>9.35</v>
+        <v>5.68</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>387.55</v>
+        <v>1592</v>
       </c>
       <c r="D15" t="n">
-        <v>361.69</v>
+        <v>1582.68</v>
       </c>
       <c r="E15" t="n">
-        <v>360.39</v>
+        <v>1510.02</v>
       </c>
       <c r="F15" t="n">
-        <v>352.31</v>
+        <v>1473.31</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>8.06</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>614</v>
+        <v>5745.5</v>
       </c>
       <c r="D16" t="n">
-        <v>601.96</v>
+        <v>5250.69</v>
       </c>
       <c r="E16" t="n">
-        <v>574.55</v>
+        <v>5085.25</v>
       </c>
       <c r="F16" t="n">
-        <v>555.83</v>
+        <v>5295.09</v>
       </c>
       <c r="G16" t="n">
-        <v>10.47</v>
+        <v>8.51</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1049.9</v>
+        <v>1273</v>
       </c>
       <c r="D17" t="n">
-        <v>988.12</v>
+        <v>1193.1</v>
       </c>
       <c r="E17" t="n">
-        <v>988.6799999999999</v>
+        <v>1155.76</v>
       </c>
       <c r="F17" t="n">
-        <v>946.22</v>
+        <v>1171.15</v>
       </c>
       <c r="G17" t="n">
-        <v>10.96</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>955</v>
+        <v>1041.6</v>
       </c>
       <c r="D18" t="n">
-        <v>912.15</v>
+        <v>991.1900000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>919.27</v>
+        <v>993.29</v>
       </c>
       <c r="F18" t="n">
-        <v>846.2</v>
+        <v>946.16</v>
       </c>
       <c r="G18" t="n">
-        <v>12.86</v>
+        <v>10.09</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14025</v>
+        <v>2115</v>
       </c>
       <c r="D19" t="n">
-        <v>13925.77</v>
+        <v>1897.98</v>
       </c>
       <c r="E19" t="n">
-        <v>13203.8</v>
+        <v>1864.22</v>
       </c>
       <c r="F19" t="n">
-        <v>12208.6</v>
+        <v>1919.96</v>
       </c>
       <c r="G19" t="n">
-        <v>14.88</v>
+        <v>10.16</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>318</v>
+        <v>388</v>
       </c>
       <c r="D20" t="n">
-        <v>300.43</v>
+        <v>362.36</v>
       </c>
       <c r="E20" t="n">
-        <v>284.04</v>
+        <v>361.34</v>
       </c>
       <c r="F20" t="n">
-        <v>272.48</v>
+        <v>351.81</v>
       </c>
       <c r="G20" t="n">
-        <v>16.71</v>
+        <v>10.29</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1806</v>
+        <v>938</v>
       </c>
       <c r="D21" t="n">
-        <v>1632.22</v>
+        <v>910.98</v>
       </c>
       <c r="E21" t="n">
-        <v>1557.04</v>
+        <v>918.5700000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>1507.04</v>
+        <v>846.03</v>
       </c>
       <c r="G21" t="n">
-        <v>19.84</v>
+        <v>10.87</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,30 +1211,215 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="D22" t="n">
+        <v>172.81</v>
+      </c>
+      <c r="E22" t="n">
+        <v>170.58</v>
+      </c>
+      <c r="F22" t="n">
+        <v>165.42</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>14150</v>
+      </c>
+      <c r="D23" t="n">
+        <v>13934.7</v>
+      </c>
+      <c r="E23" t="n">
+        <v>13209.16</v>
+      </c>
+      <c r="F23" t="n">
+        <v>12209.94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15.89</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>315.9</v>
+      </c>
+      <c r="D24" t="n">
+        <v>301.31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>285.44</v>
+      </c>
+      <c r="F24" t="n">
+        <v>272.41</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15.96</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1629.83</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1553.83</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1509.89</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1240.02</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1144.04</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1147.52</v>
+      </c>
+      <c r="G26" t="n">
+        <v>18.07</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>18-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>7660</v>
-      </c>
-      <c r="D22" t="n">
-        <v>7318.33</v>
-      </c>
-      <c r="E22" t="n">
-        <v>7159.24</v>
-      </c>
-      <c r="F22" t="n">
-        <v>6139.47</v>
-      </c>
-      <c r="G22" t="n">
-        <v>24.77</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="C27" t="n">
+        <v>7546</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7296.23</v>
+      </c>
+      <c r="E27" t="n">
+        <v>7150.27</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6127.28</v>
+      </c>
+      <c r="G27" t="n">
+        <v>23.15</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -737,16 +737,16 @@
         <v>518.25</v>
       </c>
       <c r="D9" t="n">
-        <v>500.44</v>
+        <v>498.69</v>
       </c>
       <c r="E9" t="n">
-        <v>487.24</v>
+        <v>485.07</v>
       </c>
       <c r="F9" t="n">
-        <v>493.38</v>
+        <v>493.8</v>
       </c>
       <c r="G9" t="n">
-        <v>5.04</v>
+        <v>4.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2011.2</v>
+        <v>176.35</v>
       </c>
       <c r="D10" t="n">
-        <v>1953.3</v>
+        <v>164.16</v>
       </c>
       <c r="E10" t="n">
-        <v>1882.42</v>
+        <v>160.99</v>
       </c>
       <c r="F10" t="n">
-        <v>1906.78</v>
+        <v>167.12</v>
       </c>
       <c r="G10" t="n">
-        <v>5.48</v>
+        <v>5.52</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>176.35</v>
+        <v>2186</v>
       </c>
       <c r="D11" t="n">
-        <v>164.16</v>
+        <v>2063.93</v>
       </c>
       <c r="E11" t="n">
-        <v>160.99</v>
+        <v>2015.67</v>
       </c>
       <c r="F11" t="n">
-        <v>167.12</v>
+        <v>2068.63</v>
       </c>
       <c r="G11" t="n">
-        <v>5.52</v>
+        <v>5.67</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1163.6</v>
+        <v>1592</v>
       </c>
       <c r="D12" t="n">
-        <v>1138.82</v>
+        <v>1573.25</v>
       </c>
       <c r="E12" t="n">
-        <v>1122.64</v>
+        <v>1505.51</v>
       </c>
       <c r="F12" t="n">
-        <v>1102.21</v>
+        <v>1471.69</v>
       </c>
       <c r="G12" t="n">
-        <v>5.57</v>
+        <v>8.18</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2186</v>
+        <v>1041.6</v>
       </c>
       <c r="D13" t="n">
-        <v>2063.93</v>
+        <v>991.1900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>2015.67</v>
+        <v>993.29</v>
       </c>
       <c r="F13" t="n">
-        <v>2068.63</v>
+        <v>946.16</v>
       </c>
       <c r="G13" t="n">
-        <v>5.67</v>
+        <v>10.09</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11254</v>
+        <v>388</v>
       </c>
       <c r="D14" t="n">
-        <v>10965.7</v>
+        <v>362.36</v>
       </c>
       <c r="E14" t="n">
-        <v>10771.09</v>
+        <v>361.34</v>
       </c>
       <c r="F14" t="n">
-        <v>10649.4</v>
+        <v>351.81</v>
       </c>
       <c r="G14" t="n">
-        <v>5.68</v>
+        <v>10.29</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1592</v>
+        <v>938</v>
       </c>
       <c r="D15" t="n">
-        <v>1582.68</v>
+        <v>910.98</v>
       </c>
       <c r="E15" t="n">
-        <v>1510.02</v>
+        <v>918.5700000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1473.31</v>
+        <v>846.03</v>
       </c>
       <c r="G15" t="n">
-        <v>8.06</v>
+        <v>10.87</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5745.5</v>
+        <v>185.5</v>
       </c>
       <c r="D16" t="n">
-        <v>5250.69</v>
+        <v>172.81</v>
       </c>
       <c r="E16" t="n">
-        <v>5085.25</v>
+        <v>170.58</v>
       </c>
       <c r="F16" t="n">
-        <v>5295.09</v>
+        <v>165.42</v>
       </c>
       <c r="G16" t="n">
-        <v>8.51</v>
+        <v>12.14</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1273</v>
+        <v>315.9</v>
       </c>
       <c r="D17" t="n">
-        <v>1193.1</v>
+        <v>301.36</v>
       </c>
       <c r="E17" t="n">
-        <v>1155.76</v>
+        <v>283.89</v>
       </c>
       <c r="F17" t="n">
-        <v>1171.15</v>
+        <v>272.85</v>
       </c>
       <c r="G17" t="n">
-        <v>8.699999999999999</v>
+        <v>15.78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1041.6</v>
+        <v>14150</v>
       </c>
       <c r="D18" t="n">
-        <v>991.1900000000001</v>
+        <v>13934.7</v>
       </c>
       <c r="E18" t="n">
-        <v>993.29</v>
+        <v>13209.16</v>
       </c>
       <c r="F18" t="n">
-        <v>946.16</v>
+        <v>12209.94</v>
       </c>
       <c r="G18" t="n">
-        <v>10.09</v>
+        <v>15.89</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2115</v>
+        <v>1773</v>
       </c>
       <c r="D19" t="n">
-        <v>1897.98</v>
+        <v>1629.83</v>
       </c>
       <c r="E19" t="n">
-        <v>1864.22</v>
+        <v>1553.83</v>
       </c>
       <c r="F19" t="n">
-        <v>1919.96</v>
+        <v>1509.89</v>
       </c>
       <c r="G19" t="n">
-        <v>10.16</v>
+        <v>17.43</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18-08-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>388</v>
+        <v>1354.9</v>
       </c>
       <c r="D20" t="n">
-        <v>362.36</v>
+        <v>1232.22</v>
       </c>
       <c r="E20" t="n">
-        <v>361.34</v>
+        <v>1135.31</v>
       </c>
       <c r="F20" t="n">
-        <v>351.81</v>
+        <v>1149.23</v>
       </c>
       <c r="G20" t="n">
-        <v>10.29</v>
+        <v>17.9</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1161,265 +1161,6 @@
         </is>
       </c>
       <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>938</v>
-      </c>
-      <c r="D21" t="n">
-        <v>910.98</v>
-      </c>
-      <c r="E21" t="n">
-        <v>918.5700000000001</v>
-      </c>
-      <c r="F21" t="n">
-        <v>846.03</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="D22" t="n">
-        <v>172.81</v>
-      </c>
-      <c r="E22" t="n">
-        <v>170.58</v>
-      </c>
-      <c r="F22" t="n">
-        <v>165.42</v>
-      </c>
-      <c r="G22" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>14150</v>
-      </c>
-      <c r="D23" t="n">
-        <v>13934.7</v>
-      </c>
-      <c r="E23" t="n">
-        <v>13209.16</v>
-      </c>
-      <c r="F23" t="n">
-        <v>12209.94</v>
-      </c>
-      <c r="G23" t="n">
-        <v>15.89</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>315.9</v>
-      </c>
-      <c r="D24" t="n">
-        <v>301.31</v>
-      </c>
-      <c r="E24" t="n">
-        <v>285.44</v>
-      </c>
-      <c r="F24" t="n">
-        <v>272.41</v>
-      </c>
-      <c r="G24" t="n">
-        <v>15.96</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1773</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1629.83</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1553.83</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1509.89</v>
-      </c>
-      <c r="G25" t="n">
-        <v>17.43</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1354.9</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1240.02</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1144.04</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1147.52</v>
-      </c>
-      <c r="G26" t="n">
-        <v>18.07</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>18-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>7546</v>
-      </c>
-      <c r="D27" t="n">
-        <v>7296.23</v>
-      </c>
-      <c r="E27" t="n">
-        <v>7150.27</v>
-      </c>
-      <c r="F27" t="n">
-        <v>6127.28</v>
-      </c>
-      <c r="G27" t="n">
-        <v>23.15</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1934.2</v>
+        <v>5442.5</v>
       </c>
       <c r="D2" t="n">
-        <v>1927.33</v>
+        <v>5304.86</v>
       </c>
       <c r="E2" t="n">
-        <v>1889.07</v>
+        <v>5085.55</v>
       </c>
       <c r="F2" t="n">
-        <v>1926.02</v>
+        <v>5439.93</v>
       </c>
       <c r="G2" t="n">
-        <v>0.42</v>
+        <v>0.05</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4064.3</v>
+        <v>1934.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3939.41</v>
+        <v>1927.33</v>
       </c>
       <c r="E3" t="n">
-        <v>4007.97</v>
+        <v>1889.07</v>
       </c>
       <c r="F3" t="n">
-        <v>3954.14</v>
+        <v>1926.02</v>
       </c>
       <c r="G3" t="n">
-        <v>2.79</v>
+        <v>0.42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3421.5</v>
+        <v>4064.3</v>
       </c>
       <c r="D4" t="n">
-        <v>3285.75</v>
+        <v>3939.41</v>
       </c>
       <c r="E4" t="n">
-        <v>3203.39</v>
+        <v>4007.97</v>
       </c>
       <c r="F4" t="n">
-        <v>3324.06</v>
+        <v>3954.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.93</v>
+        <v>2.79</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1053</v>
+        <v>3421.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1043.74</v>
+        <v>3285.75</v>
       </c>
       <c r="E5" t="n">
-        <v>1038.13</v>
+        <v>3203.39</v>
       </c>
       <c r="F5" t="n">
-        <v>1022.49</v>
+        <v>3324.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>875</v>
+        <v>1053</v>
       </c>
       <c r="D6" t="n">
-        <v>847.09</v>
+        <v>1043.3</v>
       </c>
       <c r="E6" t="n">
-        <v>843.37</v>
+        <v>1038.57</v>
       </c>
       <c r="F6" t="n">
-        <v>848.12</v>
+        <v>1023.03</v>
       </c>
       <c r="G6" t="n">
-        <v>3.17</v>
+        <v>2.93</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>116.5</v>
+        <v>875</v>
       </c>
       <c r="D7" t="n">
-        <v>111.01</v>
+        <v>847.09</v>
       </c>
       <c r="E7" t="n">
-        <v>109.45</v>
+        <v>843.37</v>
       </c>
       <c r="F7" t="n">
-        <v>112.71</v>
+        <v>848.12</v>
       </c>
       <c r="G7" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>286.25</v>
+        <v>116.5</v>
       </c>
       <c r="D8" t="n">
-        <v>278.44</v>
+        <v>111.01</v>
       </c>
       <c r="E8" t="n">
-        <v>279.12</v>
+        <v>109.45</v>
       </c>
       <c r="F8" t="n">
-        <v>276.52</v>
+        <v>112.71</v>
       </c>
       <c r="G8" t="n">
-        <v>3.52</v>
+        <v>3.36</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>518.25</v>
+        <v>286.25</v>
       </c>
       <c r="D9" t="n">
-        <v>498.69</v>
+        <v>278.44</v>
       </c>
       <c r="E9" t="n">
-        <v>485.07</v>
+        <v>279.12</v>
       </c>
       <c r="F9" t="n">
-        <v>493.8</v>
+        <v>276.52</v>
       </c>
       <c r="G9" t="n">
-        <v>4.95</v>
+        <v>3.52</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>176.35</v>
+        <v>518.25</v>
       </c>
       <c r="D10" t="n">
-        <v>164.16</v>
+        <v>500.44</v>
       </c>
       <c r="E10" t="n">
-        <v>160.99</v>
+        <v>487.24</v>
       </c>
       <c r="F10" t="n">
-        <v>167.12</v>
+        <v>493.38</v>
       </c>
       <c r="G10" t="n">
-        <v>5.52</v>
+        <v>5.04</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2186</v>
+        <v>176.35</v>
       </c>
       <c r="D11" t="n">
-        <v>2063.93</v>
+        <v>163.77</v>
       </c>
       <c r="E11" t="n">
-        <v>2015.67</v>
+        <v>161.17</v>
       </c>
       <c r="F11" t="n">
-        <v>2068.63</v>
+        <v>167.2</v>
       </c>
       <c r="G11" t="n">
-        <v>5.67</v>
+        <v>5.48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1592</v>
+        <v>2186</v>
       </c>
       <c r="D12" t="n">
-        <v>1573.25</v>
+        <v>2063.93</v>
       </c>
       <c r="E12" t="n">
-        <v>1505.51</v>
+        <v>2015.67</v>
       </c>
       <c r="F12" t="n">
-        <v>1471.69</v>
+        <v>2068.63</v>
       </c>
       <c r="G12" t="n">
-        <v>8.18</v>
+        <v>5.67</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1041.6</v>
+        <v>1592</v>
       </c>
       <c r="D13" t="n">
-        <v>991.1900000000001</v>
+        <v>1573.25</v>
       </c>
       <c r="E13" t="n">
-        <v>993.29</v>
+        <v>1505.51</v>
       </c>
       <c r="F13" t="n">
-        <v>946.16</v>
+        <v>1471.69</v>
       </c>
       <c r="G13" t="n">
-        <v>10.09</v>
+        <v>8.18</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -922,16 +922,16 @@
         <v>388</v>
       </c>
       <c r="D14" t="n">
-        <v>362.36</v>
+        <v>363.21</v>
       </c>
       <c r="E14" t="n">
-        <v>361.34</v>
+        <v>360.48</v>
       </c>
       <c r="F14" t="n">
-        <v>351.81</v>
+        <v>353.1</v>
       </c>
       <c r="G14" t="n">
-        <v>10.29</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>938</v>
+        <v>1041.6</v>
       </c>
       <c r="D15" t="n">
-        <v>910.98</v>
+        <v>991.1900000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>918.5700000000001</v>
+        <v>993.29</v>
       </c>
       <c r="F15" t="n">
-        <v>846.03</v>
+        <v>946.16</v>
       </c>
       <c r="G15" t="n">
-        <v>10.87</v>
+        <v>10.09</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>185.5</v>
+        <v>938</v>
       </c>
       <c r="D16" t="n">
-        <v>172.81</v>
+        <v>910.98</v>
       </c>
       <c r="E16" t="n">
-        <v>170.58</v>
+        <v>918.5700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>165.42</v>
+        <v>846.03</v>
       </c>
       <c r="G16" t="n">
-        <v>12.14</v>
+        <v>10.87</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>315.9</v>
+        <v>185.5</v>
       </c>
       <c r="D17" t="n">
-        <v>301.36</v>
+        <v>174.28</v>
       </c>
       <c r="E17" t="n">
-        <v>283.89</v>
+        <v>171.4</v>
       </c>
       <c r="F17" t="n">
-        <v>272.85</v>
+        <v>165.95</v>
       </c>
       <c r="G17" t="n">
-        <v>15.78</v>
+        <v>11.78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14150</v>
+        <v>315.9</v>
       </c>
       <c r="D18" t="n">
-        <v>13934.7</v>
+        <v>301.36</v>
       </c>
       <c r="E18" t="n">
-        <v>13209.16</v>
+        <v>283.89</v>
       </c>
       <c r="F18" t="n">
-        <v>12209.94</v>
+        <v>272.85</v>
       </c>
       <c r="G18" t="n">
-        <v>15.89</v>
+        <v>15.78</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1773</v>
+        <v>14150</v>
       </c>
       <c r="D19" t="n">
-        <v>1629.83</v>
+        <v>13934.7</v>
       </c>
       <c r="E19" t="n">
-        <v>1553.83</v>
+        <v>13209.16</v>
       </c>
       <c r="F19" t="n">
-        <v>1509.89</v>
+        <v>12209.94</v>
       </c>
       <c r="G19" t="n">
-        <v>17.43</v>
+        <v>15.89</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,30 +1137,104 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1629.83</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1553.83</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1509.89</v>
+      </c>
+      <c r="G20" t="n">
+        <v>17.43</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>NAUKRI</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C21" t="n">
         <v>1354.9</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D21" t="n">
         <v>1232.22</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E21" t="n">
         <v>1135.31</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F21" t="n">
         <v>1149.23</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G21" t="n">
         <v>17.9</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>11623</v>
+      </c>
+      <c r="D22" t="n">
+        <v>11479.4</v>
+      </c>
+      <c r="E22" t="n">
+        <v>10974.55</v>
+      </c>
+      <c r="F22" t="n">
+        <v>8606.08</v>
+      </c>
+      <c r="G22" t="n">
+        <v>35.06</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5442.5</v>
+        <v>5510</v>
       </c>
       <c r="D2" t="n">
-        <v>5304.86</v>
+        <v>5280.74</v>
       </c>
       <c r="E2" t="n">
-        <v>5085.55</v>
+        <v>5080.69</v>
       </c>
       <c r="F2" t="n">
-        <v>5439.93</v>
+        <v>5447.33</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05</v>
+        <v>1.15</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1934.2</v>
+        <v>4041.3</v>
       </c>
       <c r="D3" t="n">
-        <v>1927.33</v>
+        <v>3941.06</v>
       </c>
       <c r="E3" t="n">
-        <v>1889.07</v>
+        <v>4010.78</v>
       </c>
       <c r="F3" t="n">
-        <v>1926.02</v>
+        <v>3954.61</v>
       </c>
       <c r="G3" t="n">
-        <v>0.42</v>
+        <v>2.19</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4064.3</v>
+        <v>1048.6</v>
       </c>
       <c r="D4" t="n">
-        <v>3939.41</v>
+        <v>1044.09</v>
       </c>
       <c r="E4" t="n">
-        <v>4007.97</v>
+        <v>1039.05</v>
       </c>
       <c r="F4" t="n">
-        <v>3954.14</v>
+        <v>1023.15</v>
       </c>
       <c r="G4" t="n">
-        <v>2.79</v>
+        <v>2.49</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3421.5</v>
+        <v>3415</v>
       </c>
       <c r="D5" t="n">
-        <v>3285.75</v>
+        <v>3296.16</v>
       </c>
       <c r="E5" t="n">
-        <v>3203.39</v>
+        <v>3213.26</v>
       </c>
       <c r="F5" t="n">
-        <v>3324.06</v>
+        <v>3323.88</v>
       </c>
       <c r="G5" t="n">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,20 +619,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1053</v>
+        <v>873.15</v>
       </c>
       <c r="D6" t="n">
-        <v>1043.3</v>
+        <v>849.99</v>
       </c>
       <c r="E6" t="n">
-        <v>1038.57</v>
+        <v>843.7</v>
       </c>
       <c r="F6" t="n">
-        <v>1023.03</v>
+        <v>848.3099999999999</v>
       </c>
       <c r="G6" t="n">
         <v>2.93</v>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>875</v>
+        <v>173.1</v>
       </c>
       <c r="D7" t="n">
-        <v>847.09</v>
+        <v>164.46</v>
       </c>
       <c r="E7" t="n">
-        <v>843.37</v>
+        <v>161.58</v>
       </c>
       <c r="F7" t="n">
-        <v>848.12</v>
+        <v>167.3</v>
       </c>
       <c r="G7" t="n">
-        <v>3.17</v>
+        <v>3.47</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>116.5</v>
+        <v>288.15</v>
       </c>
       <c r="D8" t="n">
-        <v>111.01</v>
+        <v>278.84</v>
       </c>
       <c r="E8" t="n">
-        <v>109.45</v>
+        <v>279.77</v>
       </c>
       <c r="F8" t="n">
-        <v>112.71</v>
+        <v>276.63</v>
       </c>
       <c r="G8" t="n">
-        <v>3.36</v>
+        <v>4.17</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>286.25</v>
+        <v>514.35</v>
       </c>
       <c r="D9" t="n">
-        <v>278.44</v>
+        <v>499.84</v>
       </c>
       <c r="E9" t="n">
-        <v>279.12</v>
+        <v>486.48</v>
       </c>
       <c r="F9" t="n">
-        <v>276.52</v>
+        <v>493.64</v>
       </c>
       <c r="G9" t="n">
-        <v>3.52</v>
+        <v>4.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>518.25</v>
+        <v>117.48</v>
       </c>
       <c r="D10" t="n">
-        <v>500.44</v>
+        <v>111.47</v>
       </c>
       <c r="E10" t="n">
-        <v>487.24</v>
+        <v>109.67</v>
       </c>
       <c r="F10" t="n">
-        <v>493.38</v>
+        <v>112.72</v>
       </c>
       <c r="G10" t="n">
-        <v>5.04</v>
+        <v>4.23</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>176.35</v>
+        <v>2174.5</v>
       </c>
       <c r="D11" t="n">
-        <v>163.77</v>
+        <v>2073.12</v>
       </c>
       <c r="E11" t="n">
-        <v>161.17</v>
+        <v>2021.7</v>
       </c>
       <c r="F11" t="n">
-        <v>167.2</v>
+        <v>2067.43</v>
       </c>
       <c r="G11" t="n">
-        <v>5.48</v>
+        <v>5.18</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2186</v>
+        <v>2012</v>
       </c>
       <c r="D12" t="n">
-        <v>2063.93</v>
+        <v>1958.54</v>
       </c>
       <c r="E12" t="n">
-        <v>2015.67</v>
+        <v>1889.41</v>
       </c>
       <c r="F12" t="n">
-        <v>2068.63</v>
+        <v>1906.41</v>
       </c>
       <c r="G12" t="n">
-        <v>5.67</v>
+        <v>5.54</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1592</v>
+        <v>11380</v>
       </c>
       <c r="D13" t="n">
-        <v>1573.25</v>
+        <v>10982.27</v>
       </c>
       <c r="E13" t="n">
-        <v>1505.51</v>
+        <v>10768.39</v>
       </c>
       <c r="F13" t="n">
-        <v>1471.69</v>
+        <v>10659.55</v>
       </c>
       <c r="G13" t="n">
-        <v>8.18</v>
+        <v>6.76</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>388</v>
+        <v>1180.5</v>
       </c>
       <c r="D14" t="n">
-        <v>363.21</v>
+        <v>1140.4</v>
       </c>
       <c r="E14" t="n">
-        <v>360.48</v>
+        <v>1125.15</v>
       </c>
       <c r="F14" t="n">
-        <v>353.1</v>
+        <v>1102.28</v>
       </c>
       <c r="G14" t="n">
-        <v>9.880000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1041.6</v>
+        <v>5709.5</v>
       </c>
       <c r="D15" t="n">
-        <v>991.1900000000001</v>
+        <v>5278.59</v>
       </c>
       <c r="E15" t="n">
-        <v>993.29</v>
+        <v>5105.31</v>
       </c>
       <c r="F15" t="n">
-        <v>946.16</v>
+        <v>5296.81</v>
       </c>
       <c r="G15" t="n">
-        <v>10.09</v>
+        <v>7.79</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>938</v>
+        <v>1589.8</v>
       </c>
       <c r="D16" t="n">
-        <v>910.98</v>
+        <v>1579.36</v>
       </c>
       <c r="E16" t="n">
-        <v>918.5700000000001</v>
+        <v>1508</v>
       </c>
       <c r="F16" t="n">
-        <v>846.03</v>
+        <v>1472.56</v>
       </c>
       <c r="G16" t="n">
-        <v>10.87</v>
+        <v>7.96</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>185.5</v>
+        <v>1272</v>
       </c>
       <c r="D17" t="n">
-        <v>174.28</v>
+        <v>1197.57</v>
       </c>
       <c r="E17" t="n">
-        <v>171.4</v>
+        <v>1160.14</v>
       </c>
       <c r="F17" t="n">
-        <v>165.95</v>
+        <v>1171.45</v>
       </c>
       <c r="G17" t="n">
-        <v>11.78</v>
+        <v>8.58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>315.9</v>
+        <v>386.55</v>
       </c>
       <c r="D18" t="n">
-        <v>301.36</v>
+        <v>363.55</v>
       </c>
       <c r="E18" t="n">
-        <v>283.89</v>
+        <v>361.51</v>
       </c>
       <c r="F18" t="n">
-        <v>272.85</v>
+        <v>352.59</v>
       </c>
       <c r="G18" t="n">
-        <v>15.78</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14150</v>
+        <v>1038.95</v>
       </c>
       <c r="D19" t="n">
-        <v>13934.7</v>
+        <v>994.21</v>
       </c>
       <c r="E19" t="n">
-        <v>13209.16</v>
+        <v>992.33</v>
       </c>
       <c r="F19" t="n">
-        <v>12209.94</v>
+        <v>947.14</v>
       </c>
       <c r="G19" t="n">
-        <v>15.89</v>
+        <v>9.69</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1773</v>
+        <v>2121.8</v>
       </c>
       <c r="D20" t="n">
-        <v>1629.83</v>
+        <v>1908.56</v>
       </c>
       <c r="E20" t="n">
-        <v>1553.83</v>
+        <v>1870.3</v>
       </c>
       <c r="F20" t="n">
-        <v>1509.89</v>
+        <v>1921.55</v>
       </c>
       <c r="G20" t="n">
-        <v>17.43</v>
+        <v>10.42</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1354.9</v>
+        <v>942.1</v>
       </c>
       <c r="D21" t="n">
-        <v>1232.22</v>
+        <v>910.6900000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>1135.31</v>
+        <v>920.13</v>
       </c>
       <c r="F21" t="n">
-        <v>1149.23</v>
+        <v>845.65</v>
       </c>
       <c r="G21" t="n">
-        <v>17.9</v>
+        <v>11.41</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,30 +1211,215 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>186.9</v>
+      </c>
+      <c r="D22" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="E22" t="n">
+        <v>171.07</v>
+      </c>
+      <c r="F22" t="n">
+        <v>165.64</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12.83</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>320</v>
+      </c>
+      <c r="D23" t="n">
+        <v>302.58</v>
+      </c>
+      <c r="E23" t="n">
+        <v>285.33</v>
+      </c>
+      <c r="F23" t="n">
+        <v>272.8</v>
+      </c>
+      <c r="G23" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>14462</v>
+      </c>
+      <c r="D24" t="n">
+        <v>13975.37</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13266.18</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12204.04</v>
+      </c>
+      <c r="G24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1378.4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1244.1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1142.96</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1149.22</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1813.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1641.69</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1561.52</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1509.99</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>11623</v>
-      </c>
-      <c r="D22" t="n">
-        <v>11479.4</v>
-      </c>
-      <c r="E22" t="n">
-        <v>10974.55</v>
-      </c>
-      <c r="F22" t="n">
-        <v>8606.08</v>
-      </c>
-      <c r="G22" t="n">
-        <v>35.06</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="C27" t="n">
+        <v>11774</v>
+      </c>
+      <c r="D27" t="n">
+        <v>11505.13</v>
+      </c>
+      <c r="E27" t="n">
+        <v>11020.63</v>
+      </c>
+      <c r="F27" t="n">
+        <v>8624.200000000001</v>
+      </c>
+      <c r="G27" t="n">
+        <v>36.52</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5510</v>
+        <v>4041.3</v>
       </c>
       <c r="D2" t="n">
-        <v>5280.74</v>
+        <v>3938.57</v>
       </c>
       <c r="E2" t="n">
-        <v>5080.69</v>
+        <v>4008.78</v>
       </c>
       <c r="F2" t="n">
-        <v>5447.33</v>
+        <v>3953.73</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4041.3</v>
+        <v>1048.6</v>
       </c>
       <c r="D3" t="n">
-        <v>3941.06</v>
+        <v>1044.36</v>
       </c>
       <c r="E3" t="n">
-        <v>4010.78</v>
+        <v>1039.48</v>
       </c>
       <c r="F3" t="n">
-        <v>3954.61</v>
+        <v>1023.67</v>
       </c>
       <c r="G3" t="n">
-        <v>2.19</v>
+        <v>2.44</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1048.6</v>
+        <v>3415</v>
       </c>
       <c r="D4" t="n">
-        <v>1044.09</v>
+        <v>3296.16</v>
       </c>
       <c r="E4" t="n">
-        <v>1039.05</v>
+        <v>3213.26</v>
       </c>
       <c r="F4" t="n">
-        <v>1023.15</v>
+        <v>3323.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2.49</v>
+        <v>2.74</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3415</v>
+        <v>873.15</v>
       </c>
       <c r="D5" t="n">
-        <v>3296.16</v>
+        <v>849.99</v>
       </c>
       <c r="E5" t="n">
-        <v>3213.26</v>
+        <v>843.7</v>
       </c>
       <c r="F5" t="n">
-        <v>3323.88</v>
+        <v>848.3099999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.74</v>
+        <v>2.93</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>873.15</v>
+        <v>173.1</v>
       </c>
       <c r="D6" t="n">
-        <v>849.99</v>
+        <v>164.33</v>
       </c>
       <c r="E6" t="n">
-        <v>843.7</v>
+        <v>161.8</v>
       </c>
       <c r="F6" t="n">
-        <v>848.3099999999999</v>
+        <v>167.37</v>
       </c>
       <c r="G6" t="n">
-        <v>2.93</v>
+        <v>3.42</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>173.1</v>
+        <v>288.15</v>
       </c>
       <c r="D7" t="n">
-        <v>164.46</v>
+        <v>278.84</v>
       </c>
       <c r="E7" t="n">
-        <v>161.58</v>
+        <v>279.77</v>
       </c>
       <c r="F7" t="n">
-        <v>167.3</v>
+        <v>276.63</v>
       </c>
       <c r="G7" t="n">
-        <v>3.47</v>
+        <v>4.17</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>288.15</v>
+        <v>514.35</v>
       </c>
       <c r="D8" t="n">
-        <v>278.84</v>
+        <v>500.13</v>
       </c>
       <c r="E8" t="n">
-        <v>279.77</v>
+        <v>487.05</v>
       </c>
       <c r="F8" t="n">
-        <v>276.63</v>
+        <v>493.33</v>
       </c>
       <c r="G8" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>514.35</v>
+        <v>117.48</v>
       </c>
       <c r="D9" t="n">
-        <v>499.84</v>
+        <v>111.79</v>
       </c>
       <c r="E9" t="n">
-        <v>486.48</v>
+        <v>109.8</v>
       </c>
       <c r="F9" t="n">
-        <v>493.64</v>
+        <v>112.67</v>
       </c>
       <c r="G9" t="n">
-        <v>4.2</v>
+        <v>4.27</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>117.48</v>
+        <v>2174.5</v>
       </c>
       <c r="D10" t="n">
-        <v>111.47</v>
+        <v>2073.12</v>
       </c>
       <c r="E10" t="n">
-        <v>109.67</v>
+        <v>2021.7</v>
       </c>
       <c r="F10" t="n">
-        <v>112.72</v>
+        <v>2067.43</v>
       </c>
       <c r="G10" t="n">
-        <v>4.23</v>
+        <v>5.18</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2174.5</v>
+        <v>2012</v>
       </c>
       <c r="D11" t="n">
-        <v>2073.12</v>
+        <v>1958.54</v>
       </c>
       <c r="E11" t="n">
-        <v>2021.7</v>
+        <v>1889.41</v>
       </c>
       <c r="F11" t="n">
-        <v>2067.43</v>
+        <v>1906.41</v>
       </c>
       <c r="G11" t="n">
-        <v>5.18</v>
+        <v>5.54</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2012</v>
+        <v>5709.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1958.54</v>
+        <v>5310.59</v>
       </c>
       <c r="E12" t="n">
-        <v>1889.41</v>
+        <v>5127.98</v>
       </c>
       <c r="F12" t="n">
-        <v>1906.41</v>
+        <v>5296.88</v>
       </c>
       <c r="G12" t="n">
-        <v>5.54</v>
+        <v>7.79</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11380</v>
+        <v>1272</v>
       </c>
       <c r="D13" t="n">
-        <v>10982.27</v>
+        <v>1198.37</v>
       </c>
       <c r="E13" t="n">
-        <v>10768.39</v>
+        <v>1162.36</v>
       </c>
       <c r="F13" t="n">
-        <v>10659.55</v>
+        <v>1170.62</v>
       </c>
       <c r="G13" t="n">
-        <v>6.76</v>
+        <v>8.66</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1180.5</v>
+        <v>386.55</v>
       </c>
       <c r="D14" t="n">
-        <v>1140.4</v>
+        <v>364.43</v>
       </c>
       <c r="E14" t="n">
-        <v>1125.15</v>
+        <v>360.68</v>
       </c>
       <c r="F14" t="n">
-        <v>1102.28</v>
+        <v>353.9</v>
       </c>
       <c r="G14" t="n">
-        <v>7.1</v>
+        <v>9.23</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5709.5</v>
+        <v>1038.95</v>
       </c>
       <c r="D15" t="n">
-        <v>5278.59</v>
+        <v>992.8099999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>5105.31</v>
+        <v>987.73</v>
       </c>
       <c r="F15" t="n">
-        <v>5296.81</v>
+        <v>948.08</v>
       </c>
       <c r="G15" t="n">
-        <v>7.79</v>
+        <v>9.58</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1589.8</v>
+        <v>2121.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1579.36</v>
+        <v>1908.82</v>
       </c>
       <c r="E16" t="n">
-        <v>1508</v>
+        <v>1871.82</v>
       </c>
       <c r="F16" t="n">
-        <v>1472.56</v>
+        <v>1921.85</v>
       </c>
       <c r="G16" t="n">
-        <v>7.96</v>
+        <v>10.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1272</v>
+        <v>942.1</v>
       </c>
       <c r="D17" t="n">
-        <v>1197.57</v>
+        <v>912.8099999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1160.14</v>
+        <v>922.77</v>
       </c>
       <c r="F17" t="n">
-        <v>1171.45</v>
+        <v>845.67</v>
       </c>
       <c r="G17" t="n">
-        <v>8.58</v>
+        <v>11.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>386.55</v>
+        <v>186.9</v>
       </c>
       <c r="D18" t="n">
-        <v>363.55</v>
+        <v>174.8</v>
       </c>
       <c r="E18" t="n">
-        <v>361.51</v>
+        <v>171.71</v>
       </c>
       <c r="F18" t="n">
-        <v>352.59</v>
+        <v>166.03</v>
       </c>
       <c r="G18" t="n">
-        <v>9.630000000000001</v>
+        <v>12.57</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1038.95</v>
+        <v>320</v>
       </c>
       <c r="D19" t="n">
-        <v>994.21</v>
+        <v>302.42</v>
       </c>
       <c r="E19" t="n">
-        <v>992.33</v>
+        <v>287.05</v>
       </c>
       <c r="F19" t="n">
-        <v>947.14</v>
+        <v>272.42</v>
       </c>
       <c r="G19" t="n">
-        <v>9.69</v>
+        <v>17.47</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2121.8</v>
+        <v>14462</v>
       </c>
       <c r="D20" t="n">
-        <v>1908.56</v>
+        <v>14006.97</v>
       </c>
       <c r="E20" t="n">
-        <v>1870.3</v>
+        <v>13314.08</v>
       </c>
       <c r="F20" t="n">
-        <v>1921.55</v>
+        <v>12195.98</v>
       </c>
       <c r="G20" t="n">
-        <v>10.42</v>
+        <v>18.58</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>942.1</v>
+        <v>1378.4</v>
       </c>
       <c r="D21" t="n">
-        <v>910.6900000000001</v>
+        <v>1245.1</v>
       </c>
       <c r="E21" t="n">
-        <v>920.13</v>
+        <v>1147.08</v>
       </c>
       <c r="F21" t="n">
-        <v>845.65</v>
+        <v>1148.28</v>
       </c>
       <c r="G21" t="n">
-        <v>11.41</v>
+        <v>20.04</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>186.9</v>
+        <v>1813.1</v>
       </c>
       <c r="D22" t="n">
-        <v>173.6</v>
+        <v>1653.47</v>
       </c>
       <c r="E22" t="n">
-        <v>171.07</v>
+        <v>1572.73</v>
       </c>
       <c r="F22" t="n">
-        <v>165.64</v>
+        <v>1507.19</v>
       </c>
       <c r="G22" t="n">
-        <v>12.83</v>
+        <v>20.3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,28 +1243,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>320</v>
+        <v>11774</v>
       </c>
       <c r="D23" t="n">
-        <v>302.58</v>
+        <v>11505.13</v>
       </c>
       <c r="E23" t="n">
-        <v>285.33</v>
+        <v>11020.63</v>
       </c>
       <c r="F23" t="n">
-        <v>272.8</v>
+        <v>8624.200000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>17.3</v>
+        <v>36.52</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1272,154 +1272,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>14462</v>
-      </c>
-      <c r="D24" t="n">
-        <v>13975.37</v>
-      </c>
-      <c r="E24" t="n">
-        <v>13266.18</v>
-      </c>
-      <c r="F24" t="n">
-        <v>12204.04</v>
-      </c>
-      <c r="G24" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1378.4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1244.1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1142.96</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1149.22</v>
-      </c>
-      <c r="G25" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1813.1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1641.69</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1561.52</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1509.99</v>
-      </c>
-      <c r="G26" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>11774</v>
-      </c>
-      <c r="D27" t="n">
-        <v>11505.13</v>
-      </c>
-      <c r="E27" t="n">
-        <v>11020.63</v>
-      </c>
-      <c r="F27" t="n">
-        <v>8624.200000000001</v>
-      </c>
-      <c r="G27" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,16 +478,16 @@
         <v>4041.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3938.57</v>
+        <v>3941.06</v>
       </c>
       <c r="E2" t="n">
-        <v>4008.78</v>
+        <v>4010.78</v>
       </c>
       <c r="F2" t="n">
-        <v>3953.73</v>
+        <v>3954.61</v>
       </c>
       <c r="G2" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -515,16 +515,16 @@
         <v>1048.6</v>
       </c>
       <c r="D3" t="n">
-        <v>1044.36</v>
+        <v>1044.09</v>
       </c>
       <c r="E3" t="n">
-        <v>1039.48</v>
+        <v>1039.05</v>
       </c>
       <c r="F3" t="n">
-        <v>1023.67</v>
+        <v>1023.15</v>
       </c>
       <c r="G3" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -626,16 +626,16 @@
         <v>173.1</v>
       </c>
       <c r="D6" t="n">
-        <v>164.33</v>
+        <v>164.46</v>
       </c>
       <c r="E6" t="n">
-        <v>161.8</v>
+        <v>161.58</v>
       </c>
       <c r="F6" t="n">
-        <v>167.37</v>
+        <v>167.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -663,13 +663,13 @@
         <v>288.15</v>
       </c>
       <c r="D7" t="n">
-        <v>278.84</v>
+        <v>278.73</v>
       </c>
       <c r="E7" t="n">
-        <v>279.77</v>
+        <v>279.57</v>
       </c>
       <c r="F7" t="n">
-        <v>276.63</v>
+        <v>276.61</v>
       </c>
       <c r="G7" t="n">
         <v>4.17</v>
@@ -700,16 +700,16 @@
         <v>514.35</v>
       </c>
       <c r="D8" t="n">
-        <v>500.13</v>
+        <v>499.84</v>
       </c>
       <c r="E8" t="n">
-        <v>487.05</v>
+        <v>486.48</v>
       </c>
       <c r="F8" t="n">
-        <v>493.33</v>
+        <v>493.64</v>
       </c>
       <c r="G8" t="n">
-        <v>4.26</v>
+        <v>4.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -737,16 +737,16 @@
         <v>117.48</v>
       </c>
       <c r="D9" t="n">
-        <v>111.79</v>
+        <v>111.47</v>
       </c>
       <c r="E9" t="n">
-        <v>109.8</v>
+        <v>109.67</v>
       </c>
       <c r="F9" t="n">
-        <v>112.67</v>
+        <v>112.72</v>
       </c>
       <c r="G9" t="n">
-        <v>4.27</v>
+        <v>4.23</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -885,16 +885,16 @@
         <v>1272</v>
       </c>
       <c r="D13" t="n">
-        <v>1198.37</v>
+        <v>1197.57</v>
       </c>
       <c r="E13" t="n">
-        <v>1162.36</v>
+        <v>1160.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1170.62</v>
+        <v>1171.45</v>
       </c>
       <c r="G13" t="n">
-        <v>8.66</v>
+        <v>8.58</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -922,16 +922,16 @@
         <v>386.55</v>
       </c>
       <c r="D14" t="n">
-        <v>364.43</v>
+        <v>363.55</v>
       </c>
       <c r="E14" t="n">
-        <v>360.68</v>
+        <v>361.51</v>
       </c>
       <c r="F14" t="n">
-        <v>353.9</v>
+        <v>352.59</v>
       </c>
       <c r="G14" t="n">
-        <v>9.23</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -959,16 +959,16 @@
         <v>1038.95</v>
       </c>
       <c r="D15" t="n">
-        <v>992.8099999999999</v>
+        <v>994.21</v>
       </c>
       <c r="E15" t="n">
-        <v>987.73</v>
+        <v>992.33</v>
       </c>
       <c r="F15" t="n">
-        <v>948.08</v>
+        <v>947.14</v>
       </c>
       <c r="G15" t="n">
-        <v>9.58</v>
+        <v>9.69</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -996,16 +996,16 @@
         <v>2121.8</v>
       </c>
       <c r="D16" t="n">
-        <v>1908.82</v>
+        <v>1908.56</v>
       </c>
       <c r="E16" t="n">
-        <v>1871.82</v>
+        <v>1870.3</v>
       </c>
       <c r="F16" t="n">
-        <v>1921.85</v>
+        <v>1921.55</v>
       </c>
       <c r="G16" t="n">
-        <v>10.4</v>
+        <v>10.42</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1033,16 +1033,16 @@
         <v>942.1</v>
       </c>
       <c r="D17" t="n">
-        <v>912.8099999999999</v>
+        <v>910.6900000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>922.77</v>
+        <v>920.13</v>
       </c>
       <c r="F17" t="n">
-        <v>845.67</v>
+        <v>845.65</v>
       </c>
       <c r="G17" t="n">
-        <v>11.4</v>
+        <v>11.41</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1070,16 +1070,16 @@
         <v>186.9</v>
       </c>
       <c r="D18" t="n">
-        <v>174.8</v>
+        <v>173.6</v>
       </c>
       <c r="E18" t="n">
-        <v>171.71</v>
+        <v>171.07</v>
       </c>
       <c r="F18" t="n">
-        <v>166.03</v>
+        <v>165.64</v>
       </c>
       <c r="G18" t="n">
-        <v>12.57</v>
+        <v>12.83</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1107,16 +1107,16 @@
         <v>320</v>
       </c>
       <c r="D19" t="n">
-        <v>302.42</v>
+        <v>302.58</v>
       </c>
       <c r="E19" t="n">
-        <v>287.05</v>
+        <v>285.33</v>
       </c>
       <c r="F19" t="n">
-        <v>272.42</v>
+        <v>272.8</v>
       </c>
       <c r="G19" t="n">
-        <v>17.47</v>
+        <v>17.3</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1144,16 +1144,16 @@
         <v>14462</v>
       </c>
       <c r="D20" t="n">
-        <v>14006.97</v>
+        <v>13975.37</v>
       </c>
       <c r="E20" t="n">
-        <v>13314.08</v>
+        <v>13266.18</v>
       </c>
       <c r="F20" t="n">
-        <v>12195.98</v>
+        <v>12204.04</v>
       </c>
       <c r="G20" t="n">
-        <v>18.58</v>
+        <v>18.5</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1181,16 +1181,16 @@
         <v>1378.4</v>
       </c>
       <c r="D21" t="n">
-        <v>1245.1</v>
+        <v>1244.1</v>
       </c>
       <c r="E21" t="n">
-        <v>1147.08</v>
+        <v>1142.96</v>
       </c>
       <c r="F21" t="n">
-        <v>1148.28</v>
+        <v>1149.22</v>
       </c>
       <c r="G21" t="n">
-        <v>20.04</v>
+        <v>19.94</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1218,16 +1218,16 @@
         <v>1813.1</v>
       </c>
       <c r="D22" t="n">
-        <v>1653.47</v>
+        <v>1641.69</v>
       </c>
       <c r="E22" t="n">
-        <v>1572.73</v>
+        <v>1561.52</v>
       </c>
       <c r="F22" t="n">
-        <v>1507.19</v>
+        <v>1509.99</v>
       </c>
       <c r="G22" t="n">
-        <v>20.3</v>
+        <v>20.07</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1235,43 +1235,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>11774</v>
-      </c>
-      <c r="D23" t="n">
-        <v>11505.13</v>
-      </c>
-      <c r="E23" t="n">
-        <v>11020.63</v>
-      </c>
-      <c r="F23" t="n">
-        <v>8624.200000000001</v>
-      </c>
-      <c r="G23" t="n">
-        <v>36.52</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4041.3</v>
+        <v>1941.7</v>
       </c>
       <c r="D2" t="n">
-        <v>3941.06</v>
+        <v>1929.33</v>
       </c>
       <c r="E2" t="n">
-        <v>4010.78</v>
+        <v>1894.99</v>
       </c>
       <c r="F2" t="n">
-        <v>3954.61</v>
+        <v>1924.76</v>
       </c>
       <c r="G2" t="n">
-        <v>2.19</v>
+        <v>0.88</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1048.6</v>
+        <v>1048</v>
       </c>
       <c r="D3" t="n">
-        <v>1044.09</v>
+        <v>1045.12</v>
       </c>
       <c r="E3" t="n">
-        <v>1039.05</v>
+        <v>1039.94</v>
       </c>
       <c r="F3" t="n">
-        <v>1023.15</v>
+        <v>1023.78</v>
       </c>
       <c r="G3" t="n">
-        <v>2.49</v>
+        <v>2.37</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3415</v>
+        <v>871</v>
       </c>
       <c r="D4" t="n">
-        <v>3296.16</v>
+        <v>853.28</v>
       </c>
       <c r="E4" t="n">
-        <v>3213.26</v>
+        <v>844.45</v>
       </c>
       <c r="F4" t="n">
-        <v>3323.88</v>
+        <v>848.46</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>873.15</v>
+        <v>3424.8</v>
       </c>
       <c r="D5" t="n">
-        <v>849.99</v>
+        <v>3307.48</v>
       </c>
       <c r="E5" t="n">
-        <v>843.7</v>
+        <v>3222.36</v>
       </c>
       <c r="F5" t="n">
-        <v>848.3099999999999</v>
+        <v>3323.44</v>
       </c>
       <c r="G5" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>173.1</v>
+        <v>4081</v>
       </c>
       <c r="D6" t="n">
-        <v>164.46</v>
+        <v>3947.35</v>
       </c>
       <c r="E6" t="n">
-        <v>161.58</v>
+        <v>4014.05</v>
       </c>
       <c r="F6" t="n">
-        <v>167.3</v>
+        <v>3955.05</v>
       </c>
       <c r="G6" t="n">
-        <v>3.47</v>
+        <v>3.18</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>288.15</v>
+        <v>173.8</v>
       </c>
       <c r="D7" t="n">
-        <v>278.73</v>
+        <v>164.95</v>
       </c>
       <c r="E7" t="n">
-        <v>279.57</v>
+        <v>162.5</v>
       </c>
       <c r="F7" t="n">
-        <v>276.61</v>
+        <v>167.56</v>
       </c>
       <c r="G7" t="n">
-        <v>4.17</v>
+        <v>3.73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>514.35</v>
+        <v>2570</v>
       </c>
       <c r="D8" t="n">
-        <v>499.84</v>
+        <v>2423.94</v>
       </c>
       <c r="E8" t="n">
-        <v>486.48</v>
+        <v>2450.21</v>
       </c>
       <c r="F8" t="n">
-        <v>493.64</v>
+        <v>2472.46</v>
       </c>
       <c r="G8" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>117.48</v>
+        <v>5674</v>
       </c>
       <c r="D9" t="n">
-        <v>111.47</v>
+        <v>5313.23</v>
       </c>
       <c r="E9" t="n">
-        <v>109.67</v>
+        <v>5093.23</v>
       </c>
       <c r="F9" t="n">
-        <v>112.72</v>
+        <v>5446.45</v>
       </c>
       <c r="G9" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2174.5</v>
+        <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v>2073.12</v>
+        <v>112.03</v>
       </c>
       <c r="E10" t="n">
-        <v>2021.7</v>
+        <v>109.95</v>
       </c>
       <c r="F10" t="n">
-        <v>2067.43</v>
+        <v>112.71</v>
       </c>
       <c r="G10" t="n">
-        <v>5.18</v>
+        <v>4.69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2012</v>
+        <v>519</v>
       </c>
       <c r="D11" t="n">
-        <v>1958.54</v>
+        <v>501.43</v>
       </c>
       <c r="E11" t="n">
-        <v>1889.41</v>
+        <v>487.83</v>
       </c>
       <c r="F11" t="n">
-        <v>1906.41</v>
+        <v>493.53</v>
       </c>
       <c r="G11" t="n">
-        <v>5.54</v>
+        <v>5.16</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5709.5</v>
+        <v>291.4</v>
       </c>
       <c r="D12" t="n">
-        <v>5310.59</v>
+        <v>279.32</v>
       </c>
       <c r="E12" t="n">
-        <v>5127.98</v>
+        <v>280.39</v>
       </c>
       <c r="F12" t="n">
-        <v>5296.88</v>
+        <v>276.71</v>
       </c>
       <c r="G12" t="n">
-        <v>7.79</v>
+        <v>5.31</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1272</v>
+        <v>2016</v>
       </c>
       <c r="D13" t="n">
-        <v>1197.57</v>
+        <v>1962.57</v>
       </c>
       <c r="E13" t="n">
-        <v>1160.14</v>
+        <v>1896.85</v>
       </c>
       <c r="F13" t="n">
-        <v>1171.45</v>
+        <v>1906.09</v>
       </c>
       <c r="G13" t="n">
-        <v>8.58</v>
+        <v>5.77</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>386.55</v>
+        <v>11368</v>
       </c>
       <c r="D14" t="n">
-        <v>363.55</v>
+        <v>11002.57</v>
       </c>
       <c r="E14" t="n">
-        <v>361.51</v>
+        <v>10793.21</v>
       </c>
       <c r="F14" t="n">
-        <v>352.59</v>
+        <v>10654.93</v>
       </c>
       <c r="G14" t="n">
-        <v>9.630000000000001</v>
+        <v>6.69</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1038.95</v>
+        <v>480.9</v>
       </c>
       <c r="D15" t="n">
-        <v>994.21</v>
+        <v>452.22</v>
       </c>
       <c r="E15" t="n">
-        <v>992.33</v>
+        <v>438.96</v>
       </c>
       <c r="F15" t="n">
-        <v>947.14</v>
+        <v>450.14</v>
       </c>
       <c r="G15" t="n">
-        <v>9.69</v>
+        <v>6.83</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2121.8</v>
+        <v>735.85</v>
       </c>
       <c r="D16" t="n">
-        <v>1908.56</v>
+        <v>732.6900000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>1870.3</v>
+        <v>726.17</v>
       </c>
       <c r="F16" t="n">
-        <v>1921.55</v>
+        <v>685.74</v>
       </c>
       <c r="G16" t="n">
-        <v>10.42</v>
+        <v>7.31</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>942.1</v>
+        <v>676.15</v>
       </c>
       <c r="D17" t="n">
-        <v>910.6900000000001</v>
+        <v>657.7</v>
       </c>
       <c r="E17" t="n">
-        <v>920.13</v>
+        <v>644.6</v>
       </c>
       <c r="F17" t="n">
-        <v>845.65</v>
+        <v>629.26</v>
       </c>
       <c r="G17" t="n">
-        <v>11.41</v>
+        <v>7.45</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>186.9</v>
+        <v>1260.5</v>
       </c>
       <c r="D18" t="n">
-        <v>173.6</v>
+        <v>1201.94</v>
       </c>
       <c r="E18" t="n">
-        <v>171.07</v>
+        <v>1163.47</v>
       </c>
       <c r="F18" t="n">
-        <v>165.64</v>
+        <v>1171.65</v>
       </c>
       <c r="G18" t="n">
-        <v>12.83</v>
+        <v>7.58</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>320</v>
+        <v>2227</v>
       </c>
       <c r="D19" t="n">
-        <v>302.58</v>
+        <v>2083.76</v>
       </c>
       <c r="E19" t="n">
-        <v>285.33</v>
+        <v>2027.8</v>
       </c>
       <c r="F19" t="n">
-        <v>272.8</v>
+        <v>2066.54</v>
       </c>
       <c r="G19" t="n">
-        <v>17.3</v>
+        <v>7.76</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14462</v>
+        <v>5740.5</v>
       </c>
       <c r="D20" t="n">
-        <v>13975.37</v>
+        <v>5305.84</v>
       </c>
       <c r="E20" t="n">
-        <v>13266.18</v>
+        <v>5124.42</v>
       </c>
       <c r="F20" t="n">
-        <v>12204.04</v>
+        <v>5298.85</v>
       </c>
       <c r="G20" t="n">
-        <v>18.5</v>
+        <v>8.33</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1378.4</v>
+        <v>1029.85</v>
       </c>
       <c r="D21" t="n">
-        <v>1244.1</v>
+        <v>996.03</v>
       </c>
       <c r="E21" t="n">
-        <v>1142.96</v>
+        <v>991.79</v>
       </c>
       <c r="F21" t="n">
-        <v>1149.22</v>
+        <v>948.03</v>
       </c>
       <c r="G21" t="n">
-        <v>19.94</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,30 +1211,326 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1142.16</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1127.71</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1102.7</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>385.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>364.98</v>
+      </c>
+      <c r="E23" t="n">
+        <v>361.54</v>
+      </c>
+      <c r="F23" t="n">
+        <v>353.37</v>
+      </c>
+      <c r="G23" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>184.68</v>
+      </c>
+      <c r="D24" t="n">
+        <v>176.27</v>
+      </c>
+      <c r="E24" t="n">
+        <v>172.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>166.36</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2140</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1919.23</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1877.12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1923.32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11.27</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>973.4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>912.8099999999999</v>
+      </c>
+      <c r="E26" t="n">
+        <v>922.77</v>
+      </c>
+      <c r="F26" t="n">
+        <v>845.67</v>
+      </c>
+      <c r="G26" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1360.9</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1250.94</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1150.59</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1149.16</v>
+      </c>
+      <c r="G27" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="D28" t="n">
+        <v>303.87</v>
+      </c>
+      <c r="E28" t="n">
+        <v>286.97</v>
+      </c>
+      <c r="F28" t="n">
+        <v>272.79</v>
+      </c>
+      <c r="G28" t="n">
+        <v>20.22</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14039.23</v>
+      </c>
+      <c r="E29" t="n">
+        <v>13333.44</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12200.82</v>
+      </c>
+      <c r="G29" t="n">
+        <v>21.71</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>1813.1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>1641.69</v>
-      </c>
-      <c r="E22" t="n">
-        <v>1561.52</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1509.99</v>
-      </c>
-      <c r="G22" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="C30" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1655.25</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1570.86</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1510.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>24.59</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -663,16 +663,16 @@
         <v>173.8</v>
       </c>
       <c r="D7" t="n">
-        <v>164.95</v>
+        <v>165.04</v>
       </c>
       <c r="E7" t="n">
-        <v>162.5</v>
+        <v>162.22</v>
       </c>
       <c r="F7" t="n">
-        <v>167.56</v>
+        <v>167.48</v>
       </c>
       <c r="G7" t="n">
-        <v>3.73</v>
+        <v>3.78</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>519</v>
+        <v>291.4</v>
       </c>
       <c r="D11" t="n">
-        <v>501.43</v>
+        <v>279.39</v>
       </c>
       <c r="E11" t="n">
-        <v>487.83</v>
+        <v>280.09</v>
       </c>
       <c r="F11" t="n">
-        <v>493.53</v>
+        <v>276.71</v>
       </c>
       <c r="G11" t="n">
-        <v>5.16</v>
+        <v>5.31</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>291.4</v>
+        <v>480.9</v>
       </c>
       <c r="D12" t="n">
-        <v>279.32</v>
+        <v>452.22</v>
       </c>
       <c r="E12" t="n">
-        <v>280.39</v>
+        <v>438.96</v>
       </c>
       <c r="F12" t="n">
-        <v>276.71</v>
+        <v>450.14</v>
       </c>
       <c r="G12" t="n">
-        <v>5.31</v>
+        <v>6.83</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2016</v>
+        <v>676.15</v>
       </c>
       <c r="D13" t="n">
-        <v>1962.57</v>
+        <v>656.83</v>
       </c>
       <c r="E13" t="n">
-        <v>1896.85</v>
+        <v>640.77</v>
       </c>
       <c r="F13" t="n">
-        <v>1906.09</v>
+        <v>630.3200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>5.77</v>
+        <v>7.27</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11368</v>
+        <v>735.85</v>
       </c>
       <c r="D14" t="n">
-        <v>11002.57</v>
+        <v>733.08</v>
       </c>
       <c r="E14" t="n">
-        <v>10793.21</v>
+        <v>724.8200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10654.93</v>
+        <v>685.86</v>
       </c>
       <c r="G14" t="n">
-        <v>6.69</v>
+        <v>7.29</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>480.9</v>
+        <v>1592.1</v>
       </c>
       <c r="D15" t="n">
-        <v>452.22</v>
+        <v>1584.18</v>
       </c>
       <c r="E15" t="n">
-        <v>438.96</v>
+        <v>1510.92</v>
       </c>
       <c r="F15" t="n">
-        <v>450.14</v>
+        <v>1473.53</v>
       </c>
       <c r="G15" t="n">
-        <v>6.83</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>735.85</v>
+        <v>1029.85</v>
       </c>
       <c r="D16" t="n">
-        <v>732.6900000000001</v>
+        <v>996.03</v>
       </c>
       <c r="E16" t="n">
-        <v>726.17</v>
+        <v>991.79</v>
       </c>
       <c r="F16" t="n">
-        <v>685.74</v>
+        <v>948.03</v>
       </c>
       <c r="G16" t="n">
-        <v>7.31</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>676.15</v>
+        <v>1203</v>
       </c>
       <c r="D17" t="n">
-        <v>657.7</v>
+        <v>1142.16</v>
       </c>
       <c r="E17" t="n">
-        <v>644.6</v>
+        <v>1127.71</v>
       </c>
       <c r="F17" t="n">
-        <v>629.26</v>
+        <v>1102.7</v>
       </c>
       <c r="G17" t="n">
-        <v>7.45</v>
+        <v>9.1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1260.5</v>
+        <v>385.6</v>
       </c>
       <c r="D18" t="n">
-        <v>1201.94</v>
+        <v>364.98</v>
       </c>
       <c r="E18" t="n">
-        <v>1163.47</v>
+        <v>361.54</v>
       </c>
       <c r="F18" t="n">
-        <v>1171.65</v>
+        <v>353.37</v>
       </c>
       <c r="G18" t="n">
-        <v>7.58</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2227</v>
+        <v>184.68</v>
       </c>
       <c r="D19" t="n">
-        <v>2083.76</v>
+        <v>174.39</v>
       </c>
       <c r="E19" t="n">
-        <v>2027.8</v>
+        <v>171.56</v>
       </c>
       <c r="F19" t="n">
-        <v>2066.54</v>
+        <v>165.86</v>
       </c>
       <c r="G19" t="n">
-        <v>7.76</v>
+        <v>11.35</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5740.5</v>
+        <v>973.4</v>
       </c>
       <c r="D20" t="n">
-        <v>5305.84</v>
+        <v>912.8099999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>5124.42</v>
+        <v>922.77</v>
       </c>
       <c r="F20" t="n">
-        <v>5298.85</v>
+        <v>845.67</v>
       </c>
       <c r="G20" t="n">
-        <v>8.33</v>
+        <v>15.1</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1029.85</v>
+        <v>327.95</v>
       </c>
       <c r="D21" t="n">
-        <v>996.03</v>
+        <v>303.87</v>
       </c>
       <c r="E21" t="n">
-        <v>991.79</v>
+        <v>286.97</v>
       </c>
       <c r="F21" t="n">
-        <v>948.03</v>
+        <v>272.79</v>
       </c>
       <c r="G21" t="n">
-        <v>8.630000000000001</v>
+        <v>20.22</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1203</v>
+        <v>14850</v>
       </c>
       <c r="D22" t="n">
-        <v>1142.16</v>
+        <v>14039.23</v>
       </c>
       <c r="E22" t="n">
-        <v>1127.71</v>
+        <v>13333.44</v>
       </c>
       <c r="F22" t="n">
-        <v>1102.7</v>
+        <v>12200.82</v>
       </c>
       <c r="G22" t="n">
-        <v>9.1</v>
+        <v>21.71</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,28 +1243,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>21-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>385.6</v>
+        <v>1882</v>
       </c>
       <c r="D23" t="n">
-        <v>364.98</v>
+        <v>1655.25</v>
       </c>
       <c r="E23" t="n">
-        <v>361.54</v>
+        <v>1570.86</v>
       </c>
       <c r="F23" t="n">
-        <v>353.37</v>
+        <v>1510.5</v>
       </c>
       <c r="G23" t="n">
-        <v>9.119999999999999</v>
+        <v>24.59</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1272,265 +1272,6 @@
         </is>
       </c>
       <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>184.68</v>
-      </c>
-      <c r="D24" t="n">
-        <v>176.27</v>
-      </c>
-      <c r="E24" t="n">
-        <v>172.4</v>
-      </c>
-      <c r="F24" t="n">
-        <v>166.36</v>
-      </c>
-      <c r="G24" t="n">
-        <v>11.01</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2140</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1919.23</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1877.12</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1923.32</v>
-      </c>
-      <c r="G25" t="n">
-        <v>11.27</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>973.4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>912.8099999999999</v>
-      </c>
-      <c r="E26" t="n">
-        <v>922.77</v>
-      </c>
-      <c r="F26" t="n">
-        <v>845.67</v>
-      </c>
-      <c r="G26" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1360.9</v>
-      </c>
-      <c r="D27" t="n">
-        <v>1250.94</v>
-      </c>
-      <c r="E27" t="n">
-        <v>1150.59</v>
-      </c>
-      <c r="F27" t="n">
-        <v>1149.16</v>
-      </c>
-      <c r="G27" t="n">
-        <v>18.43</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>327.95</v>
-      </c>
-      <c r="D28" t="n">
-        <v>303.87</v>
-      </c>
-      <c r="E28" t="n">
-        <v>286.97</v>
-      </c>
-      <c r="F28" t="n">
-        <v>272.79</v>
-      </c>
-      <c r="G28" t="n">
-        <v>20.22</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>14850</v>
-      </c>
-      <c r="D29" t="n">
-        <v>14039.23</v>
-      </c>
-      <c r="E29" t="n">
-        <v>13333.44</v>
-      </c>
-      <c r="F29" t="n">
-        <v>12200.82</v>
-      </c>
-      <c r="G29" t="n">
-        <v>21.71</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>20-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1882</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1655.25</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1570.86</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1510.5</v>
-      </c>
-      <c r="G30" t="n">
-        <v>24.59</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1941.7</v>
+        <v>1946</v>
       </c>
       <c r="D2" t="n">
-        <v>1929.33</v>
+        <v>1933.28</v>
       </c>
       <c r="E2" t="n">
-        <v>1894.99</v>
+        <v>1904.46</v>
       </c>
       <c r="F2" t="n">
-        <v>1924.76</v>
+        <v>1922.88</v>
       </c>
       <c r="G2" t="n">
-        <v>0.88</v>
+        <v>1.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1048</v>
+        <v>1048.7</v>
       </c>
       <c r="D3" t="n">
-        <v>1045.12</v>
+        <v>1045.64</v>
       </c>
       <c r="E3" t="n">
-        <v>1039.94</v>
+        <v>1041.06</v>
       </c>
       <c r="F3" t="n">
-        <v>1023.78</v>
+        <v>1024.79</v>
       </c>
       <c r="G3" t="n">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>871</v>
+        <v>3412.2</v>
       </c>
       <c r="D4" t="n">
-        <v>853.28</v>
+        <v>3316.9</v>
       </c>
       <c r="E4" t="n">
-        <v>844.45</v>
+        <v>3230.38</v>
       </c>
       <c r="F4" t="n">
-        <v>848.46</v>
+        <v>3322.78</v>
       </c>
       <c r="G4" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3424.8</v>
+        <v>173</v>
       </c>
       <c r="D5" t="n">
-        <v>3307.48</v>
+        <v>165.47</v>
       </c>
       <c r="E5" t="n">
-        <v>3222.36</v>
+        <v>162.91</v>
       </c>
       <c r="F5" t="n">
-        <v>3323.44</v>
+        <v>167.74</v>
       </c>
       <c r="G5" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4081</v>
+        <v>2552</v>
       </c>
       <c r="D6" t="n">
-        <v>3947.35</v>
+        <v>2427.61</v>
       </c>
       <c r="E6" t="n">
-        <v>4014.05</v>
+        <v>2453.12</v>
       </c>
       <c r="F6" t="n">
-        <v>3955.05</v>
+        <v>2469.93</v>
       </c>
       <c r="G6" t="n">
-        <v>3.18</v>
+        <v>3.32</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>173.8</v>
+        <v>876.9</v>
       </c>
       <c r="D7" t="n">
-        <v>165.04</v>
+        <v>854.9299999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>162.22</v>
+        <v>845.3</v>
       </c>
       <c r="F7" t="n">
-        <v>167.48</v>
+        <v>848.4400000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2570</v>
+        <v>116.55</v>
       </c>
       <c r="D8" t="n">
-        <v>2423.94</v>
+        <v>112.65</v>
       </c>
       <c r="E8" t="n">
-        <v>2450.21</v>
+        <v>110.29</v>
       </c>
       <c r="F8" t="n">
-        <v>2472.46</v>
+        <v>112.65</v>
       </c>
       <c r="G8" t="n">
-        <v>3.95</v>
+        <v>3.46</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5674</v>
+        <v>4093</v>
       </c>
       <c r="D9" t="n">
-        <v>5313.23</v>
+        <v>3949.97</v>
       </c>
       <c r="E9" t="n">
-        <v>5093.23</v>
+        <v>4014.03</v>
       </c>
       <c r="F9" t="n">
-        <v>5446.45</v>
+        <v>3955.46</v>
       </c>
       <c r="G9" t="n">
-        <v>4.18</v>
+        <v>3.48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>118</v>
+        <v>5667.5</v>
       </c>
       <c r="D10" t="n">
-        <v>112.03</v>
+        <v>5379.83</v>
       </c>
       <c r="E10" t="n">
-        <v>109.95</v>
+        <v>5131.33</v>
       </c>
       <c r="F10" t="n">
-        <v>112.71</v>
+        <v>5436.28</v>
       </c>
       <c r="G10" t="n">
-        <v>4.69</v>
+        <v>4.25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>291.4</v>
+        <v>515.05</v>
       </c>
       <c r="D11" t="n">
-        <v>279.39</v>
+        <v>506.45</v>
       </c>
       <c r="E11" t="n">
-        <v>280.09</v>
+        <v>491.57</v>
       </c>
       <c r="F11" t="n">
-        <v>276.71</v>
+        <v>493.05</v>
       </c>
       <c r="G11" t="n">
-        <v>5.31</v>
+        <v>4.46</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>480.9</v>
+        <v>475</v>
       </c>
       <c r="D12" t="n">
-        <v>452.22</v>
+        <v>454.83</v>
       </c>
       <c r="E12" t="n">
-        <v>438.96</v>
+        <v>440.54</v>
       </c>
       <c r="F12" t="n">
-        <v>450.14</v>
+        <v>450.53</v>
       </c>
       <c r="G12" t="n">
-        <v>6.83</v>
+        <v>5.43</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>676.15</v>
+        <v>293</v>
       </c>
       <c r="D13" t="n">
-        <v>656.83</v>
+        <v>279.79</v>
       </c>
       <c r="E13" t="n">
-        <v>640.77</v>
+        <v>280.76</v>
       </c>
       <c r="F13" t="n">
-        <v>630.3200000000001</v>
+        <v>276.82</v>
       </c>
       <c r="G13" t="n">
-        <v>7.27</v>
+        <v>5.84</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>735.85</v>
+        <v>11320</v>
       </c>
       <c r="D14" t="n">
-        <v>733.08</v>
+        <v>11048.93</v>
       </c>
       <c r="E14" t="n">
-        <v>724.8200000000001</v>
+        <v>10858.65</v>
       </c>
       <c r="F14" t="n">
-        <v>685.86</v>
+        <v>10639.37</v>
       </c>
       <c r="G14" t="n">
-        <v>7.29</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1592.1</v>
+        <v>2032.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1584.18</v>
+        <v>1966.45</v>
       </c>
       <c r="E15" t="n">
-        <v>1510.92</v>
+        <v>1903.75</v>
       </c>
       <c r="F15" t="n">
-        <v>1473.53</v>
+        <v>1905.89</v>
       </c>
       <c r="G15" t="n">
-        <v>8.050000000000001</v>
+        <v>6.64</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1029.85</v>
+        <v>2218.8</v>
       </c>
       <c r="D16" t="n">
-        <v>996.03</v>
+        <v>2092.18</v>
       </c>
       <c r="E16" t="n">
-        <v>991.79</v>
+        <v>2032.75</v>
       </c>
       <c r="F16" t="n">
-        <v>948.03</v>
+        <v>2065.77</v>
       </c>
       <c r="G16" t="n">
-        <v>8.630000000000001</v>
+        <v>7.41</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1203</v>
+        <v>678.1</v>
       </c>
       <c r="D17" t="n">
-        <v>1142.16</v>
+        <v>657.73</v>
       </c>
       <c r="E17" t="n">
-        <v>1127.71</v>
+        <v>646.5700000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1102.7</v>
+        <v>628.83</v>
       </c>
       <c r="G17" t="n">
-        <v>9.1</v>
+        <v>7.84</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>385.6</v>
+        <v>1265</v>
       </c>
       <c r="D18" t="n">
-        <v>364.98</v>
+        <v>1205.2</v>
       </c>
       <c r="E18" t="n">
-        <v>361.54</v>
+        <v>1170.37</v>
       </c>
       <c r="F18" t="n">
-        <v>353.37</v>
+        <v>1170.69</v>
       </c>
       <c r="G18" t="n">
-        <v>9.119999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>184.68</v>
+        <v>5735</v>
       </c>
       <c r="D19" t="n">
-        <v>174.39</v>
+        <v>5369.61</v>
       </c>
       <c r="E19" t="n">
-        <v>171.56</v>
+        <v>5164.36</v>
       </c>
       <c r="F19" t="n">
-        <v>165.86</v>
+        <v>5301.82</v>
       </c>
       <c r="G19" t="n">
-        <v>11.35</v>
+        <v>8.17</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>973.4</v>
+        <v>1631</v>
       </c>
       <c r="D20" t="n">
-        <v>912.8099999999999</v>
+        <v>1627.87</v>
       </c>
       <c r="E20" t="n">
-        <v>922.77</v>
+        <v>1610.11</v>
       </c>
       <c r="F20" t="n">
-        <v>845.67</v>
+        <v>1504.15</v>
       </c>
       <c r="G20" t="n">
-        <v>15.1</v>
+        <v>8.43</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>327.95</v>
+        <v>1199</v>
       </c>
       <c r="D21" t="n">
-        <v>303.87</v>
+        <v>1145.73</v>
       </c>
       <c r="E21" t="n">
-        <v>286.97</v>
+        <v>1132.01</v>
       </c>
       <c r="F21" t="n">
-        <v>272.79</v>
+        <v>1103.46</v>
       </c>
       <c r="G21" t="n">
-        <v>20.22</v>
+        <v>8.66</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>14850</v>
+        <v>1034</v>
       </c>
       <c r="D22" t="n">
-        <v>14039.23</v>
+        <v>997.67</v>
       </c>
       <c r="E22" t="n">
-        <v>13333.44</v>
+        <v>987.11</v>
       </c>
       <c r="F22" t="n">
-        <v>12200.82</v>
+        <v>950.71</v>
       </c>
       <c r="G22" t="n">
-        <v>21.71</v>
+        <v>8.76</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,30 +1248,400 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1795.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1636.63</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1628.54</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1649.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="D24" t="n">
+        <v>176.91</v>
+      </c>
+      <c r="E24" t="n">
+        <v>172.77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>166.54</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>394.45</v>
+      </c>
+      <c r="D25" t="n">
+        <v>366.96</v>
+      </c>
+      <c r="E25" t="n">
+        <v>361.34</v>
+      </c>
+      <c r="F25" t="n">
+        <v>355.52</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2139</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1930.73</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1885.76</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1925.37</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>990</v>
+      </c>
+      <c r="D27" t="n">
+        <v>914.1900000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>927.64</v>
+      </c>
+      <c r="F27" t="n">
+        <v>845.59</v>
+      </c>
+      <c r="G27" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1350.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1257.21</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1167.86</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1147.73</v>
+      </c>
+      <c r="G28" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>328</v>
+      </c>
+      <c r="D29" t="n">
+        <v>304.88</v>
+      </c>
+      <c r="E29" t="n">
+        <v>290.59</v>
+      </c>
+      <c r="F29" t="n">
+        <v>272.52</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D30" t="n">
+        <v>14100.37</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13449.74</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12190.78</v>
+      </c>
+      <c r="G30" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3185</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2818.39</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2822.63</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2575.29</v>
+      </c>
+      <c r="G31" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>COFORGE</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>1882</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1655.25</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1570.86</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1510.5</v>
-      </c>
-      <c r="G23" t="n">
-        <v>24.59</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="C32" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1680.64</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1593.24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1508.38</v>
+      </c>
+      <c r="G32" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>21-08-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>11724</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11530.63</v>
+      </c>
+      <c r="E33" t="n">
+        <v>11119.77</v>
+      </c>
+      <c r="F33" t="n">
+        <v>8660.620000000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>35.37</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>876.9</v>
+        <v>116.55</v>
       </c>
       <c r="D7" t="n">
-        <v>854.9299999999999</v>
+        <v>112.65</v>
       </c>
       <c r="E7" t="n">
-        <v>845.3</v>
+        <v>110.29</v>
       </c>
       <c r="F7" t="n">
-        <v>848.4400000000001</v>
+        <v>112.65</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>116.55</v>
+        <v>4093</v>
       </c>
       <c r="D8" t="n">
-        <v>112.65</v>
+        <v>3949.97</v>
       </c>
       <c r="E8" t="n">
-        <v>110.29</v>
+        <v>4014.03</v>
       </c>
       <c r="F8" t="n">
-        <v>112.65</v>
+        <v>3955.46</v>
       </c>
       <c r="G8" t="n">
-        <v>3.46</v>
+        <v>3.48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4093</v>
+        <v>5667.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3949.97</v>
+        <v>5379.83</v>
       </c>
       <c r="E9" t="n">
-        <v>4014.03</v>
+        <v>5131.33</v>
       </c>
       <c r="F9" t="n">
-        <v>3955.46</v>
+        <v>5436.28</v>
       </c>
       <c r="G9" t="n">
-        <v>3.48</v>
+        <v>4.25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5667.5</v>
+        <v>515.05</v>
       </c>
       <c r="D10" t="n">
-        <v>5379.83</v>
+        <v>506.45</v>
       </c>
       <c r="E10" t="n">
-        <v>5131.33</v>
+        <v>491.57</v>
       </c>
       <c r="F10" t="n">
-        <v>5436.28</v>
+        <v>493.05</v>
       </c>
       <c r="G10" t="n">
-        <v>4.25</v>
+        <v>4.46</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>515.05</v>
+        <v>475</v>
       </c>
       <c r="D11" t="n">
-        <v>506.45</v>
+        <v>454.83</v>
       </c>
       <c r="E11" t="n">
-        <v>491.57</v>
+        <v>440.54</v>
       </c>
       <c r="F11" t="n">
-        <v>493.05</v>
+        <v>450.53</v>
       </c>
       <c r="G11" t="n">
-        <v>4.46</v>
+        <v>5.43</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>475</v>
+        <v>2032.5</v>
       </c>
       <c r="D12" t="n">
-        <v>454.83</v>
+        <v>1966.45</v>
       </c>
       <c r="E12" t="n">
-        <v>440.54</v>
+        <v>1903.75</v>
       </c>
       <c r="F12" t="n">
-        <v>450.53</v>
+        <v>1905.89</v>
       </c>
       <c r="G12" t="n">
-        <v>5.43</v>
+        <v>6.64</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>293</v>
+        <v>678.1</v>
       </c>
       <c r="D13" t="n">
-        <v>279.79</v>
+        <v>657.73</v>
       </c>
       <c r="E13" t="n">
-        <v>280.76</v>
+        <v>646.5700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>276.82</v>
+        <v>628.83</v>
       </c>
       <c r="G13" t="n">
-        <v>5.84</v>
+        <v>7.84</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11320</v>
+        <v>1631</v>
       </c>
       <c r="D14" t="n">
-        <v>11048.93</v>
+        <v>1627.87</v>
       </c>
       <c r="E14" t="n">
-        <v>10858.65</v>
+        <v>1610.11</v>
       </c>
       <c r="F14" t="n">
-        <v>10639.37</v>
+        <v>1504.15</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4</v>
+        <v>8.43</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2032.5</v>
+        <v>183.45</v>
       </c>
       <c r="D15" t="n">
-        <v>1966.45</v>
+        <v>176.91</v>
       </c>
       <c r="E15" t="n">
-        <v>1903.75</v>
+        <v>172.77</v>
       </c>
       <c r="F15" t="n">
-        <v>1905.89</v>
+        <v>166.54</v>
       </c>
       <c r="G15" t="n">
-        <v>6.64</v>
+        <v>10.16</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2218.8</v>
+        <v>394.45</v>
       </c>
       <c r="D16" t="n">
-        <v>2092.18</v>
+        <v>366.96</v>
       </c>
       <c r="E16" t="n">
-        <v>2032.75</v>
+        <v>361.34</v>
       </c>
       <c r="F16" t="n">
-        <v>2065.77</v>
+        <v>355.52</v>
       </c>
       <c r="G16" t="n">
-        <v>7.41</v>
+        <v>10.95</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>678.1</v>
+        <v>2139</v>
       </c>
       <c r="D17" t="n">
-        <v>657.73</v>
+        <v>1930.73</v>
       </c>
       <c r="E17" t="n">
-        <v>646.5700000000001</v>
+        <v>1885.76</v>
       </c>
       <c r="F17" t="n">
-        <v>628.83</v>
+        <v>1925.37</v>
       </c>
       <c r="G17" t="n">
-        <v>7.84</v>
+        <v>11.1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1265</v>
+        <v>328</v>
       </c>
       <c r="D18" t="n">
-        <v>1205.2</v>
+        <v>304.88</v>
       </c>
       <c r="E18" t="n">
-        <v>1170.37</v>
+        <v>290.59</v>
       </c>
       <c r="F18" t="n">
-        <v>1170.69</v>
+        <v>272.52</v>
       </c>
       <c r="G18" t="n">
-        <v>8.06</v>
+        <v>20.36</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5735</v>
+        <v>14850</v>
       </c>
       <c r="D19" t="n">
-        <v>5369.61</v>
+        <v>14100.37</v>
       </c>
       <c r="E19" t="n">
-        <v>5164.36</v>
+        <v>13449.74</v>
       </c>
       <c r="F19" t="n">
-        <v>5301.82</v>
+        <v>12190.78</v>
       </c>
       <c r="G19" t="n">
-        <v>8.17</v>
+        <v>21.81</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1631</v>
+        <v>3185</v>
       </c>
       <c r="D20" t="n">
-        <v>1627.87</v>
+        <v>2818.39</v>
       </c>
       <c r="E20" t="n">
-        <v>1610.11</v>
+        <v>2822.63</v>
       </c>
       <c r="F20" t="n">
-        <v>1504.15</v>
+        <v>2575.29</v>
       </c>
       <c r="G20" t="n">
-        <v>8.43</v>
+        <v>23.68</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1199</v>
+        <v>1891.7</v>
       </c>
       <c r="D21" t="n">
-        <v>1145.73</v>
+        <v>1680.64</v>
       </c>
       <c r="E21" t="n">
-        <v>1132.01</v>
+        <v>1593.24</v>
       </c>
       <c r="F21" t="n">
-        <v>1103.46</v>
+        <v>1508.38</v>
       </c>
       <c r="G21" t="n">
-        <v>8.66</v>
+        <v>25.41</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21-08-2026</t>
+          <t>22-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1034</v>
+        <v>11724</v>
       </c>
       <c r="D22" t="n">
-        <v>997.67</v>
+        <v>11530.63</v>
       </c>
       <c r="E22" t="n">
-        <v>987.11</v>
+        <v>11119.77</v>
       </c>
       <c r="F22" t="n">
-        <v>950.71</v>
+        <v>8660.620000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>8.76</v>
+        <v>35.37</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1235,413 +1235,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1795.2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1636.63</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1628.54</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1649.76</v>
-      </c>
-      <c r="G23" t="n">
-        <v>8.82</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>183.45</v>
-      </c>
-      <c r="D24" t="n">
-        <v>176.91</v>
-      </c>
-      <c r="E24" t="n">
-        <v>172.77</v>
-      </c>
-      <c r="F24" t="n">
-        <v>166.54</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>394.45</v>
-      </c>
-      <c r="D25" t="n">
-        <v>366.96</v>
-      </c>
-      <c r="E25" t="n">
-        <v>361.34</v>
-      </c>
-      <c r="F25" t="n">
-        <v>355.52</v>
-      </c>
-      <c r="G25" t="n">
-        <v>10.95</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>2139</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1930.73</v>
-      </c>
-      <c r="E26" t="n">
-        <v>1885.76</v>
-      </c>
-      <c r="F26" t="n">
-        <v>1925.37</v>
-      </c>
-      <c r="G26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>990</v>
-      </c>
-      <c r="D27" t="n">
-        <v>914.1900000000001</v>
-      </c>
-      <c r="E27" t="n">
-        <v>927.64</v>
-      </c>
-      <c r="F27" t="n">
-        <v>845.59</v>
-      </c>
-      <c r="G27" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1350.1</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1257.21</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1167.86</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1147.73</v>
-      </c>
-      <c r="G28" t="n">
-        <v>17.63</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>328</v>
-      </c>
-      <c r="D29" t="n">
-        <v>304.88</v>
-      </c>
-      <c r="E29" t="n">
-        <v>290.59</v>
-      </c>
-      <c r="F29" t="n">
-        <v>272.52</v>
-      </c>
-      <c r="G29" t="n">
-        <v>20.36</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>14850</v>
-      </c>
-      <c r="D30" t="n">
-        <v>14100.37</v>
-      </c>
-      <c r="E30" t="n">
-        <v>13449.74</v>
-      </c>
-      <c r="F30" t="n">
-        <v>12190.78</v>
-      </c>
-      <c r="G30" t="n">
-        <v>21.81</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>3185</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2818.39</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2822.63</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2575.29</v>
-      </c>
-      <c r="G31" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1891.7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1680.64</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1593.24</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1508.38</v>
-      </c>
-      <c r="G32" t="n">
-        <v>25.41</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>21-08-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>11724</v>
-      </c>
-      <c r="D33" t="n">
-        <v>11530.63</v>
-      </c>
-      <c r="E33" t="n">
-        <v>11119.77</v>
-      </c>
-      <c r="F33" t="n">
-        <v>8660.620000000001</v>
-      </c>
-      <c r="G33" t="n">
-        <v>35.37</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>116.55</v>
+        <v>876.9</v>
       </c>
       <c r="D7" t="n">
-        <v>112.65</v>
+        <v>854.9299999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>110.29</v>
+        <v>845.3</v>
       </c>
       <c r="F7" t="n">
-        <v>112.65</v>
+        <v>848.4400000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4093</v>
+        <v>116.55</v>
       </c>
       <c r="D8" t="n">
-        <v>3949.97</v>
+        <v>112.65</v>
       </c>
       <c r="E8" t="n">
-        <v>4014.03</v>
+        <v>110.29</v>
       </c>
       <c r="F8" t="n">
-        <v>3955.46</v>
+        <v>112.65</v>
       </c>
       <c r="G8" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5667.5</v>
+        <v>4093</v>
       </c>
       <c r="D9" t="n">
-        <v>5379.83</v>
+        <v>3949.97</v>
       </c>
       <c r="E9" t="n">
-        <v>5131.33</v>
+        <v>4014.03</v>
       </c>
       <c r="F9" t="n">
-        <v>5436.28</v>
+        <v>3955.46</v>
       </c>
       <c r="G9" t="n">
-        <v>4.25</v>
+        <v>3.48</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>515.05</v>
+        <v>5667.5</v>
       </c>
       <c r="D10" t="n">
-        <v>506.45</v>
+        <v>5379.83</v>
       </c>
       <c r="E10" t="n">
-        <v>491.57</v>
+        <v>5131.33</v>
       </c>
       <c r="F10" t="n">
-        <v>493.05</v>
+        <v>5436.28</v>
       </c>
       <c r="G10" t="n">
-        <v>4.46</v>
+        <v>4.25</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>475</v>
+        <v>515.05</v>
       </c>
       <c r="D11" t="n">
-        <v>454.83</v>
+        <v>506.45</v>
       </c>
       <c r="E11" t="n">
-        <v>440.54</v>
+        <v>491.57</v>
       </c>
       <c r="F11" t="n">
-        <v>450.53</v>
+        <v>493.05</v>
       </c>
       <c r="G11" t="n">
-        <v>5.43</v>
+        <v>4.46</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2032.5</v>
+        <v>475</v>
       </c>
       <c r="D12" t="n">
-        <v>1966.45</v>
+        <v>454.83</v>
       </c>
       <c r="E12" t="n">
-        <v>1903.75</v>
+        <v>440.54</v>
       </c>
       <c r="F12" t="n">
-        <v>1905.89</v>
+        <v>450.53</v>
       </c>
       <c r="G12" t="n">
-        <v>6.64</v>
+        <v>5.43</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>678.1</v>
+        <v>293</v>
       </c>
       <c r="D13" t="n">
-        <v>657.73</v>
+        <v>279.79</v>
       </c>
       <c r="E13" t="n">
-        <v>646.5700000000001</v>
+        <v>280.76</v>
       </c>
       <c r="F13" t="n">
-        <v>628.83</v>
+        <v>276.82</v>
       </c>
       <c r="G13" t="n">
-        <v>7.84</v>
+        <v>5.84</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1631</v>
+        <v>11320</v>
       </c>
       <c r="D14" t="n">
-        <v>1627.87</v>
+        <v>11048.93</v>
       </c>
       <c r="E14" t="n">
-        <v>1610.11</v>
+        <v>10858.65</v>
       </c>
       <c r="F14" t="n">
-        <v>1504.15</v>
+        <v>10639.37</v>
       </c>
       <c r="G14" t="n">
-        <v>8.43</v>
+        <v>6.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>183.45</v>
+        <v>2032.5</v>
       </c>
       <c r="D15" t="n">
-        <v>176.91</v>
+        <v>1966.45</v>
       </c>
       <c r="E15" t="n">
-        <v>172.77</v>
+        <v>1903.75</v>
       </c>
       <c r="F15" t="n">
-        <v>166.54</v>
+        <v>1905.89</v>
       </c>
       <c r="G15" t="n">
-        <v>10.16</v>
+        <v>6.64</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>394.45</v>
+        <v>2218.8</v>
       </c>
       <c r="D16" t="n">
-        <v>366.96</v>
+        <v>2092.18</v>
       </c>
       <c r="E16" t="n">
-        <v>361.34</v>
+        <v>2032.75</v>
       </c>
       <c r="F16" t="n">
-        <v>355.52</v>
+        <v>2065.77</v>
       </c>
       <c r="G16" t="n">
-        <v>10.95</v>
+        <v>7.41</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2139</v>
+        <v>678.1</v>
       </c>
       <c r="D17" t="n">
-        <v>1930.73</v>
+        <v>657.73</v>
       </c>
       <c r="E17" t="n">
-        <v>1885.76</v>
+        <v>646.5700000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1925.37</v>
+        <v>628.83</v>
       </c>
       <c r="G17" t="n">
-        <v>11.1</v>
+        <v>7.84</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>328</v>
+        <v>1265</v>
       </c>
       <c r="D18" t="n">
-        <v>304.88</v>
+        <v>1205.2</v>
       </c>
       <c r="E18" t="n">
-        <v>290.59</v>
+        <v>1170.37</v>
       </c>
       <c r="F18" t="n">
-        <v>272.52</v>
+        <v>1170.69</v>
       </c>
       <c r="G18" t="n">
-        <v>20.36</v>
+        <v>8.06</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14850</v>
+        <v>5735</v>
       </c>
       <c r="D19" t="n">
-        <v>14100.37</v>
+        <v>5369.61</v>
       </c>
       <c r="E19" t="n">
-        <v>13449.74</v>
+        <v>5164.36</v>
       </c>
       <c r="F19" t="n">
-        <v>12190.78</v>
+        <v>5301.82</v>
       </c>
       <c r="G19" t="n">
-        <v>21.81</v>
+        <v>8.17</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3185</v>
+        <v>1631</v>
       </c>
       <c r="D20" t="n">
-        <v>2818.39</v>
+        <v>1627.87</v>
       </c>
       <c r="E20" t="n">
-        <v>2822.63</v>
+        <v>1610.11</v>
       </c>
       <c r="F20" t="n">
-        <v>2575.29</v>
+        <v>1504.15</v>
       </c>
       <c r="G20" t="n">
-        <v>23.68</v>
+        <v>8.43</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1891.7</v>
+        <v>1199</v>
       </c>
       <c r="D21" t="n">
-        <v>1680.64</v>
+        <v>1145.73</v>
       </c>
       <c r="E21" t="n">
-        <v>1593.24</v>
+        <v>1132.01</v>
       </c>
       <c r="F21" t="n">
-        <v>1508.38</v>
+        <v>1103.46</v>
       </c>
       <c r="G21" t="n">
-        <v>25.41</v>
+        <v>8.66</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,35 +1206,442 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>22-08-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D22" t="n">
+        <v>997.67</v>
+      </c>
+      <c r="E22" t="n">
+        <v>987.11</v>
+      </c>
+      <c r="F22" t="n">
+        <v>950.71</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1795.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1636.63</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1628.54</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1649.76</v>
+      </c>
+      <c r="G23" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>183.45</v>
+      </c>
+      <c r="D24" t="n">
+        <v>176.91</v>
+      </c>
+      <c r="E24" t="n">
+        <v>172.77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>166.54</v>
+      </c>
+      <c r="G24" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>393.45</v>
+      </c>
+      <c r="D25" t="n">
+        <v>366.03</v>
+      </c>
+      <c r="E25" t="n">
+        <v>360.42</v>
+      </c>
+      <c r="F25" t="n">
+        <v>354.61</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2139</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1930.73</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1885.76</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1925.37</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>990</v>
+      </c>
+      <c r="D27" t="n">
+        <v>914.1900000000001</v>
+      </c>
+      <c r="E27" t="n">
+        <v>927.64</v>
+      </c>
+      <c r="F27" t="n">
+        <v>845.59</v>
+      </c>
+      <c r="G27" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1350.1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1257.21</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1167.86</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1147.73</v>
+      </c>
+      <c r="G28" t="n">
+        <v>17.63</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>328</v>
+      </c>
+      <c r="D29" t="n">
+        <v>304.88</v>
+      </c>
+      <c r="E29" t="n">
+        <v>290.59</v>
+      </c>
+      <c r="F29" t="n">
+        <v>272.52</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D30" t="n">
+        <v>14100.37</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13449.74</v>
+      </c>
+      <c r="F30" t="n">
+        <v>12190.78</v>
+      </c>
+      <c r="G30" t="n">
+        <v>21.81</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3185</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2818.39</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2822.63</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2575.29</v>
+      </c>
+      <c r="G31" t="n">
+        <v>23.68</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1891.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1680.64</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1593.24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1508.38</v>
+      </c>
+      <c r="G32" t="n">
+        <v>25.41</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>OFSS</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C33" t="n">
         <v>11724</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D33" t="n">
         <v>11530.63</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E33" t="n">
         <v>11119.77</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F33" t="n">
         <v>8660.620000000001</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G33" t="n">
         <v>35.37</v>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1946</v>
+        <v>870.45</v>
       </c>
       <c r="D2" t="n">
-        <v>1933.28</v>
+        <v>855.86</v>
       </c>
       <c r="E2" t="n">
-        <v>1904.46</v>
+        <v>845.71</v>
       </c>
       <c r="F2" t="n">
-        <v>1922.88</v>
+        <v>848.5599999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>1.2</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1048.7</v>
+        <v>3414.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1045.64</v>
+        <v>3325.36</v>
       </c>
       <c r="E3" t="n">
-        <v>1041.06</v>
+        <v>3236.62</v>
       </c>
       <c r="F3" t="n">
-        <v>1024.79</v>
+        <v>3321.95</v>
       </c>
       <c r="G3" t="n">
-        <v>2.33</v>
+        <v>2.77</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3412.2</v>
+        <v>2540</v>
       </c>
       <c r="D4" t="n">
-        <v>3316.9</v>
+        <v>2432.33</v>
       </c>
       <c r="E4" t="n">
-        <v>3230.38</v>
+        <v>2455.2</v>
       </c>
       <c r="F4" t="n">
-        <v>3322.78</v>
+        <v>2469.55</v>
       </c>
       <c r="G4" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>173</v>
+        <v>115.86</v>
       </c>
       <c r="D5" t="n">
-        <v>165.47</v>
+        <v>112.97</v>
       </c>
       <c r="E5" t="n">
-        <v>162.91</v>
+        <v>110.45</v>
       </c>
       <c r="F5" t="n">
-        <v>167.74</v>
+        <v>112.64</v>
       </c>
       <c r="G5" t="n">
-        <v>3.14</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2552</v>
+        <v>173.29</v>
       </c>
       <c r="D6" t="n">
-        <v>2427.61</v>
+        <v>165.94</v>
       </c>
       <c r="E6" t="n">
-        <v>2453.12</v>
+        <v>163.22</v>
       </c>
       <c r="F6" t="n">
-        <v>2469.93</v>
+        <v>167.91</v>
       </c>
       <c r="G6" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>876.9</v>
+        <v>4090</v>
       </c>
       <c r="D7" t="n">
-        <v>854.9299999999999</v>
+        <v>3955.36</v>
       </c>
       <c r="E7" t="n">
-        <v>845.3</v>
+        <v>4012.44</v>
       </c>
       <c r="F7" t="n">
-        <v>848.4400000000001</v>
+        <v>3956.69</v>
       </c>
       <c r="G7" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>116.55</v>
+        <v>11120</v>
       </c>
       <c r="D8" t="n">
-        <v>112.65</v>
+        <v>11061.2</v>
       </c>
       <c r="E8" t="n">
-        <v>110.29</v>
+        <v>10877.85</v>
       </c>
       <c r="F8" t="n">
-        <v>112.65</v>
+        <v>10630.09</v>
       </c>
       <c r="G8" t="n">
-        <v>3.46</v>
+        <v>4.61</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4093</v>
+        <v>516.4</v>
       </c>
       <c r="D9" t="n">
-        <v>3949.97</v>
+        <v>508.25</v>
       </c>
       <c r="E9" t="n">
-        <v>4014.03</v>
+        <v>492.74</v>
       </c>
       <c r="F9" t="n">
-        <v>3955.46</v>
+        <v>493.08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.48</v>
+        <v>4.73</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5667.5</v>
+        <v>5694</v>
       </c>
       <c r="D10" t="n">
-        <v>5379.83</v>
+        <v>5397.14</v>
       </c>
       <c r="E10" t="n">
-        <v>5131.33</v>
+        <v>5147.74</v>
       </c>
       <c r="F10" t="n">
-        <v>5436.28</v>
+        <v>5435.75</v>
       </c>
       <c r="G10" t="n">
-        <v>4.25</v>
+        <v>4.75</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>515.05</v>
+        <v>2001.7</v>
       </c>
       <c r="D11" t="n">
-        <v>506.45</v>
+        <v>1969.57</v>
       </c>
       <c r="E11" t="n">
-        <v>491.57</v>
+        <v>1908.81</v>
       </c>
       <c r="F11" t="n">
-        <v>493.05</v>
+        <v>1905.59</v>
       </c>
       <c r="G11" t="n">
-        <v>4.46</v>
+        <v>5.04</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D12" t="n">
-        <v>454.83</v>
+        <v>456.36</v>
       </c>
       <c r="E12" t="n">
-        <v>440.54</v>
+        <v>441.73</v>
       </c>
       <c r="F12" t="n">
-        <v>450.53</v>
+        <v>450.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.43</v>
+        <v>5.81</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>293</v>
+        <v>295.95</v>
       </c>
       <c r="D13" t="n">
-        <v>279.79</v>
+        <v>280.35</v>
       </c>
       <c r="E13" t="n">
-        <v>280.76</v>
+        <v>280.96</v>
       </c>
       <c r="F13" t="n">
-        <v>276.82</v>
+        <v>276.98</v>
       </c>
       <c r="G13" t="n">
-        <v>5.84</v>
+        <v>6.85</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11320</v>
+        <v>2207</v>
       </c>
       <c r="D14" t="n">
-        <v>11048.93</v>
+        <v>2099.9</v>
       </c>
       <c r="E14" t="n">
-        <v>10858.65</v>
+        <v>2036.68</v>
       </c>
       <c r="F14" t="n">
-        <v>10639.37</v>
+        <v>2065.15</v>
       </c>
       <c r="G14" t="n">
-        <v>6.4</v>
+        <v>6.87</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2032.5</v>
+        <v>1251.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1966.45</v>
+        <v>1208.5</v>
       </c>
       <c r="E15" t="n">
-        <v>1903.75</v>
+        <v>1172.88</v>
       </c>
       <c r="F15" t="n">
-        <v>1905.89</v>
+        <v>1170.79</v>
       </c>
       <c r="G15" t="n">
-        <v>6.64</v>
+        <v>6.88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2218.8</v>
+        <v>5685</v>
       </c>
       <c r="D16" t="n">
-        <v>2092.18</v>
+        <v>5396.43</v>
       </c>
       <c r="E16" t="n">
-        <v>2032.75</v>
+        <v>5179.03</v>
       </c>
       <c r="F16" t="n">
-        <v>2065.77</v>
+        <v>5304.51</v>
       </c>
       <c r="G16" t="n">
-        <v>7.41</v>
+        <v>7.17</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>678.1</v>
+        <v>1785</v>
       </c>
       <c r="D17" t="n">
-        <v>657.73</v>
+        <v>1642.97</v>
       </c>
       <c r="E17" t="n">
-        <v>646.5700000000001</v>
+        <v>1632.62</v>
       </c>
       <c r="F17" t="n">
-        <v>628.83</v>
+        <v>1649.57</v>
       </c>
       <c r="G17" t="n">
-        <v>7.84</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1265</v>
+        <v>1635.8</v>
       </c>
       <c r="D18" t="n">
-        <v>1205.2</v>
+        <v>1624.99</v>
       </c>
       <c r="E18" t="n">
-        <v>1170.37</v>
+        <v>1613.42</v>
       </c>
       <c r="F18" t="n">
-        <v>1170.69</v>
+        <v>1503.71</v>
       </c>
       <c r="G18" t="n">
-        <v>8.06</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5735</v>
+        <v>689</v>
       </c>
       <c r="D19" t="n">
-        <v>5369.61</v>
+        <v>658.23</v>
       </c>
       <c r="E19" t="n">
-        <v>5164.36</v>
+        <v>648.21</v>
       </c>
       <c r="F19" t="n">
-        <v>5301.82</v>
+        <v>628.53</v>
       </c>
       <c r="G19" t="n">
-        <v>8.17</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1631</v>
+        <v>183.6</v>
       </c>
       <c r="D20" t="n">
-        <v>1627.87</v>
+        <v>177.35</v>
       </c>
       <c r="E20" t="n">
-        <v>1610.11</v>
+        <v>173.11</v>
       </c>
       <c r="F20" t="n">
-        <v>1504.15</v>
+        <v>166.73</v>
       </c>
       <c r="G20" t="n">
-        <v>8.43</v>
+        <v>10.12</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1199</v>
+        <v>1058.5</v>
       </c>
       <c r="D21" t="n">
-        <v>1145.73</v>
+        <v>1000.73</v>
       </c>
       <c r="E21" t="n">
-        <v>1132.01</v>
+        <v>988.11</v>
       </c>
       <c r="F21" t="n">
-        <v>1103.46</v>
+        <v>952.08</v>
       </c>
       <c r="G21" t="n">
-        <v>8.66</v>
+        <v>11.18</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1034</v>
+        <v>2145</v>
       </c>
       <c r="D22" t="n">
-        <v>997.67</v>
+        <v>1941.27</v>
       </c>
       <c r="E22" t="n">
-        <v>987.11</v>
+        <v>1891.99</v>
       </c>
       <c r="F22" t="n">
-        <v>950.71</v>
+        <v>1927.17</v>
       </c>
       <c r="G22" t="n">
-        <v>8.76</v>
+        <v>11.3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1795.2</v>
+        <v>403.3</v>
       </c>
       <c r="D23" t="n">
-        <v>1636.63</v>
+        <v>367.66</v>
       </c>
       <c r="E23" t="n">
-        <v>1628.54</v>
+        <v>360.86</v>
       </c>
       <c r="F23" t="n">
-        <v>1649.76</v>
+        <v>355.52</v>
       </c>
       <c r="G23" t="n">
-        <v>8.82</v>
+        <v>13.44</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>183.45</v>
+        <v>990</v>
       </c>
       <c r="D24" t="n">
-        <v>176.91</v>
+        <v>914.4299999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>172.77</v>
+        <v>928.65</v>
       </c>
       <c r="F24" t="n">
-        <v>166.54</v>
+        <v>845.64</v>
       </c>
       <c r="G24" t="n">
-        <v>10.16</v>
+        <v>17.07</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>393.45</v>
+        <v>1349</v>
       </c>
       <c r="D25" t="n">
-        <v>366.03</v>
+        <v>1262.6</v>
       </c>
       <c r="E25" t="n">
-        <v>360.42</v>
+        <v>1175.25</v>
       </c>
       <c r="F25" t="n">
-        <v>354.61</v>
+        <v>1147.88</v>
       </c>
       <c r="G25" t="n">
-        <v>10.95</v>
+        <v>17.52</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2139</v>
+        <v>14570</v>
       </c>
       <c r="D26" t="n">
-        <v>1930.73</v>
+        <v>14136.37</v>
       </c>
       <c r="E26" t="n">
-        <v>1885.76</v>
+        <v>13502</v>
       </c>
       <c r="F26" t="n">
-        <v>1925.37</v>
+        <v>12188.24</v>
       </c>
       <c r="G26" t="n">
-        <v>11.1</v>
+        <v>19.54</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1396,23 +1396,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>990</v>
+        <v>327.15</v>
       </c>
       <c r="D27" t="n">
-        <v>914.1900000000001</v>
+        <v>306.28</v>
       </c>
       <c r="E27" t="n">
-        <v>927.64</v>
+        <v>292.09</v>
       </c>
       <c r="F27" t="n">
-        <v>845.59</v>
+        <v>272.63</v>
       </c>
       <c r="G27" t="n">
-        <v>17.08</v>
+        <v>20</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1433,23 +1433,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1350.1</v>
+        <v>1873</v>
       </c>
       <c r="D28" t="n">
-        <v>1257.21</v>
+        <v>1691.95</v>
       </c>
       <c r="E28" t="n">
-        <v>1167.86</v>
+        <v>1602.78</v>
       </c>
       <c r="F28" t="n">
-        <v>1147.73</v>
+        <v>1508.98</v>
       </c>
       <c r="G28" t="n">
-        <v>17.63</v>
+        <v>24.12</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1470,23 +1470,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>328</v>
+        <v>3268</v>
       </c>
       <c r="D29" t="n">
-        <v>304.88</v>
+        <v>2834.58</v>
       </c>
       <c r="E29" t="n">
-        <v>290.59</v>
+        <v>2830.08</v>
       </c>
       <c r="F29" t="n">
-        <v>272.52</v>
+        <v>2582.38</v>
       </c>
       <c r="G29" t="n">
-        <v>20.36</v>
+        <v>26.55</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1494,154 +1494,6 @@
         </is>
       </c>
       <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>14850</v>
-      </c>
-      <c r="D30" t="n">
-        <v>14100.37</v>
-      </c>
-      <c r="E30" t="n">
-        <v>13449.74</v>
-      </c>
-      <c r="F30" t="n">
-        <v>12190.78</v>
-      </c>
-      <c r="G30" t="n">
-        <v>21.81</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>3185</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2818.39</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2822.63</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2575.29</v>
-      </c>
-      <c r="G31" t="n">
-        <v>23.68</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1891.7</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1680.64</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1593.24</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1508.38</v>
-      </c>
-      <c r="G32" t="n">
-        <v>25.41</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>11724</v>
-      </c>
-      <c r="D33" t="n">
-        <v>11530.63</v>
-      </c>
-      <c r="E33" t="n">
-        <v>11119.77</v>
-      </c>
-      <c r="F33" t="n">
-        <v>8660.620000000001</v>
-      </c>
-      <c r="G33" t="n">
-        <v>35.37</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2540</v>
+        <v>115.86</v>
       </c>
       <c r="D4" t="n">
-        <v>2432.33</v>
+        <v>112.97</v>
       </c>
       <c r="E4" t="n">
-        <v>2455.2</v>
+        <v>110.45</v>
       </c>
       <c r="F4" t="n">
-        <v>2469.55</v>
+        <v>112.64</v>
       </c>
       <c r="G4" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>115.86</v>
+        <v>173.29</v>
       </c>
       <c r="D5" t="n">
-        <v>112.97</v>
+        <v>165.94</v>
       </c>
       <c r="E5" t="n">
-        <v>110.45</v>
+        <v>163.22</v>
       </c>
       <c r="F5" t="n">
-        <v>112.64</v>
+        <v>167.91</v>
       </c>
       <c r="G5" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>173.29</v>
+        <v>11120</v>
       </c>
       <c r="D6" t="n">
-        <v>165.94</v>
+        <v>11061.2</v>
       </c>
       <c r="E6" t="n">
-        <v>163.22</v>
+        <v>10877.85</v>
       </c>
       <c r="F6" t="n">
-        <v>167.91</v>
+        <v>10630.09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>4.61</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4090</v>
+        <v>516.4</v>
       </c>
       <c r="D7" t="n">
-        <v>3955.36</v>
+        <v>508.25</v>
       </c>
       <c r="E7" t="n">
-        <v>4012.44</v>
+        <v>492.74</v>
       </c>
       <c r="F7" t="n">
-        <v>3956.69</v>
+        <v>493.08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.37</v>
+        <v>4.73</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11120</v>
+        <v>5694</v>
       </c>
       <c r="D8" t="n">
-        <v>11061.2</v>
+        <v>5397.14</v>
       </c>
       <c r="E8" t="n">
-        <v>10877.85</v>
+        <v>5147.74</v>
       </c>
       <c r="F8" t="n">
-        <v>10630.09</v>
+        <v>5435.75</v>
       </c>
       <c r="G8" t="n">
-        <v>4.61</v>
+        <v>4.75</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>516.4</v>
+        <v>2001.7</v>
       </c>
       <c r="D9" t="n">
-        <v>508.25</v>
+        <v>1969.57</v>
       </c>
       <c r="E9" t="n">
-        <v>492.74</v>
+        <v>1908.81</v>
       </c>
       <c r="F9" t="n">
-        <v>493.08</v>
+        <v>1905.59</v>
       </c>
       <c r="G9" t="n">
-        <v>4.73</v>
+        <v>5.04</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5694</v>
+        <v>477</v>
       </c>
       <c r="D10" t="n">
-        <v>5397.14</v>
+        <v>456.36</v>
       </c>
       <c r="E10" t="n">
-        <v>5147.74</v>
+        <v>441.73</v>
       </c>
       <c r="F10" t="n">
-        <v>5435.75</v>
+        <v>450.8</v>
       </c>
       <c r="G10" t="n">
-        <v>4.75</v>
+        <v>5.81</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2001.7</v>
+        <v>295.95</v>
       </c>
       <c r="D11" t="n">
-        <v>1969.57</v>
+        <v>280.35</v>
       </c>
       <c r="E11" t="n">
-        <v>1908.81</v>
+        <v>280.96</v>
       </c>
       <c r="F11" t="n">
-        <v>1905.59</v>
+        <v>276.98</v>
       </c>
       <c r="G11" t="n">
-        <v>5.04</v>
+        <v>6.85</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>477</v>
+        <v>2207</v>
       </c>
       <c r="D12" t="n">
-        <v>456.36</v>
+        <v>2099.9</v>
       </c>
       <c r="E12" t="n">
-        <v>441.73</v>
+        <v>2036.68</v>
       </c>
       <c r="F12" t="n">
-        <v>450.8</v>
+        <v>2065.15</v>
       </c>
       <c r="G12" t="n">
-        <v>5.81</v>
+        <v>6.87</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>295.95</v>
+        <v>1189.8</v>
       </c>
       <c r="D13" t="n">
-        <v>280.35</v>
+        <v>1148.12</v>
       </c>
       <c r="E13" t="n">
-        <v>280.96</v>
+        <v>1133.19</v>
       </c>
       <c r="F13" t="n">
-        <v>276.98</v>
+        <v>1104.05</v>
       </c>
       <c r="G13" t="n">
-        <v>6.85</v>
+        <v>7.77</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2207</v>
+        <v>689</v>
       </c>
       <c r="D14" t="n">
-        <v>2099.9</v>
+        <v>658.23</v>
       </c>
       <c r="E14" t="n">
-        <v>2036.68</v>
+        <v>648.21</v>
       </c>
       <c r="F14" t="n">
-        <v>2065.15</v>
+        <v>628.53</v>
       </c>
       <c r="G14" t="n">
-        <v>6.87</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1251.3</v>
+        <v>183.6</v>
       </c>
       <c r="D15" t="n">
-        <v>1208.5</v>
+        <v>177.35</v>
       </c>
       <c r="E15" t="n">
-        <v>1172.88</v>
+        <v>173.11</v>
       </c>
       <c r="F15" t="n">
-        <v>1170.79</v>
+        <v>166.73</v>
       </c>
       <c r="G15" t="n">
-        <v>6.88</v>
+        <v>10.12</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5685</v>
+        <v>1058.5</v>
       </c>
       <c r="D16" t="n">
-        <v>5396.43</v>
+        <v>1000.73</v>
       </c>
       <c r="E16" t="n">
-        <v>5179.03</v>
+        <v>988.11</v>
       </c>
       <c r="F16" t="n">
-        <v>5304.51</v>
+        <v>952.08</v>
       </c>
       <c r="G16" t="n">
-        <v>7.17</v>
+        <v>11.18</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1785</v>
+        <v>403.3</v>
       </c>
       <c r="D17" t="n">
-        <v>1642.97</v>
+        <v>367.66</v>
       </c>
       <c r="E17" t="n">
-        <v>1632.62</v>
+        <v>360.86</v>
       </c>
       <c r="F17" t="n">
-        <v>1649.57</v>
+        <v>355.52</v>
       </c>
       <c r="G17" t="n">
-        <v>8.210000000000001</v>
+        <v>13.44</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1635.8</v>
+        <v>990</v>
       </c>
       <c r="D18" t="n">
-        <v>1624.99</v>
+        <v>914.4299999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>1613.42</v>
+        <v>928.65</v>
       </c>
       <c r="F18" t="n">
-        <v>1503.71</v>
+        <v>845.64</v>
       </c>
       <c r="G18" t="n">
-        <v>8.779999999999999</v>
+        <v>17.07</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>689</v>
+        <v>14570</v>
       </c>
       <c r="D19" t="n">
-        <v>658.23</v>
+        <v>14136.37</v>
       </c>
       <c r="E19" t="n">
-        <v>648.21</v>
+        <v>13502</v>
       </c>
       <c r="F19" t="n">
-        <v>628.53</v>
+        <v>12188.24</v>
       </c>
       <c r="G19" t="n">
-        <v>9.619999999999999</v>
+        <v>19.54</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>183.6</v>
+        <v>327.15</v>
       </c>
       <c r="D20" t="n">
-        <v>177.35</v>
+        <v>306.28</v>
       </c>
       <c r="E20" t="n">
-        <v>173.11</v>
+        <v>292.09</v>
       </c>
       <c r="F20" t="n">
-        <v>166.73</v>
+        <v>272.63</v>
       </c>
       <c r="G20" t="n">
-        <v>10.12</v>
+        <v>20</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1058.5</v>
+        <v>1873</v>
       </c>
       <c r="D21" t="n">
-        <v>1000.73</v>
+        <v>1691.95</v>
       </c>
       <c r="E21" t="n">
-        <v>988.11</v>
+        <v>1602.78</v>
       </c>
       <c r="F21" t="n">
-        <v>952.08</v>
+        <v>1508.98</v>
       </c>
       <c r="G21" t="n">
-        <v>11.18</v>
+        <v>24.12</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2145</v>
+        <v>3268</v>
       </c>
       <c r="D22" t="n">
-        <v>1941.27</v>
+        <v>2834.58</v>
       </c>
       <c r="E22" t="n">
-        <v>1891.99</v>
+        <v>2830.08</v>
       </c>
       <c r="F22" t="n">
-        <v>1927.17</v>
+        <v>2582.38</v>
       </c>
       <c r="G22" t="n">
-        <v>11.3</v>
+        <v>26.55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1235,265 +1235,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NATIONALUM</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>403.3</v>
-      </c>
-      <c r="D23" t="n">
-        <v>367.66</v>
-      </c>
-      <c r="E23" t="n">
-        <v>360.86</v>
-      </c>
-      <c r="F23" t="n">
-        <v>355.52</v>
-      </c>
-      <c r="G23" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>990</v>
-      </c>
-      <c r="D24" t="n">
-        <v>914.4299999999999</v>
-      </c>
-      <c r="E24" t="n">
-        <v>928.65</v>
-      </c>
-      <c r="F24" t="n">
-        <v>845.64</v>
-      </c>
-      <c r="G24" t="n">
-        <v>17.07</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1349</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1262.6</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1175.25</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1147.88</v>
-      </c>
-      <c r="G25" t="n">
-        <v>17.52</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>14570</v>
-      </c>
-      <c r="D26" t="n">
-        <v>14136.37</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13502</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12188.24</v>
-      </c>
-      <c r="G26" t="n">
-        <v>19.54</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>327.15</v>
-      </c>
-      <c r="D27" t="n">
-        <v>306.28</v>
-      </c>
-      <c r="E27" t="n">
-        <v>292.09</v>
-      </c>
-      <c r="F27" t="n">
-        <v>272.63</v>
-      </c>
-      <c r="G27" t="n">
-        <v>20</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1873</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1691.95</v>
-      </c>
-      <c r="E28" t="n">
-        <v>1602.78</v>
-      </c>
-      <c r="F28" t="n">
-        <v>1508.98</v>
-      </c>
-      <c r="G28" t="n">
-        <v>24.12</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>3268</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2834.58</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2830.08</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2582.38</v>
-      </c>
-      <c r="G29" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>870.45</v>
+        <v>1947</v>
       </c>
       <c r="D2" t="n">
-        <v>855.86</v>
+        <v>1936.33</v>
       </c>
       <c r="E2" t="n">
-        <v>845.71</v>
+        <v>1909.13</v>
       </c>
       <c r="F2" t="n">
-        <v>848.5599999999999</v>
+        <v>1922.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3414.1</v>
+        <v>1048</v>
       </c>
       <c r="D3" t="n">
-        <v>3325.36</v>
+        <v>1046.81</v>
       </c>
       <c r="E3" t="n">
-        <v>3236.62</v>
+        <v>1042.08</v>
       </c>
       <c r="F3" t="n">
-        <v>3321.95</v>
+        <v>1025.81</v>
       </c>
       <c r="G3" t="n">
-        <v>2.77</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.86</v>
+        <v>115.93</v>
       </c>
       <c r="D4" t="n">
-        <v>112.97</v>
+        <v>113.33</v>
       </c>
       <c r="E4" t="n">
-        <v>110.45</v>
+        <v>110.61</v>
       </c>
       <c r="F4" t="n">
-        <v>112.64</v>
+        <v>112.63</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>173.29</v>
+        <v>878</v>
       </c>
       <c r="D5" t="n">
-        <v>165.94</v>
+        <v>857.35</v>
       </c>
       <c r="E5" t="n">
-        <v>163.22</v>
+        <v>846.21</v>
       </c>
       <c r="F5" t="n">
-        <v>167.91</v>
+        <v>848.67</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11120</v>
+        <v>467.5</v>
       </c>
       <c r="D6" t="n">
-        <v>11061.2</v>
+        <v>457.24</v>
       </c>
       <c r="E6" t="n">
-        <v>10877.85</v>
+        <v>442.69</v>
       </c>
       <c r="F6" t="n">
-        <v>10630.09</v>
+        <v>451.02</v>
       </c>
       <c r="G6" t="n">
-        <v>4.61</v>
+        <v>3.65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>516.4</v>
+        <v>3443</v>
       </c>
       <c r="D7" t="n">
-        <v>508.25</v>
+        <v>3337.02</v>
       </c>
       <c r="E7" t="n">
-        <v>492.74</v>
+        <v>3243.38</v>
       </c>
       <c r="F7" t="n">
-        <v>493.08</v>
+        <v>3320.9</v>
       </c>
       <c r="G7" t="n">
-        <v>4.73</v>
+        <v>3.68</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5694</v>
+        <v>174.69</v>
       </c>
       <c r="D8" t="n">
-        <v>5397.14</v>
+        <v>166.59</v>
       </c>
       <c r="E8" t="n">
-        <v>5147.74</v>
+        <v>163.55</v>
       </c>
       <c r="F8" t="n">
-        <v>5435.75</v>
+        <v>168.1</v>
       </c>
       <c r="G8" t="n">
-        <v>4.75</v>
+        <v>3.92</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2001.7</v>
+        <v>5655</v>
       </c>
       <c r="D9" t="n">
-        <v>1969.57</v>
+        <v>5415.27</v>
       </c>
       <c r="E9" t="n">
-        <v>1908.81</v>
+        <v>5160.86</v>
       </c>
       <c r="F9" t="n">
-        <v>1905.59</v>
+        <v>5435.32</v>
       </c>
       <c r="G9" t="n">
-        <v>5.04</v>
+        <v>4.04</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>477</v>
+        <v>4119</v>
       </c>
       <c r="D10" t="n">
-        <v>456.36</v>
+        <v>3956.32</v>
       </c>
       <c r="E10" t="n">
-        <v>441.73</v>
+        <v>4013.02</v>
       </c>
       <c r="F10" t="n">
-        <v>450.8</v>
+        <v>3956.84</v>
       </c>
       <c r="G10" t="n">
-        <v>5.81</v>
+        <v>4.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>295.95</v>
+        <v>516</v>
       </c>
       <c r="D11" t="n">
-        <v>280.35</v>
+        <v>509.06</v>
       </c>
       <c r="E11" t="n">
-        <v>280.96</v>
+        <v>493.82</v>
       </c>
       <c r="F11" t="n">
-        <v>276.98</v>
+        <v>493.09</v>
       </c>
       <c r="G11" t="n">
-        <v>6.85</v>
+        <v>4.65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2207</v>
+        <v>2004</v>
       </c>
       <c r="D12" t="n">
-        <v>2099.9</v>
+        <v>1974.07</v>
       </c>
       <c r="E12" t="n">
-        <v>2036.68</v>
+        <v>1913.17</v>
       </c>
       <c r="F12" t="n">
-        <v>2065.15</v>
+        <v>1905.11</v>
       </c>
       <c r="G12" t="n">
-        <v>6.87</v>
+        <v>5.19</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1189.8</v>
+        <v>292.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1148.12</v>
+        <v>280.9</v>
       </c>
       <c r="E13" t="n">
-        <v>1133.19</v>
+        <v>281</v>
       </c>
       <c r="F13" t="n">
-        <v>1104.05</v>
+        <v>277.1</v>
       </c>
       <c r="G13" t="n">
-        <v>7.77</v>
+        <v>5.56</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>689</v>
+        <v>2610</v>
       </c>
       <c r="D14" t="n">
-        <v>658.23</v>
+        <v>2434.66</v>
       </c>
       <c r="E14" t="n">
-        <v>648.21</v>
+        <v>2456.6</v>
       </c>
       <c r="F14" t="n">
-        <v>628.53</v>
+        <v>2469.9</v>
       </c>
       <c r="G14" t="n">
-        <v>9.619999999999999</v>
+        <v>5.67</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>183.6</v>
+        <v>5624.5</v>
       </c>
       <c r="D15" t="n">
-        <v>177.35</v>
+        <v>5394.41</v>
       </c>
       <c r="E15" t="n">
-        <v>173.11</v>
+        <v>5177.82</v>
       </c>
       <c r="F15" t="n">
-        <v>166.73</v>
+        <v>5304.2</v>
       </c>
       <c r="G15" t="n">
-        <v>10.12</v>
+        <v>6.04</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1058.5</v>
+        <v>11290</v>
       </c>
       <c r="D16" t="n">
-        <v>1000.73</v>
+        <v>11088</v>
       </c>
       <c r="E16" t="n">
-        <v>988.11</v>
+        <v>10896.94</v>
       </c>
       <c r="F16" t="n">
-        <v>952.08</v>
+        <v>10624.41</v>
       </c>
       <c r="G16" t="n">
-        <v>11.18</v>
+        <v>6.26</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>403.3</v>
+        <v>1253.4</v>
       </c>
       <c r="D17" t="n">
-        <v>367.66</v>
+        <v>1208.57</v>
       </c>
       <c r="E17" t="n">
-        <v>360.86</v>
+        <v>1172.92</v>
       </c>
       <c r="F17" t="n">
-        <v>355.52</v>
+        <v>1170.8</v>
       </c>
       <c r="G17" t="n">
-        <v>13.44</v>
+        <v>7.05</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>990</v>
+        <v>2232.5</v>
       </c>
       <c r="D18" t="n">
-        <v>914.4299999999999</v>
+        <v>2109.61</v>
       </c>
       <c r="E18" t="n">
-        <v>928.65</v>
+        <v>2042.21</v>
       </c>
       <c r="F18" t="n">
-        <v>845.64</v>
+        <v>2064.79</v>
       </c>
       <c r="G18" t="n">
-        <v>17.07</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14570</v>
+        <v>682.95</v>
       </c>
       <c r="D19" t="n">
-        <v>14136.37</v>
+        <v>658.89</v>
       </c>
       <c r="E19" t="n">
-        <v>13502</v>
+        <v>649.4400000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>12188.24</v>
+        <v>628.1900000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>19.54</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>327.15</v>
+        <v>1798.3</v>
       </c>
       <c r="D20" t="n">
-        <v>306.28</v>
+        <v>1643.42</v>
       </c>
       <c r="E20" t="n">
-        <v>292.09</v>
+        <v>1632.88</v>
       </c>
       <c r="F20" t="n">
-        <v>272.63</v>
+        <v>1649.63</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>9.01</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1873</v>
+        <v>1210</v>
       </c>
       <c r="D21" t="n">
-        <v>1691.95</v>
+        <v>1151.83</v>
       </c>
       <c r="E21" t="n">
-        <v>1602.78</v>
+        <v>1134.72</v>
       </c>
       <c r="F21" t="n">
-        <v>1508.98</v>
+        <v>1104.79</v>
       </c>
       <c r="G21" t="n">
-        <v>24.12</v>
+        <v>9.52</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,30 +1211,400 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>HINDALCO</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1051.05</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1003.29</v>
+      </c>
+      <c r="E22" t="n">
+        <v>989.58</v>
+      </c>
+      <c r="F22" t="n">
+        <v>953.4</v>
+      </c>
+      <c r="G22" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2139.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1941.08</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1891.87</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1927.14</v>
+      </c>
+      <c r="G23" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NATIONALUM</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>397.8</v>
+      </c>
+      <c r="D24" t="n">
+        <v>368.79</v>
+      </c>
+      <c r="E24" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>356.37</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11.62</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>186.98</v>
+      </c>
+      <c r="D25" t="n">
+        <v>177.89</v>
+      </c>
+      <c r="E25" t="n">
+        <v>173.54</v>
+      </c>
+      <c r="F25" t="n">
+        <v>166.92</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1350</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1262.63</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1175.27</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1147.89</v>
+      </c>
+      <c r="G26" t="n">
+        <v>17.61</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1011.5</v>
+      </c>
+      <c r="D27" t="n">
+        <v>915.91</v>
+      </c>
+      <c r="E27" t="n">
+        <v>929.99</v>
+      </c>
+      <c r="F27" t="n">
+        <v>845.75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>331</v>
+      </c>
+      <c r="D28" t="n">
+        <v>307.78</v>
+      </c>
+      <c r="E28" t="n">
+        <v>293.64</v>
+      </c>
+      <c r="F28" t="n">
+        <v>272.75</v>
+      </c>
+      <c r="G28" t="n">
+        <v>21.36</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>14990</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14190.53</v>
+      </c>
+      <c r="E29" t="n">
+        <v>13557.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12188.94</v>
+      </c>
+      <c r="G29" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1892.8</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1704.13</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1611.47</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1509.81</v>
+      </c>
+      <c r="G30" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>3268</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2834.58</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2830.08</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2582.38</v>
-      </c>
-      <c r="G22" t="n">
-        <v>26.55</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="C31" t="n">
+        <v>3280</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2847.54</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2837.97</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2589.35</v>
+      </c>
+      <c r="G31" t="n">
+        <v>26.67</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OFSS</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11729</v>
+      </c>
+      <c r="D32" t="n">
+        <v>11525.8</v>
+      </c>
+      <c r="E32" t="n">
+        <v>11207.24</v>
+      </c>
+      <c r="F32" t="n">
+        <v>8697.67</v>
+      </c>
+      <c r="G32" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.93</v>
+        <v>1540</v>
       </c>
       <c r="D4" t="n">
-        <v>113.33</v>
+        <v>1464.58</v>
       </c>
       <c r="E4" t="n">
-        <v>110.61</v>
+        <v>1447.92</v>
       </c>
       <c r="F4" t="n">
-        <v>112.63</v>
+        <v>1505.19</v>
       </c>
       <c r="G4" t="n">
-        <v>2.93</v>
+        <v>2.31</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>878</v>
+        <v>115.93</v>
       </c>
       <c r="D5" t="n">
-        <v>857.35</v>
+        <v>113.33</v>
       </c>
       <c r="E5" t="n">
-        <v>846.21</v>
+        <v>110.61</v>
       </c>
       <c r="F5" t="n">
-        <v>848.67</v>
+        <v>112.63</v>
       </c>
       <c r="G5" t="n">
-        <v>3.46</v>
+        <v>2.93</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>467.5</v>
+        <v>878</v>
       </c>
       <c r="D6" t="n">
-        <v>457.24</v>
+        <v>857.35</v>
       </c>
       <c r="E6" t="n">
-        <v>442.69</v>
+        <v>846.21</v>
       </c>
       <c r="F6" t="n">
-        <v>451.02</v>
+        <v>848.67</v>
       </c>
       <c r="G6" t="n">
-        <v>3.65</v>
+        <v>3.46</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3443</v>
+        <v>467.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3337.02</v>
+        <v>457.24</v>
       </c>
       <c r="E7" t="n">
-        <v>3243.38</v>
+        <v>442.69</v>
       </c>
       <c r="F7" t="n">
-        <v>3320.9</v>
+        <v>451.02</v>
       </c>
       <c r="G7" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>174.69</v>
+        <v>3443</v>
       </c>
       <c r="D8" t="n">
-        <v>166.59</v>
+        <v>3337.02</v>
       </c>
       <c r="E8" t="n">
-        <v>163.55</v>
+        <v>3243.38</v>
       </c>
       <c r="F8" t="n">
-        <v>168.1</v>
+        <v>3320.9</v>
       </c>
       <c r="G8" t="n">
-        <v>3.92</v>
+        <v>3.68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5655</v>
+        <v>174.69</v>
       </c>
       <c r="D9" t="n">
-        <v>5415.27</v>
+        <v>166.59</v>
       </c>
       <c r="E9" t="n">
-        <v>5160.86</v>
+        <v>163.55</v>
       </c>
       <c r="F9" t="n">
-        <v>5435.32</v>
+        <v>168.1</v>
       </c>
       <c r="G9" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4119</v>
+        <v>5655</v>
       </c>
       <c r="D10" t="n">
-        <v>3956.32</v>
+        <v>5415.27</v>
       </c>
       <c r="E10" t="n">
-        <v>4013.02</v>
+        <v>5160.86</v>
       </c>
       <c r="F10" t="n">
-        <v>3956.84</v>
+        <v>5435.32</v>
       </c>
       <c r="G10" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>516</v>
+        <v>4119</v>
       </c>
       <c r="D11" t="n">
-        <v>509.06</v>
+        <v>3964.37</v>
       </c>
       <c r="E11" t="n">
-        <v>493.82</v>
+        <v>4011.09</v>
       </c>
       <c r="F11" t="n">
-        <v>493.09</v>
+        <v>3958.06</v>
       </c>
       <c r="G11" t="n">
-        <v>4.65</v>
+        <v>4.07</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2004</v>
+        <v>516</v>
       </c>
       <c r="D12" t="n">
-        <v>1974.07</v>
+        <v>509.06</v>
       </c>
       <c r="E12" t="n">
-        <v>1913.17</v>
+        <v>493.82</v>
       </c>
       <c r="F12" t="n">
-        <v>1905.11</v>
+        <v>493.09</v>
       </c>
       <c r="G12" t="n">
-        <v>5.19</v>
+        <v>4.65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>292.5</v>
+        <v>2004</v>
       </c>
       <c r="D13" t="n">
-        <v>280.9</v>
+        <v>1974.07</v>
       </c>
       <c r="E13" t="n">
-        <v>281</v>
+        <v>1913.17</v>
       </c>
       <c r="F13" t="n">
-        <v>277.1</v>
+        <v>1905.11</v>
       </c>
       <c r="G13" t="n">
-        <v>5.56</v>
+        <v>5.19</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2610</v>
+        <v>292.5</v>
       </c>
       <c r="D14" t="n">
-        <v>2434.66</v>
+        <v>280.9</v>
       </c>
       <c r="E14" t="n">
-        <v>2456.6</v>
+        <v>281</v>
       </c>
       <c r="F14" t="n">
-        <v>2469.9</v>
+        <v>277.1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.67</v>
+        <v>5.56</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5624.5</v>
+        <v>2610</v>
       </c>
       <c r="D15" t="n">
-        <v>5394.41</v>
+        <v>2440.81</v>
       </c>
       <c r="E15" t="n">
-        <v>5177.82</v>
+        <v>2458.14</v>
       </c>
       <c r="F15" t="n">
-        <v>5304.2</v>
+        <v>2469.31</v>
       </c>
       <c r="G15" t="n">
-        <v>6.04</v>
+        <v>5.7</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>11290</v>
+        <v>5624.5</v>
       </c>
       <c r="D16" t="n">
-        <v>11088</v>
+        <v>5423.66</v>
       </c>
       <c r="E16" t="n">
-        <v>10896.94</v>
+        <v>5192.36</v>
       </c>
       <c r="F16" t="n">
-        <v>10624.41</v>
+        <v>5307.03</v>
       </c>
       <c r="G16" t="n">
-        <v>6.26</v>
+        <v>5.98</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1253.4</v>
+        <v>2232.5</v>
       </c>
       <c r="D17" t="n">
-        <v>1208.57</v>
+        <v>2109.61</v>
       </c>
       <c r="E17" t="n">
-        <v>1172.92</v>
+        <v>2042.21</v>
       </c>
       <c r="F17" t="n">
-        <v>1170.8</v>
+        <v>2064.79</v>
       </c>
       <c r="G17" t="n">
-        <v>7.05</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2232.5</v>
+        <v>682.95</v>
       </c>
       <c r="D18" t="n">
-        <v>2109.61</v>
+        <v>658.89</v>
       </c>
       <c r="E18" t="n">
-        <v>2042.21</v>
+        <v>649.4400000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>2064.79</v>
+        <v>628.1900000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>8.119999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>682.95</v>
+        <v>1798.3</v>
       </c>
       <c r="D19" t="n">
-        <v>658.89</v>
+        <v>1650.69</v>
       </c>
       <c r="E19" t="n">
-        <v>649.4400000000001</v>
+        <v>1636.65</v>
       </c>
       <c r="F19" t="n">
-        <v>628.1900000000001</v>
+        <v>1649.77</v>
       </c>
       <c r="G19" t="n">
-        <v>8.720000000000001</v>
+        <v>9</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1798.3</v>
+        <v>1051.05</v>
       </c>
       <c r="D20" t="n">
-        <v>1643.42</v>
+        <v>1003.29</v>
       </c>
       <c r="E20" t="n">
-        <v>1632.88</v>
+        <v>989.58</v>
       </c>
       <c r="F20" t="n">
-        <v>1649.63</v>
+        <v>953.4</v>
       </c>
       <c r="G20" t="n">
-        <v>9.01</v>
+        <v>10.24</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1210</v>
+        <v>2139.3</v>
       </c>
       <c r="D21" t="n">
-        <v>1151.83</v>
+        <v>1952.61</v>
       </c>
       <c r="E21" t="n">
-        <v>1134.72</v>
+        <v>1897.93</v>
       </c>
       <c r="F21" t="n">
-        <v>1104.79</v>
+        <v>1928.86</v>
       </c>
       <c r="G21" t="n">
-        <v>9.52</v>
+        <v>10.91</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1051.05</v>
+        <v>397.8</v>
       </c>
       <c r="D22" t="n">
-        <v>1003.29</v>
+        <v>368.79</v>
       </c>
       <c r="E22" t="n">
-        <v>989.58</v>
+        <v>361.5</v>
       </c>
       <c r="F22" t="n">
-        <v>953.4</v>
+        <v>356.37</v>
       </c>
       <c r="G22" t="n">
-        <v>10.24</v>
+        <v>11.62</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,28 +1243,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2139.3</v>
+        <v>186.98</v>
       </c>
       <c r="D23" t="n">
-        <v>1941.08</v>
+        <v>177.89</v>
       </c>
       <c r="E23" t="n">
-        <v>1891.87</v>
+        <v>173.54</v>
       </c>
       <c r="F23" t="n">
-        <v>1927.14</v>
+        <v>166.92</v>
       </c>
       <c r="G23" t="n">
-        <v>11.01</v>
+        <v>12.02</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1280,28 +1280,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>397.8</v>
+        <v>1011.5</v>
       </c>
       <c r="D24" t="n">
-        <v>368.79</v>
+        <v>915.91</v>
       </c>
       <c r="E24" t="n">
-        <v>361.5</v>
+        <v>929.99</v>
       </c>
       <c r="F24" t="n">
-        <v>356.37</v>
+        <v>845.75</v>
       </c>
       <c r="G24" t="n">
-        <v>11.62</v>
+        <v>19.6</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1317,28 +1317,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>186.98</v>
+        <v>331</v>
       </c>
       <c r="D25" t="n">
-        <v>177.89</v>
+        <v>307.78</v>
       </c>
       <c r="E25" t="n">
-        <v>173.54</v>
+        <v>293.64</v>
       </c>
       <c r="F25" t="n">
-        <v>166.92</v>
+        <v>272.75</v>
       </c>
       <c r="G25" t="n">
-        <v>12.02</v>
+        <v>21.36</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1354,28 +1354,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1350</v>
+        <v>14990</v>
       </c>
       <c r="D26" t="n">
-        <v>1262.63</v>
+        <v>14190.53</v>
       </c>
       <c r="E26" t="n">
-        <v>1175.27</v>
+        <v>13557.1</v>
       </c>
       <c r="F26" t="n">
-        <v>1147.89</v>
+        <v>12188.94</v>
       </c>
       <c r="G26" t="n">
-        <v>17.61</v>
+        <v>22.98</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1391,28 +1391,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1011.5</v>
+        <v>1892.8</v>
       </c>
       <c r="D27" t="n">
-        <v>915.91</v>
+        <v>1704.13</v>
       </c>
       <c r="E27" t="n">
-        <v>929.99</v>
+        <v>1611.47</v>
       </c>
       <c r="F27" t="n">
-        <v>845.75</v>
+        <v>1509.81</v>
       </c>
       <c r="G27" t="n">
-        <v>19.6</v>
+        <v>25.37</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1428,28 +1428,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>331</v>
+        <v>3280</v>
       </c>
       <c r="D28" t="n">
-        <v>307.78</v>
+        <v>2847.54</v>
       </c>
       <c r="E28" t="n">
-        <v>293.64</v>
+        <v>2837.97</v>
       </c>
       <c r="F28" t="n">
-        <v>272.75</v>
+        <v>2589.35</v>
       </c>
       <c r="G28" t="n">
-        <v>21.36</v>
+        <v>26.67</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1457,154 +1457,6 @@
         </is>
       </c>
       <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>14990</v>
-      </c>
-      <c r="D29" t="n">
-        <v>14190.53</v>
-      </c>
-      <c r="E29" t="n">
-        <v>13557.1</v>
-      </c>
-      <c r="F29" t="n">
-        <v>12188.94</v>
-      </c>
-      <c r="G29" t="n">
-        <v>22.98</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1892.8</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1704.13</v>
-      </c>
-      <c r="E30" t="n">
-        <v>1611.47</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1509.81</v>
-      </c>
-      <c r="G30" t="n">
-        <v>25.37</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>3280</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2847.54</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2837.97</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2589.35</v>
-      </c>
-      <c r="G31" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>25-08-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>OFSS</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>11729</v>
-      </c>
-      <c r="D32" t="n">
-        <v>11525.8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>11207.24</v>
-      </c>
-      <c r="F32" t="n">
-        <v>8697.67</v>
-      </c>
-      <c r="G32" t="n">
-        <v>34.85</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1947</v>
+        <v>1526.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1936.33</v>
+        <v>1470.19</v>
       </c>
       <c r="E2" t="n">
-        <v>1909.13</v>
+        <v>1447.19</v>
       </c>
       <c r="F2" t="n">
-        <v>1922.06</v>
+        <v>1505</v>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1048</v>
+        <v>4038.1</v>
       </c>
       <c r="D3" t="n">
-        <v>1046.81</v>
+        <v>3972.84</v>
       </c>
       <c r="E3" t="n">
-        <v>1042.08</v>
+        <v>4007.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1025.81</v>
+        <v>3958.85</v>
       </c>
       <c r="G3" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1540</v>
+        <v>3398.2</v>
       </c>
       <c r="D4" t="n">
-        <v>1464.58</v>
+        <v>3347.53</v>
       </c>
       <c r="E4" t="n">
-        <v>1447.92</v>
+        <v>3249.34</v>
       </c>
       <c r="F4" t="n">
-        <v>1505.19</v>
+        <v>3319.77</v>
       </c>
       <c r="G4" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>115.93</v>
+        <v>1052</v>
       </c>
       <c r="D5" t="n">
-        <v>113.33</v>
+        <v>1047.54</v>
       </c>
       <c r="E5" t="n">
-        <v>110.61</v>
+        <v>1042.59</v>
       </c>
       <c r="F5" t="n">
-        <v>112.63</v>
+        <v>1026.4</v>
       </c>
       <c r="G5" t="n">
-        <v>2.93</v>
+        <v>2.49</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>878</v>
+        <v>5590.5</v>
       </c>
       <c r="D6" t="n">
-        <v>857.35</v>
+        <v>5433.01</v>
       </c>
       <c r="E6" t="n">
-        <v>846.21</v>
+        <v>5172.12</v>
       </c>
       <c r="F6" t="n">
-        <v>848.67</v>
+        <v>5434.16</v>
       </c>
       <c r="G6" t="n">
-        <v>3.46</v>
+        <v>2.88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>467.5</v>
+        <v>116.7</v>
       </c>
       <c r="D7" t="n">
-        <v>457.24</v>
+        <v>113.7</v>
       </c>
       <c r="E7" t="n">
-        <v>442.69</v>
+        <v>110.77</v>
       </c>
       <c r="F7" t="n">
-        <v>451.02</v>
+        <v>112.62</v>
       </c>
       <c r="G7" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3443</v>
+        <v>469.15</v>
       </c>
       <c r="D8" t="n">
-        <v>3337.02</v>
+        <v>458.31</v>
       </c>
       <c r="E8" t="n">
-        <v>3243.38</v>
+        <v>443.73</v>
       </c>
       <c r="F8" t="n">
-        <v>3320.9</v>
+        <v>451.26</v>
       </c>
       <c r="G8" t="n">
-        <v>3.68</v>
+        <v>3.97</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>174.69</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>166.59</v>
+        <v>281.25</v>
       </c>
       <c r="E9" t="n">
-        <v>163.55</v>
+        <v>280.94</v>
       </c>
       <c r="F9" t="n">
-        <v>168.1</v>
+        <v>277.2</v>
       </c>
       <c r="G9" t="n">
-        <v>3.92</v>
+        <v>4.26</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5655</v>
+        <v>889</v>
       </c>
       <c r="D10" t="n">
-        <v>5415.27</v>
+        <v>859.3</v>
       </c>
       <c r="E10" t="n">
-        <v>5160.86</v>
+        <v>846.46</v>
       </c>
       <c r="F10" t="n">
-        <v>5435.32</v>
+        <v>848.8200000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>4.04</v>
+        <v>4.73</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4119</v>
+        <v>517</v>
       </c>
       <c r="D11" t="n">
-        <v>3964.37</v>
+        <v>509.92</v>
       </c>
       <c r="E11" t="n">
-        <v>4011.09</v>
+        <v>494.85</v>
       </c>
       <c r="F11" t="n">
-        <v>3958.06</v>
+        <v>493.1</v>
       </c>
       <c r="G11" t="n">
-        <v>4.07</v>
+        <v>4.85</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>516</v>
+        <v>5595</v>
       </c>
       <c r="D12" t="n">
-        <v>509.06</v>
+        <v>5449.98</v>
       </c>
       <c r="E12" t="n">
-        <v>493.82</v>
+        <v>5205.39</v>
       </c>
       <c r="F12" t="n">
-        <v>493.09</v>
+        <v>5309.1</v>
       </c>
       <c r="G12" t="n">
-        <v>4.65</v>
+        <v>5.39</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -882,19 +882,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2004</v>
+        <v>2010</v>
       </c>
       <c r="D13" t="n">
-        <v>1974.07</v>
+        <v>1979.41</v>
       </c>
       <c r="E13" t="n">
-        <v>1913.17</v>
+        <v>1918.11</v>
       </c>
       <c r="F13" t="n">
-        <v>1905.11</v>
+        <v>1904.58</v>
       </c>
       <c r="G13" t="n">
-        <v>5.19</v>
+        <v>5.54</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>292.5</v>
+        <v>2625</v>
       </c>
       <c r="D14" t="n">
-        <v>280.9</v>
+        <v>2449.47</v>
       </c>
       <c r="E14" t="n">
-        <v>281</v>
+        <v>2459.68</v>
       </c>
       <c r="F14" t="n">
-        <v>277.1</v>
+        <v>2468.97</v>
       </c>
       <c r="G14" t="n">
-        <v>5.56</v>
+        <v>6.32</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2610</v>
+        <v>179.05</v>
       </c>
       <c r="D15" t="n">
-        <v>2440.81</v>
+        <v>167.34</v>
       </c>
       <c r="E15" t="n">
-        <v>2458.14</v>
+        <v>163.94</v>
       </c>
       <c r="F15" t="n">
-        <v>2469.31</v>
+        <v>168.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.7</v>
+        <v>6.39</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5624.5</v>
+        <v>5250.5</v>
       </c>
       <c r="D16" t="n">
-        <v>5423.66</v>
+        <v>5244.63</v>
       </c>
       <c r="E16" t="n">
-        <v>5192.36</v>
+        <v>5247.85</v>
       </c>
       <c r="F16" t="n">
-        <v>5307.03</v>
+        <v>4902.27</v>
       </c>
       <c r="G16" t="n">
-        <v>5.98</v>
+        <v>7.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2232.5</v>
+        <v>672.5</v>
       </c>
       <c r="D17" t="n">
-        <v>2109.61</v>
+        <v>659.65</v>
       </c>
       <c r="E17" t="n">
-        <v>2042.21</v>
+        <v>650.5700000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>2064.79</v>
+        <v>627.8</v>
       </c>
       <c r="G17" t="n">
-        <v>8.119999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>682.95</v>
+        <v>1260</v>
       </c>
       <c r="D18" t="n">
-        <v>658.89</v>
+        <v>1215.79</v>
       </c>
       <c r="E18" t="n">
-        <v>649.4400000000001</v>
+        <v>1179.6</v>
       </c>
       <c r="F18" t="n">
-        <v>628.1900000000001</v>
+        <v>1170.64</v>
       </c>
       <c r="G18" t="n">
-        <v>8.720000000000001</v>
+        <v>7.63</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1798.3</v>
+        <v>1197.2</v>
       </c>
       <c r="D19" t="n">
-        <v>1650.69</v>
+        <v>1155.11</v>
       </c>
       <c r="E19" t="n">
-        <v>1636.65</v>
+        <v>1135.92</v>
       </c>
       <c r="F19" t="n">
-        <v>1649.77</v>
+        <v>1105.47</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1051.05</v>
+        <v>11540</v>
       </c>
       <c r="D20" t="n">
-        <v>1003.29</v>
+        <v>11121.63</v>
       </c>
       <c r="E20" t="n">
-        <v>989.58</v>
+        <v>10920.32</v>
       </c>
       <c r="F20" t="n">
-        <v>953.4</v>
+        <v>10619.81</v>
       </c>
       <c r="G20" t="n">
-        <v>10.24</v>
+        <v>8.66</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2139.3</v>
+        <v>2250</v>
       </c>
       <c r="D21" t="n">
-        <v>1952.61</v>
+        <v>2118.48</v>
       </c>
       <c r="E21" t="n">
-        <v>1897.93</v>
+        <v>2048.05</v>
       </c>
       <c r="F21" t="n">
-        <v>1928.86</v>
+        <v>2064.37</v>
       </c>
       <c r="G21" t="n">
-        <v>10.91</v>
+        <v>8.99</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>397.8</v>
+        <v>1053</v>
       </c>
       <c r="D22" t="n">
-        <v>368.79</v>
+        <v>1006.53</v>
       </c>
       <c r="E22" t="n">
-        <v>361.5</v>
+        <v>990.59</v>
       </c>
       <c r="F22" t="n">
-        <v>356.37</v>
+        <v>954.76</v>
       </c>
       <c r="G22" t="n">
-        <v>11.62</v>
+        <v>10.29</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>186.98</v>
+        <v>1840</v>
       </c>
       <c r="D23" t="n">
-        <v>177.89</v>
+        <v>1658.33</v>
       </c>
       <c r="E23" t="n">
-        <v>173.54</v>
+        <v>1640.95</v>
       </c>
       <c r="F23" t="n">
-        <v>166.92</v>
+        <v>1650.05</v>
       </c>
       <c r="G23" t="n">
-        <v>12.02</v>
+        <v>11.51</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1011.5</v>
+        <v>399.3</v>
       </c>
       <c r="D24" t="n">
-        <v>915.91</v>
+        <v>370.08</v>
       </c>
       <c r="E24" t="n">
-        <v>929.99</v>
+        <v>362.11</v>
       </c>
       <c r="F24" t="n">
-        <v>845.75</v>
+        <v>357.13</v>
       </c>
       <c r="G24" t="n">
-        <v>19.6</v>
+        <v>11.81</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>331</v>
+        <v>2159</v>
       </c>
       <c r="D25" t="n">
-        <v>307.78</v>
+        <v>1964.01</v>
       </c>
       <c r="E25" t="n">
-        <v>293.64</v>
+        <v>1904.02</v>
       </c>
       <c r="F25" t="n">
-        <v>272.75</v>
+        <v>1930.66</v>
       </c>
       <c r="G25" t="n">
-        <v>21.36</v>
+        <v>11.83</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14990</v>
+        <v>187.52</v>
       </c>
       <c r="D26" t="n">
-        <v>14190.53</v>
+        <v>178.39</v>
       </c>
       <c r="E26" t="n">
-        <v>13557.1</v>
+        <v>173.91</v>
       </c>
       <c r="F26" t="n">
-        <v>12188.94</v>
+        <v>167.11</v>
       </c>
       <c r="G26" t="n">
-        <v>22.98</v>
+        <v>12.22</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1396,23 +1396,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1892.8</v>
+        <v>1323.5</v>
       </c>
       <c r="D27" t="n">
-        <v>1704.13</v>
+        <v>1272.83</v>
       </c>
       <c r="E27" t="n">
-        <v>1611.47</v>
+        <v>1188.55</v>
       </c>
       <c r="F27" t="n">
-        <v>1509.81</v>
+        <v>1147.91</v>
       </c>
       <c r="G27" t="n">
-        <v>25.37</v>
+        <v>15.3</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1433,30 +1433,178 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>327</v>
+      </c>
+      <c r="D28" t="n">
+        <v>308.85</v>
+      </c>
+      <c r="E28" t="n">
+        <v>295.01</v>
+      </c>
+      <c r="F28" t="n">
+        <v>272.88</v>
+      </c>
+      <c r="G28" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>14735</v>
+      </c>
+      <c r="D29" t="n">
+        <v>14226.67</v>
+      </c>
+      <c r="E29" t="n">
+        <v>13595.14</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12188.28</v>
+      </c>
+      <c r="G29" t="n">
+        <v>20.89</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D30" t="n">
+        <v>918.33</v>
+      </c>
+      <c r="E30" t="n">
+        <v>931.9400000000001</v>
+      </c>
+      <c r="F30" t="n">
+        <v>845.98</v>
+      </c>
+      <c r="G30" t="n">
+        <v>22.93</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1715.92</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1619.9</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1510.48</v>
+      </c>
+      <c r="G31" t="n">
+        <v>24.46</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C28" t="n">
-        <v>3280</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2847.54</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2837.97</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2589.35</v>
-      </c>
-      <c r="G28" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="C32" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2862.79</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2847.83</v>
+      </c>
+      <c r="F32" t="n">
+        <v>2596.57</v>
+      </c>
+      <c r="G32" t="n">
+        <v>29.02</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1526.1</v>
+        <v>3362.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1470.19</v>
+        <v>3346.32</v>
       </c>
       <c r="E2" t="n">
-        <v>1447.19</v>
+        <v>3248.61</v>
       </c>
       <c r="F2" t="n">
-        <v>1505</v>
+        <v>3319.59</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4038.1</v>
+        <v>1529.2</v>
       </c>
       <c r="D3" t="n">
-        <v>3972.84</v>
+        <v>1475.34</v>
       </c>
       <c r="E3" t="n">
-        <v>4007.7</v>
+        <v>1446.51</v>
       </c>
       <c r="F3" t="n">
-        <v>3958.85</v>
+        <v>1504.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3398.2</v>
+        <v>4035</v>
       </c>
       <c r="D4" t="n">
-        <v>3347.53</v>
+        <v>3981.49</v>
       </c>
       <c r="E4" t="n">
-        <v>3249.34</v>
+        <v>4004.6</v>
       </c>
       <c r="F4" t="n">
-        <v>3319.77</v>
+        <v>3959.44</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>1.91</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1052</v>
+        <v>5616.5</v>
       </c>
       <c r="D5" t="n">
-        <v>1047.54</v>
+        <v>5452.17</v>
       </c>
       <c r="E5" t="n">
-        <v>1042.59</v>
+        <v>5185.98</v>
       </c>
       <c r="F5" t="n">
-        <v>1026.4</v>
+        <v>5432.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.49</v>
+        <v>3.39</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5590.5</v>
+        <v>116.45</v>
       </c>
       <c r="D6" t="n">
-        <v>5433.01</v>
+        <v>114.07</v>
       </c>
       <c r="E6" t="n">
-        <v>5172.12</v>
+        <v>110.9</v>
       </c>
       <c r="F6" t="n">
-        <v>5434.16</v>
+        <v>112.6</v>
       </c>
       <c r="G6" t="n">
-        <v>2.88</v>
+        <v>3.41</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>116.7</v>
+        <v>466.9</v>
       </c>
       <c r="D7" t="n">
-        <v>113.7</v>
+        <v>459.55</v>
       </c>
       <c r="E7" t="n">
-        <v>110.77</v>
+        <v>444.66</v>
       </c>
       <c r="F7" t="n">
-        <v>112.62</v>
+        <v>451.46</v>
       </c>
       <c r="G7" t="n">
-        <v>3.63</v>
+        <v>3.42</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>469.15</v>
+        <v>5516</v>
       </c>
       <c r="D8" t="n">
-        <v>458.31</v>
+        <v>5472.94</v>
       </c>
       <c r="E8" t="n">
-        <v>443.73</v>
+        <v>5216.73</v>
       </c>
       <c r="F8" t="n">
-        <v>451.26</v>
+        <v>5310.5</v>
       </c>
       <c r="G8" t="n">
-        <v>3.97</v>
+        <v>3.87</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>289</v>
+        <v>515</v>
       </c>
       <c r="D9" t="n">
-        <v>281.25</v>
+        <v>510.79</v>
       </c>
       <c r="E9" t="n">
-        <v>280.94</v>
+        <v>495.83</v>
       </c>
       <c r="F9" t="n">
-        <v>277.2</v>
+        <v>493.1</v>
       </c>
       <c r="G9" t="n">
-        <v>4.26</v>
+        <v>4.44</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>889</v>
+        <v>888.2</v>
       </c>
       <c r="D10" t="n">
-        <v>859.3</v>
+        <v>861.5700000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>846.46</v>
+        <v>846.71</v>
       </c>
       <c r="F10" t="n">
-        <v>848.8200000000001</v>
+        <v>849.01</v>
       </c>
       <c r="G10" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>517</v>
+        <v>177.54</v>
       </c>
       <c r="D11" t="n">
-        <v>509.92</v>
+        <v>168.1</v>
       </c>
       <c r="E11" t="n">
-        <v>494.85</v>
+        <v>164.32</v>
       </c>
       <c r="F11" t="n">
-        <v>493.1</v>
+        <v>168.47</v>
       </c>
       <c r="G11" t="n">
-        <v>4.85</v>
+        <v>5.38</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5595</v>
+        <v>2008</v>
       </c>
       <c r="D12" t="n">
-        <v>5449.98</v>
+        <v>1979.35</v>
       </c>
       <c r="E12" t="n">
-        <v>5205.39</v>
+        <v>1918.07</v>
       </c>
       <c r="F12" t="n">
-        <v>5309.1</v>
+        <v>1904.57</v>
       </c>
       <c r="G12" t="n">
-        <v>5.39</v>
+        <v>5.43</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2010</v>
+        <v>2608</v>
       </c>
       <c r="D13" t="n">
-        <v>1979.41</v>
+        <v>2457.84</v>
       </c>
       <c r="E13" t="n">
-        <v>1918.11</v>
+        <v>2461.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1904.58</v>
+        <v>2468.32</v>
       </c>
       <c r="G13" t="n">
-        <v>5.54</v>
+        <v>5.66</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2625</v>
+        <v>293.25</v>
       </c>
       <c r="D14" t="n">
-        <v>2449.47</v>
+        <v>281.83</v>
       </c>
       <c r="E14" t="n">
-        <v>2459.68</v>
+        <v>281.04</v>
       </c>
       <c r="F14" t="n">
-        <v>2468.97</v>
+        <v>277.33</v>
       </c>
       <c r="G14" t="n">
-        <v>6.32</v>
+        <v>5.74</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>179.05</v>
+        <v>11470</v>
       </c>
       <c r="D15" t="n">
-        <v>167.34</v>
+        <v>11119.3</v>
       </c>
       <c r="E15" t="n">
-        <v>163.94</v>
+        <v>10918.92</v>
       </c>
       <c r="F15" t="n">
-        <v>168.3</v>
+        <v>10619.46</v>
       </c>
       <c r="G15" t="n">
-        <v>6.39</v>
+        <v>8.01</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5250.5</v>
+        <v>679.75</v>
       </c>
       <c r="D16" t="n">
-        <v>5244.63</v>
+        <v>660.98</v>
       </c>
       <c r="E16" t="n">
-        <v>5247.85</v>
+        <v>651.51</v>
       </c>
       <c r="F16" t="n">
-        <v>4902.27</v>
+        <v>627.42</v>
       </c>
       <c r="G16" t="n">
-        <v>7.1</v>
+        <v>8.34</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>672.5</v>
+        <v>1198.7</v>
       </c>
       <c r="D17" t="n">
-        <v>659.65</v>
+        <v>1159.03</v>
       </c>
       <c r="E17" t="n">
-        <v>650.5700000000001</v>
+        <v>1137.07</v>
       </c>
       <c r="F17" t="n">
-        <v>627.8</v>
+        <v>1106.13</v>
       </c>
       <c r="G17" t="n">
-        <v>7.12</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1260</v>
+        <v>1271</v>
       </c>
       <c r="D18" t="n">
-        <v>1215.79</v>
+        <v>1216.16</v>
       </c>
       <c r="E18" t="n">
-        <v>1179.6</v>
+        <v>1179.82</v>
       </c>
       <c r="F18" t="n">
-        <v>1170.64</v>
+        <v>1170.7</v>
       </c>
       <c r="G18" t="n">
-        <v>7.63</v>
+        <v>8.57</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1197.2</v>
+        <v>1040.85</v>
       </c>
       <c r="D19" t="n">
-        <v>1155.11</v>
+        <v>1009.25</v>
       </c>
       <c r="E19" t="n">
-        <v>1135.92</v>
+        <v>991.34</v>
       </c>
       <c r="F19" t="n">
-        <v>1105.47</v>
+        <v>956.02</v>
       </c>
       <c r="G19" t="n">
-        <v>8.300000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11540</v>
+        <v>2269.5</v>
       </c>
       <c r="D20" t="n">
-        <v>11121.63</v>
+        <v>2119.13</v>
       </c>
       <c r="E20" t="n">
-        <v>10920.32</v>
+        <v>2048.44</v>
       </c>
       <c r="F20" t="n">
-        <v>10619.81</v>
+        <v>2064.47</v>
       </c>
       <c r="G20" t="n">
-        <v>8.66</v>
+        <v>9.93</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2250</v>
+        <v>396.3</v>
       </c>
       <c r="D21" t="n">
-        <v>2118.48</v>
+        <v>371.5</v>
       </c>
       <c r="E21" t="n">
-        <v>2048.05</v>
+        <v>362.7</v>
       </c>
       <c r="F21" t="n">
-        <v>2064.37</v>
+        <v>357.83</v>
       </c>
       <c r="G21" t="n">
-        <v>8.99</v>
+        <v>10.75</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1053</v>
+        <v>2064.2</v>
       </c>
       <c r="D22" t="n">
-        <v>1006.53</v>
+        <v>2063.63</v>
       </c>
       <c r="E22" t="n">
-        <v>990.59</v>
+        <v>2018.89</v>
       </c>
       <c r="F22" t="n">
-        <v>954.76</v>
+        <v>1862.98</v>
       </c>
       <c r="G22" t="n">
-        <v>10.29</v>
+        <v>10.8</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1840</v>
+        <v>1836.5</v>
       </c>
       <c r="D23" t="n">
-        <v>1658.33</v>
+        <v>1658.21</v>
       </c>
       <c r="E23" t="n">
-        <v>1640.95</v>
+        <v>1640.88</v>
       </c>
       <c r="F23" t="n">
-        <v>1650.05</v>
+        <v>1650.03</v>
       </c>
       <c r="G23" t="n">
-        <v>11.51</v>
+        <v>11.3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1280,28 +1280,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>399.3</v>
+        <v>186.75</v>
       </c>
       <c r="D24" t="n">
-        <v>370.08</v>
+        <v>178.99</v>
       </c>
       <c r="E24" t="n">
-        <v>362.11</v>
+        <v>174.23</v>
       </c>
       <c r="F24" t="n">
-        <v>357.13</v>
+        <v>167.3</v>
       </c>
       <c r="G24" t="n">
-        <v>11.81</v>
+        <v>11.63</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2159</v>
+        <v>2193.6</v>
       </c>
       <c r="D25" t="n">
-        <v>1964.01</v>
+        <v>1965.16</v>
       </c>
       <c r="E25" t="n">
-        <v>1904.02</v>
+        <v>1904.71</v>
       </c>
       <c r="F25" t="n">
-        <v>1930.66</v>
+        <v>1930.83</v>
       </c>
       <c r="G25" t="n">
-        <v>11.83</v>
+        <v>13.61</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1354,28 +1354,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>187.52</v>
+        <v>1339.7</v>
       </c>
       <c r="D26" t="n">
-        <v>178.39</v>
+        <v>1277.37</v>
       </c>
       <c r="E26" t="n">
-        <v>173.91</v>
+        <v>1195.27</v>
       </c>
       <c r="F26" t="n">
-        <v>167.11</v>
+        <v>1147.95</v>
       </c>
       <c r="G26" t="n">
-        <v>12.22</v>
+        <v>16.7</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1391,28 +1391,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1323.5</v>
+        <v>327.1</v>
       </c>
       <c r="D27" t="n">
-        <v>1272.83</v>
+        <v>310.21</v>
       </c>
       <c r="E27" t="n">
-        <v>1188.55</v>
+        <v>296.38</v>
       </c>
       <c r="F27" t="n">
-        <v>1147.91</v>
+        <v>272.99</v>
       </c>
       <c r="G27" t="n">
-        <v>15.3</v>
+        <v>19.82</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1428,28 +1428,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>327</v>
+        <v>14701</v>
       </c>
       <c r="D28" t="n">
-        <v>308.85</v>
+        <v>14233.13</v>
       </c>
       <c r="E28" t="n">
-        <v>295.01</v>
+        <v>13635.84</v>
       </c>
       <c r="F28" t="n">
-        <v>272.88</v>
+        <v>12186.32</v>
       </c>
       <c r="G28" t="n">
-        <v>19.83</v>
+        <v>20.64</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1465,28 +1465,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14735</v>
+        <v>1028.2</v>
       </c>
       <c r="D29" t="n">
-        <v>14226.67</v>
+        <v>920.77</v>
       </c>
       <c r="E29" t="n">
-        <v>13595.14</v>
+        <v>933.54</v>
       </c>
       <c r="F29" t="n">
-        <v>12188.28</v>
+        <v>846.22</v>
       </c>
       <c r="G29" t="n">
-        <v>20.89</v>
+        <v>21.5</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1502,28 +1502,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1040</v>
+        <v>1895.6</v>
       </c>
       <c r="D30" t="n">
-        <v>918.33</v>
+        <v>1728.32</v>
       </c>
       <c r="E30" t="n">
-        <v>931.9400000000001</v>
+        <v>1628.28</v>
       </c>
       <c r="F30" t="n">
-        <v>845.98</v>
+        <v>1511.03</v>
       </c>
       <c r="G30" t="n">
-        <v>22.93</v>
+        <v>25.45</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1539,28 +1539,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1880</v>
+        <v>3303</v>
       </c>
       <c r="D31" t="n">
-        <v>1715.92</v>
+        <v>2879.04</v>
       </c>
       <c r="E31" t="n">
-        <v>1619.9</v>
+        <v>2857.54</v>
       </c>
       <c r="F31" t="n">
-        <v>1510.48</v>
+        <v>2603.59</v>
       </c>
       <c r="G31" t="n">
-        <v>24.46</v>
+        <v>26.86</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1576,28 +1576,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>27-08-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3350</v>
+        <v>11770</v>
       </c>
       <c r="D32" t="n">
-        <v>2862.79</v>
+        <v>11530.63</v>
       </c>
       <c r="E32" t="n">
-        <v>2847.83</v>
+        <v>11253.75</v>
       </c>
       <c r="F32" t="n">
-        <v>2596.57</v>
+        <v>8716.780000000001</v>
       </c>
       <c r="G32" t="n">
-        <v>29.02</v>
+        <v>35.03</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3362.1</v>
+        <v>1529.2</v>
       </c>
       <c r="D2" t="n">
-        <v>3346.32</v>
+        <v>1475.34</v>
       </c>
       <c r="E2" t="n">
-        <v>3248.61</v>
+        <v>1446.51</v>
       </c>
       <c r="F2" t="n">
-        <v>3319.59</v>
+        <v>1504.88</v>
       </c>
       <c r="G2" t="n">
-        <v>1.28</v>
+        <v>1.62</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1529.2</v>
+        <v>4027</v>
       </c>
       <c r="D3" t="n">
-        <v>1475.34</v>
+        <v>3981.22</v>
       </c>
       <c r="E3" t="n">
-        <v>1446.51</v>
+        <v>4004.44</v>
       </c>
       <c r="F3" t="n">
-        <v>1504.88</v>
+        <v>3959.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4035</v>
+        <v>115.4</v>
       </c>
       <c r="D4" t="n">
-        <v>3981.49</v>
+        <v>114.04</v>
       </c>
       <c r="E4" t="n">
-        <v>4004.6</v>
+        <v>110.88</v>
       </c>
       <c r="F4" t="n">
-        <v>3959.44</v>
+        <v>112.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.91</v>
+        <v>2.49</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5616.5</v>
+        <v>469.85</v>
       </c>
       <c r="D5" t="n">
-        <v>5452.17</v>
+        <v>459.65</v>
       </c>
       <c r="E5" t="n">
-        <v>5185.98</v>
+        <v>444.72</v>
       </c>
       <c r="F5" t="n">
-        <v>5432.3</v>
+        <v>451.48</v>
       </c>
       <c r="G5" t="n">
-        <v>3.39</v>
+        <v>4.07</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>116.45</v>
+        <v>5654</v>
       </c>
       <c r="D6" t="n">
-        <v>114.07</v>
+        <v>5453.42</v>
       </c>
       <c r="E6" t="n">
-        <v>110.9</v>
+        <v>5186.73</v>
       </c>
       <c r="F6" t="n">
-        <v>112.6</v>
+        <v>5432.48</v>
       </c>
       <c r="G6" t="n">
-        <v>3.41</v>
+        <v>4.08</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>466.9</v>
+        <v>884.4</v>
       </c>
       <c r="D7" t="n">
-        <v>459.55</v>
+        <v>861.45</v>
       </c>
       <c r="E7" t="n">
-        <v>444.66</v>
+        <v>846.63</v>
       </c>
       <c r="F7" t="n">
-        <v>451.46</v>
+        <v>848.99</v>
       </c>
       <c r="G7" t="n">
-        <v>3.42</v>
+        <v>4.17</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5516</v>
+        <v>5550</v>
       </c>
       <c r="D8" t="n">
-        <v>5472.94</v>
+        <v>5474.08</v>
       </c>
       <c r="E8" t="n">
-        <v>5216.73</v>
+        <v>5217.41</v>
       </c>
       <c r="F8" t="n">
-        <v>5310.5</v>
+        <v>5310.67</v>
       </c>
       <c r="G8" t="n">
-        <v>3.87</v>
+        <v>4.51</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>515</v>
+        <v>2588</v>
       </c>
       <c r="D9" t="n">
-        <v>510.79</v>
+        <v>2457.17</v>
       </c>
       <c r="E9" t="n">
-        <v>495.83</v>
+        <v>2460.85</v>
       </c>
       <c r="F9" t="n">
-        <v>493.1</v>
+        <v>2468.22</v>
       </c>
       <c r="G9" t="n">
-        <v>4.44</v>
+        <v>4.85</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>888.2</v>
+        <v>290.95</v>
       </c>
       <c r="D10" t="n">
-        <v>861.5700000000001</v>
+        <v>281.76</v>
       </c>
       <c r="E10" t="n">
-        <v>846.71</v>
+        <v>280.99</v>
       </c>
       <c r="F10" t="n">
-        <v>849.01</v>
+        <v>277.32</v>
       </c>
       <c r="G10" t="n">
-        <v>4.62</v>
+        <v>4.91</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,10 +808,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>177.54</v>
+        <v>177.4</v>
       </c>
       <c r="D11" t="n">
-        <v>168.1</v>
+        <v>168.09</v>
       </c>
       <c r="E11" t="n">
         <v>164.32</v>
@@ -820,7 +820,7 @@
         <v>168.47</v>
       </c>
       <c r="G11" t="n">
-        <v>5.38</v>
+        <v>5.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="D12" t="n">
-        <v>1979.35</v>
+        <v>1985.16</v>
       </c>
       <c r="E12" t="n">
-        <v>1918.07</v>
+        <v>1922.93</v>
       </c>
       <c r="F12" t="n">
-        <v>1904.57</v>
+        <v>1904.7</v>
       </c>
       <c r="G12" t="n">
-        <v>5.43</v>
+        <v>5.58</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2608</v>
+        <v>1024</v>
       </c>
       <c r="D13" t="n">
-        <v>2457.84</v>
+        <v>1008.68</v>
       </c>
       <c r="E13" t="n">
-        <v>2461.25</v>
+        <v>991</v>
       </c>
       <c r="F13" t="n">
-        <v>2468.32</v>
+        <v>955.9299999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>5.66</v>
+        <v>7.12</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>293.25</v>
+        <v>11399</v>
       </c>
       <c r="D14" t="n">
-        <v>281.83</v>
+        <v>11154.37</v>
       </c>
       <c r="E14" t="n">
-        <v>281.04</v>
+        <v>10937.4</v>
       </c>
       <c r="F14" t="n">
-        <v>277.33</v>
+        <v>10616.77</v>
       </c>
       <c r="G14" t="n">
-        <v>5.74</v>
+        <v>7.37</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11470</v>
+        <v>676.15</v>
       </c>
       <c r="D15" t="n">
-        <v>11119.3</v>
+        <v>660.86</v>
       </c>
       <c r="E15" t="n">
-        <v>10918.92</v>
+        <v>651.4400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10619.46</v>
+        <v>627.41</v>
       </c>
       <c r="G15" t="n">
-        <v>8.01</v>
+        <v>7.77</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>679.75</v>
+        <v>1623</v>
       </c>
       <c r="D16" t="n">
-        <v>660.98</v>
+        <v>1619.86</v>
       </c>
       <c r="E16" t="n">
-        <v>651.51</v>
+        <v>1619.35</v>
       </c>
       <c r="F16" t="n">
-        <v>627.42</v>
+        <v>1501.81</v>
       </c>
       <c r="G16" t="n">
-        <v>8.34</v>
+        <v>8.07</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1198.7</v>
+        <v>389.3</v>
       </c>
       <c r="D17" t="n">
-        <v>1159.03</v>
+        <v>371.27</v>
       </c>
       <c r="E17" t="n">
-        <v>1137.07</v>
+        <v>362.56</v>
       </c>
       <c r="F17" t="n">
-        <v>1106.13</v>
+        <v>357.79</v>
       </c>
       <c r="G17" t="n">
-        <v>8.369999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1271</v>
+        <v>1204</v>
       </c>
       <c r="D18" t="n">
-        <v>1216.16</v>
+        <v>1159.2</v>
       </c>
       <c r="E18" t="n">
-        <v>1179.82</v>
+        <v>1137.18</v>
       </c>
       <c r="F18" t="n">
-        <v>1170.7</v>
+        <v>1106.15</v>
       </c>
       <c r="G18" t="n">
-        <v>8.57</v>
+        <v>8.85</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1040.85</v>
+        <v>2253</v>
       </c>
       <c r="D19" t="n">
-        <v>1009.25</v>
+        <v>2126.71</v>
       </c>
       <c r="E19" t="n">
-        <v>991.34</v>
+        <v>2053.95</v>
       </c>
       <c r="F19" t="n">
-        <v>956.02</v>
+        <v>2063.97</v>
       </c>
       <c r="G19" t="n">
-        <v>8.869999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2269.5</v>
+        <v>1280</v>
       </c>
       <c r="D20" t="n">
-        <v>2119.13</v>
+        <v>1220.11</v>
       </c>
       <c r="E20" t="n">
-        <v>2048.44</v>
+        <v>1183.24</v>
       </c>
       <c r="F20" t="n">
-        <v>2064.47</v>
+        <v>1170.5</v>
       </c>
       <c r="G20" t="n">
-        <v>9.93</v>
+        <v>9.35</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>396.3</v>
+        <v>184.5</v>
       </c>
       <c r="D21" t="n">
-        <v>371.5</v>
+        <v>178.92</v>
       </c>
       <c r="E21" t="n">
-        <v>362.7</v>
+        <v>174.18</v>
       </c>
       <c r="F21" t="n">
-        <v>357.83</v>
+        <v>167.29</v>
       </c>
       <c r="G21" t="n">
-        <v>10.75</v>
+        <v>10.29</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2064.2</v>
+        <v>321.9</v>
       </c>
       <c r="D22" t="n">
-        <v>2063.63</v>
+        <v>313.29</v>
       </c>
       <c r="E22" t="n">
-        <v>2018.89</v>
+        <v>312.16</v>
       </c>
       <c r="F22" t="n">
-        <v>1862.98</v>
+        <v>291.18</v>
       </c>
       <c r="G22" t="n">
-        <v>10.8</v>
+        <v>10.55</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1836.5</v>
+        <v>2069.4</v>
       </c>
       <c r="D23" t="n">
-        <v>1658.21</v>
+        <v>2063.81</v>
       </c>
       <c r="E23" t="n">
-        <v>1640.88</v>
+        <v>2019</v>
       </c>
       <c r="F23" t="n">
-        <v>1650.03</v>
+        <v>1863.01</v>
       </c>
       <c r="G23" t="n">
-        <v>11.3</v>
+        <v>11.08</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>186.75</v>
+        <v>1837.9</v>
       </c>
       <c r="D24" t="n">
-        <v>178.99</v>
+        <v>1667.55</v>
       </c>
       <c r="E24" t="n">
-        <v>174.23</v>
+        <v>1645.36</v>
       </c>
       <c r="F24" t="n">
-        <v>167.3</v>
+        <v>1650.25</v>
       </c>
       <c r="G24" t="n">
-        <v>11.63</v>
+        <v>11.37</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2193.6</v>
+        <v>1872.9</v>
       </c>
       <c r="D25" t="n">
-        <v>1965.16</v>
+        <v>1843.5</v>
       </c>
       <c r="E25" t="n">
-        <v>1904.71</v>
+        <v>1836.83</v>
       </c>
       <c r="F25" t="n">
-        <v>1930.83</v>
+        <v>1664.88</v>
       </c>
       <c r="G25" t="n">
-        <v>13.61</v>
+        <v>12.49</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1339.7</v>
+        <v>2188</v>
       </c>
       <c r="D26" t="n">
-        <v>1277.37</v>
+        <v>1977.19</v>
       </c>
       <c r="E26" t="n">
-        <v>1195.27</v>
+        <v>1910.56</v>
       </c>
       <c r="F26" t="n">
-        <v>1147.95</v>
+        <v>1932.64</v>
       </c>
       <c r="G26" t="n">
-        <v>16.7</v>
+        <v>13.21</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1396,23 +1396,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>327.1</v>
+        <v>1330</v>
       </c>
       <c r="D27" t="n">
-        <v>310.21</v>
+        <v>1277.05</v>
       </c>
       <c r="E27" t="n">
-        <v>296.38</v>
+        <v>1195.08</v>
       </c>
       <c r="F27" t="n">
-        <v>272.99</v>
+        <v>1147.9</v>
       </c>
       <c r="G27" t="n">
-        <v>19.82</v>
+        <v>15.86</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1433,23 +1433,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>14701</v>
+        <v>328.5</v>
       </c>
       <c r="D28" t="n">
-        <v>14233.13</v>
+        <v>310.25</v>
       </c>
       <c r="E28" t="n">
-        <v>13635.84</v>
+        <v>296.41</v>
       </c>
       <c r="F28" t="n">
-        <v>12186.32</v>
+        <v>272.99</v>
       </c>
       <c r="G28" t="n">
-        <v>20.64</v>
+        <v>20.33</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1470,23 +1470,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1028.2</v>
+        <v>14711</v>
       </c>
       <c r="D29" t="n">
-        <v>920.77</v>
+        <v>14233.47</v>
       </c>
       <c r="E29" t="n">
-        <v>933.54</v>
+        <v>13636.04</v>
       </c>
       <c r="F29" t="n">
-        <v>846.22</v>
+        <v>12186.36</v>
       </c>
       <c r="G29" t="n">
-        <v>21.5</v>
+        <v>20.72</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1507,23 +1507,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1895.6</v>
+        <v>1038.1</v>
       </c>
       <c r="D30" t="n">
-        <v>1728.32</v>
+        <v>921.1</v>
       </c>
       <c r="E30" t="n">
-        <v>1628.28</v>
+        <v>933.73</v>
       </c>
       <c r="F30" t="n">
-        <v>1511.03</v>
+        <v>846.27</v>
       </c>
       <c r="G30" t="n">
-        <v>25.45</v>
+        <v>22.67</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1548,19 +1548,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3303</v>
+        <v>3273</v>
       </c>
       <c r="D31" t="n">
-        <v>2879.04</v>
+        <v>2878.04</v>
       </c>
       <c r="E31" t="n">
-        <v>2857.54</v>
+        <v>2856.94</v>
       </c>
       <c r="F31" t="n">
-        <v>2603.59</v>
+        <v>2603.44</v>
       </c>
       <c r="G31" t="n">
-        <v>26.86</v>
+        <v>25.72</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1581,23 +1581,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>11770</v>
+        <v>1901.8</v>
       </c>
       <c r="D32" t="n">
-        <v>11530.63</v>
+        <v>1728.53</v>
       </c>
       <c r="E32" t="n">
-        <v>11253.75</v>
+        <v>1628.41</v>
       </c>
       <c r="F32" t="n">
-        <v>8716.780000000001</v>
+        <v>1511.07</v>
       </c>
       <c r="G32" t="n">
-        <v>35.03</v>
+        <v>25.86</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1529.2</v>
+        <v>1531.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1475.34</v>
+        <v>1480.52</v>
       </c>
       <c r="E2" t="n">
-        <v>1446.51</v>
+        <v>1446.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1504.88</v>
+        <v>1504.62</v>
       </c>
       <c r="G2" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4027</v>
+        <v>4029.7</v>
       </c>
       <c r="D3" t="n">
-        <v>3981.22</v>
+        <v>3981.31</v>
       </c>
       <c r="E3" t="n">
-        <v>4004.44</v>
+        <v>4004.49</v>
       </c>
       <c r="F3" t="n">
-        <v>3959.4</v>
+        <v>3959.41</v>
       </c>
       <c r="G3" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -549,16 +549,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.4</v>
+        <v>115.39</v>
       </c>
       <c r="D4" t="n">
-        <v>114.04</v>
+        <v>114.36</v>
       </c>
       <c r="E4" t="n">
-        <v>110.88</v>
+        <v>111.01</v>
       </c>
       <c r="F4" t="n">
-        <v>112.6</v>
+        <v>112.58</v>
       </c>
       <c r="G4" t="n">
         <v>2.49</v>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>469.85</v>
+        <v>876.7</v>
       </c>
       <c r="D5" t="n">
-        <v>459.65</v>
+        <v>861.1900000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>444.72</v>
+        <v>846.48</v>
       </c>
       <c r="F5" t="n">
-        <v>451.48</v>
+        <v>848.96</v>
       </c>
       <c r="G5" t="n">
-        <v>4.07</v>
+        <v>3.27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5654</v>
+        <v>2554.7</v>
       </c>
       <c r="D6" t="n">
-        <v>5453.42</v>
+        <v>2464.37</v>
       </c>
       <c r="E6" t="n">
-        <v>5186.73</v>
+        <v>2461.67</v>
       </c>
       <c r="F6" t="n">
-        <v>5432.48</v>
+        <v>2467.27</v>
       </c>
       <c r="G6" t="n">
-        <v>4.08</v>
+        <v>3.54</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>884.4</v>
+        <v>175.9</v>
       </c>
       <c r="D7" t="n">
-        <v>861.45</v>
+        <v>168.78</v>
       </c>
       <c r="E7" t="n">
-        <v>846.63</v>
+        <v>164.7</v>
       </c>
       <c r="F7" t="n">
-        <v>848.99</v>
+        <v>168.65</v>
       </c>
       <c r="G7" t="n">
-        <v>4.17</v>
+        <v>4.3</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5550</v>
+        <v>1988.5</v>
       </c>
       <c r="D8" t="n">
-        <v>5474.08</v>
+        <v>1984.41</v>
       </c>
       <c r="E8" t="n">
-        <v>5217.41</v>
+        <v>1922.48</v>
       </c>
       <c r="F8" t="n">
-        <v>5310.67</v>
+        <v>1904.58</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51</v>
+        <v>4.41</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2588</v>
+        <v>517.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2457.17</v>
+        <v>510.87</v>
       </c>
       <c r="E9" t="n">
-        <v>2460.85</v>
+        <v>495.88</v>
       </c>
       <c r="F9" t="n">
-        <v>2468.22</v>
+        <v>493.11</v>
       </c>
       <c r="G9" t="n">
-        <v>4.85</v>
+        <v>4.95</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>290.95</v>
+        <v>291.65</v>
       </c>
       <c r="D10" t="n">
-        <v>281.76</v>
+        <v>281.78</v>
       </c>
       <c r="E10" t="n">
-        <v>280.99</v>
+        <v>281.01</v>
       </c>
       <c r="F10" t="n">
-        <v>277.32</v>
+        <v>277.33</v>
       </c>
       <c r="G10" t="n">
-        <v>4.91</v>
+        <v>5.17</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>177.4</v>
+        <v>5616</v>
       </c>
       <c r="D11" t="n">
-        <v>168.09</v>
+        <v>5476.28</v>
       </c>
       <c r="E11" t="n">
-        <v>164.32</v>
+        <v>5218.73</v>
       </c>
       <c r="F11" t="n">
-        <v>168.47</v>
+        <v>5311</v>
       </c>
       <c r="G11" t="n">
-        <v>5.3</v>
+        <v>5.74</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2011</v>
+        <v>481.6</v>
       </c>
       <c r="D12" t="n">
-        <v>1985.16</v>
+        <v>461.19</v>
       </c>
       <c r="E12" t="n">
-        <v>1922.93</v>
+        <v>445.99</v>
       </c>
       <c r="F12" t="n">
-        <v>1904.7</v>
+        <v>451.73</v>
       </c>
       <c r="G12" t="n">
-        <v>5.58</v>
+        <v>6.61</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1024</v>
+        <v>11359</v>
       </c>
       <c r="D13" t="n">
-        <v>1008.68</v>
+        <v>11153.03</v>
       </c>
       <c r="E13" t="n">
-        <v>991</v>
+        <v>10936.6</v>
       </c>
       <c r="F13" t="n">
-        <v>955.9299999999999</v>
+        <v>10616.57</v>
       </c>
       <c r="G13" t="n">
-        <v>7.12</v>
+        <v>6.99</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11399</v>
+        <v>674.5</v>
       </c>
       <c r="D14" t="n">
-        <v>11154.37</v>
+        <v>661.36</v>
       </c>
       <c r="E14" t="n">
-        <v>10937.4</v>
+        <v>652.6</v>
       </c>
       <c r="F14" t="n">
-        <v>10616.77</v>
+        <v>627.02</v>
       </c>
       <c r="G14" t="n">
-        <v>7.37</v>
+        <v>7.57</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>676.15</v>
+        <v>1033.95</v>
       </c>
       <c r="D15" t="n">
-        <v>660.86</v>
+        <v>1011.68</v>
       </c>
       <c r="E15" t="n">
-        <v>651.4400000000001</v>
+        <v>991.59</v>
       </c>
       <c r="F15" t="n">
-        <v>627.41</v>
+        <v>957.15</v>
       </c>
       <c r="G15" t="n">
-        <v>7.77</v>
+        <v>8.02</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1623</v>
+        <v>315.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1619.86</v>
+        <v>313.08</v>
       </c>
       <c r="E16" t="n">
-        <v>1619.35</v>
+        <v>312.03</v>
       </c>
       <c r="F16" t="n">
-        <v>1501.81</v>
+        <v>291.14</v>
       </c>
       <c r="G16" t="n">
-        <v>8.07</v>
+        <v>8.33</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>389.3</v>
+        <v>5900.5</v>
       </c>
       <c r="D17" t="n">
-        <v>371.27</v>
+        <v>5461.63</v>
       </c>
       <c r="E17" t="n">
-        <v>362.56</v>
+        <v>5191.66</v>
       </c>
       <c r="F17" t="n">
-        <v>357.79</v>
+        <v>5433.72</v>
       </c>
       <c r="G17" t="n">
-        <v>8.81</v>
+        <v>8.59</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1204</v>
+        <v>1205.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1159.2</v>
+        <v>1159.24</v>
       </c>
       <c r="E18" t="n">
-        <v>1137.18</v>
+        <v>1137.2</v>
       </c>
       <c r="F18" t="n">
-        <v>1106.15</v>
+        <v>1106.16</v>
       </c>
       <c r="G18" t="n">
-        <v>8.85</v>
+        <v>8.94</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2253</v>
+        <v>2258.8</v>
       </c>
       <c r="D19" t="n">
-        <v>2126.71</v>
+        <v>2136.19</v>
       </c>
       <c r="E19" t="n">
-        <v>2053.95</v>
+        <v>2060.03</v>
       </c>
       <c r="F19" t="n">
-        <v>2063.97</v>
+        <v>2063.4</v>
       </c>
       <c r="G19" t="n">
-        <v>9.16</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1280</v>
+        <v>1281.4</v>
       </c>
       <c r="D20" t="n">
-        <v>1220.11</v>
+        <v>1220.15</v>
       </c>
       <c r="E20" t="n">
-        <v>1183.24</v>
+        <v>1183.27</v>
       </c>
       <c r="F20" t="n">
-        <v>1170.5</v>
+        <v>1170.51</v>
       </c>
       <c r="G20" t="n">
-        <v>9.35</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>184.5</v>
+        <v>392.55</v>
       </c>
       <c r="D21" t="n">
-        <v>178.92</v>
+        <v>373.05</v>
       </c>
       <c r="E21" t="n">
-        <v>174.18</v>
+        <v>362.91</v>
       </c>
       <c r="F21" t="n">
-        <v>167.29</v>
+        <v>358.47</v>
       </c>
       <c r="G21" t="n">
-        <v>10.29</v>
+        <v>9.51</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>321.9</v>
+        <v>1636.5</v>
       </c>
       <c r="D22" t="n">
-        <v>313.29</v>
+        <v>1611.4</v>
       </c>
       <c r="E22" t="n">
-        <v>312.16</v>
+        <v>1539.42</v>
       </c>
       <c r="F22" t="n">
-        <v>291.18</v>
+        <v>1481.88</v>
       </c>
       <c r="G22" t="n">
-        <v>10.55</v>
+        <v>10.43</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1243,28 +1243,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2069.4</v>
+        <v>184.91</v>
       </c>
       <c r="D23" t="n">
-        <v>2063.81</v>
+        <v>179.47</v>
       </c>
       <c r="E23" t="n">
-        <v>2019</v>
+        <v>174.46</v>
       </c>
       <c r="F23" t="n">
-        <v>1863.01</v>
+        <v>167.45</v>
       </c>
       <c r="G23" t="n">
-        <v>11.08</v>
+        <v>10.43</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1289,19 +1289,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1837.9</v>
+        <v>1822.8</v>
       </c>
       <c r="D24" t="n">
-        <v>1667.55</v>
+        <v>1667.05</v>
       </c>
       <c r="E24" t="n">
-        <v>1645.36</v>
+        <v>1645.06</v>
       </c>
       <c r="F24" t="n">
-        <v>1650.25</v>
+        <v>1650.17</v>
       </c>
       <c r="G24" t="n">
-        <v>11.37</v>
+        <v>10.46</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1317,7 +1317,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1872.9</v>
+        <v>1869.2</v>
       </c>
       <c r="D25" t="n">
-        <v>1843.5</v>
+        <v>1842.71</v>
       </c>
       <c r="E25" t="n">
-        <v>1836.83</v>
+        <v>1840.58</v>
       </c>
       <c r="F25" t="n">
-        <v>1664.88</v>
+        <v>1665.44</v>
       </c>
       <c r="G25" t="n">
-        <v>12.49</v>
+        <v>12.23</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1363,19 +1363,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2188</v>
+        <v>2250.3</v>
       </c>
       <c r="D26" t="n">
-        <v>1977.19</v>
+        <v>1979.27</v>
       </c>
       <c r="E26" t="n">
-        <v>1910.56</v>
+        <v>1911.81</v>
       </c>
       <c r="F26" t="n">
-        <v>1932.64</v>
+        <v>1932.96</v>
       </c>
       <c r="G26" t="n">
-        <v>13.21</v>
+        <v>16.42</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1400,19 +1400,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1330</v>
+        <v>1353.7</v>
       </c>
       <c r="D27" t="n">
-        <v>1277.05</v>
+        <v>1282.72</v>
       </c>
       <c r="E27" t="n">
-        <v>1195.08</v>
+        <v>1202.53</v>
       </c>
       <c r="F27" t="n">
-        <v>1147.9</v>
+        <v>1147.83</v>
       </c>
       <c r="G27" t="n">
-        <v>15.86</v>
+        <v>17.94</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1437,19 +1437,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>328.5</v>
+        <v>329.3</v>
       </c>
       <c r="D28" t="n">
-        <v>310.25</v>
+        <v>311.68</v>
       </c>
       <c r="E28" t="n">
-        <v>296.41</v>
+        <v>297.71</v>
       </c>
       <c r="F28" t="n">
-        <v>272.99</v>
+        <v>273.1</v>
       </c>
       <c r="G28" t="n">
-        <v>20.33</v>
+        <v>20.58</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1474,19 +1474,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14711</v>
+        <v>14703</v>
       </c>
       <c r="D29" t="n">
-        <v>14233.47</v>
+        <v>14245.93</v>
       </c>
       <c r="E29" t="n">
-        <v>13636.04</v>
+        <v>13679.76</v>
       </c>
       <c r="F29" t="n">
-        <v>12186.36</v>
+        <v>12183.34</v>
       </c>
       <c r="G29" t="n">
-        <v>20.72</v>
+        <v>20.68</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1502,7 +1502,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1511,19 +1511,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1038.1</v>
+        <v>1047.5</v>
       </c>
       <c r="D30" t="n">
-        <v>921.1</v>
+        <v>921.42</v>
       </c>
       <c r="E30" t="n">
-        <v>933.73</v>
+        <v>933.92</v>
       </c>
       <c r="F30" t="n">
-        <v>846.27</v>
+        <v>846.3200000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>22.67</v>
+        <v>23.77</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>27-08-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1548,19 +1548,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3273</v>
+        <v>3312.4</v>
       </c>
       <c r="D31" t="n">
-        <v>2878.04</v>
+        <v>2890.06</v>
       </c>
       <c r="E31" t="n">
-        <v>2856.94</v>
+        <v>2860.27</v>
       </c>
       <c r="F31" t="n">
-        <v>2603.44</v>
+        <v>2604.23</v>
       </c>
       <c r="G31" t="n">
-        <v>25.72</v>
+        <v>27.19</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -1568,43 +1568,6 @@
         </is>
       </c>
       <c r="I31" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>27-08-2026</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>1901.8</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1728.53</v>
-      </c>
-      <c r="E32" t="n">
-        <v>1628.41</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1511.07</v>
-      </c>
-      <c r="G32" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1531.1</v>
+        <v>1532.3</v>
       </c>
       <c r="D2" t="n">
-        <v>1480.52</v>
+        <v>1480.56</v>
       </c>
       <c r="E2" t="n">
-        <v>1446.33</v>
+        <v>1446.36</v>
       </c>
       <c r="F2" t="n">
         <v>1504.62</v>
       </c>
       <c r="G2" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4029.7</v>
+        <v>4045.8</v>
       </c>
       <c r="D3" t="n">
-        <v>3981.31</v>
+        <v>3988.93</v>
       </c>
       <c r="E3" t="n">
-        <v>4004.49</v>
+        <v>4001.17</v>
       </c>
       <c r="F3" t="n">
-        <v>3959.41</v>
+        <v>3960.05</v>
       </c>
       <c r="G3" t="n">
-        <v>1.78</v>
+        <v>2.17</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.39</v>
+        <v>115.4</v>
       </c>
       <c r="D4" t="n">
         <v>114.36</v>
@@ -561,7 +561,7 @@
         <v>112.58</v>
       </c>
       <c r="G4" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>876.7</v>
+        <v>2555</v>
       </c>
       <c r="D5" t="n">
-        <v>861.1900000000001</v>
+        <v>2464.38</v>
       </c>
       <c r="E5" t="n">
-        <v>846.48</v>
+        <v>2461.67</v>
       </c>
       <c r="F5" t="n">
-        <v>848.96</v>
+        <v>2467.27</v>
       </c>
       <c r="G5" t="n">
-        <v>3.27</v>
+        <v>3.56</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2554.7</v>
+        <v>882.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2464.37</v>
+        <v>863.11</v>
       </c>
       <c r="E6" t="n">
-        <v>2461.67</v>
+        <v>846.88</v>
       </c>
       <c r="F6" t="n">
-        <v>2467.27</v>
+        <v>849.16</v>
       </c>
       <c r="G6" t="n">
-        <v>3.54</v>
+        <v>3.91</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,7 +660,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>175.9</v>
+        <v>175.77</v>
       </c>
       <c r="D7" t="n">
         <v>168.78</v>
@@ -672,7 +672,7 @@
         <v>168.65</v>
       </c>
       <c r="G7" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1988.5</v>
+        <v>2002</v>
       </c>
       <c r="D8" t="n">
-        <v>1984.41</v>
+        <v>1990.09</v>
       </c>
       <c r="E8" t="n">
-        <v>1922.48</v>
+        <v>1927.61</v>
       </c>
       <c r="F8" t="n">
-        <v>1904.58</v>
+        <v>1904.54</v>
       </c>
       <c r="G8" t="n">
-        <v>4.41</v>
+        <v>5.12</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>517.5</v>
+        <v>292</v>
       </c>
       <c r="D9" t="n">
-        <v>510.87</v>
+        <v>282.36</v>
       </c>
       <c r="E9" t="n">
-        <v>495.88</v>
+        <v>281.06</v>
       </c>
       <c r="F9" t="n">
-        <v>493.11</v>
+        <v>277.43</v>
       </c>
       <c r="G9" t="n">
-        <v>4.95</v>
+        <v>5.25</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>291.65</v>
+        <v>5600</v>
       </c>
       <c r="D10" t="n">
-        <v>281.78</v>
+        <v>5499.45</v>
       </c>
       <c r="E10" t="n">
-        <v>281.01</v>
+        <v>5231.36</v>
       </c>
       <c r="F10" t="n">
-        <v>277.33</v>
+        <v>5311.92</v>
       </c>
       <c r="G10" t="n">
-        <v>5.17</v>
+        <v>5.42</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5616</v>
+        <v>11340</v>
       </c>
       <c r="D11" t="n">
-        <v>5476.28</v>
+        <v>11185.77</v>
       </c>
       <c r="E11" t="n">
-        <v>5218.73</v>
+        <v>10953.28</v>
       </c>
       <c r="F11" t="n">
-        <v>5311</v>
+        <v>10614.22</v>
       </c>
       <c r="G11" t="n">
-        <v>5.74</v>
+        <v>6.84</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -845,19 +845,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>481.6</v>
+        <v>482.85</v>
       </c>
       <c r="D12" t="n">
-        <v>461.19</v>
+        <v>461.24</v>
       </c>
       <c r="E12" t="n">
-        <v>445.99</v>
+        <v>446.01</v>
       </c>
       <c r="F12" t="n">
         <v>451.73</v>
       </c>
       <c r="G12" t="n">
-        <v>6.61</v>
+        <v>6.89</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11359</v>
+        <v>5875</v>
       </c>
       <c r="D13" t="n">
-        <v>11153.03</v>
+        <v>5477.05</v>
       </c>
       <c r="E13" t="n">
-        <v>10936.6</v>
+        <v>5207.98</v>
       </c>
       <c r="F13" t="n">
-        <v>10616.57</v>
+        <v>5431.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.99</v>
+        <v>8.17</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>674.5</v>
+        <v>1037.4</v>
       </c>
       <c r="D14" t="n">
-        <v>661.36</v>
+        <v>1011.79</v>
       </c>
       <c r="E14" t="n">
-        <v>652.6</v>
+        <v>991.66</v>
       </c>
       <c r="F14" t="n">
-        <v>627.02</v>
+        <v>957.17</v>
       </c>
       <c r="G14" t="n">
-        <v>7.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1033.95</v>
+        <v>679.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1011.68</v>
+        <v>661.53</v>
       </c>
       <c r="E15" t="n">
-        <v>991.59</v>
+        <v>652.7</v>
       </c>
       <c r="F15" t="n">
-        <v>957.15</v>
+        <v>627.05</v>
       </c>
       <c r="G15" t="n">
-        <v>8.02</v>
+        <v>8.41</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>315.4</v>
+        <v>1200</v>
       </c>
       <c r="D16" t="n">
-        <v>313.08</v>
+        <v>1162.08</v>
       </c>
       <c r="E16" t="n">
-        <v>312.03</v>
+        <v>1138.27</v>
       </c>
       <c r="F16" t="n">
-        <v>291.14</v>
+        <v>1106.83</v>
       </c>
       <c r="G16" t="n">
-        <v>8.33</v>
+        <v>8.42</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5900.5</v>
+        <v>1276</v>
       </c>
       <c r="D17" t="n">
-        <v>5461.63</v>
+        <v>1224.15</v>
       </c>
       <c r="E17" t="n">
-        <v>5191.66</v>
+        <v>1186.45</v>
       </c>
       <c r="F17" t="n">
-        <v>5433.72</v>
+        <v>1170.23</v>
       </c>
       <c r="G17" t="n">
-        <v>8.59</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1205.1</v>
+        <v>1811.5</v>
       </c>
       <c r="D18" t="n">
-        <v>1159.24</v>
+        <v>1675.47</v>
       </c>
       <c r="E18" t="n">
-        <v>1137.2</v>
+        <v>1648.85</v>
       </c>
       <c r="F18" t="n">
-        <v>1106.16</v>
+        <v>1650.32</v>
       </c>
       <c r="G18" t="n">
-        <v>8.94</v>
+        <v>9.77</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2258.8</v>
+        <v>2267</v>
       </c>
       <c r="D19" t="n">
-        <v>2136.19</v>
+        <v>2136.47</v>
       </c>
       <c r="E19" t="n">
-        <v>2060.03</v>
+        <v>2060.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2063.4</v>
+        <v>2063.44</v>
       </c>
       <c r="G19" t="n">
-        <v>9.470000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1281.4</v>
+        <v>394.95</v>
       </c>
       <c r="D20" t="n">
-        <v>1220.15</v>
+        <v>373.13</v>
       </c>
       <c r="E20" t="n">
-        <v>1183.27</v>
+        <v>362.95</v>
       </c>
       <c r="F20" t="n">
-        <v>1170.51</v>
+        <v>358.48</v>
       </c>
       <c r="G20" t="n">
-        <v>9.470000000000001</v>
+        <v>10.17</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>392.55</v>
+        <v>1640.9</v>
       </c>
       <c r="D21" t="n">
-        <v>373.05</v>
+        <v>1611.55</v>
       </c>
       <c r="E21" t="n">
-        <v>362.91</v>
+        <v>1539.51</v>
       </c>
       <c r="F21" t="n">
-        <v>358.47</v>
+        <v>1481.9</v>
       </c>
       <c r="G21" t="n">
-        <v>9.51</v>
+        <v>10.73</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1636.5</v>
+        <v>186</v>
       </c>
       <c r="D22" t="n">
-        <v>1611.4</v>
+        <v>179.5</v>
       </c>
       <c r="E22" t="n">
-        <v>1539.42</v>
+        <v>174.49</v>
       </c>
       <c r="F22" t="n">
-        <v>1481.88</v>
+        <v>167.46</v>
       </c>
       <c r="G22" t="n">
-        <v>10.43</v>
+        <v>11.07</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>184.91</v>
+        <v>1870</v>
       </c>
       <c r="D23" t="n">
-        <v>179.47</v>
+        <v>1842.74</v>
       </c>
       <c r="E23" t="n">
-        <v>174.46</v>
+        <v>1840.59</v>
       </c>
       <c r="F23" t="n">
-        <v>167.45</v>
+        <v>1665.45</v>
       </c>
       <c r="G23" t="n">
-        <v>10.43</v>
+        <v>12.28</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1822.8</v>
+        <v>2265.6</v>
       </c>
       <c r="D24" t="n">
-        <v>1667.05</v>
+        <v>1992.86</v>
       </c>
       <c r="E24" t="n">
-        <v>1645.06</v>
+        <v>1918.44</v>
       </c>
       <c r="F24" t="n">
-        <v>1650.17</v>
+        <v>1934.99</v>
       </c>
       <c r="G24" t="n">
-        <v>10.46</v>
+        <v>17.09</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1869.2</v>
+        <v>1354</v>
       </c>
       <c r="D25" t="n">
-        <v>1842.71</v>
+        <v>1282.73</v>
       </c>
       <c r="E25" t="n">
-        <v>1840.58</v>
+        <v>1202.53</v>
       </c>
       <c r="F25" t="n">
-        <v>1665.44</v>
+        <v>1147.83</v>
       </c>
       <c r="G25" t="n">
-        <v>12.23</v>
+        <v>17.96</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1359,23 +1359,23 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2250.3</v>
+        <v>328</v>
       </c>
       <c r="D26" t="n">
-        <v>1979.27</v>
+        <v>311.63</v>
       </c>
       <c r="E26" t="n">
-        <v>1911.81</v>
+        <v>297.68</v>
       </c>
       <c r="F26" t="n">
-        <v>1932.96</v>
+        <v>273.09</v>
       </c>
       <c r="G26" t="n">
-        <v>16.42</v>
+        <v>20.11</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1396,23 +1396,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1353.7</v>
+        <v>14650</v>
       </c>
       <c r="D27" t="n">
-        <v>1282.72</v>
+        <v>14244.17</v>
       </c>
       <c r="E27" t="n">
-        <v>1202.53</v>
+        <v>13678.7</v>
       </c>
       <c r="F27" t="n">
-        <v>1147.83</v>
+        <v>12183.08</v>
       </c>
       <c r="G27" t="n">
-        <v>17.94</v>
+        <v>20.25</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1433,23 +1433,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>329.3</v>
+        <v>1038.3</v>
       </c>
       <c r="D28" t="n">
-        <v>311.68</v>
+        <v>923.48</v>
       </c>
       <c r="E28" t="n">
-        <v>297.71</v>
+        <v>935.4299999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>273.1</v>
+        <v>846.52</v>
       </c>
       <c r="G28" t="n">
-        <v>20.58</v>
+        <v>22.66</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -1470,23 +1470,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>14703</v>
+        <v>3332</v>
       </c>
       <c r="D29" t="n">
-        <v>14245.93</v>
+        <v>2890.71</v>
       </c>
       <c r="E29" t="n">
-        <v>13679.76</v>
+        <v>2860.66</v>
       </c>
       <c r="F29" t="n">
-        <v>12183.34</v>
+        <v>2604.33</v>
       </c>
       <c r="G29" t="n">
-        <v>20.68</v>
+        <v>27.94</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -1494,80 +1494,6 @@
         </is>
       </c>
       <c r="I29" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>1047.5</v>
-      </c>
-      <c r="D30" t="n">
-        <v>921.42</v>
-      </c>
-      <c r="E30" t="n">
-        <v>933.92</v>
-      </c>
-      <c r="F30" t="n">
-        <v>846.3200000000001</v>
-      </c>
-      <c r="G30" t="n">
-        <v>23.77</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>3312.4</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2890.06</v>
-      </c>
-      <c r="E31" t="n">
-        <v>2860.27</v>
-      </c>
-      <c r="F31" t="n">
-        <v>2604.23</v>
-      </c>
-      <c r="G31" t="n">
-        <v>27.19</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>292</v>
+        <v>5600</v>
       </c>
       <c r="D9" t="n">
-        <v>282.36</v>
+        <v>5499.45</v>
       </c>
       <c r="E9" t="n">
-        <v>281.06</v>
+        <v>5231.36</v>
       </c>
       <c r="F9" t="n">
-        <v>277.43</v>
+        <v>5311.92</v>
       </c>
       <c r="G9" t="n">
-        <v>5.25</v>
+        <v>5.42</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5600</v>
+        <v>5875</v>
       </c>
       <c r="D10" t="n">
-        <v>5499.45</v>
+        <v>5477.05</v>
       </c>
       <c r="E10" t="n">
-        <v>5231.36</v>
+        <v>5207.98</v>
       </c>
       <c r="F10" t="n">
-        <v>5311.92</v>
+        <v>5431.4</v>
       </c>
       <c r="G10" t="n">
-        <v>5.42</v>
+        <v>8.17</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11340</v>
+        <v>1037.4</v>
       </c>
       <c r="D11" t="n">
-        <v>11185.77</v>
+        <v>1011.79</v>
       </c>
       <c r="E11" t="n">
-        <v>10953.28</v>
+        <v>991.66</v>
       </c>
       <c r="F11" t="n">
-        <v>10614.22</v>
+        <v>957.17</v>
       </c>
       <c r="G11" t="n">
-        <v>6.84</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>482.85</v>
+        <v>679.8</v>
       </c>
       <c r="D12" t="n">
-        <v>461.24</v>
+        <v>661.53</v>
       </c>
       <c r="E12" t="n">
-        <v>446.01</v>
+        <v>652.7</v>
       </c>
       <c r="F12" t="n">
-        <v>451.73</v>
+        <v>627.05</v>
       </c>
       <c r="G12" t="n">
-        <v>6.89</v>
+        <v>8.41</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5875</v>
+        <v>1811.5</v>
       </c>
       <c r="D13" t="n">
-        <v>5477.05</v>
+        <v>1675.47</v>
       </c>
       <c r="E13" t="n">
-        <v>5207.98</v>
+        <v>1648.85</v>
       </c>
       <c r="F13" t="n">
-        <v>5431.4</v>
+        <v>1650.32</v>
       </c>
       <c r="G13" t="n">
-        <v>8.17</v>
+        <v>9.77</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1037.4</v>
+        <v>2267</v>
       </c>
       <c r="D14" t="n">
-        <v>1011.79</v>
+        <v>2136.47</v>
       </c>
       <c r="E14" t="n">
-        <v>991.66</v>
+        <v>2060.2</v>
       </c>
       <c r="F14" t="n">
-        <v>957.17</v>
+        <v>2063.44</v>
       </c>
       <c r="G14" t="n">
-        <v>8.380000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>679.8</v>
+        <v>1640.9</v>
       </c>
       <c r="D15" t="n">
-        <v>661.53</v>
+        <v>1611.55</v>
       </c>
       <c r="E15" t="n">
-        <v>652.7</v>
+        <v>1539.51</v>
       </c>
       <c r="F15" t="n">
-        <v>627.05</v>
+        <v>1481.9</v>
       </c>
       <c r="G15" t="n">
-        <v>8.41</v>
+        <v>10.73</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1200</v>
+        <v>186</v>
       </c>
       <c r="D16" t="n">
-        <v>1162.08</v>
+        <v>179.5</v>
       </c>
       <c r="E16" t="n">
-        <v>1138.27</v>
+        <v>174.49</v>
       </c>
       <c r="F16" t="n">
-        <v>1106.83</v>
+        <v>167.46</v>
       </c>
       <c r="G16" t="n">
-        <v>8.42</v>
+        <v>11.07</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1276</v>
+        <v>2265.6</v>
       </c>
       <c r="D17" t="n">
-        <v>1224.15</v>
+        <v>1992.86</v>
       </c>
       <c r="E17" t="n">
-        <v>1186.45</v>
+        <v>1918.44</v>
       </c>
       <c r="F17" t="n">
-        <v>1170.23</v>
+        <v>1934.99</v>
       </c>
       <c r="G17" t="n">
-        <v>9.039999999999999</v>
+        <v>17.09</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1811.5</v>
+        <v>1354</v>
       </c>
       <c r="D18" t="n">
-        <v>1675.47</v>
+        <v>1282.73</v>
       </c>
       <c r="E18" t="n">
-        <v>1648.85</v>
+        <v>1202.53</v>
       </c>
       <c r="F18" t="n">
-        <v>1650.32</v>
+        <v>1147.83</v>
       </c>
       <c r="G18" t="n">
-        <v>9.77</v>
+        <v>17.96</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2267</v>
+        <v>328</v>
       </c>
       <c r="D19" t="n">
-        <v>2136.47</v>
+        <v>311.63</v>
       </c>
       <c r="E19" t="n">
-        <v>2060.2</v>
+        <v>297.68</v>
       </c>
       <c r="F19" t="n">
-        <v>2063.44</v>
+        <v>273.09</v>
       </c>
       <c r="G19" t="n">
-        <v>9.859999999999999</v>
+        <v>20.11</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>394.95</v>
+        <v>14650</v>
       </c>
       <c r="D20" t="n">
-        <v>373.13</v>
+        <v>14244.17</v>
       </c>
       <c r="E20" t="n">
-        <v>362.95</v>
+        <v>13678.7</v>
       </c>
       <c r="F20" t="n">
-        <v>358.48</v>
+        <v>12183.08</v>
       </c>
       <c r="G20" t="n">
-        <v>10.17</v>
+        <v>20.25</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1640.9</v>
+        <v>1038.3</v>
       </c>
       <c r="D21" t="n">
-        <v>1611.55</v>
+        <v>923.48</v>
       </c>
       <c r="E21" t="n">
-        <v>1539.51</v>
+        <v>935.4299999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>1481.9</v>
+        <v>846.52</v>
       </c>
       <c r="G21" t="n">
-        <v>10.73</v>
+        <v>22.66</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>29-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>186</v>
+        <v>3332</v>
       </c>
       <c r="D22" t="n">
-        <v>179.5</v>
+        <v>2890.71</v>
       </c>
       <c r="E22" t="n">
-        <v>174.49</v>
+        <v>2860.66</v>
       </c>
       <c r="F22" t="n">
-        <v>167.46</v>
+        <v>2604.33</v>
       </c>
       <c r="G22" t="n">
-        <v>11.07</v>
+        <v>27.94</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1235,265 +1235,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1842.74</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1840.59</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1665.45</v>
-      </c>
-      <c r="G23" t="n">
-        <v>12.28</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>2265.6</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1992.86</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1918.44</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1934.99</v>
-      </c>
-      <c r="G24" t="n">
-        <v>17.09</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1354</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1282.73</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1202.53</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1147.83</v>
-      </c>
-      <c r="G25" t="n">
-        <v>17.96</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>328</v>
-      </c>
-      <c r="D26" t="n">
-        <v>311.63</v>
-      </c>
-      <c r="E26" t="n">
-        <v>297.68</v>
-      </c>
-      <c r="F26" t="n">
-        <v>273.09</v>
-      </c>
-      <c r="G26" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>14650</v>
-      </c>
-      <c r="D27" t="n">
-        <v>14244.17</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13678.7</v>
-      </c>
-      <c r="F27" t="n">
-        <v>12183.08</v>
-      </c>
-      <c r="G27" t="n">
-        <v>20.25</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1038.3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>923.48</v>
-      </c>
-      <c r="E28" t="n">
-        <v>935.4299999999999</v>
-      </c>
-      <c r="F28" t="n">
-        <v>846.52</v>
-      </c>
-      <c r="G28" t="n">
-        <v>22.66</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>28-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>3332</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2890.71</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2860.66</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2604.33</v>
-      </c>
-      <c r="G29" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>29-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1532.3</v>
+        <v>4002.3</v>
       </c>
       <c r="D2" t="n">
-        <v>1480.56</v>
+        <v>3994.38</v>
       </c>
       <c r="E2" t="n">
-        <v>1446.36</v>
+        <v>3997.19</v>
       </c>
       <c r="F2" t="n">
-        <v>1504.62</v>
+        <v>3960.24</v>
       </c>
       <c r="G2" t="n">
-        <v>1.84</v>
+        <v>1.06</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4045.8</v>
+        <v>1542.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3988.93</v>
+        <v>1485.5</v>
       </c>
       <c r="E3" t="n">
-        <v>4001.17</v>
+        <v>1446.09</v>
       </c>
       <c r="F3" t="n">
-        <v>3960.05</v>
+        <v>1504.59</v>
       </c>
       <c r="G3" t="n">
-        <v>2.17</v>
+        <v>2.49</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.4</v>
+        <v>871.75</v>
       </c>
       <c r="D4" t="n">
-        <v>114.36</v>
+        <v>863.55</v>
       </c>
       <c r="E4" t="n">
-        <v>111.01</v>
+        <v>847.09</v>
       </c>
       <c r="F4" t="n">
-        <v>112.58</v>
+        <v>849.26</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2555</v>
+        <v>5619</v>
       </c>
       <c r="D5" t="n">
-        <v>2464.38</v>
+        <v>5491.99</v>
       </c>
       <c r="E5" t="n">
-        <v>2461.67</v>
+        <v>5223.49</v>
       </c>
       <c r="F5" t="n">
-        <v>2467.27</v>
+        <v>5429.03</v>
       </c>
       <c r="G5" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>882.4</v>
+        <v>176.35</v>
       </c>
       <c r="D6" t="n">
-        <v>863.11</v>
+        <v>169.5</v>
       </c>
       <c r="E6" t="n">
-        <v>846.88</v>
+        <v>165.08</v>
       </c>
       <c r="F6" t="n">
-        <v>849.16</v>
+        <v>168.8</v>
       </c>
       <c r="G6" t="n">
-        <v>3.91</v>
+        <v>4.47</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>175.77</v>
+        <v>5557.5</v>
       </c>
       <c r="D7" t="n">
-        <v>168.78</v>
+        <v>5521.18</v>
       </c>
       <c r="E7" t="n">
-        <v>164.7</v>
+        <v>5244.28</v>
       </c>
       <c r="F7" t="n">
-        <v>168.65</v>
+        <v>5313.08</v>
       </c>
       <c r="G7" t="n">
-        <v>4.22</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2002</v>
+        <v>291.25</v>
       </c>
       <c r="D8" t="n">
-        <v>1990.09</v>
+        <v>282.9</v>
       </c>
       <c r="E8" t="n">
-        <v>1927.61</v>
+        <v>281.15</v>
       </c>
       <c r="F8" t="n">
-        <v>1904.54</v>
+        <v>277.54</v>
       </c>
       <c r="G8" t="n">
-        <v>5.12</v>
+        <v>4.94</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5600</v>
+        <v>379.5</v>
       </c>
       <c r="D9" t="n">
-        <v>5499.45</v>
+        <v>374.38</v>
       </c>
       <c r="E9" t="n">
-        <v>5231.36</v>
+        <v>363</v>
       </c>
       <c r="F9" t="n">
-        <v>5311.92</v>
+        <v>359.08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.42</v>
+        <v>5.69</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5875</v>
+        <v>1173.1</v>
       </c>
       <c r="D10" t="n">
-        <v>5477.05</v>
+        <v>1163.63</v>
       </c>
       <c r="E10" t="n">
-        <v>5207.98</v>
+        <v>1138.95</v>
       </c>
       <c r="F10" t="n">
-        <v>5431.4</v>
+        <v>1107.28</v>
       </c>
       <c r="G10" t="n">
-        <v>8.17</v>
+        <v>5.94</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1037.4</v>
+        <v>1015.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1011.79</v>
+        <v>1014.04</v>
       </c>
       <c r="E11" t="n">
-        <v>991.66</v>
+        <v>991.78</v>
       </c>
       <c r="F11" t="n">
-        <v>957.17</v>
+        <v>958.21</v>
       </c>
       <c r="G11" t="n">
-        <v>8.380000000000001</v>
+        <v>5.95</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>679.8</v>
+        <v>483.8</v>
       </c>
       <c r="D12" t="n">
-        <v>661.53</v>
+        <v>462.24</v>
       </c>
       <c r="E12" t="n">
-        <v>652.7</v>
+        <v>447.24</v>
       </c>
       <c r="F12" t="n">
-        <v>627.05</v>
+        <v>452.03</v>
       </c>
       <c r="G12" t="n">
-        <v>8.41</v>
+        <v>7.03</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1811.5</v>
+        <v>11360</v>
       </c>
       <c r="D13" t="n">
-        <v>1675.47</v>
+        <v>11221.13</v>
       </c>
       <c r="E13" t="n">
-        <v>1648.85</v>
+        <v>10965.25</v>
       </c>
       <c r="F13" t="n">
-        <v>1650.32</v>
+        <v>10611.85</v>
       </c>
       <c r="G13" t="n">
-        <v>9.77</v>
+        <v>7.05</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2267</v>
+        <v>670.95</v>
       </c>
       <c r="D14" t="n">
-        <v>2136.47</v>
+        <v>661.89</v>
       </c>
       <c r="E14" t="n">
-        <v>2060.2</v>
+        <v>653.72</v>
       </c>
       <c r="F14" t="n">
-        <v>2063.44</v>
+        <v>626.62</v>
       </c>
       <c r="G14" t="n">
-        <v>9.859999999999999</v>
+        <v>7.07</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -956,19 +956,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1640.9</v>
+        <v>1613.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1611.55</v>
+        <v>1612.77</v>
       </c>
       <c r="E15" t="n">
-        <v>1539.51</v>
+        <v>1543.79</v>
       </c>
       <c r="F15" t="n">
-        <v>1481.9</v>
+        <v>1482.89</v>
       </c>
       <c r="G15" t="n">
-        <v>10.73</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>186</v>
+        <v>183.09</v>
       </c>
       <c r="D16" t="n">
-        <v>179.5</v>
+        <v>179.74</v>
       </c>
       <c r="E16" t="n">
-        <v>174.49</v>
+        <v>174.72</v>
       </c>
       <c r="F16" t="n">
-        <v>167.46</v>
+        <v>167.64</v>
       </c>
       <c r="G16" t="n">
-        <v>11.07</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2265.6</v>
+        <v>2256.7</v>
       </c>
       <c r="D17" t="n">
-        <v>1992.86</v>
+        <v>2146.57</v>
       </c>
       <c r="E17" t="n">
-        <v>1918.44</v>
+        <v>2065.93</v>
       </c>
       <c r="F17" t="n">
-        <v>1934.99</v>
+        <v>2062.77</v>
       </c>
       <c r="G17" t="n">
-        <v>17.09</v>
+        <v>9.4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1354</v>
+        <v>1289.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1282.73</v>
+        <v>1228.64</v>
       </c>
       <c r="E18" t="n">
-        <v>1202.53</v>
+        <v>1189.89</v>
       </c>
       <c r="F18" t="n">
-        <v>1147.83</v>
+        <v>1170.18</v>
       </c>
       <c r="G18" t="n">
-        <v>17.96</v>
+        <v>10.16</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>328</v>
+        <v>1820.7</v>
       </c>
       <c r="D19" t="n">
-        <v>311.63</v>
+        <v>1683.34</v>
       </c>
       <c r="E19" t="n">
-        <v>297.68</v>
+        <v>1651.89</v>
       </c>
       <c r="F19" t="n">
-        <v>273.09</v>
+        <v>1650.5</v>
       </c>
       <c r="G19" t="n">
-        <v>20.11</v>
+        <v>10.31</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>14650</v>
+        <v>1864.5</v>
       </c>
       <c r="D20" t="n">
-        <v>14244.17</v>
+        <v>1842.2</v>
       </c>
       <c r="E20" t="n">
-        <v>13678.7</v>
+        <v>1844.1</v>
       </c>
       <c r="F20" t="n">
-        <v>12183.08</v>
+        <v>1666.11</v>
       </c>
       <c r="G20" t="n">
-        <v>20.25</v>
+        <v>11.91</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1038.3</v>
+        <v>2241.7</v>
       </c>
       <c r="D21" t="n">
-        <v>923.48</v>
+        <v>2007.11</v>
       </c>
       <c r="E21" t="n">
-        <v>935.4299999999999</v>
+        <v>1926.18</v>
       </c>
       <c r="F21" t="n">
-        <v>846.52</v>
+        <v>1937.37</v>
       </c>
       <c r="G21" t="n">
-        <v>22.66</v>
+        <v>15.71</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,30 +1211,178 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1347.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1288.04</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1209.85</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1147.88</v>
+      </c>
+      <c r="G22" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>328.15</v>
+      </c>
+      <c r="D23" t="n">
+        <v>313</v>
+      </c>
+      <c r="E23" t="n">
+        <v>298.97</v>
+      </c>
+      <c r="F23" t="n">
+        <v>273.24</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>14721</v>
+      </c>
+      <c r="D24" t="n">
+        <v>14248.57</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13726.4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>12180.07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1031.8</v>
+      </c>
+      <c r="D25" t="n">
+        <v>925.4299999999999</v>
+      </c>
+      <c r="E25" t="n">
+        <v>937.09</v>
+      </c>
+      <c r="F25" t="n">
+        <v>846.76</v>
+      </c>
+      <c r="G25" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>3332</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2890.71</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2860.66</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2604.33</v>
-      </c>
-      <c r="G22" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="C26" t="n">
+        <v>3346.6</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2908.56</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2870.32</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2611.49</v>
+      </c>
+      <c r="G26" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ASTRAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4002.3</v>
+        <v>1522.2</v>
       </c>
       <c r="D2" t="n">
-        <v>3994.38</v>
+        <v>1484.84</v>
       </c>
       <c r="E2" t="n">
-        <v>3997.19</v>
+        <v>1445.7</v>
       </c>
       <c r="F2" t="n">
-        <v>3960.24</v>
+        <v>1504.49</v>
       </c>
       <c r="G2" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1542.1</v>
+        <v>4044.9</v>
       </c>
       <c r="D3" t="n">
-        <v>1485.5</v>
+        <v>3995.8</v>
       </c>
       <c r="E3" t="n">
-        <v>1446.09</v>
+        <v>3998.04</v>
       </c>
       <c r="F3" t="n">
-        <v>1504.59</v>
+        <v>3960.45</v>
       </c>
       <c r="G3" t="n">
-        <v>2.49</v>
+        <v>2.13</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>871.75</v>
+        <v>5594.5</v>
       </c>
       <c r="D4" t="n">
-        <v>863.55</v>
+        <v>5491.18</v>
       </c>
       <c r="E4" t="n">
-        <v>847.09</v>
+        <v>5223</v>
       </c>
       <c r="F4" t="n">
-        <v>849.26</v>
+        <v>5428.9</v>
       </c>
       <c r="G4" t="n">
-        <v>2.65</v>
+        <v>3.05</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5619</v>
+        <v>1060</v>
       </c>
       <c r="D5" t="n">
-        <v>5491.99</v>
+        <v>1048.04</v>
       </c>
       <c r="E5" t="n">
-        <v>5223.49</v>
+        <v>1043.23</v>
       </c>
       <c r="F5" t="n">
-        <v>5429.03</v>
+        <v>1028.08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>176.35</v>
+        <v>175.64</v>
       </c>
       <c r="D6" t="n">
-        <v>169.5</v>
+        <v>169.47</v>
       </c>
       <c r="E6" t="n">
-        <v>165.08</v>
+        <v>165.07</v>
       </c>
       <c r="F6" t="n">
         <v>168.8</v>
       </c>
       <c r="G6" t="n">
-        <v>4.47</v>
+        <v>4.05</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5557.5</v>
+        <v>898.75</v>
       </c>
       <c r="D7" t="n">
-        <v>5521.18</v>
+        <v>864.45</v>
       </c>
       <c r="E7" t="n">
-        <v>5244.28</v>
+        <v>847.63</v>
       </c>
       <c r="F7" t="n">
-        <v>5313.08</v>
+        <v>849.4</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>5.81</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>291.25</v>
+        <v>1015.45</v>
       </c>
       <c r="D8" t="n">
-        <v>282.9</v>
+        <v>1014.05</v>
       </c>
       <c r="E8" t="n">
-        <v>281.15</v>
+        <v>991.79</v>
       </c>
       <c r="F8" t="n">
-        <v>277.54</v>
+        <v>958.21</v>
       </c>
       <c r="G8" t="n">
-        <v>4.94</v>
+        <v>5.97</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>379.5</v>
+        <v>2021</v>
       </c>
       <c r="D9" t="n">
-        <v>374.38</v>
+        <v>1995.41</v>
       </c>
       <c r="E9" t="n">
-        <v>363</v>
+        <v>1932.42</v>
       </c>
       <c r="F9" t="n">
-        <v>359.08</v>
+        <v>1904.37</v>
       </c>
       <c r="G9" t="n">
-        <v>5.69</v>
+        <v>6.12</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1173.1</v>
+        <v>1175</v>
       </c>
       <c r="D10" t="n">
-        <v>1163.63</v>
+        <v>1161.25</v>
       </c>
       <c r="E10" t="n">
-        <v>1138.95</v>
+        <v>1137.77</v>
       </c>
       <c r="F10" t="n">
-        <v>1107.28</v>
+        <v>1106.71</v>
       </c>
       <c r="G10" t="n">
-        <v>5.94</v>
+        <v>6.17</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1015.2</v>
+        <v>381.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1014.04</v>
+        <v>372.68</v>
       </c>
       <c r="E11" t="n">
-        <v>991.78</v>
+        <v>362.68</v>
       </c>
       <c r="F11" t="n">
-        <v>958.21</v>
+        <v>358.41</v>
       </c>
       <c r="G11" t="n">
-        <v>5.95</v>
+        <v>6.44</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>483.8</v>
+        <v>2205</v>
       </c>
       <c r="D12" t="n">
-        <v>462.24</v>
+        <v>2144.85</v>
       </c>
       <c r="E12" t="n">
-        <v>447.24</v>
+        <v>2064.9</v>
       </c>
       <c r="F12" t="n">
-        <v>452.03</v>
+        <v>2062.51</v>
       </c>
       <c r="G12" t="n">
-        <v>7.03</v>
+        <v>6.91</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11360</v>
+        <v>483.15</v>
       </c>
       <c r="D13" t="n">
-        <v>11221.13</v>
+        <v>461.25</v>
       </c>
       <c r="E13" t="n">
-        <v>10965.25</v>
+        <v>446.02</v>
       </c>
       <c r="F13" t="n">
-        <v>10611.85</v>
+        <v>451.74</v>
       </c>
       <c r="G13" t="n">
-        <v>7.05</v>
+        <v>6.95</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>670.95</v>
+        <v>737.9</v>
       </c>
       <c r="D14" t="n">
-        <v>661.89</v>
+        <v>730.0599999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>653.72</v>
+        <v>729.4400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>626.62</v>
+        <v>686.4299999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>7.07</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1613.1</v>
+        <v>300.6</v>
       </c>
       <c r="D15" t="n">
-        <v>1612.77</v>
+        <v>282.65</v>
       </c>
       <c r="E15" t="n">
-        <v>1543.79</v>
+        <v>281.23</v>
       </c>
       <c r="F15" t="n">
-        <v>1482.89</v>
+        <v>277.47</v>
       </c>
       <c r="G15" t="n">
-        <v>8.779999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>183.09</v>
+        <v>1633</v>
       </c>
       <c r="D16" t="n">
-        <v>179.74</v>
+        <v>1615.3</v>
       </c>
       <c r="E16" t="n">
-        <v>174.72</v>
+        <v>1623.65</v>
       </c>
       <c r="F16" t="n">
-        <v>167.64</v>
+        <v>1500.66</v>
       </c>
       <c r="G16" t="n">
-        <v>9.220000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2256.7</v>
+        <v>1276</v>
       </c>
       <c r="D17" t="n">
-        <v>2146.57</v>
+        <v>1224.15</v>
       </c>
       <c r="E17" t="n">
-        <v>2065.93</v>
+        <v>1186.45</v>
       </c>
       <c r="F17" t="n">
-        <v>2062.77</v>
+        <v>1170.23</v>
       </c>
       <c r="G17" t="n">
-        <v>9.4</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1289.1</v>
+        <v>11644</v>
       </c>
       <c r="D18" t="n">
-        <v>1228.64</v>
+        <v>11195.9</v>
       </c>
       <c r="E18" t="n">
-        <v>1189.89</v>
+        <v>10959.36</v>
       </c>
       <c r="F18" t="n">
-        <v>1170.18</v>
+        <v>10615.74</v>
       </c>
       <c r="G18" t="n">
-        <v>10.16</v>
+        <v>9.69</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1820.7</v>
+        <v>1628</v>
       </c>
       <c r="D19" t="n">
-        <v>1683.34</v>
+        <v>1613.27</v>
       </c>
       <c r="E19" t="n">
-        <v>1651.89</v>
+        <v>1544.09</v>
       </c>
       <c r="F19" t="n">
-        <v>1650.5</v>
+        <v>1482.96</v>
       </c>
       <c r="G19" t="n">
-        <v>10.31</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1864.5</v>
+        <v>691.05</v>
       </c>
       <c r="D20" t="n">
-        <v>1842.2</v>
+        <v>662.5599999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>1844.1</v>
+        <v>654.13</v>
       </c>
       <c r="F20" t="n">
-        <v>1666.11</v>
+        <v>626.72</v>
       </c>
       <c r="G20" t="n">
-        <v>11.91</v>
+        <v>10.26</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2241.7</v>
+        <v>1868</v>
       </c>
       <c r="D21" t="n">
-        <v>2007.11</v>
+        <v>1842.67</v>
       </c>
       <c r="E21" t="n">
-        <v>1926.18</v>
+        <v>1840.55</v>
       </c>
       <c r="F21" t="n">
-        <v>1937.37</v>
+        <v>1665.44</v>
       </c>
       <c r="G21" t="n">
-        <v>15.71</v>
+        <v>12.16</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1347.2</v>
+        <v>188.63</v>
       </c>
       <c r="D22" t="n">
-        <v>1288.04</v>
+        <v>179.93</v>
       </c>
       <c r="E22" t="n">
-        <v>1209.85</v>
+        <v>174.83</v>
       </c>
       <c r="F22" t="n">
-        <v>1147.88</v>
+        <v>167.66</v>
       </c>
       <c r="G22" t="n">
-        <v>17.36</v>
+        <v>12.51</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>328.15</v>
+        <v>1875</v>
       </c>
       <c r="D23" t="n">
-        <v>313</v>
+        <v>1685.15</v>
       </c>
       <c r="E23" t="n">
-        <v>298.97</v>
+        <v>1652.98</v>
       </c>
       <c r="F23" t="n">
-        <v>273.24</v>
+        <v>1650.77</v>
       </c>
       <c r="G23" t="n">
-        <v>20.1</v>
+        <v>13.58</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14721</v>
+        <v>1313</v>
       </c>
       <c r="D24" t="n">
-        <v>14248.57</v>
+        <v>1286.9</v>
       </c>
       <c r="E24" t="n">
-        <v>13726.4</v>
+        <v>1209.16</v>
       </c>
       <c r="F24" t="n">
-        <v>12180.07</v>
+        <v>1147.71</v>
       </c>
       <c r="G24" t="n">
-        <v>20.86</v>
+        <v>14.4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1322,23 +1322,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1031.8</v>
+        <v>2223.4</v>
       </c>
       <c r="D25" t="n">
-        <v>925.4299999999999</v>
+        <v>2006.5</v>
       </c>
       <c r="E25" t="n">
-        <v>937.09</v>
+        <v>1925.81</v>
       </c>
       <c r="F25" t="n">
-        <v>846.76</v>
+        <v>1937.28</v>
       </c>
       <c r="G25" t="n">
-        <v>21.85</v>
+        <v>14.77</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1359,30 +1359,141 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>328.1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>313</v>
+      </c>
+      <c r="E26" t="n">
+        <v>298.97</v>
+      </c>
+      <c r="F26" t="n">
+        <v>273.24</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20.08</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>14850</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14252.87</v>
+      </c>
+      <c r="E27" t="n">
+        <v>13728.98</v>
+      </c>
+      <c r="F27" t="n">
+        <v>12180.72</v>
+      </c>
+      <c r="G27" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1042.9</v>
+      </c>
+      <c r="D28" t="n">
+        <v>925.8</v>
+      </c>
+      <c r="E28" t="n">
+        <v>937.3099999999999</v>
+      </c>
+      <c r="F28" t="n">
+        <v>846.8200000000001</v>
+      </c>
+      <c r="G28" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C26" t="n">
-        <v>3346.6</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2908.56</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2870.32</v>
-      </c>
-      <c r="F26" t="n">
-        <v>2611.49</v>
-      </c>
-      <c r="G26" t="n">
-        <v>28.15</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
+      <c r="C29" t="n">
+        <v>3400</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2910.34</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2871.39</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2611.76</v>
+      </c>
+      <c r="G29" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1015.45</v>
+        <v>2021</v>
       </c>
       <c r="D8" t="n">
-        <v>1014.05</v>
+        <v>1995.41</v>
       </c>
       <c r="E8" t="n">
-        <v>991.79</v>
+        <v>1932.42</v>
       </c>
       <c r="F8" t="n">
-        <v>958.21</v>
+        <v>1904.37</v>
       </c>
       <c r="G8" t="n">
-        <v>5.97</v>
+        <v>6.12</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2021</v>
+        <v>381.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1995.41</v>
+        <v>374.45</v>
       </c>
       <c r="E9" t="n">
-        <v>1932.42</v>
+        <v>363.04</v>
       </c>
       <c r="F9" t="n">
-        <v>1904.37</v>
+        <v>359.09</v>
       </c>
       <c r="G9" t="n">
-        <v>6.12</v>
+        <v>6.24</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1175</v>
+        <v>483.15</v>
       </c>
       <c r="D10" t="n">
-        <v>1161.25</v>
+        <v>462.22</v>
       </c>
       <c r="E10" t="n">
-        <v>1137.77</v>
+        <v>447.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1106.71</v>
+        <v>452.03</v>
       </c>
       <c r="G10" t="n">
-        <v>6.17</v>
+        <v>6.89</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>381.5</v>
+        <v>2205</v>
       </c>
       <c r="D11" t="n">
-        <v>372.68</v>
+        <v>2144.85</v>
       </c>
       <c r="E11" t="n">
-        <v>362.68</v>
+        <v>2064.9</v>
       </c>
       <c r="F11" t="n">
-        <v>358.41</v>
+        <v>2062.51</v>
       </c>
       <c r="G11" t="n">
-        <v>6.44</v>
+        <v>6.91</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2205</v>
+        <v>737.9</v>
       </c>
       <c r="D12" t="n">
-        <v>2144.85</v>
+        <v>730.0599999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>2064.9</v>
+        <v>729.4400000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2062.51</v>
+        <v>686.4299999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>6.91</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>PRESTIGE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>483.15</v>
+        <v>1633</v>
       </c>
       <c r="D13" t="n">
-        <v>461.25</v>
+        <v>1615.3</v>
       </c>
       <c r="E13" t="n">
-        <v>446.02</v>
+        <v>1623.65</v>
       </c>
       <c r="F13" t="n">
-        <v>451.74</v>
+        <v>1500.66</v>
       </c>
       <c r="G13" t="n">
-        <v>6.95</v>
+        <v>8.82</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>737.9</v>
+        <v>11644</v>
       </c>
       <c r="D14" t="n">
-        <v>730.0599999999999</v>
+        <v>11230.6</v>
       </c>
       <c r="E14" t="n">
-        <v>729.4400000000001</v>
+        <v>10970.93</v>
       </c>
       <c r="F14" t="n">
-        <v>686.4299999999999</v>
+        <v>10613.27</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>300.6</v>
+        <v>1628</v>
       </c>
       <c r="D15" t="n">
-        <v>282.65</v>
+        <v>1613.27</v>
       </c>
       <c r="E15" t="n">
-        <v>281.23</v>
+        <v>1544.09</v>
       </c>
       <c r="F15" t="n">
-        <v>277.47</v>
+        <v>1482.96</v>
       </c>
       <c r="G15" t="n">
-        <v>8.33</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1633</v>
+        <v>691.05</v>
       </c>
       <c r="D16" t="n">
-        <v>1615.3</v>
+        <v>662.5599999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1623.65</v>
+        <v>654.13</v>
       </c>
       <c r="F16" t="n">
-        <v>1500.66</v>
+        <v>626.72</v>
       </c>
       <c r="G16" t="n">
-        <v>8.82</v>
+        <v>10.26</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1276</v>
+        <v>188.63</v>
       </c>
       <c r="D17" t="n">
-        <v>1224.15</v>
+        <v>179.93</v>
       </c>
       <c r="E17" t="n">
-        <v>1186.45</v>
+        <v>174.83</v>
       </c>
       <c r="F17" t="n">
-        <v>1170.23</v>
+        <v>167.66</v>
       </c>
       <c r="G17" t="n">
-        <v>9.039999999999999</v>
+        <v>12.51</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11644</v>
+        <v>1313</v>
       </c>
       <c r="D18" t="n">
-        <v>11195.9</v>
+        <v>1286.9</v>
       </c>
       <c r="E18" t="n">
-        <v>10959.36</v>
+        <v>1209.16</v>
       </c>
       <c r="F18" t="n">
-        <v>10615.74</v>
+        <v>1147.71</v>
       </c>
       <c r="G18" t="n">
-        <v>9.69</v>
+        <v>14.4</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1095,28 +1095,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1628</v>
+        <v>2223.4</v>
       </c>
       <c r="D19" t="n">
-        <v>1613.27</v>
+        <v>2006.5</v>
       </c>
       <c r="E19" t="n">
-        <v>1544.09</v>
+        <v>1925.81</v>
       </c>
       <c r="F19" t="n">
-        <v>1482.96</v>
+        <v>1937.28</v>
       </c>
       <c r="G19" t="n">
-        <v>9.779999999999999</v>
+        <v>14.77</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1132,28 +1132,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>691.05</v>
+        <v>328.1</v>
       </c>
       <c r="D20" t="n">
-        <v>662.5599999999999</v>
+        <v>313</v>
       </c>
       <c r="E20" t="n">
-        <v>654.13</v>
+        <v>298.97</v>
       </c>
       <c r="F20" t="n">
-        <v>626.72</v>
+        <v>273.24</v>
       </c>
       <c r="G20" t="n">
-        <v>10.26</v>
+        <v>20.08</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1169,28 +1169,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1868</v>
+        <v>14850</v>
       </c>
       <c r="D21" t="n">
-        <v>1842.67</v>
+        <v>14252.87</v>
       </c>
       <c r="E21" t="n">
-        <v>1840.55</v>
+        <v>13728.98</v>
       </c>
       <c r="F21" t="n">
-        <v>1665.44</v>
+        <v>12180.72</v>
       </c>
       <c r="G21" t="n">
-        <v>12.16</v>
+        <v>21.91</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1206,28 +1206,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>188.63</v>
+        <v>3400</v>
       </c>
       <c r="D22" t="n">
-        <v>179.93</v>
+        <v>2910.34</v>
       </c>
       <c r="E22" t="n">
-        <v>174.83</v>
+        <v>2871.39</v>
       </c>
       <c r="F22" t="n">
-        <v>167.66</v>
+        <v>2611.76</v>
       </c>
       <c r="G22" t="n">
-        <v>12.51</v>
+        <v>30.18</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1235,265 +1235,6 @@
         </is>
       </c>
       <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1875</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1685.15</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1652.98</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1650.77</v>
-      </c>
-      <c r="G23" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1313</v>
-      </c>
-      <c r="D24" t="n">
-        <v>1286.9</v>
-      </c>
-      <c r="E24" t="n">
-        <v>1209.16</v>
-      </c>
-      <c r="F24" t="n">
-        <v>1147.71</v>
-      </c>
-      <c r="G24" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>2223.4</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2006.5</v>
-      </c>
-      <c r="E25" t="n">
-        <v>1925.81</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1937.28</v>
-      </c>
-      <c r="G25" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>328.1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>313</v>
-      </c>
-      <c r="E26" t="n">
-        <v>298.97</v>
-      </c>
-      <c r="F26" t="n">
-        <v>273.24</v>
-      </c>
-      <c r="G26" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>14850</v>
-      </c>
-      <c r="D27" t="n">
-        <v>14252.87</v>
-      </c>
-      <c r="E27" t="n">
-        <v>13728.98</v>
-      </c>
-      <c r="F27" t="n">
-        <v>12180.72</v>
-      </c>
-      <c r="G27" t="n">
-        <v>21.91</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>1042.9</v>
-      </c>
-      <c r="D28" t="n">
-        <v>925.8</v>
-      </c>
-      <c r="E28" t="n">
-        <v>937.3099999999999</v>
-      </c>
-      <c r="F28" t="n">
-        <v>846.8200000000001</v>
-      </c>
-      <c r="G28" t="n">
-        <v>23.16</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>31-08-2026</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D29" t="n">
-        <v>2910.34</v>
-      </c>
-      <c r="E29" t="n">
-        <v>2871.39</v>
-      </c>
-      <c r="F29" t="n">
-        <v>2611.76</v>
-      </c>
-      <c r="G29" t="n">
-        <v>30.18</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1522.2</v>
+        <v>1525.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1484.84</v>
+        <v>1488.58</v>
       </c>
       <c r="E2" t="n">
-        <v>1445.7</v>
+        <v>1445.78</v>
       </c>
       <c r="F2" t="n">
-        <v>1504.49</v>
+        <v>1504.56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4044.9</v>
+        <v>4027.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3995.8</v>
+        <v>4001.84</v>
       </c>
       <c r="E3" t="n">
-        <v>3998.04</v>
+        <v>3995.01</v>
       </c>
       <c r="F3" t="n">
-        <v>3960.45</v>
+        <v>3960.76</v>
       </c>
       <c r="G3" t="n">
-        <v>2.13</v>
+        <v>1.7</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5594.5</v>
+        <v>115.64</v>
       </c>
       <c r="D4" t="n">
-        <v>5491.18</v>
+        <v>114.56</v>
       </c>
       <c r="E4" t="n">
-        <v>5223</v>
+        <v>111.27</v>
       </c>
       <c r="F4" t="n">
-        <v>5428.9</v>
+        <v>112.55</v>
       </c>
       <c r="G4" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1060</v>
+        <v>174.32</v>
       </c>
       <c r="D5" t="n">
-        <v>1048.04</v>
+        <v>170.15</v>
       </c>
       <c r="E5" t="n">
-        <v>1043.23</v>
+        <v>165.52</v>
       </c>
       <c r="F5" t="n">
-        <v>1028.08</v>
+        <v>168.94</v>
       </c>
       <c r="G5" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>175.64</v>
+        <v>1391.6</v>
       </c>
       <c r="D6" t="n">
-        <v>169.47</v>
+        <v>1354.83</v>
       </c>
       <c r="E6" t="n">
-        <v>165.07</v>
+        <v>1354.78</v>
       </c>
       <c r="F6" t="n">
-        <v>168.8</v>
+        <v>1336.53</v>
       </c>
       <c r="G6" t="n">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>898.75</v>
+        <v>885.6</v>
       </c>
       <c r="D7" t="n">
-        <v>864.45</v>
+        <v>865.46</v>
       </c>
       <c r="E7" t="n">
-        <v>847.63</v>
+        <v>848.42</v>
       </c>
       <c r="F7" t="n">
-        <v>849.4</v>
+        <v>849.5700000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>5.81</v>
+        <v>4.24</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2021</v>
+        <v>376.05</v>
       </c>
       <c r="D8" t="n">
-        <v>1995.41</v>
+        <v>375.58</v>
       </c>
       <c r="E8" t="n">
-        <v>1932.42</v>
+        <v>363.47</v>
       </c>
       <c r="F8" t="n">
-        <v>1904.37</v>
+        <v>359.68</v>
       </c>
       <c r="G8" t="n">
-        <v>6.12</v>
+        <v>4.55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>381.5</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>374.45</v>
+        <v>282.96</v>
       </c>
       <c r="E9" t="n">
-        <v>363.04</v>
+        <v>281.19</v>
       </c>
       <c r="F9" t="n">
-        <v>359.09</v>
+        <v>277.55</v>
       </c>
       <c r="G9" t="n">
-        <v>6.24</v>
+        <v>5.57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>483.15</v>
+        <v>1172</v>
       </c>
       <c r="D10" t="n">
-        <v>462.22</v>
+        <v>1163.6</v>
       </c>
       <c r="E10" t="n">
-        <v>447.22</v>
+        <v>1138.93</v>
       </c>
       <c r="F10" t="n">
-        <v>452.03</v>
+        <v>1107.28</v>
       </c>
       <c r="G10" t="n">
-        <v>6.89</v>
+        <v>5.85</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2205</v>
+        <v>5625.5</v>
       </c>
       <c r="D11" t="n">
-        <v>2144.85</v>
+        <v>5539.75</v>
       </c>
       <c r="E11" t="n">
-        <v>2064.9</v>
+        <v>5256.59</v>
       </c>
       <c r="F11" t="n">
-        <v>2062.51</v>
+        <v>5313.9</v>
       </c>
       <c r="G11" t="n">
-        <v>6.91</v>
+        <v>5.86</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>737.9</v>
+        <v>5760</v>
       </c>
       <c r="D12" t="n">
-        <v>730.0599999999999</v>
+        <v>5509.81</v>
       </c>
       <c r="E12" t="n">
-        <v>729.4400000000001</v>
+        <v>5241.8</v>
       </c>
       <c r="F12" t="n">
-        <v>686.4299999999999</v>
+        <v>5427.41</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>6.13</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1633</v>
+        <v>11356</v>
       </c>
       <c r="D13" t="n">
-        <v>1615.3</v>
+        <v>11260.93</v>
       </c>
       <c r="E13" t="n">
-        <v>1623.65</v>
+        <v>10988.36</v>
       </c>
       <c r="F13" t="n">
-        <v>1500.66</v>
+        <v>10607.97</v>
       </c>
       <c r="G13" t="n">
-        <v>8.82</v>
+        <v>7.05</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11644</v>
+        <v>1028.1</v>
       </c>
       <c r="D14" t="n">
-        <v>11230.6</v>
+        <v>1014.47</v>
       </c>
       <c r="E14" t="n">
-        <v>10970.93</v>
+        <v>992.04</v>
       </c>
       <c r="F14" t="n">
-        <v>10613.27</v>
+        <v>958.27</v>
       </c>
       <c r="G14" t="n">
-        <v>9.710000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1628</v>
+        <v>672.15</v>
       </c>
       <c r="D15" t="n">
-        <v>1613.27</v>
+        <v>662.79</v>
       </c>
       <c r="E15" t="n">
-        <v>1544.09</v>
+        <v>655.47</v>
       </c>
       <c r="F15" t="n">
-        <v>1482.96</v>
+        <v>626.3099999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>9.779999999999999</v>
+        <v>7.32</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>691.05</v>
+        <v>2221</v>
       </c>
       <c r="D16" t="n">
-        <v>662.5599999999999</v>
+        <v>2154.21</v>
       </c>
       <c r="E16" t="n">
-        <v>654.13</v>
+        <v>2070.31</v>
       </c>
       <c r="F16" t="n">
-        <v>626.72</v>
+        <v>2061.94</v>
       </c>
       <c r="G16" t="n">
-        <v>10.26</v>
+        <v>7.71</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>188.63</v>
+        <v>489.85</v>
       </c>
       <c r="D17" t="n">
-        <v>179.93</v>
+        <v>463.71</v>
       </c>
       <c r="E17" t="n">
-        <v>174.83</v>
+        <v>448.69</v>
       </c>
       <c r="F17" t="n">
-        <v>167.66</v>
+        <v>452.34</v>
       </c>
       <c r="G17" t="n">
-        <v>12.51</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1313</v>
+        <v>1632</v>
       </c>
       <c r="D18" t="n">
-        <v>1286.9</v>
+        <v>1615.13</v>
       </c>
       <c r="E18" t="n">
-        <v>1209.16</v>
+        <v>1549.14</v>
       </c>
       <c r="F18" t="n">
-        <v>1147.71</v>
+        <v>1484.11</v>
       </c>
       <c r="G18" t="n">
-        <v>14.4</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2223.4</v>
+        <v>1293.3</v>
       </c>
       <c r="D19" t="n">
-        <v>2006.5</v>
+        <v>1228.78</v>
       </c>
       <c r="E19" t="n">
-        <v>1925.81</v>
+        <v>1189.98</v>
       </c>
       <c r="F19" t="n">
-        <v>1937.28</v>
+        <v>1170.2</v>
       </c>
       <c r="G19" t="n">
-        <v>14.77</v>
+        <v>10.52</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>328.1</v>
+        <v>186.07</v>
       </c>
       <c r="D20" t="n">
-        <v>313</v>
+        <v>180.26</v>
       </c>
       <c r="E20" t="n">
-        <v>298.97</v>
+        <v>175.15</v>
       </c>
       <c r="F20" t="n">
-        <v>273.24</v>
+        <v>167.85</v>
       </c>
       <c r="G20" t="n">
-        <v>20.08</v>
+        <v>10.85</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>14850</v>
+        <v>1841.9</v>
       </c>
       <c r="D21" t="n">
-        <v>14252.87</v>
+        <v>1684.05</v>
       </c>
       <c r="E21" t="n">
-        <v>13728.98</v>
+        <v>1652.32</v>
       </c>
       <c r="F21" t="n">
-        <v>12180.72</v>
+        <v>1650.6</v>
       </c>
       <c r="G21" t="n">
-        <v>21.91</v>
+        <v>11.59</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,30 +1211,252 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1879.8</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1842.71</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1844.4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1666.18</v>
+      </c>
+      <c r="G22" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2242.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2020.6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1933.82</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1939.68</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1366.5</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1292.32</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1216.32</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1147.97</v>
+      </c>
+      <c r="G24" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="D25" t="n">
+        <v>314.38</v>
+      </c>
+      <c r="E25" t="n">
+        <v>300.35</v>
+      </c>
+      <c r="F25" t="n">
+        <v>273.36</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>14700</v>
+      </c>
+      <c r="D26" t="n">
+        <v>14272.27</v>
+      </c>
+      <c r="E26" t="n">
+        <v>13784.34</v>
+      </c>
+      <c r="F26" t="n">
+        <v>12177.12</v>
+      </c>
+      <c r="G26" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1029.1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>925.34</v>
+      </c>
+      <c r="E27" t="n">
+        <v>937.04</v>
+      </c>
+      <c r="F27" t="n">
+        <v>846.75</v>
+      </c>
+      <c r="G27" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>3400</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2910.34</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2871.39</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2611.76</v>
-      </c>
-      <c r="G22" t="n">
-        <v>30.18</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="C28" t="n">
+        <v>3315.5</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2927.71</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2881.22</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2618.69</v>
+      </c>
+      <c r="G28" t="n">
+        <v>26.61</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASTRAL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1525.1</v>
+        <v>170.53</v>
       </c>
       <c r="D2" t="n">
-        <v>1488.58</v>
+        <v>170.03</v>
       </c>
       <c r="E2" t="n">
-        <v>1445.78</v>
+        <v>165.45</v>
       </c>
       <c r="F2" t="n">
-        <v>1504.56</v>
+        <v>168.93</v>
       </c>
       <c r="G2" t="n">
-        <v>1.37</v>
+        <v>0.95</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4027.9</v>
+        <v>115.22</v>
       </c>
       <c r="D3" t="n">
-        <v>4001.84</v>
+        <v>114.54</v>
       </c>
       <c r="E3" t="n">
-        <v>3995.01</v>
+        <v>111.26</v>
       </c>
       <c r="F3" t="n">
-        <v>3960.76</v>
+        <v>112.55</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.64</v>
+        <v>881.75</v>
       </c>
       <c r="D4" t="n">
-        <v>114.56</v>
+        <v>865.33</v>
       </c>
       <c r="E4" t="n">
-        <v>111.27</v>
+        <v>848.34</v>
       </c>
       <c r="F4" t="n">
-        <v>112.55</v>
+        <v>849.55</v>
       </c>
       <c r="G4" t="n">
-        <v>2.75</v>
+        <v>3.79</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>174.32</v>
+        <v>1391</v>
       </c>
       <c r="D5" t="n">
-        <v>170.15</v>
+        <v>1354.81</v>
       </c>
       <c r="E5" t="n">
-        <v>165.52</v>
+        <v>1354.77</v>
       </c>
       <c r="F5" t="n">
-        <v>168.94</v>
+        <v>1336.53</v>
       </c>
       <c r="G5" t="n">
-        <v>3.18</v>
+        <v>4.08</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1391.6</v>
+        <v>5555</v>
       </c>
       <c r="D6" t="n">
-        <v>1354.83</v>
+        <v>5537.4</v>
       </c>
       <c r="E6" t="n">
-        <v>1354.78</v>
+        <v>5255.18</v>
       </c>
       <c r="F6" t="n">
-        <v>1336.53</v>
+        <v>5313.55</v>
       </c>
       <c r="G6" t="n">
-        <v>4.12</v>
+        <v>4.54</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>885.6</v>
+        <v>1165.6</v>
       </c>
       <c r="D7" t="n">
-        <v>865.46</v>
+        <v>1165.23</v>
       </c>
       <c r="E7" t="n">
-        <v>848.42</v>
+        <v>1139.96</v>
       </c>
       <c r="F7" t="n">
-        <v>849.5700000000001</v>
+        <v>1107.73</v>
       </c>
       <c r="G7" t="n">
-        <v>4.24</v>
+        <v>5.22</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>376.05</v>
+        <v>292.3</v>
       </c>
       <c r="D8" t="n">
-        <v>375.58</v>
+        <v>283.74</v>
       </c>
       <c r="E8" t="n">
-        <v>363.47</v>
+        <v>281.49</v>
       </c>
       <c r="F8" t="n">
-        <v>359.68</v>
+        <v>277.7</v>
       </c>
       <c r="G8" t="n">
-        <v>4.55</v>
+        <v>5.26</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>2179.8</v>
       </c>
       <c r="D9" t="n">
-        <v>282.96</v>
+        <v>2152.84</v>
       </c>
       <c r="E9" t="n">
-        <v>281.19</v>
+        <v>2069.49</v>
       </c>
       <c r="F9" t="n">
-        <v>277.55</v>
+        <v>2061.74</v>
       </c>
       <c r="G9" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1172</v>
+        <v>11310</v>
       </c>
       <c r="D10" t="n">
-        <v>1163.6</v>
+        <v>11259.4</v>
       </c>
       <c r="E10" t="n">
-        <v>1138.93</v>
+        <v>10987.44</v>
       </c>
       <c r="F10" t="n">
-        <v>1107.28</v>
+        <v>10607.74</v>
       </c>
       <c r="G10" t="n">
-        <v>5.85</v>
+        <v>6.62</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5625.5</v>
+        <v>5800</v>
       </c>
       <c r="D11" t="n">
-        <v>5539.75</v>
+        <v>5511.14</v>
       </c>
       <c r="E11" t="n">
-        <v>5256.59</v>
+        <v>5242.6</v>
       </c>
       <c r="F11" t="n">
-        <v>5313.9</v>
+        <v>5427.61</v>
       </c>
       <c r="G11" t="n">
-        <v>5.86</v>
+        <v>6.86</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5760</v>
+        <v>675.15</v>
       </c>
       <c r="D12" t="n">
-        <v>5509.81</v>
+        <v>662.89</v>
       </c>
       <c r="E12" t="n">
-        <v>5241.8</v>
+        <v>655.53</v>
       </c>
       <c r="F12" t="n">
-        <v>5427.41</v>
+        <v>626.3200000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>6.13</v>
+        <v>7.8</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>11356</v>
+        <v>490</v>
       </c>
       <c r="D13" t="n">
-        <v>11260.93</v>
+        <v>463.72</v>
       </c>
       <c r="E13" t="n">
-        <v>10988.36</v>
+        <v>448.7</v>
       </c>
       <c r="F13" t="n">
-        <v>10607.97</v>
+        <v>452.34</v>
       </c>
       <c r="G13" t="n">
-        <v>7.05</v>
+        <v>8.32</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1028.1</v>
+        <v>1274.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1014.47</v>
+        <v>1232.43</v>
       </c>
       <c r="E14" t="n">
-        <v>992.04</v>
+        <v>1192.75</v>
       </c>
       <c r="F14" t="n">
-        <v>958.27</v>
+        <v>1169.96</v>
       </c>
       <c r="G14" t="n">
-        <v>7.29</v>
+        <v>8.93</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>672.15</v>
+        <v>184.9</v>
       </c>
       <c r="D15" t="n">
-        <v>662.79</v>
+        <v>180.22</v>
       </c>
       <c r="E15" t="n">
-        <v>655.47</v>
+        <v>175.12</v>
       </c>
       <c r="F15" t="n">
-        <v>626.3099999999999</v>
+        <v>167.85</v>
       </c>
       <c r="G15" t="n">
-        <v>7.32</v>
+        <v>10.16</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2221</v>
+        <v>1638</v>
       </c>
       <c r="D16" t="n">
-        <v>2154.21</v>
+        <v>1615.33</v>
       </c>
       <c r="E16" t="n">
-        <v>2070.31</v>
+        <v>1549.26</v>
       </c>
       <c r="F16" t="n">
-        <v>2061.94</v>
+        <v>1484.14</v>
       </c>
       <c r="G16" t="n">
-        <v>7.71</v>
+        <v>10.37</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>489.85</v>
+        <v>1829.2</v>
       </c>
       <c r="D17" t="n">
-        <v>463.71</v>
+        <v>1694.04</v>
       </c>
       <c r="E17" t="n">
-        <v>448.69</v>
+        <v>1657.11</v>
       </c>
       <c r="F17" t="n">
-        <v>452.34</v>
+        <v>1651.24</v>
       </c>
       <c r="G17" t="n">
-        <v>8.289999999999999</v>
+        <v>10.78</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1632</v>
+        <v>1880.7</v>
       </c>
       <c r="D18" t="n">
-        <v>1615.13</v>
+        <v>1842.25</v>
       </c>
       <c r="E18" t="n">
-        <v>1549.14</v>
+        <v>1847.73</v>
       </c>
       <c r="F18" t="n">
-        <v>1484.11</v>
+        <v>1666.84</v>
       </c>
       <c r="G18" t="n">
-        <v>9.960000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1293.3</v>
+        <v>2234</v>
       </c>
       <c r="D19" t="n">
-        <v>1228.78</v>
+        <v>2020.31</v>
       </c>
       <c r="E19" t="n">
-        <v>1189.98</v>
+        <v>1933.65</v>
       </c>
       <c r="F19" t="n">
-        <v>1170.2</v>
+        <v>1939.63</v>
       </c>
       <c r="G19" t="n">
-        <v>10.52</v>
+        <v>15.18</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>186.07</v>
+        <v>1356</v>
       </c>
       <c r="D20" t="n">
-        <v>180.26</v>
+        <v>1291.97</v>
       </c>
       <c r="E20" t="n">
-        <v>175.15</v>
+        <v>1216.11</v>
       </c>
       <c r="F20" t="n">
-        <v>167.85</v>
+        <v>1147.92</v>
       </c>
       <c r="G20" t="n">
-        <v>10.85</v>
+        <v>18.13</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1841.9</v>
+        <v>14461</v>
       </c>
       <c r="D21" t="n">
-        <v>1684.05</v>
+        <v>14264.3</v>
       </c>
       <c r="E21" t="n">
-        <v>1652.32</v>
+        <v>13779.56</v>
       </c>
       <c r="F21" t="n">
-        <v>1650.6</v>
+        <v>12175.92</v>
       </c>
       <c r="G21" t="n">
-        <v>11.59</v>
+        <v>18.77</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1879.8</v>
+        <v>327.75</v>
       </c>
       <c r="D22" t="n">
-        <v>1842.71</v>
+        <v>314.38</v>
       </c>
       <c r="E22" t="n">
-        <v>1844.4</v>
+        <v>300.35</v>
       </c>
       <c r="F22" t="n">
-        <v>1666.18</v>
+        <v>273.36</v>
       </c>
       <c r="G22" t="n">
-        <v>12.82</v>
+        <v>19.9</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2242.6</v>
+        <v>1016</v>
       </c>
       <c r="D23" t="n">
-        <v>2020.6</v>
+        <v>927.51</v>
       </c>
       <c r="E23" t="n">
-        <v>1933.82</v>
+        <v>938.91</v>
       </c>
       <c r="F23" t="n">
-        <v>1939.68</v>
+        <v>846.98</v>
       </c>
       <c r="G23" t="n">
-        <v>15.62</v>
+        <v>19.96</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1366.5</v>
+        <v>3303</v>
       </c>
       <c r="D24" t="n">
-        <v>1292.32</v>
+        <v>2927.29</v>
       </c>
       <c r="E24" t="n">
-        <v>1216.32</v>
+        <v>2880.97</v>
       </c>
       <c r="F24" t="n">
-        <v>1147.97</v>
+        <v>2618.63</v>
       </c>
       <c r="G24" t="n">
-        <v>19.04</v>
+        <v>26.13</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1309,154 +1309,6 @@
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>327.95</v>
-      </c>
-      <c r="D25" t="n">
-        <v>314.38</v>
-      </c>
-      <c r="E25" t="n">
-        <v>300.35</v>
-      </c>
-      <c r="F25" t="n">
-        <v>273.36</v>
-      </c>
-      <c r="G25" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>14700</v>
-      </c>
-      <c r="D26" t="n">
-        <v>14272.27</v>
-      </c>
-      <c r="E26" t="n">
-        <v>13784.34</v>
-      </c>
-      <c r="F26" t="n">
-        <v>12177.12</v>
-      </c>
-      <c r="G26" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>1029.1</v>
-      </c>
-      <c r="D27" t="n">
-        <v>925.34</v>
-      </c>
-      <c r="E27" t="n">
-        <v>937.04</v>
-      </c>
-      <c r="F27" t="n">
-        <v>846.75</v>
-      </c>
-      <c r="G27" t="n">
-        <v>21.54</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>3315.5</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2927.71</v>
-      </c>
-      <c r="E28" t="n">
-        <v>2881.22</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2618.69</v>
-      </c>
-      <c r="G28" t="n">
-        <v>26.61</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1165.6</v>
+        <v>292.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1165.23</v>
+        <v>283.74</v>
       </c>
       <c r="E7" t="n">
-        <v>1139.96</v>
+        <v>281.49</v>
       </c>
       <c r="F7" t="n">
-        <v>1107.73</v>
+        <v>277.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>292.3</v>
+        <v>11310</v>
       </c>
       <c r="D8" t="n">
-        <v>283.74</v>
+        <v>11259.4</v>
       </c>
       <c r="E8" t="n">
-        <v>281.49</v>
+        <v>10987.44</v>
       </c>
       <c r="F8" t="n">
-        <v>277.7</v>
+        <v>10607.74</v>
       </c>
       <c r="G8" t="n">
-        <v>5.26</v>
+        <v>6.62</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2179.8</v>
+        <v>5800</v>
       </c>
       <c r="D9" t="n">
-        <v>2152.84</v>
+        <v>5511.14</v>
       </c>
       <c r="E9" t="n">
-        <v>2069.49</v>
+        <v>5242.6</v>
       </c>
       <c r="F9" t="n">
-        <v>2061.74</v>
+        <v>5427.61</v>
       </c>
       <c r="G9" t="n">
-        <v>5.73</v>
+        <v>6.86</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>11310</v>
+        <v>490</v>
       </c>
       <c r="D10" t="n">
-        <v>11259.4</v>
+        <v>463.72</v>
       </c>
       <c r="E10" t="n">
-        <v>10987.44</v>
+        <v>448.7</v>
       </c>
       <c r="F10" t="n">
-        <v>10607.74</v>
+        <v>452.34</v>
       </c>
       <c r="G10" t="n">
-        <v>6.62</v>
+        <v>8.32</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5800</v>
+        <v>184.9</v>
       </c>
       <c r="D11" t="n">
-        <v>5511.14</v>
+        <v>180.22</v>
       </c>
       <c r="E11" t="n">
-        <v>5242.6</v>
+        <v>175.12</v>
       </c>
       <c r="F11" t="n">
-        <v>5427.61</v>
+        <v>167.85</v>
       </c>
       <c r="G11" t="n">
-        <v>6.86</v>
+        <v>10.16</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>675.15</v>
+        <v>1638</v>
       </c>
       <c r="D12" t="n">
-        <v>662.89</v>
+        <v>1615.33</v>
       </c>
       <c r="E12" t="n">
-        <v>655.53</v>
+        <v>1549.26</v>
       </c>
       <c r="F12" t="n">
-        <v>626.3200000000001</v>
+        <v>1484.14</v>
       </c>
       <c r="G12" t="n">
-        <v>7.8</v>
+        <v>10.37</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>490</v>
+        <v>1829.2</v>
       </c>
       <c r="D13" t="n">
-        <v>463.72</v>
+        <v>1694.04</v>
       </c>
       <c r="E13" t="n">
-        <v>448.7</v>
+        <v>1657.11</v>
       </c>
       <c r="F13" t="n">
-        <v>452.34</v>
+        <v>1651.24</v>
       </c>
       <c r="G13" t="n">
-        <v>8.32</v>
+        <v>10.78</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1274.4</v>
+        <v>2234</v>
       </c>
       <c r="D14" t="n">
-        <v>1232.43</v>
+        <v>2020.31</v>
       </c>
       <c r="E14" t="n">
-        <v>1192.75</v>
+        <v>1933.65</v>
       </c>
       <c r="F14" t="n">
-        <v>1169.96</v>
+        <v>1939.63</v>
       </c>
       <c r="G14" t="n">
-        <v>8.93</v>
+        <v>15.18</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>184.9</v>
+        <v>14461</v>
       </c>
       <c r="D15" t="n">
-        <v>180.22</v>
+        <v>14264.3</v>
       </c>
       <c r="E15" t="n">
-        <v>175.12</v>
+        <v>13779.56</v>
       </c>
       <c r="F15" t="n">
-        <v>167.85</v>
+        <v>12175.92</v>
       </c>
       <c r="G15" t="n">
-        <v>10.16</v>
+        <v>18.77</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1638</v>
+        <v>327.75</v>
       </c>
       <c r="D16" t="n">
-        <v>1615.33</v>
+        <v>314.38</v>
       </c>
       <c r="E16" t="n">
-        <v>1549.26</v>
+        <v>300.35</v>
       </c>
       <c r="F16" t="n">
-        <v>1484.14</v>
+        <v>273.36</v>
       </c>
       <c r="G16" t="n">
-        <v>10.37</v>
+        <v>19.9</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1829.2</v>
+        <v>1016</v>
       </c>
       <c r="D17" t="n">
-        <v>1694.04</v>
+        <v>927.51</v>
       </c>
       <c r="E17" t="n">
-        <v>1657.11</v>
+        <v>938.91</v>
       </c>
       <c r="F17" t="n">
-        <v>1651.24</v>
+        <v>846.98</v>
       </c>
       <c r="G17" t="n">
-        <v>10.78</v>
+        <v>19.96</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1058,28 +1058,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1880.7</v>
+        <v>3303</v>
       </c>
       <c r="D18" t="n">
-        <v>1842.25</v>
+        <v>2927.29</v>
       </c>
       <c r="E18" t="n">
-        <v>1847.73</v>
+        <v>2880.97</v>
       </c>
       <c r="F18" t="n">
-        <v>1666.84</v>
+        <v>2618.63</v>
       </c>
       <c r="G18" t="n">
-        <v>12.83</v>
+        <v>26.13</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1087,228 +1087,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>2234</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2020.31</v>
-      </c>
-      <c r="E19" t="n">
-        <v>1933.65</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1939.63</v>
-      </c>
-      <c r="G19" t="n">
-        <v>15.18</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1356</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1291.97</v>
-      </c>
-      <c r="E20" t="n">
-        <v>1216.11</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1147.92</v>
-      </c>
-      <c r="G20" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>14461</v>
-      </c>
-      <c r="D21" t="n">
-        <v>14264.3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>13779.56</v>
-      </c>
-      <c r="F21" t="n">
-        <v>12175.92</v>
-      </c>
-      <c r="G21" t="n">
-        <v>18.77</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>327.75</v>
-      </c>
-      <c r="D22" t="n">
-        <v>314.38</v>
-      </c>
-      <c r="E22" t="n">
-        <v>300.35</v>
-      </c>
-      <c r="F22" t="n">
-        <v>273.36</v>
-      </c>
-      <c r="G22" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1016</v>
-      </c>
-      <c r="D23" t="n">
-        <v>927.51</v>
-      </c>
-      <c r="E23" t="n">
-        <v>938.91</v>
-      </c>
-      <c r="F23" t="n">
-        <v>846.98</v>
-      </c>
-      <c r="G23" t="n">
-        <v>19.96</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>01-09-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>3303</v>
-      </c>
-      <c r="D24" t="n">
-        <v>2927.29</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2880.97</v>
-      </c>
-      <c r="F24" t="n">
-        <v>2618.63</v>
-      </c>
-      <c r="G24" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>170.53</v>
+        <v>1362.8</v>
       </c>
       <c r="D2" t="n">
-        <v>170.03</v>
+        <v>1355.58</v>
       </c>
       <c r="E2" t="n">
-        <v>165.45</v>
+        <v>1355.63</v>
       </c>
       <c r="F2" t="n">
-        <v>168.93</v>
+        <v>1335.26</v>
       </c>
       <c r="G2" t="n">
-        <v>0.95</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115.22</v>
+        <v>589</v>
       </c>
       <c r="D3" t="n">
-        <v>114.54</v>
+        <v>574.2</v>
       </c>
       <c r="E3" t="n">
-        <v>111.26</v>
+        <v>555.97</v>
       </c>
       <c r="F3" t="n">
-        <v>112.55</v>
+        <v>573.3099999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.38</v>
+        <v>2.74</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>881.75</v>
+        <v>874.45</v>
       </c>
       <c r="D4" t="n">
-        <v>865.33</v>
+        <v>866.9</v>
       </c>
       <c r="E4" t="n">
-        <v>848.34</v>
+        <v>848.96</v>
       </c>
       <c r="F4" t="n">
-        <v>849.55</v>
+        <v>849.5700000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>3.79</v>
+        <v>2.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1391</v>
+        <v>116.36</v>
       </c>
       <c r="D5" t="n">
-        <v>1354.81</v>
+        <v>114.73</v>
       </c>
       <c r="E5" t="n">
-        <v>1354.77</v>
+        <v>111.43</v>
       </c>
       <c r="F5" t="n">
-        <v>1336.53</v>
+        <v>112.53</v>
       </c>
       <c r="G5" t="n">
-        <v>4.08</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5555</v>
+        <v>5663</v>
       </c>
       <c r="D6" t="n">
-        <v>5537.4</v>
+        <v>5530.54</v>
       </c>
       <c r="E6" t="n">
-        <v>5255.18</v>
+        <v>5257.64</v>
       </c>
       <c r="F6" t="n">
-        <v>5313.55</v>
+        <v>5425.56</v>
       </c>
       <c r="G6" t="n">
-        <v>4.54</v>
+        <v>4.38</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>292.3</v>
+        <v>290.5</v>
       </c>
       <c r="D7" t="n">
-        <v>283.74</v>
+        <v>284.1</v>
       </c>
       <c r="E7" t="n">
-        <v>281.49</v>
+        <v>281.54</v>
       </c>
       <c r="F7" t="n">
-        <v>277.7</v>
+        <v>277.79</v>
       </c>
       <c r="G7" t="n">
-        <v>5.26</v>
+        <v>4.58</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>11310</v>
+        <v>1235.2</v>
       </c>
       <c r="D8" t="n">
-        <v>11259.4</v>
+        <v>1231.13</v>
       </c>
       <c r="E8" t="n">
-        <v>10987.44</v>
+        <v>1191.97</v>
       </c>
       <c r="F8" t="n">
-        <v>10607.74</v>
+        <v>1169.77</v>
       </c>
       <c r="G8" t="n">
-        <v>6.62</v>
+        <v>5.59</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5800</v>
+        <v>486</v>
       </c>
       <c r="D9" t="n">
-        <v>5511.14</v>
+        <v>464.88</v>
       </c>
       <c r="E9" t="n">
-        <v>5242.6</v>
+        <v>450.06</v>
       </c>
       <c r="F9" t="n">
-        <v>5427.61</v>
+        <v>452.64</v>
       </c>
       <c r="G9" t="n">
-        <v>6.86</v>
+        <v>7.37</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>490</v>
+        <v>184.57</v>
       </c>
       <c r="D10" t="n">
-        <v>463.72</v>
+        <v>180.68</v>
       </c>
       <c r="E10" t="n">
-        <v>448.7</v>
+        <v>175.42</v>
       </c>
       <c r="F10" t="n">
-        <v>452.34</v>
+        <v>168.02</v>
       </c>
       <c r="G10" t="n">
-        <v>8.32</v>
+        <v>9.85</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>184.9</v>
+        <v>1838.4</v>
       </c>
       <c r="D11" t="n">
-        <v>180.22</v>
+        <v>1703.71</v>
       </c>
       <c r="E11" t="n">
-        <v>175.12</v>
+        <v>1661.16</v>
       </c>
       <c r="F11" t="n">
-        <v>167.85</v>
+        <v>1651.74</v>
       </c>
       <c r="G11" t="n">
-        <v>10.16</v>
+        <v>11.3</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1638</v>
+        <v>2200.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1615.33</v>
+        <v>2032.9</v>
       </c>
       <c r="E12" t="n">
-        <v>1549.26</v>
+        <v>1941.14</v>
       </c>
       <c r="F12" t="n">
-        <v>1484.14</v>
+        <v>1941.75</v>
       </c>
       <c r="G12" t="n">
-        <v>10.37</v>
+        <v>13.33</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1829.2</v>
+        <v>1328.1</v>
       </c>
       <c r="D13" t="n">
-        <v>1694.04</v>
+        <v>1291.04</v>
       </c>
       <c r="E13" t="n">
-        <v>1657.11</v>
+        <v>1215.55</v>
       </c>
       <c r="F13" t="n">
-        <v>1651.24</v>
+        <v>1147.78</v>
       </c>
       <c r="G13" t="n">
-        <v>10.78</v>
+        <v>15.71</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2234</v>
+        <v>321.4</v>
       </c>
       <c r="D14" t="n">
-        <v>2020.31</v>
+        <v>315.61</v>
       </c>
       <c r="E14" t="n">
-        <v>1933.65</v>
+        <v>301.65</v>
       </c>
       <c r="F14" t="n">
-        <v>1939.63</v>
+        <v>273.42</v>
       </c>
       <c r="G14" t="n">
-        <v>15.18</v>
+        <v>17.55</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14461</v>
+        <v>998.5</v>
       </c>
       <c r="D15" t="n">
-        <v>14264.3</v>
+        <v>929.36</v>
       </c>
       <c r="E15" t="n">
-        <v>13779.56</v>
+        <v>940.1799999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>12175.92</v>
+        <v>847.09</v>
       </c>
       <c r="G15" t="n">
-        <v>18.77</v>
+        <v>17.87</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>327.75</v>
+        <v>14420</v>
       </c>
       <c r="D16" t="n">
-        <v>314.38</v>
+        <v>14282.23</v>
       </c>
       <c r="E16" t="n">
-        <v>300.35</v>
+        <v>13826.24</v>
       </c>
       <c r="F16" t="n">
-        <v>273.36</v>
+        <v>12169.82</v>
       </c>
       <c r="G16" t="n">
-        <v>19.9</v>
+        <v>18.49</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1016</v>
+        <v>3275.2</v>
       </c>
       <c r="D17" t="n">
-        <v>927.51</v>
+        <v>2943.23</v>
       </c>
       <c r="E17" t="n">
-        <v>938.91</v>
+        <v>2889.8</v>
       </c>
       <c r="F17" t="n">
-        <v>846.98</v>
+        <v>2625.33</v>
       </c>
       <c r="G17" t="n">
-        <v>19.96</v>
+        <v>24.75</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1050,43 +1050,6 @@
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3303</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2927.29</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2880.97</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2618.63</v>
-      </c>
-      <c r="G18" t="n">
-        <v>26.13</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,19 +475,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1362.8</v>
+        <v>1365.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1355.58</v>
+        <v>1355.66</v>
       </c>
       <c r="E2" t="n">
-        <v>1355.63</v>
+        <v>1355.68</v>
       </c>
       <c r="F2" t="n">
-        <v>1335.26</v>
+        <v>1335.27</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>589</v>
+        <v>588.4</v>
       </c>
       <c r="D3" t="n">
-        <v>574.2</v>
+        <v>574.1799999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>555.97</v>
+        <v>555.96</v>
       </c>
       <c r="F3" t="n">
         <v>573.3099999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>874.45</v>
+        <v>878.8</v>
       </c>
       <c r="D4" t="n">
-        <v>866.9</v>
+        <v>867.04</v>
       </c>
       <c r="E4" t="n">
-        <v>848.96</v>
+        <v>849.04</v>
       </c>
       <c r="F4" t="n">
-        <v>849.5700000000001</v>
+        <v>849.59</v>
       </c>
       <c r="G4" t="n">
-        <v>2.93</v>
+        <v>3.44</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,19 +586,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116.36</v>
+        <v>117</v>
       </c>
       <c r="D5" t="n">
-        <v>114.73</v>
+        <v>114.75</v>
       </c>
       <c r="E5" t="n">
-        <v>111.43</v>
+        <v>111.45</v>
       </c>
       <c r="F5" t="n">
         <v>112.53</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>3.97</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5663</v>
+        <v>289.2</v>
       </c>
       <c r="D6" t="n">
-        <v>5530.54</v>
+        <v>284.06</v>
       </c>
       <c r="E6" t="n">
-        <v>5257.64</v>
+        <v>281.51</v>
       </c>
       <c r="F6" t="n">
-        <v>5425.56</v>
+        <v>277.78</v>
       </c>
       <c r="G6" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>290.5</v>
+        <v>5690</v>
       </c>
       <c r="D7" t="n">
-        <v>284.1</v>
+        <v>5531.44</v>
       </c>
       <c r="E7" t="n">
-        <v>281.54</v>
+        <v>5258.18</v>
       </c>
       <c r="F7" t="n">
-        <v>277.79</v>
+        <v>5425.7</v>
       </c>
       <c r="G7" t="n">
-        <v>4.58</v>
+        <v>4.87</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1235.2</v>
+        <v>1236</v>
       </c>
       <c r="D8" t="n">
-        <v>1231.13</v>
+        <v>1235.94</v>
       </c>
       <c r="E8" t="n">
-        <v>1191.97</v>
+        <v>1195.4</v>
       </c>
       <c r="F8" t="n">
-        <v>1169.77</v>
+        <v>1169.66</v>
       </c>
       <c r="G8" t="n">
-        <v>5.59</v>
+        <v>5.67</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>486</v>
+        <v>1181.3</v>
       </c>
       <c r="D9" t="n">
-        <v>464.88</v>
+        <v>1168.15</v>
       </c>
       <c r="E9" t="n">
-        <v>450.06</v>
+        <v>1141.59</v>
       </c>
       <c r="F9" t="n">
-        <v>452.64</v>
+        <v>1108.34</v>
       </c>
       <c r="G9" t="n">
-        <v>7.37</v>
+        <v>6.58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>184.57</v>
+        <v>673.55</v>
       </c>
       <c r="D10" t="n">
-        <v>180.68</v>
+        <v>663.89</v>
       </c>
       <c r="E10" t="n">
-        <v>175.42</v>
+        <v>656.79</v>
       </c>
       <c r="F10" t="n">
-        <v>168.02</v>
+        <v>625.9</v>
       </c>
       <c r="G10" t="n">
-        <v>9.85</v>
+        <v>7.61</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1838.4</v>
+        <v>1623</v>
       </c>
       <c r="D11" t="n">
-        <v>1703.71</v>
+        <v>1617.41</v>
       </c>
       <c r="E11" t="n">
-        <v>1661.16</v>
+        <v>1553.22</v>
       </c>
       <c r="F11" t="n">
-        <v>1651.74</v>
+        <v>1485.18</v>
       </c>
       <c r="G11" t="n">
-        <v>11.3</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2200.5</v>
+        <v>498.15</v>
       </c>
       <c r="D12" t="n">
-        <v>2032.9</v>
+        <v>465.28</v>
       </c>
       <c r="E12" t="n">
-        <v>1941.14</v>
+        <v>450.3</v>
       </c>
       <c r="F12" t="n">
-        <v>1941.75</v>
+        <v>452.7</v>
       </c>
       <c r="G12" t="n">
-        <v>13.33</v>
+        <v>10.04</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1328.1</v>
+        <v>186.86</v>
       </c>
       <c r="D13" t="n">
-        <v>1291.04</v>
+        <v>180.76</v>
       </c>
       <c r="E13" t="n">
-        <v>1215.55</v>
+        <v>175.46</v>
       </c>
       <c r="F13" t="n">
-        <v>1147.78</v>
+        <v>168.03</v>
       </c>
       <c r="G13" t="n">
-        <v>15.71</v>
+        <v>11.21</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>321.4</v>
+        <v>1866</v>
       </c>
       <c r="D14" t="n">
-        <v>315.61</v>
+        <v>1842.8</v>
       </c>
       <c r="E14" t="n">
-        <v>301.65</v>
+        <v>1850.03</v>
       </c>
       <c r="F14" t="n">
-        <v>273.42</v>
+        <v>1667.44</v>
       </c>
       <c r="G14" t="n">
-        <v>17.55</v>
+        <v>11.91</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>998.5</v>
+        <v>1851.9</v>
       </c>
       <c r="D15" t="n">
-        <v>929.36</v>
+        <v>1704.16</v>
       </c>
       <c r="E15" t="n">
-        <v>940.1799999999999</v>
+        <v>1661.43</v>
       </c>
       <c r="F15" t="n">
-        <v>847.09</v>
+        <v>1651.81</v>
       </c>
       <c r="G15" t="n">
-        <v>17.87</v>
+        <v>12.11</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>14420</v>
+        <v>2210</v>
       </c>
       <c r="D16" t="n">
-        <v>14282.23</v>
+        <v>2033.22</v>
       </c>
       <c r="E16" t="n">
-        <v>13826.24</v>
+        <v>1941.33</v>
       </c>
       <c r="F16" t="n">
-        <v>12169.82</v>
+        <v>1941.8</v>
       </c>
       <c r="G16" t="n">
-        <v>18.49</v>
+        <v>13.81</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,30 +1026,178 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1343.7</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1297.24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1222.85</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1148.02</v>
+      </c>
+      <c r="G17" t="n">
+        <v>17.04</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>327.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>315.8</v>
+      </c>
+      <c r="E18" t="n">
+        <v>301.77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>273.45</v>
+      </c>
+      <c r="G18" t="n">
+        <v>19.69</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>14590</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14287.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13829.64</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12170.67</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19.88</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1017.6</v>
+      </c>
+      <c r="D20" t="n">
+        <v>930</v>
+      </c>
+      <c r="E20" t="n">
+        <v>940.5599999999999</v>
+      </c>
+      <c r="F20" t="n">
+        <v>847.1900000000001</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20.12</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C17" t="n">
-        <v>3275.2</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2943.23</v>
-      </c>
-      <c r="E17" t="n">
-        <v>2889.8</v>
-      </c>
-      <c r="F17" t="n">
-        <v>2625.33</v>
-      </c>
-      <c r="G17" t="n">
-        <v>24.75</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="C21" t="n">
+        <v>3286</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2943.59</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2890.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2625.38</v>
+      </c>
+      <c r="G21" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>878.8</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
-        <v>867.04</v>
+        <v>114.75</v>
       </c>
       <c r="E4" t="n">
-        <v>849.04</v>
+        <v>111.45</v>
       </c>
       <c r="F4" t="n">
-        <v>849.59</v>
+        <v>112.53</v>
       </c>
       <c r="G4" t="n">
-        <v>3.44</v>
+        <v>3.97</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117</v>
+        <v>5690</v>
       </c>
       <c r="D5" t="n">
-        <v>114.75</v>
+        <v>5531.44</v>
       </c>
       <c r="E5" t="n">
-        <v>111.45</v>
+        <v>5258.18</v>
       </c>
       <c r="F5" t="n">
-        <v>112.53</v>
+        <v>5425.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.97</v>
+        <v>4.87</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>360ONE</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>289.2</v>
+        <v>1181.3</v>
       </c>
       <c r="D6" t="n">
-        <v>284.06</v>
+        <v>1168.15</v>
       </c>
       <c r="E6" t="n">
-        <v>281.51</v>
+        <v>1141.59</v>
       </c>
       <c r="F6" t="n">
-        <v>277.78</v>
+        <v>1108.34</v>
       </c>
       <c r="G6" t="n">
-        <v>4.11</v>
+        <v>6.58</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5690</v>
+        <v>1623</v>
       </c>
       <c r="D7" t="n">
-        <v>5531.44</v>
+        <v>1617.41</v>
       </c>
       <c r="E7" t="n">
-        <v>5258.18</v>
+        <v>1553.22</v>
       </c>
       <c r="F7" t="n">
-        <v>5425.7</v>
+        <v>1485.18</v>
       </c>
       <c r="G7" t="n">
-        <v>4.87</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1236</v>
+        <v>498.15</v>
       </c>
       <c r="D8" t="n">
-        <v>1235.94</v>
+        <v>465.28</v>
       </c>
       <c r="E8" t="n">
-        <v>1195.4</v>
+        <v>450.3</v>
       </c>
       <c r="F8" t="n">
-        <v>1169.66</v>
+        <v>452.7</v>
       </c>
       <c r="G8" t="n">
-        <v>5.67</v>
+        <v>10.04</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1181.3</v>
+        <v>186.86</v>
       </c>
       <c r="D9" t="n">
-        <v>1168.15</v>
+        <v>180.76</v>
       </c>
       <c r="E9" t="n">
-        <v>1141.59</v>
+        <v>175.46</v>
       </c>
       <c r="F9" t="n">
-        <v>1108.34</v>
+        <v>168.03</v>
       </c>
       <c r="G9" t="n">
-        <v>6.58</v>
+        <v>11.21</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>673.55</v>
+        <v>2210</v>
       </c>
       <c r="D10" t="n">
-        <v>663.89</v>
+        <v>2033.22</v>
       </c>
       <c r="E10" t="n">
-        <v>656.79</v>
+        <v>1941.33</v>
       </c>
       <c r="F10" t="n">
-        <v>625.9</v>
+        <v>1941.8</v>
       </c>
       <c r="G10" t="n">
-        <v>7.61</v>
+        <v>13.81</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1623</v>
+        <v>1343.7</v>
       </c>
       <c r="D11" t="n">
-        <v>1617.41</v>
+        <v>1297.24</v>
       </c>
       <c r="E11" t="n">
-        <v>1553.22</v>
+        <v>1222.85</v>
       </c>
       <c r="F11" t="n">
-        <v>1485.18</v>
+        <v>1148.02</v>
       </c>
       <c r="G11" t="n">
-        <v>9.279999999999999</v>
+        <v>17.04</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>498.15</v>
+        <v>327.3</v>
       </c>
       <c r="D12" t="n">
-        <v>465.28</v>
+        <v>315.8</v>
       </c>
       <c r="E12" t="n">
-        <v>450.3</v>
+        <v>301.77</v>
       </c>
       <c r="F12" t="n">
-        <v>452.7</v>
+        <v>273.45</v>
       </c>
       <c r="G12" t="n">
-        <v>10.04</v>
+        <v>19.69</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>186.86</v>
+        <v>14590</v>
       </c>
       <c r="D13" t="n">
-        <v>180.76</v>
+        <v>14287.9</v>
       </c>
       <c r="E13" t="n">
-        <v>175.46</v>
+        <v>13829.64</v>
       </c>
       <c r="F13" t="n">
-        <v>168.03</v>
+        <v>12170.67</v>
       </c>
       <c r="G13" t="n">
-        <v>11.21</v>
+        <v>19.88</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1866</v>
+        <v>1017.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1842.8</v>
+        <v>930</v>
       </c>
       <c r="E14" t="n">
-        <v>1850.03</v>
+        <v>940.5599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1667.44</v>
+        <v>847.1900000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>11.91</v>
+        <v>20.12</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1851.9</v>
+        <v>3286</v>
       </c>
       <c r="D15" t="n">
-        <v>1704.16</v>
+        <v>2943.59</v>
       </c>
       <c r="E15" t="n">
-        <v>1661.43</v>
+        <v>2890.02</v>
       </c>
       <c r="F15" t="n">
-        <v>1651.81</v>
+        <v>2625.38</v>
       </c>
       <c r="G15" t="n">
-        <v>12.11</v>
+        <v>25.16</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -976,228 +976,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>2210</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2033.22</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1941.33</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1941.8</v>
-      </c>
-      <c r="G16" t="n">
-        <v>13.81</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1343.7</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1297.24</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1222.85</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1148.02</v>
-      </c>
-      <c r="G17" t="n">
-        <v>17.04</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>327.3</v>
-      </c>
-      <c r="D18" t="n">
-        <v>315.8</v>
-      </c>
-      <c r="E18" t="n">
-        <v>301.77</v>
-      </c>
-      <c r="F18" t="n">
-        <v>273.45</v>
-      </c>
-      <c r="G18" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>14590</v>
-      </c>
-      <c r="D19" t="n">
-        <v>14287.9</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13829.64</v>
-      </c>
-      <c r="F19" t="n">
-        <v>12170.67</v>
-      </c>
-      <c r="G19" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1017.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>930</v>
-      </c>
-      <c r="E20" t="n">
-        <v>940.5599999999999</v>
-      </c>
-      <c r="F20" t="n">
-        <v>847.1900000000001</v>
-      </c>
-      <c r="G20" t="n">
-        <v>20.12</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>02-09-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>3286</v>
-      </c>
-      <c r="D21" t="n">
-        <v>2943.59</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2890.02</v>
-      </c>
-      <c r="F21" t="n">
-        <v>2625.38</v>
-      </c>
-      <c r="G21" t="n">
-        <v>25.16</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1365.2</v>
+        <v>586</v>
       </c>
       <c r="D2" t="n">
-        <v>1355.66</v>
+        <v>576.01</v>
       </c>
       <c r="E2" t="n">
-        <v>1355.68</v>
+        <v>557.3200000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1335.27</v>
+        <v>573.9</v>
       </c>
       <c r="G2" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>588.4</v>
+        <v>1372</v>
       </c>
       <c r="D3" t="n">
-        <v>574.1799999999999</v>
+        <v>1357.28</v>
       </c>
       <c r="E3" t="n">
-        <v>555.96</v>
+        <v>1357.02</v>
       </c>
       <c r="F3" t="n">
-        <v>573.3099999999999</v>
+        <v>1334.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.63</v>
+        <v>2.84</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>5622</v>
       </c>
       <c r="D4" t="n">
-        <v>114.75</v>
+        <v>5552.69</v>
       </c>
       <c r="E4" t="n">
-        <v>111.45</v>
+        <v>5274.12</v>
       </c>
       <c r="F4" t="n">
-        <v>112.53</v>
+        <v>5423.62</v>
       </c>
       <c r="G4" t="n">
-        <v>3.97</v>
+        <v>3.66</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5690</v>
+        <v>117.56</v>
       </c>
       <c r="D5" t="n">
-        <v>5531.44</v>
+        <v>115</v>
       </c>
       <c r="E5" t="n">
-        <v>5258.18</v>
+        <v>111.64</v>
       </c>
       <c r="F5" t="n">
-        <v>5425.7</v>
+        <v>112.53</v>
       </c>
       <c r="G5" t="n">
-        <v>4.87</v>
+        <v>4.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1181.3</v>
+        <v>292.35</v>
       </c>
       <c r="D6" t="n">
-        <v>1168.15</v>
+        <v>284.16</v>
       </c>
       <c r="E6" t="n">
-        <v>1141.59</v>
+        <v>281.58</v>
       </c>
       <c r="F6" t="n">
-        <v>1108.34</v>
+        <v>277.8</v>
       </c>
       <c r="G6" t="n">
-        <v>6.58</v>
+        <v>5.24</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1623</v>
+        <v>895.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1617.41</v>
+        <v>867.6</v>
       </c>
       <c r="E7" t="n">
-        <v>1553.22</v>
+        <v>849.38</v>
       </c>
       <c r="F7" t="n">
-        <v>1485.18</v>
+        <v>849.67</v>
       </c>
       <c r="G7" t="n">
-        <v>9.279999999999999</v>
+        <v>5.39</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>498.15</v>
+        <v>1245.5</v>
       </c>
       <c r="D8" t="n">
-        <v>465.28</v>
+        <v>1236.25</v>
       </c>
       <c r="E8" t="n">
-        <v>450.3</v>
+        <v>1195.59</v>
       </c>
       <c r="F8" t="n">
-        <v>452.7</v>
+        <v>1169.7</v>
       </c>
       <c r="G8" t="n">
-        <v>10.04</v>
+        <v>6.48</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>186.86</v>
+        <v>678.85</v>
       </c>
       <c r="D9" t="n">
-        <v>180.76</v>
+        <v>664.0700000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>175.46</v>
+        <v>656.9</v>
       </c>
       <c r="F9" t="n">
-        <v>168.03</v>
+        <v>625.92</v>
       </c>
       <c r="G9" t="n">
-        <v>11.21</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2210</v>
+        <v>492.05</v>
       </c>
       <c r="D10" t="n">
-        <v>2033.22</v>
+        <v>466.39</v>
       </c>
       <c r="E10" t="n">
-        <v>1941.33</v>
+        <v>452</v>
       </c>
       <c r="F10" t="n">
-        <v>1941.8</v>
+        <v>453.05</v>
       </c>
       <c r="G10" t="n">
-        <v>13.81</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1343.7</v>
+        <v>2162.8</v>
       </c>
       <c r="D11" t="n">
-        <v>1297.24</v>
+        <v>2044.28</v>
       </c>
       <c r="E11" t="n">
-        <v>1222.85</v>
+        <v>1948.71</v>
       </c>
       <c r="F11" t="n">
-        <v>1148.02</v>
+        <v>1943.79</v>
       </c>
       <c r="G11" t="n">
-        <v>17.04</v>
+        <v>11.27</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>327.3</v>
+        <v>1850</v>
       </c>
       <c r="D12" t="n">
-        <v>315.8</v>
+        <v>1704.1</v>
       </c>
       <c r="E12" t="n">
-        <v>301.77</v>
+        <v>1661.39</v>
       </c>
       <c r="F12" t="n">
-        <v>273.45</v>
+        <v>1651.8</v>
       </c>
       <c r="G12" t="n">
-        <v>19.69</v>
+        <v>12</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>14590</v>
+        <v>189.5</v>
       </c>
       <c r="D13" t="n">
-        <v>14287.9</v>
+        <v>181.46</v>
       </c>
       <c r="E13" t="n">
-        <v>13829.64</v>
+        <v>175.86</v>
       </c>
       <c r="F13" t="n">
-        <v>12170.67</v>
+        <v>168.24</v>
       </c>
       <c r="G13" t="n">
-        <v>19.88</v>
+        <v>12.64</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1017.6</v>
+        <v>1891</v>
       </c>
       <c r="D14" t="n">
-        <v>930</v>
+        <v>1843.63</v>
       </c>
       <c r="E14" t="n">
-        <v>940.5599999999999</v>
+        <v>1850.53</v>
       </c>
       <c r="F14" t="n">
-        <v>847.1900000000001</v>
+        <v>1667.57</v>
       </c>
       <c r="G14" t="n">
-        <v>20.12</v>
+        <v>13.4</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,30 +952,252 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1302.79</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1148.11</v>
+      </c>
+      <c r="G15" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1009.2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>932.29</v>
+      </c>
+      <c r="E16" t="n">
+        <v>941.8200000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>847.41</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>196.6</v>
+      </c>
+      <c r="D17" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="E17" t="n">
+        <v>173.06</v>
+      </c>
+      <c r="F17" t="n">
+        <v>164.37</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>328.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>317.19</v>
+      </c>
+      <c r="E18" t="n">
+        <v>303.24</v>
+      </c>
+      <c r="F18" t="n">
+        <v>273.56</v>
+      </c>
+      <c r="G18" t="n">
+        <v>20.19</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>14627</v>
+      </c>
+      <c r="D19" t="n">
+        <v>14314.5</v>
+      </c>
+      <c r="E19" t="n">
+        <v>13881.92</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12165.32</v>
+      </c>
+      <c r="G19" t="n">
+        <v>20.24</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>3286</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2943.59</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2890.02</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2625.38</v>
-      </c>
-      <c r="G15" t="n">
-        <v>25.16</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="C20" t="n">
+        <v>3187.5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2958.31</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2897.27</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2631.68</v>
+      </c>
+      <c r="G20" t="n">
+        <v>21.12</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1810.5</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1757.56</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1803.04</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1494.38</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>586</v>
+        <v>1145</v>
       </c>
       <c r="D2" t="n">
-        <v>576.01</v>
+        <v>1117.85</v>
       </c>
       <c r="E2" t="n">
-        <v>557.3200000000001</v>
+        <v>1086.78</v>
       </c>
       <c r="F2" t="n">
-        <v>573.9</v>
+        <v>1126.14</v>
       </c>
       <c r="G2" t="n">
-        <v>2.11</v>
+        <v>1.67</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1372</v>
+        <v>587.95</v>
       </c>
       <c r="D3" t="n">
-        <v>1357.28</v>
+        <v>576.0700000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>1357.02</v>
+        <v>557.36</v>
       </c>
       <c r="F3" t="n">
-        <v>1334.18</v>
+        <v>573.91</v>
       </c>
       <c r="G3" t="n">
-        <v>2.84</v>
+        <v>2.45</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5622</v>
+        <v>116.32</v>
       </c>
       <c r="D4" t="n">
-        <v>5552.69</v>
+        <v>114.96</v>
       </c>
       <c r="E4" t="n">
-        <v>5274.12</v>
+        <v>111.61</v>
       </c>
       <c r="F4" t="n">
-        <v>5423.62</v>
+        <v>112.52</v>
       </c>
       <c r="G4" t="n">
-        <v>3.66</v>
+        <v>3.38</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117.56</v>
+        <v>289.5</v>
       </c>
       <c r="D5" t="n">
-        <v>115</v>
+        <v>284.72</v>
       </c>
       <c r="E5" t="n">
-        <v>111.64</v>
+        <v>281.66</v>
       </c>
       <c r="F5" t="n">
-        <v>112.53</v>
+        <v>277.87</v>
       </c>
       <c r="G5" t="n">
-        <v>4.47</v>
+        <v>4.19</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>292.35</v>
+        <v>5657</v>
       </c>
       <c r="D6" t="n">
-        <v>284.16</v>
+        <v>5553.85</v>
       </c>
       <c r="E6" t="n">
-        <v>281.58</v>
+        <v>5274.82</v>
       </c>
       <c r="F6" t="n">
-        <v>277.8</v>
+        <v>5423.8</v>
       </c>
       <c r="G6" t="n">
-        <v>5.24</v>
+        <v>4.3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>895.5</v>
+        <v>1394</v>
       </c>
       <c r="D7" t="n">
-        <v>867.6</v>
+        <v>1358.02</v>
       </c>
       <c r="E7" t="n">
-        <v>849.38</v>
+        <v>1357.46</v>
       </c>
       <c r="F7" t="n">
-        <v>849.67</v>
+        <v>1334.29</v>
       </c>
       <c r="G7" t="n">
-        <v>5.39</v>
+        <v>4.48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1245.5</v>
+        <v>888.75</v>
       </c>
       <c r="D8" t="n">
-        <v>1236.25</v>
+        <v>869.09</v>
       </c>
       <c r="E8" t="n">
-        <v>1195.59</v>
+        <v>850.17</v>
       </c>
       <c r="F8" t="n">
-        <v>1169.7</v>
+        <v>849.6900000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>6.48</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>678.85</v>
+        <v>732</v>
       </c>
       <c r="D9" t="n">
-        <v>664.0700000000001</v>
+        <v>729.97</v>
       </c>
       <c r="E9" t="n">
-        <v>656.9</v>
+        <v>729.59</v>
       </c>
       <c r="F9" t="n">
-        <v>625.92</v>
+        <v>686.59</v>
       </c>
       <c r="G9" t="n">
-        <v>8.460000000000001</v>
+        <v>6.61</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>492.05</v>
+        <v>490</v>
       </c>
       <c r="D10" t="n">
-        <v>466.39</v>
+        <v>466.32</v>
       </c>
       <c r="E10" t="n">
-        <v>452</v>
+        <v>451.96</v>
       </c>
       <c r="F10" t="n">
-        <v>453.05</v>
+        <v>453.04</v>
       </c>
       <c r="G10" t="n">
-        <v>8.609999999999999</v>
+        <v>8.16</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2162.8</v>
+        <v>1269</v>
       </c>
       <c r="D11" t="n">
-        <v>2044.28</v>
+        <v>1240.57</v>
       </c>
       <c r="E11" t="n">
-        <v>1948.71</v>
+        <v>1198.05</v>
       </c>
       <c r="F11" t="n">
-        <v>1943.79</v>
+        <v>1169.55</v>
       </c>
       <c r="G11" t="n">
-        <v>11.27</v>
+        <v>8.5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1850</v>
+        <v>681.65</v>
       </c>
       <c r="D12" t="n">
-        <v>1704.1</v>
+        <v>665.47</v>
       </c>
       <c r="E12" t="n">
-        <v>1661.39</v>
+        <v>658.15</v>
       </c>
       <c r="F12" t="n">
-        <v>1651.8</v>
+        <v>625.6</v>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>189.5</v>
+        <v>2159.4</v>
       </c>
       <c r="D13" t="n">
-        <v>181.46</v>
+        <v>2044.17</v>
       </c>
       <c r="E13" t="n">
-        <v>175.86</v>
+        <v>1948.65</v>
       </c>
       <c r="F13" t="n">
-        <v>168.24</v>
+        <v>1943.77</v>
       </c>
       <c r="G13" t="n">
-        <v>12.64</v>
+        <v>11.09</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1891</v>
+        <v>189</v>
       </c>
       <c r="D14" t="n">
-        <v>1843.63</v>
+        <v>181.45</v>
       </c>
       <c r="E14" t="n">
-        <v>1850.53</v>
+        <v>175.85</v>
       </c>
       <c r="F14" t="n">
-        <v>1667.57</v>
+        <v>168.23</v>
       </c>
       <c r="G14" t="n">
-        <v>13.4</v>
+        <v>12.34</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1333</v>
+        <v>1870</v>
       </c>
       <c r="D15" t="n">
-        <v>1302.79</v>
+        <v>1715.61</v>
       </c>
       <c r="E15" t="n">
-        <v>1230</v>
+        <v>1666.52</v>
       </c>
       <c r="F15" t="n">
-        <v>1148.11</v>
+        <v>1652.08</v>
       </c>
       <c r="G15" t="n">
-        <v>16.1</v>
+        <v>13.19</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1009.2</v>
+        <v>1902</v>
       </c>
       <c r="D16" t="n">
-        <v>932.29</v>
+        <v>1845.59</v>
       </c>
       <c r="E16" t="n">
-        <v>941.8200000000001</v>
+        <v>1853.12</v>
       </c>
       <c r="F16" t="n">
-        <v>847.41</v>
+        <v>1668.26</v>
       </c>
       <c r="G16" t="n">
-        <v>19.09</v>
+        <v>14.01</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>196.6</v>
+        <v>1330</v>
       </c>
       <c r="D17" t="n">
-        <v>177.4</v>
+        <v>1302.69</v>
       </c>
       <c r="E17" t="n">
-        <v>173.06</v>
+        <v>1229.94</v>
       </c>
       <c r="F17" t="n">
-        <v>164.37</v>
+        <v>1148.1</v>
       </c>
       <c r="G17" t="n">
-        <v>19.61</v>
+        <v>15.84</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>328.8</v>
+        <v>324.8</v>
       </c>
       <c r="D18" t="n">
-        <v>317.19</v>
+        <v>317.06</v>
       </c>
       <c r="E18" t="n">
-        <v>303.24</v>
+        <v>303.16</v>
       </c>
       <c r="F18" t="n">
-        <v>273.56</v>
+        <v>273.54</v>
       </c>
       <c r="G18" t="n">
-        <v>20.19</v>
+        <v>18.74</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1104,19 +1104,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>14627</v>
+        <v>14445</v>
       </c>
       <c r="D19" t="n">
-        <v>14314.5</v>
+        <v>14308.43</v>
       </c>
       <c r="E19" t="n">
-        <v>13881.92</v>
+        <v>13878.28</v>
       </c>
       <c r="F19" t="n">
-        <v>12165.32</v>
+        <v>12164.41</v>
       </c>
       <c r="G19" t="n">
-        <v>20.24</v>
+        <v>18.75</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3187.5</v>
+        <v>1012.8</v>
       </c>
       <c r="D20" t="n">
-        <v>2958.31</v>
+        <v>932.41</v>
       </c>
       <c r="E20" t="n">
-        <v>2897.27</v>
+        <v>941.89</v>
       </c>
       <c r="F20" t="n">
-        <v>2631.68</v>
+        <v>847.4299999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>21.12</v>
+        <v>19.51</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,30 +1174,104 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>197</v>
+      </c>
+      <c r="D21" t="n">
+        <v>177.42</v>
+      </c>
+      <c r="E21" t="n">
+        <v>173.07</v>
+      </c>
+      <c r="F21" t="n">
+        <v>164.37</v>
+      </c>
+      <c r="G21" t="n">
+        <v>19.85</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>3170.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2957.74</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2896.93</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2631.59</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20.47</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>03-09-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>NUVAMA</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>1810.5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1757.56</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1803.04</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1494.38</v>
-      </c>
-      <c r="G21" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="C23" t="n">
+        <v>1839.2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1758.52</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1803.62</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1494.52</v>
+      </c>
+      <c r="G23" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>732</v>
+        <v>1330</v>
       </c>
       <c r="D9" t="n">
-        <v>729.97</v>
+        <v>1302.69</v>
       </c>
       <c r="E9" t="n">
-        <v>729.59</v>
+        <v>1229.94</v>
       </c>
       <c r="F9" t="n">
-        <v>686.59</v>
+        <v>1148.1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.61</v>
+        <v>15.84</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>490</v>
+        <v>324.8</v>
       </c>
       <c r="D10" t="n">
-        <v>466.32</v>
+        <v>317.06</v>
       </c>
       <c r="E10" t="n">
-        <v>451.96</v>
+        <v>303.16</v>
       </c>
       <c r="F10" t="n">
-        <v>453.04</v>
+        <v>273.54</v>
       </c>
       <c r="G10" t="n">
-        <v>8.16</v>
+        <v>18.74</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1269</v>
+        <v>14445</v>
       </c>
       <c r="D11" t="n">
-        <v>1240.57</v>
+        <v>14308.43</v>
       </c>
       <c r="E11" t="n">
-        <v>1198.05</v>
+        <v>13878.28</v>
       </c>
       <c r="F11" t="n">
-        <v>1169.55</v>
+        <v>12164.41</v>
       </c>
       <c r="G11" t="n">
-        <v>8.5</v>
+        <v>18.75</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>681.65</v>
+        <v>197</v>
       </c>
       <c r="D12" t="n">
-        <v>665.47</v>
+        <v>177.42</v>
       </c>
       <c r="E12" t="n">
-        <v>658.15</v>
+        <v>173.07</v>
       </c>
       <c r="F12" t="n">
-        <v>625.6</v>
+        <v>164.37</v>
       </c>
       <c r="G12" t="n">
-        <v>8.960000000000001</v>
+        <v>19.85</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2159.4</v>
+        <v>3170.2</v>
       </c>
       <c r="D13" t="n">
-        <v>2044.17</v>
+        <v>2957.74</v>
       </c>
       <c r="E13" t="n">
-        <v>1948.65</v>
+        <v>2896.93</v>
       </c>
       <c r="F13" t="n">
-        <v>1943.77</v>
+        <v>2631.59</v>
       </c>
       <c r="G13" t="n">
-        <v>11.09</v>
+        <v>20.47</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>04-09-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>189</v>
+        <v>1839.2</v>
       </c>
       <c r="D14" t="n">
-        <v>181.45</v>
+        <v>1758.52</v>
       </c>
       <c r="E14" t="n">
-        <v>175.85</v>
+        <v>1803.62</v>
       </c>
       <c r="F14" t="n">
-        <v>168.23</v>
+        <v>1494.52</v>
       </c>
       <c r="G14" t="n">
-        <v>12.34</v>
+        <v>23.06</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -939,339 +939,6 @@
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>POLICYBZR</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>1870</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1715.61</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1666.52</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1652.08</v>
-      </c>
-      <c r="G15" t="n">
-        <v>13.19</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>OBEROIRLTY</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1902</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1845.59</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1853.12</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1668.26</v>
-      </c>
-      <c r="G16" t="n">
-        <v>14.01</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1330</v>
-      </c>
-      <c r="D17" t="n">
-        <v>1302.69</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1229.94</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1148.1</v>
-      </c>
-      <c r="G17" t="n">
-        <v>15.84</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>324.8</v>
-      </c>
-      <c r="D18" t="n">
-        <v>317.06</v>
-      </c>
-      <c r="E18" t="n">
-        <v>303.16</v>
-      </c>
-      <c r="F18" t="n">
-        <v>273.54</v>
-      </c>
-      <c r="G18" t="n">
-        <v>18.74</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DIXON</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>14445</v>
-      </c>
-      <c r="D19" t="n">
-        <v>14308.43</v>
-      </c>
-      <c r="E19" t="n">
-        <v>13878.28</v>
-      </c>
-      <c r="F19" t="n">
-        <v>12164.41</v>
-      </c>
-      <c r="G19" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1012.8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>932.41</v>
-      </c>
-      <c r="E20" t="n">
-        <v>941.89</v>
-      </c>
-      <c r="F20" t="n">
-        <v>847.4299999999999</v>
-      </c>
-      <c r="G20" t="n">
-        <v>19.51</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>197</v>
-      </c>
-      <c r="D21" t="n">
-        <v>177.42</v>
-      </c>
-      <c r="E21" t="n">
-        <v>173.07</v>
-      </c>
-      <c r="F21" t="n">
-        <v>164.37</v>
-      </c>
-      <c r="G21" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>3170.2</v>
-      </c>
-      <c r="D22" t="n">
-        <v>2957.74</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2896.93</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2631.59</v>
-      </c>
-      <c r="G22" t="n">
-        <v>20.47</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>1839.2</v>
-      </c>
-      <c r="D23" t="n">
-        <v>1758.52</v>
-      </c>
-      <c r="E23" t="n">
-        <v>1803.62</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1494.52</v>
-      </c>
-      <c r="G23" t="n">
-        <v>23.06</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1145</v>
+        <v>172.1</v>
       </c>
       <c r="D2" t="n">
-        <v>1117.85</v>
+        <v>171.86</v>
       </c>
       <c r="E2" t="n">
-        <v>1086.78</v>
+        <v>166.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1126.14</v>
+        <v>169.31</v>
       </c>
       <c r="G2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>587.95</v>
+        <v>595.95</v>
       </c>
       <c r="D3" t="n">
-        <v>576.0700000000001</v>
+        <v>578.2</v>
       </c>
       <c r="E3" t="n">
-        <v>557.36</v>
+        <v>558.91</v>
       </c>
       <c r="F3" t="n">
-        <v>573.91</v>
+        <v>574.55</v>
       </c>
       <c r="G3" t="n">
-        <v>2.45</v>
+        <v>3.72</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116.32</v>
+        <v>884.1</v>
       </c>
       <c r="D4" t="n">
-        <v>114.96</v>
+        <v>871.02</v>
       </c>
       <c r="E4" t="n">
-        <v>111.61</v>
+        <v>851.2</v>
       </c>
       <c r="F4" t="n">
-        <v>112.52</v>
+        <v>849.78</v>
       </c>
       <c r="G4" t="n">
-        <v>3.38</v>
+        <v>4.04</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>289.5</v>
+        <v>117.3</v>
       </c>
       <c r="D5" t="n">
-        <v>284.72</v>
+        <v>115.19</v>
       </c>
       <c r="E5" t="n">
-        <v>281.66</v>
+        <v>111.8</v>
       </c>
       <c r="F5" t="n">
-        <v>277.87</v>
+        <v>112.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5657</v>
+        <v>290.2</v>
       </c>
       <c r="D6" t="n">
-        <v>5553.85</v>
+        <v>285.24</v>
       </c>
       <c r="E6" t="n">
-        <v>5274.82</v>
+        <v>281.82</v>
       </c>
       <c r="F6" t="n">
-        <v>5423.8</v>
+        <v>277.96</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1394</v>
+        <v>5672.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1358.02</v>
+        <v>5570.19</v>
       </c>
       <c r="E7" t="n">
-        <v>1357.46</v>
+        <v>5291.78</v>
       </c>
       <c r="F7" t="n">
-        <v>1334.29</v>
+        <v>5420.8</v>
       </c>
       <c r="G7" t="n">
-        <v>4.48</v>
+        <v>4.64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>888.75</v>
+        <v>1403.4</v>
       </c>
       <c r="D8" t="n">
-        <v>869.09</v>
+        <v>1360.36</v>
       </c>
       <c r="E8" t="n">
-        <v>850.17</v>
+        <v>1359.42</v>
       </c>
       <c r="F8" t="n">
-        <v>849.6900000000001</v>
+        <v>1333.26</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>5.26</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1330</v>
+        <v>423.7</v>
       </c>
       <c r="D9" t="n">
-        <v>1302.69</v>
+        <v>401.06</v>
       </c>
       <c r="E9" t="n">
-        <v>1229.94</v>
+        <v>394.41</v>
       </c>
       <c r="F9" t="n">
-        <v>1148.1</v>
+        <v>399.97</v>
       </c>
       <c r="G9" t="n">
-        <v>15.84</v>
+        <v>5.93</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>324.8</v>
+        <v>2183.1</v>
       </c>
       <c r="D10" t="n">
-        <v>317.06</v>
+        <v>2168.65</v>
       </c>
       <c r="E10" t="n">
-        <v>303.16</v>
+        <v>2078.74</v>
       </c>
       <c r="F10" t="n">
-        <v>273.54</v>
+        <v>2059.81</v>
       </c>
       <c r="G10" t="n">
-        <v>18.74</v>
+        <v>5.99</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>14445</v>
+        <v>1240.2</v>
       </c>
       <c r="D11" t="n">
-        <v>14308.43</v>
+        <v>1239.61</v>
       </c>
       <c r="E11" t="n">
-        <v>13878.28</v>
+        <v>1197.48</v>
       </c>
       <c r="F11" t="n">
-        <v>12164.41</v>
+        <v>1169.41</v>
       </c>
       <c r="G11" t="n">
-        <v>18.75</v>
+        <v>6.05</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>197</v>
+        <v>11305</v>
       </c>
       <c r="D12" t="n">
-        <v>177.42</v>
+        <v>11304.2</v>
       </c>
       <c r="E12" t="n">
-        <v>173.07</v>
+        <v>11017.1</v>
       </c>
       <c r="F12" t="n">
-        <v>164.37</v>
+        <v>10601.26</v>
       </c>
       <c r="G12" t="n">
-        <v>19.85</v>
+        <v>6.64</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3170.2</v>
+        <v>490.6</v>
       </c>
       <c r="D13" t="n">
-        <v>2957.74</v>
+        <v>466.34</v>
       </c>
       <c r="E13" t="n">
-        <v>2896.93</v>
+        <v>451.98</v>
       </c>
       <c r="F13" t="n">
-        <v>2631.59</v>
+        <v>453.04</v>
       </c>
       <c r="G13" t="n">
-        <v>20.47</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,30 +915,474 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>PRESTIGE</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1632.5</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1609.34</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1628.47</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1498.01</v>
+      </c>
+      <c r="G14" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>DLF</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>686.55</v>
+      </c>
+      <c r="D15" t="n">
+        <v>665.63</v>
+      </c>
+      <c r="E15" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="F15" t="n">
+        <v>625.62</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1847.4</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1714.85</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1666.07</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1651.96</v>
+      </c>
+      <c r="G16" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>188.36</v>
+      </c>
+      <c r="D17" t="n">
+        <v>181.43</v>
+      </c>
+      <c r="E17" t="n">
+        <v>175.84</v>
+      </c>
+      <c r="F17" t="n">
+        <v>168.23</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2180.1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2044.86</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1949.06</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1943.88</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OBEROIRLTY</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1920.6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1846.21</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1853.49</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1668.35</v>
+      </c>
+      <c r="G19" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1308.28</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1237.08</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1148</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>324.2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>318.53</v>
+      </c>
+      <c r="E21" t="n">
+        <v>304.54</v>
+      </c>
+      <c r="F21" t="n">
+        <v>273.63</v>
+      </c>
+      <c r="G21" t="n">
+        <v>18.48</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>178.63</v>
+      </c>
+      <c r="E22" t="n">
+        <v>173.61</v>
+      </c>
+      <c r="F22" t="n">
+        <v>164.66</v>
+      </c>
+      <c r="G22" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1024.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>932.8</v>
+      </c>
+      <c r="E23" t="n">
+        <v>942.12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>847.49</v>
+      </c>
+      <c r="G23" t="n">
+        <v>20.86</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>NUVAMA</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>1839.2</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1758.52</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1803.62</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1494.52</v>
-      </c>
-      <c r="G14" t="n">
-        <v>23.06</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="C24" t="n">
+        <v>1834.7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1753.67</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1805.34</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1496.42</v>
+      </c>
+      <c r="G24" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3238.1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2974.9</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2905.19</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2638.01</v>
+      </c>
+      <c r="G25" t="n">
+        <v>22.75</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>433.65</v>
+      </c>
+      <c r="D26" t="n">
+        <v>417.92</v>
+      </c>
+      <c r="E26" t="n">
+        <v>412.56</v>
+      </c>
+      <c r="F26" t="n">
+        <v>334.42</v>
+      </c>
+      <c r="G26" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>172.1</v>
+        <v>1165</v>
       </c>
       <c r="D2" t="n">
-        <v>171.86</v>
+        <v>1122.22</v>
       </c>
       <c r="E2" t="n">
-        <v>166.11</v>
+        <v>1088.93</v>
       </c>
       <c r="F2" t="n">
-        <v>169.31</v>
+        <v>1126.62</v>
       </c>
       <c r="G2" t="n">
-        <v>1.65</v>
+        <v>3.41</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>595.95</v>
+        <v>879.7</v>
       </c>
       <c r="D3" t="n">
-        <v>578.2</v>
+        <v>870.88</v>
       </c>
       <c r="E3" t="n">
-        <v>558.91</v>
+        <v>851.11</v>
       </c>
       <c r="F3" t="n">
-        <v>574.55</v>
+        <v>849.75</v>
       </c>
       <c r="G3" t="n">
-        <v>3.72</v>
+        <v>3.52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>884.1</v>
+        <v>288.1</v>
       </c>
       <c r="D4" t="n">
-        <v>871.02</v>
+        <v>285.17</v>
       </c>
       <c r="E4" t="n">
-        <v>851.2</v>
+        <v>281.78</v>
       </c>
       <c r="F4" t="n">
-        <v>849.78</v>
+        <v>277.95</v>
       </c>
       <c r="G4" t="n">
-        <v>4.04</v>
+        <v>3.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117.3</v>
+        <v>117</v>
       </c>
       <c r="D5" t="n">
-        <v>115.19</v>
+        <v>115.18</v>
       </c>
       <c r="E5" t="n">
         <v>111.8</v>
@@ -598,7 +598,7 @@
         <v>112.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.27</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>290.2</v>
+        <v>5643</v>
       </c>
       <c r="D6" t="n">
-        <v>285.24</v>
+        <v>5569.2</v>
       </c>
       <c r="E6" t="n">
-        <v>281.82</v>
+        <v>5291.19</v>
       </c>
       <c r="F6" t="n">
-        <v>277.96</v>
+        <v>5420.65</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5672.5</v>
+        <v>601</v>
       </c>
       <c r="D7" t="n">
-        <v>5570.19</v>
+        <v>578.37</v>
       </c>
       <c r="E7" t="n">
-        <v>5291.78</v>
+        <v>559.02</v>
       </c>
       <c r="F7" t="n">
-        <v>5420.8</v>
+        <v>574.58</v>
       </c>
       <c r="G7" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1403.4</v>
+        <v>1394.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1360.36</v>
+        <v>1360.07</v>
       </c>
       <c r="E8" t="n">
-        <v>1359.42</v>
+        <v>1359.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1333.26</v>
+        <v>1333.22</v>
       </c>
       <c r="G8" t="n">
-        <v>5.26</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>423.7</v>
+        <v>424.5</v>
       </c>
       <c r="D9" t="n">
-        <v>401.06</v>
+        <v>401.08</v>
       </c>
       <c r="E9" t="n">
-        <v>394.41</v>
+        <v>394.43</v>
       </c>
       <c r="F9" t="n">
         <v>399.97</v>
       </c>
       <c r="G9" t="n">
-        <v>5.93</v>
+        <v>6.13</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2183.1</v>
+        <v>1249.7</v>
       </c>
       <c r="D10" t="n">
-        <v>2168.65</v>
+        <v>1244.66</v>
       </c>
       <c r="E10" t="n">
-        <v>2078.74</v>
+        <v>1200.32</v>
       </c>
       <c r="F10" t="n">
-        <v>2059.81</v>
+        <v>1169.29</v>
       </c>
       <c r="G10" t="n">
-        <v>5.99</v>
+        <v>6.88</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1240.2</v>
+        <v>2205</v>
       </c>
       <c r="D11" t="n">
-        <v>1239.61</v>
+        <v>2176.64</v>
       </c>
       <c r="E11" t="n">
-        <v>1197.48</v>
+        <v>2083.21</v>
       </c>
       <c r="F11" t="n">
-        <v>1169.41</v>
+        <v>2058.69</v>
       </c>
       <c r="G11" t="n">
-        <v>6.05</v>
+        <v>7.11</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>11305</v>
+        <v>488.3</v>
       </c>
       <c r="D12" t="n">
-        <v>11304.2</v>
+        <v>466.69</v>
       </c>
       <c r="E12" t="n">
-        <v>11017.1</v>
+        <v>452.69</v>
       </c>
       <c r="F12" t="n">
-        <v>10601.26</v>
+        <v>452.42</v>
       </c>
       <c r="G12" t="n">
-        <v>6.64</v>
+        <v>7.93</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>490.6</v>
+        <v>681.9</v>
       </c>
       <c r="D13" t="n">
-        <v>466.34</v>
+        <v>666.96</v>
       </c>
       <c r="E13" t="n">
-        <v>451.98</v>
+        <v>659.52</v>
       </c>
       <c r="F13" t="n">
-        <v>453.04</v>
+        <v>625.34</v>
       </c>
       <c r="G13" t="n">
-        <v>8.289999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PRESTIGE</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1632.5</v>
+        <v>1836</v>
       </c>
       <c r="D14" t="n">
-        <v>1609.34</v>
+        <v>1725.57</v>
       </c>
       <c r="E14" t="n">
-        <v>1628.47</v>
+        <v>1670.94</v>
       </c>
       <c r="F14" t="n">
-        <v>1498.01</v>
+        <v>1652.26</v>
       </c>
       <c r="G14" t="n">
-        <v>8.98</v>
+        <v>11.12</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>686.55</v>
+        <v>187.22</v>
       </c>
       <c r="D15" t="n">
-        <v>665.63</v>
+        <v>182</v>
       </c>
       <c r="E15" t="n">
-        <v>658.25</v>
+        <v>176.2</v>
       </c>
       <c r="F15" t="n">
-        <v>625.62</v>
+        <v>168.42</v>
       </c>
       <c r="G15" t="n">
-        <v>9.74</v>
+        <v>11.16</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1847.4</v>
+        <v>1875.6</v>
       </c>
       <c r="D16" t="n">
-        <v>1714.85</v>
+        <v>1847.41</v>
       </c>
       <c r="E16" t="n">
-        <v>1666.07</v>
+        <v>1855.69</v>
       </c>
       <c r="F16" t="n">
-        <v>1651.96</v>
+        <v>1669.11</v>
       </c>
       <c r="G16" t="n">
-        <v>11.83</v>
+        <v>12.37</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>188.36</v>
+        <v>1319.8</v>
       </c>
       <c r="D17" t="n">
-        <v>181.43</v>
+        <v>1307.84</v>
       </c>
       <c r="E17" t="n">
-        <v>175.84</v>
+        <v>1236.81</v>
       </c>
       <c r="F17" t="n">
-        <v>168.23</v>
+        <v>1147.93</v>
       </c>
       <c r="G17" t="n">
-        <v>11.97</v>
+        <v>14.97</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2180.1</v>
+        <v>2250</v>
       </c>
       <c r="D18" t="n">
-        <v>2044.86</v>
+        <v>2058.41</v>
       </c>
       <c r="E18" t="n">
-        <v>1949.06</v>
+        <v>1957.78</v>
       </c>
       <c r="F18" t="n">
-        <v>1943.88</v>
+        <v>1946.42</v>
       </c>
       <c r="G18" t="n">
-        <v>12.15</v>
+        <v>15.6</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1920.6</v>
+        <v>322.75</v>
       </c>
       <c r="D19" t="n">
-        <v>1846.21</v>
+        <v>318.49</v>
       </c>
       <c r="E19" t="n">
-        <v>1853.49</v>
+        <v>304.51</v>
       </c>
       <c r="F19" t="n">
-        <v>1668.35</v>
+        <v>273.62</v>
       </c>
       <c r="G19" t="n">
-        <v>15.12</v>
+        <v>17.95</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1137,23 +1137,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1333</v>
+        <v>196.8</v>
       </c>
       <c r="D20" t="n">
-        <v>1308.28</v>
+        <v>178.6</v>
       </c>
       <c r="E20" t="n">
-        <v>1237.08</v>
+        <v>173.59</v>
       </c>
       <c r="F20" t="n">
-        <v>1148</v>
+        <v>164.65</v>
       </c>
       <c r="G20" t="n">
-        <v>16.12</v>
+        <v>19.52</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1174,23 +1174,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>324.2</v>
+        <v>1815.6</v>
       </c>
       <c r="D21" t="n">
-        <v>318.53</v>
+        <v>1753.03</v>
       </c>
       <c r="E21" t="n">
-        <v>304.54</v>
+        <v>1804.96</v>
       </c>
       <c r="F21" t="n">
-        <v>273.63</v>
+        <v>1496.32</v>
       </c>
       <c r="G21" t="n">
-        <v>18.48</v>
+        <v>21.34</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1211,23 +1211,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>197.7</v>
+        <v>1037</v>
       </c>
       <c r="D22" t="n">
-        <v>178.63</v>
+        <v>937.92</v>
       </c>
       <c r="E22" t="n">
-        <v>173.61</v>
+        <v>943.71</v>
       </c>
       <c r="F22" t="n">
-        <v>164.66</v>
+        <v>847.8200000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>20.07</v>
+        <v>22.31</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1248,23 +1248,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1024.3</v>
+        <v>3275.4</v>
       </c>
       <c r="D23" t="n">
-        <v>932.8</v>
+        <v>2976.14</v>
       </c>
       <c r="E23" t="n">
-        <v>942.12</v>
+        <v>2905.94</v>
       </c>
       <c r="F23" t="n">
-        <v>847.49</v>
+        <v>2638.2</v>
       </c>
       <c r="G23" t="n">
-        <v>20.86</v>
+        <v>24.15</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1285,23 +1285,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1834.7</v>
+        <v>431.1</v>
       </c>
       <c r="D24" t="n">
-        <v>1753.67</v>
+        <v>417.83</v>
       </c>
       <c r="E24" t="n">
-        <v>1805.34</v>
+        <v>412.51</v>
       </c>
       <c r="F24" t="n">
-        <v>1496.42</v>
+        <v>334.41</v>
       </c>
       <c r="G24" t="n">
-        <v>22.61</v>
+        <v>28.91</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1309,80 +1309,6 @@
         </is>
       </c>
       <c r="I24" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>3238.1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>2974.9</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2905.19</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2638.01</v>
-      </c>
-      <c r="G25" t="n">
-        <v>22.75</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>433.65</v>
-      </c>
-      <c r="D26" t="n">
-        <v>417.92</v>
-      </c>
-      <c r="E26" t="n">
-        <v>412.56</v>
-      </c>
-      <c r="F26" t="n">
-        <v>334.42</v>
-      </c>
-      <c r="G26" t="n">
-        <v>29.67</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,25 +651,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>601</v>
+        <v>1394.6</v>
       </c>
       <c r="D7" t="n">
-        <v>578.37</v>
+        <v>1360.07</v>
       </c>
       <c r="E7" t="n">
-        <v>559.02</v>
+        <v>1359.25</v>
       </c>
       <c r="F7" t="n">
-        <v>574.58</v>
+        <v>1333.22</v>
       </c>
       <c r="G7" t="n">
         <v>4.6</v>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1394.6</v>
+        <v>1249.7</v>
       </c>
       <c r="D8" t="n">
-        <v>1360.07</v>
+        <v>1244.66</v>
       </c>
       <c r="E8" t="n">
-        <v>1359.25</v>
+        <v>1200.32</v>
       </c>
       <c r="F8" t="n">
-        <v>1333.22</v>
+        <v>1169.29</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>6.88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>424.5</v>
+        <v>2205</v>
       </c>
       <c r="D9" t="n">
-        <v>401.08</v>
+        <v>2176.64</v>
       </c>
       <c r="E9" t="n">
-        <v>394.43</v>
+        <v>2083.21</v>
       </c>
       <c r="F9" t="n">
-        <v>399.97</v>
+        <v>2058.69</v>
       </c>
       <c r="G9" t="n">
-        <v>6.13</v>
+        <v>7.11</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1249.7</v>
+        <v>488.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1244.66</v>
+        <v>466.69</v>
       </c>
       <c r="E10" t="n">
-        <v>1200.32</v>
+        <v>452.69</v>
       </c>
       <c r="F10" t="n">
-        <v>1169.29</v>
+        <v>452.42</v>
       </c>
       <c r="G10" t="n">
-        <v>6.88</v>
+        <v>7.93</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2205</v>
+        <v>187.22</v>
       </c>
       <c r="D11" t="n">
-        <v>2176.64</v>
+        <v>182</v>
       </c>
       <c r="E11" t="n">
-        <v>2083.21</v>
+        <v>176.2</v>
       </c>
       <c r="F11" t="n">
-        <v>2058.69</v>
+        <v>168.42</v>
       </c>
       <c r="G11" t="n">
-        <v>7.11</v>
+        <v>11.16</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>488.3</v>
+        <v>322.75</v>
       </c>
       <c r="D12" t="n">
-        <v>466.69</v>
+        <v>318.49</v>
       </c>
       <c r="E12" t="n">
-        <v>452.69</v>
+        <v>304.51</v>
       </c>
       <c r="F12" t="n">
-        <v>452.42</v>
+        <v>273.62</v>
       </c>
       <c r="G12" t="n">
-        <v>7.93</v>
+        <v>17.95</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>681.9</v>
+        <v>196.8</v>
       </c>
       <c r="D13" t="n">
-        <v>666.96</v>
+        <v>178.6</v>
       </c>
       <c r="E13" t="n">
-        <v>659.52</v>
+        <v>173.59</v>
       </c>
       <c r="F13" t="n">
-        <v>625.34</v>
+        <v>164.65</v>
       </c>
       <c r="G13" t="n">
-        <v>9.050000000000001</v>
+        <v>19.52</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1836</v>
+        <v>1815.6</v>
       </c>
       <c r="D14" t="n">
-        <v>1725.57</v>
+        <v>1753.03</v>
       </c>
       <c r="E14" t="n">
-        <v>1670.94</v>
+        <v>1804.96</v>
       </c>
       <c r="F14" t="n">
-        <v>1652.26</v>
+        <v>1496.32</v>
       </c>
       <c r="G14" t="n">
-        <v>11.12</v>
+        <v>21.34</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>187.22</v>
+        <v>1037</v>
       </c>
       <c r="D15" t="n">
-        <v>182</v>
+        <v>937.92</v>
       </c>
       <c r="E15" t="n">
-        <v>176.2</v>
+        <v>943.71</v>
       </c>
       <c r="F15" t="n">
-        <v>168.42</v>
+        <v>847.8200000000001</v>
       </c>
       <c r="G15" t="n">
-        <v>11.16</v>
+        <v>22.31</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -984,28 +984,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1875.6</v>
+        <v>3275.4</v>
       </c>
       <c r="D16" t="n">
-        <v>1847.41</v>
+        <v>2976.14</v>
       </c>
       <c r="E16" t="n">
-        <v>1855.69</v>
+        <v>2905.94</v>
       </c>
       <c r="F16" t="n">
-        <v>1669.11</v>
+        <v>2638.2</v>
       </c>
       <c r="G16" t="n">
-        <v>12.37</v>
+        <v>24.15</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1021,28 +1021,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>05-09-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1319.8</v>
+        <v>431.1</v>
       </c>
       <c r="D17" t="n">
-        <v>1307.84</v>
+        <v>417.83</v>
       </c>
       <c r="E17" t="n">
-        <v>1236.81</v>
+        <v>412.51</v>
       </c>
       <c r="F17" t="n">
-        <v>1147.93</v>
+        <v>334.41</v>
       </c>
       <c r="G17" t="n">
-        <v>14.97</v>
+        <v>28.91</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1050,265 +1050,6 @@
         </is>
       </c>
       <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>2250</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2058.41</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1957.78</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1946.42</v>
-      </c>
-      <c r="G18" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>322.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>318.49</v>
-      </c>
-      <c r="E19" t="n">
-        <v>304.51</v>
-      </c>
-      <c r="F19" t="n">
-        <v>273.62</v>
-      </c>
-      <c r="G19" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>178.6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>173.59</v>
-      </c>
-      <c r="F20" t="n">
-        <v>164.65</v>
-      </c>
-      <c r="G20" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1815.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1753.03</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1804.96</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1496.32</v>
-      </c>
-      <c r="G21" t="n">
-        <v>21.34</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1037</v>
-      </c>
-      <c r="D22" t="n">
-        <v>937.92</v>
-      </c>
-      <c r="E22" t="n">
-        <v>943.71</v>
-      </c>
-      <c r="F22" t="n">
-        <v>847.8200000000001</v>
-      </c>
-      <c r="G22" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>3275.4</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2976.14</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2905.94</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2638.2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>04-09-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>431.1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>417.83</v>
-      </c>
-      <c r="E24" t="n">
-        <v>412.51</v>
-      </c>
-      <c r="F24" t="n">
-        <v>334.41</v>
-      </c>
-      <c r="G24" t="n">
-        <v>28.91</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -656,20 +656,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1394.6</v>
+        <v>601</v>
       </c>
       <c r="D7" t="n">
-        <v>1360.07</v>
+        <v>578.37</v>
       </c>
       <c r="E7" t="n">
-        <v>1359.25</v>
+        <v>559.02</v>
       </c>
       <c r="F7" t="n">
-        <v>1333.22</v>
+        <v>574.58</v>
       </c>
       <c r="G7" t="n">
         <v>4.6</v>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1249.7</v>
+        <v>1394.6</v>
       </c>
       <c r="D8" t="n">
-        <v>1244.66</v>
+        <v>1360.07</v>
       </c>
       <c r="E8" t="n">
-        <v>1200.32</v>
+        <v>1359.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1169.29</v>
+        <v>1333.22</v>
       </c>
       <c r="G8" t="n">
-        <v>6.88</v>
+        <v>4.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2205</v>
+        <v>424.5</v>
       </c>
       <c r="D9" t="n">
-        <v>2176.64</v>
+        <v>401.08</v>
       </c>
       <c r="E9" t="n">
-        <v>2083.21</v>
+        <v>394.43</v>
       </c>
       <c r="F9" t="n">
-        <v>2058.69</v>
+        <v>399.97</v>
       </c>
       <c r="G9" t="n">
-        <v>7.11</v>
+        <v>6.13</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>488.3</v>
+        <v>1249.7</v>
       </c>
       <c r="D10" t="n">
-        <v>466.69</v>
+        <v>1244.66</v>
       </c>
       <c r="E10" t="n">
-        <v>452.69</v>
+        <v>1200.32</v>
       </c>
       <c r="F10" t="n">
-        <v>452.42</v>
+        <v>1169.29</v>
       </c>
       <c r="G10" t="n">
-        <v>7.93</v>
+        <v>6.88</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>187.22</v>
+        <v>2205</v>
       </c>
       <c r="D11" t="n">
-        <v>182</v>
+        <v>2176.64</v>
       </c>
       <c r="E11" t="n">
-        <v>176.2</v>
+        <v>2083.21</v>
       </c>
       <c r="F11" t="n">
-        <v>168.42</v>
+        <v>2058.69</v>
       </c>
       <c r="G11" t="n">
-        <v>11.16</v>
+        <v>7.11</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>322.75</v>
+        <v>488.3</v>
       </c>
       <c r="D12" t="n">
-        <v>318.49</v>
+        <v>466.69</v>
       </c>
       <c r="E12" t="n">
-        <v>304.51</v>
+        <v>452.69</v>
       </c>
       <c r="F12" t="n">
-        <v>273.62</v>
+        <v>452.42</v>
       </c>
       <c r="G12" t="n">
-        <v>17.95</v>
+        <v>7.93</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>196.8</v>
+        <v>681.9</v>
       </c>
       <c r="D13" t="n">
-        <v>178.6</v>
+        <v>666.96</v>
       </c>
       <c r="E13" t="n">
-        <v>173.59</v>
+        <v>659.52</v>
       </c>
       <c r="F13" t="n">
-        <v>164.65</v>
+        <v>625.34</v>
       </c>
       <c r="G13" t="n">
-        <v>19.52</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1815.6</v>
+        <v>1836</v>
       </c>
       <c r="D14" t="n">
-        <v>1753.03</v>
+        <v>1725.57</v>
       </c>
       <c r="E14" t="n">
-        <v>1804.96</v>
+        <v>1670.94</v>
       </c>
       <c r="F14" t="n">
-        <v>1496.32</v>
+        <v>1652.26</v>
       </c>
       <c r="G14" t="n">
-        <v>21.34</v>
+        <v>11.12</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1037</v>
+        <v>187.22</v>
       </c>
       <c r="D15" t="n">
-        <v>937.92</v>
+        <v>182</v>
       </c>
       <c r="E15" t="n">
-        <v>943.71</v>
+        <v>176.2</v>
       </c>
       <c r="F15" t="n">
-        <v>847.8200000000001</v>
+        <v>168.42</v>
       </c>
       <c r="G15" t="n">
-        <v>22.31</v>
+        <v>11.16</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3275.4</v>
+        <v>1875.6</v>
       </c>
       <c r="D16" t="n">
-        <v>2976.14</v>
+        <v>1847.41</v>
       </c>
       <c r="E16" t="n">
-        <v>2905.94</v>
+        <v>1855.69</v>
       </c>
       <c r="F16" t="n">
-        <v>2638.2</v>
+        <v>1669.11</v>
       </c>
       <c r="G16" t="n">
-        <v>24.15</v>
+        <v>12.37</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,30 +1026,289 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1319.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1307.84</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1236.81</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1147.93</v>
+      </c>
+      <c r="G17" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2250</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2058.41</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1957.78</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1946.42</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>322.75</v>
+      </c>
+      <c r="D19" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="E19" t="n">
+        <v>304.51</v>
+      </c>
+      <c r="F19" t="n">
+        <v>273.62</v>
+      </c>
+      <c r="G19" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="D20" t="n">
+        <v>178.6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>173.59</v>
+      </c>
+      <c r="F20" t="n">
+        <v>164.65</v>
+      </c>
+      <c r="G20" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1815.6</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1753.03</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1804.96</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1496.32</v>
+      </c>
+      <c r="G21" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1037</v>
+      </c>
+      <c r="D22" t="n">
+        <v>937.92</v>
+      </c>
+      <c r="E22" t="n">
+        <v>943.71</v>
+      </c>
+      <c r="F22" t="n">
+        <v>847.8200000000001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>3275.4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2976.14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>2905.94</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2638.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C24" t="n">
         <v>431.1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D24" t="n">
         <v>417.83</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E24" t="n">
         <v>412.51</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F24" t="n">
         <v>334.41</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G24" t="n">
         <v>28.91</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,7 +577,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -614,7 +614,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -651,7 +651,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -725,7 +725,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,7 +762,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -799,7 +799,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -836,7 +836,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -873,7 +873,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -910,7 +910,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -984,7 +984,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1058,7 +1058,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1095,7 +1095,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1132,7 +1132,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1206,7 +1206,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>05-09-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1165</v>
+        <v>591</v>
       </c>
       <c r="D2" t="n">
-        <v>1122.22</v>
+        <v>580.42</v>
       </c>
       <c r="E2" t="n">
-        <v>1088.93</v>
+        <v>560.33</v>
       </c>
       <c r="F2" t="n">
-        <v>1126.62</v>
+        <v>575.21</v>
       </c>
       <c r="G2" t="n">
-        <v>3.41</v>
+        <v>2.74</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>879.7</v>
+        <v>115.71</v>
       </c>
       <c r="D3" t="n">
-        <v>870.88</v>
+        <v>115.32</v>
       </c>
       <c r="E3" t="n">
-        <v>851.11</v>
+        <v>111.97</v>
       </c>
       <c r="F3" t="n">
-        <v>849.75</v>
+        <v>112.48</v>
       </c>
       <c r="G3" t="n">
-        <v>3.52</v>
+        <v>2.88</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>288.1</v>
+        <v>290.4</v>
       </c>
       <c r="D4" t="n">
-        <v>285.17</v>
+        <v>285.75</v>
       </c>
       <c r="E4" t="n">
-        <v>281.78</v>
+        <v>281.96</v>
       </c>
       <c r="F4" t="n">
-        <v>277.95</v>
+        <v>278.05</v>
       </c>
       <c r="G4" t="n">
-        <v>3.65</v>
+        <v>4.44</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117</v>
+        <v>422.45</v>
       </c>
       <c r="D5" t="n">
-        <v>115.18</v>
+        <v>402.34</v>
       </c>
       <c r="E5" t="n">
-        <v>111.8</v>
+        <v>394.98</v>
       </c>
       <c r="F5" t="n">
-        <v>112.5</v>
+        <v>399.99</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>5.62</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5643</v>
+        <v>483.6</v>
       </c>
       <c r="D6" t="n">
-        <v>5569.2</v>
+        <v>468.11</v>
       </c>
       <c r="E6" t="n">
-        <v>5291.19</v>
+        <v>454.12</v>
       </c>
       <c r="F6" t="n">
-        <v>5420.65</v>
+        <v>452.71</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>6.82</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>601</v>
+        <v>2201.9</v>
       </c>
       <c r="D7" t="n">
-        <v>578.37</v>
+        <v>2184.51</v>
       </c>
       <c r="E7" t="n">
-        <v>559.02</v>
+        <v>2089.75</v>
       </c>
       <c r="F7" t="n">
-        <v>574.58</v>
+        <v>2058.12</v>
       </c>
       <c r="G7" t="n">
-        <v>4.6</v>
+        <v>6.99</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1394.6</v>
+        <v>1431.8</v>
       </c>
       <c r="D8" t="n">
-        <v>1360.07</v>
+        <v>1363.49</v>
       </c>
       <c r="E8" t="n">
-        <v>1359.25</v>
+        <v>1362.16</v>
       </c>
       <c r="F8" t="n">
-        <v>1333.22</v>
+        <v>1332.25</v>
       </c>
       <c r="G8" t="n">
-        <v>4.6</v>
+        <v>7.47</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>424.5</v>
+        <v>675.85</v>
       </c>
       <c r="D9" t="n">
-        <v>401.08</v>
+        <v>667.79</v>
       </c>
       <c r="E9" t="n">
-        <v>394.43</v>
+        <v>660.89</v>
       </c>
       <c r="F9" t="n">
-        <v>399.97</v>
+        <v>625.0599999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>6.13</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1249.7</v>
+        <v>183.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1244.66</v>
+        <v>182.46</v>
       </c>
       <c r="E10" t="n">
-        <v>1200.32</v>
+        <v>176.48</v>
       </c>
       <c r="F10" t="n">
-        <v>1169.29</v>
+        <v>168.59</v>
       </c>
       <c r="G10" t="n">
-        <v>6.88</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2205</v>
+        <v>1809.6</v>
       </c>
       <c r="D11" t="n">
-        <v>2176.64</v>
+        <v>1734.11</v>
       </c>
       <c r="E11" t="n">
-        <v>2083.21</v>
+        <v>1674.67</v>
       </c>
       <c r="F11" t="n">
-        <v>2058.69</v>
+        <v>1652.05</v>
       </c>
       <c r="G11" t="n">
-        <v>7.11</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>488.3</v>
+        <v>2212.1</v>
       </c>
       <c r="D12" t="n">
-        <v>466.69</v>
+        <v>2070.48</v>
       </c>
       <c r="E12" t="n">
-        <v>452.69</v>
+        <v>1966.27</v>
       </c>
       <c r="F12" t="n">
-        <v>452.42</v>
+        <v>1948.87</v>
       </c>
       <c r="G12" t="n">
-        <v>7.93</v>
+        <v>13.51</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>681.9</v>
+        <v>189.22</v>
       </c>
       <c r="D13" t="n">
-        <v>666.96</v>
+        <v>179.48</v>
       </c>
       <c r="E13" t="n">
-        <v>659.52</v>
+        <v>173.87</v>
       </c>
       <c r="F13" t="n">
-        <v>625.34</v>
+        <v>164.91</v>
       </c>
       <c r="G13" t="n">
-        <v>9.050000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1836</v>
+        <v>321.75</v>
       </c>
       <c r="D14" t="n">
-        <v>1725.57</v>
+        <v>319.35</v>
       </c>
       <c r="E14" t="n">
-        <v>1670.94</v>
+        <v>305.76</v>
       </c>
       <c r="F14" t="n">
-        <v>1652.26</v>
+        <v>273.7</v>
       </c>
       <c r="G14" t="n">
-        <v>11.12</v>
+        <v>17.56</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>187.22</v>
+        <v>1817.7</v>
       </c>
       <c r="D15" t="n">
-        <v>182</v>
+        <v>1749.74</v>
       </c>
       <c r="E15" t="n">
-        <v>176.2</v>
+        <v>1805.89</v>
       </c>
       <c r="F15" t="n">
-        <v>168.42</v>
+        <v>1498.15</v>
       </c>
       <c r="G15" t="n">
-        <v>11.16</v>
+        <v>21.33</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1875.6</v>
+        <v>1054.9</v>
       </c>
       <c r="D16" t="n">
-        <v>1847.41</v>
+        <v>944.1</v>
       </c>
       <c r="E16" t="n">
-        <v>1855.69</v>
+        <v>945.85</v>
       </c>
       <c r="F16" t="n">
-        <v>1669.11</v>
+        <v>848.37</v>
       </c>
       <c r="G16" t="n">
-        <v>12.37</v>
+        <v>24.34</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1319.8</v>
+        <v>420.8</v>
       </c>
       <c r="D17" t="n">
-        <v>1307.84</v>
+        <v>417.99</v>
       </c>
       <c r="E17" t="n">
-        <v>1236.81</v>
+        <v>412.67</v>
       </c>
       <c r="F17" t="n">
-        <v>1147.93</v>
+        <v>335.09</v>
       </c>
       <c r="G17" t="n">
-        <v>14.97</v>
+        <v>25.58</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,23 +1063,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2250</v>
+        <v>3335.6</v>
       </c>
       <c r="D18" t="n">
-        <v>2058.41</v>
+        <v>2995.71</v>
       </c>
       <c r="E18" t="n">
-        <v>1957.78</v>
+        <v>2914.5</v>
       </c>
       <c r="F18" t="n">
-        <v>1946.42</v>
+        <v>2645.04</v>
       </c>
       <c r="G18" t="n">
-        <v>15.6</v>
+        <v>26.11</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1087,228 +1087,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>322.75</v>
-      </c>
-      <c r="D19" t="n">
-        <v>318.49</v>
-      </c>
-      <c r="E19" t="n">
-        <v>304.51</v>
-      </c>
-      <c r="F19" t="n">
-        <v>273.62</v>
-      </c>
-      <c r="G19" t="n">
-        <v>17.95</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>196.8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>178.6</v>
-      </c>
-      <c r="E20" t="n">
-        <v>173.59</v>
-      </c>
-      <c r="F20" t="n">
-        <v>164.65</v>
-      </c>
-      <c r="G20" t="n">
-        <v>19.52</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1815.6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1753.03</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1804.96</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1496.32</v>
-      </c>
-      <c r="G21" t="n">
-        <v>21.34</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1037</v>
-      </c>
-      <c r="D22" t="n">
-        <v>937.92</v>
-      </c>
-      <c r="E22" t="n">
-        <v>943.71</v>
-      </c>
-      <c r="F22" t="n">
-        <v>847.8200000000001</v>
-      </c>
-      <c r="G22" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>3275.4</v>
-      </c>
-      <c r="D23" t="n">
-        <v>2976.14</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2905.94</v>
-      </c>
-      <c r="F23" t="n">
-        <v>2638.2</v>
-      </c>
-      <c r="G23" t="n">
-        <v>24.15</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>431.1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>417.83</v>
-      </c>
-      <c r="E24" t="n">
-        <v>412.51</v>
-      </c>
-      <c r="F24" t="n">
-        <v>334.41</v>
-      </c>
-      <c r="G24" t="n">
-        <v>28.91</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>591</v>
+        <v>1147.9</v>
       </c>
       <c r="D2" t="n">
-        <v>580.42</v>
+        <v>1125.03</v>
       </c>
       <c r="E2" t="n">
-        <v>560.33</v>
+        <v>1090.57</v>
       </c>
       <c r="F2" t="n">
-        <v>575.21</v>
+        <v>1127.02</v>
       </c>
       <c r="G2" t="n">
-        <v>2.74</v>
+        <v>1.85</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115.71</v>
+        <v>589.15</v>
       </c>
       <c r="D3" t="n">
-        <v>115.32</v>
+        <v>580.36</v>
       </c>
       <c r="E3" t="n">
-        <v>111.97</v>
+        <v>560.29</v>
       </c>
       <c r="F3" t="n">
-        <v>112.48</v>
+        <v>575.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.88</v>
+        <v>2.42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>290.4</v>
+        <v>115.6</v>
       </c>
       <c r="D4" t="n">
-        <v>285.75</v>
+        <v>115.31</v>
       </c>
       <c r="E4" t="n">
-        <v>281.96</v>
+        <v>111.97</v>
       </c>
       <c r="F4" t="n">
-        <v>278.05</v>
+        <v>112.47</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44</v>
+        <v>2.78</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>422.45</v>
+        <v>290.95</v>
       </c>
       <c r="D5" t="n">
-        <v>402.34</v>
+        <v>285.77</v>
       </c>
       <c r="E5" t="n">
-        <v>394.98</v>
+        <v>281.97</v>
       </c>
       <c r="F5" t="n">
-        <v>399.99</v>
+        <v>278.05</v>
       </c>
       <c r="G5" t="n">
-        <v>5.62</v>
+        <v>4.64</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>483.6</v>
+        <v>422.1</v>
       </c>
       <c r="D6" t="n">
-        <v>468.11</v>
+        <v>402.33</v>
       </c>
       <c r="E6" t="n">
-        <v>454.12</v>
+        <v>394.97</v>
       </c>
       <c r="F6" t="n">
-        <v>452.71</v>
+        <v>399.99</v>
       </c>
       <c r="G6" t="n">
-        <v>6.82</v>
+        <v>5.53</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2201.9</v>
+        <v>1414.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2184.51</v>
+        <v>1362.93</v>
       </c>
       <c r="E7" t="n">
-        <v>2089.75</v>
+        <v>1361.82</v>
       </c>
       <c r="F7" t="n">
-        <v>2058.12</v>
+        <v>1332.17</v>
       </c>
       <c r="G7" t="n">
-        <v>6.99</v>
+        <v>6.21</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1431.8</v>
+        <v>2210</v>
       </c>
       <c r="D8" t="n">
-        <v>1363.49</v>
+        <v>2184.78</v>
       </c>
       <c r="E8" t="n">
-        <v>1362.16</v>
+        <v>2089.91</v>
       </c>
       <c r="F8" t="n">
-        <v>1332.25</v>
+        <v>2058.16</v>
       </c>
       <c r="G8" t="n">
-        <v>7.47</v>
+        <v>7.38</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>675.85</v>
+        <v>487</v>
       </c>
       <c r="D9" t="n">
-        <v>667.79</v>
+        <v>468.22</v>
       </c>
       <c r="E9" t="n">
-        <v>660.89</v>
+        <v>454.19</v>
       </c>
       <c r="F9" t="n">
-        <v>625.0599999999999</v>
+        <v>452.73</v>
       </c>
       <c r="G9" t="n">
-        <v>8.130000000000001</v>
+        <v>7.57</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>183.7</v>
+        <v>672.7</v>
       </c>
       <c r="D10" t="n">
-        <v>182.46</v>
+        <v>667.6900000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>176.48</v>
+        <v>660.83</v>
       </c>
       <c r="F10" t="n">
-        <v>168.59</v>
+        <v>625.04</v>
       </c>
       <c r="G10" t="n">
-        <v>8.960000000000001</v>
+        <v>7.62</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1809.6</v>
+        <v>1792</v>
       </c>
       <c r="D11" t="n">
-        <v>1734.11</v>
+        <v>1733.53</v>
       </c>
       <c r="E11" t="n">
-        <v>1674.67</v>
+        <v>1674.32</v>
       </c>
       <c r="F11" t="n">
-        <v>1652.05</v>
+        <v>1651.96</v>
       </c>
       <c r="G11" t="n">
-        <v>9.539999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2212.1</v>
+        <v>186.04</v>
       </c>
       <c r="D12" t="n">
-        <v>2070.48</v>
+        <v>182.54</v>
       </c>
       <c r="E12" t="n">
-        <v>1966.27</v>
+        <v>176.53</v>
       </c>
       <c r="F12" t="n">
-        <v>1948.87</v>
+        <v>168.61</v>
       </c>
       <c r="G12" t="n">
-        <v>13.51</v>
+        <v>10.34</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>189.22</v>
+        <v>2215</v>
       </c>
       <c r="D13" t="n">
-        <v>179.48</v>
+        <v>2070.58</v>
       </c>
       <c r="E13" t="n">
-        <v>173.87</v>
+        <v>1966.33</v>
       </c>
       <c r="F13" t="n">
-        <v>164.91</v>
+        <v>1948.89</v>
       </c>
       <c r="G13" t="n">
-        <v>14.74</v>
+        <v>13.65</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>321.75</v>
+        <v>187.9</v>
       </c>
       <c r="D14" t="n">
-        <v>319.35</v>
+        <v>179.44</v>
       </c>
       <c r="E14" t="n">
-        <v>305.76</v>
+        <v>173.84</v>
       </c>
       <c r="F14" t="n">
-        <v>273.7</v>
+        <v>164.9</v>
       </c>
       <c r="G14" t="n">
-        <v>17.56</v>
+        <v>13.95</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1817.7</v>
+        <v>320.8</v>
       </c>
       <c r="D15" t="n">
-        <v>1749.74</v>
+        <v>319.32</v>
       </c>
       <c r="E15" t="n">
-        <v>1805.89</v>
+        <v>305.74</v>
       </c>
       <c r="F15" t="n">
-        <v>1498.15</v>
+        <v>273.69</v>
       </c>
       <c r="G15" t="n">
-        <v>21.33</v>
+        <v>17.21</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1054.9</v>
+        <v>1832.4</v>
       </c>
       <c r="D16" t="n">
-        <v>944.1</v>
+        <v>1750.23</v>
       </c>
       <c r="E16" t="n">
-        <v>945.85</v>
+        <v>1806.18</v>
       </c>
       <c r="F16" t="n">
-        <v>848.37</v>
+        <v>1498.22</v>
       </c>
       <c r="G16" t="n">
-        <v>24.34</v>
+        <v>22.31</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>420.8</v>
+        <v>1055</v>
       </c>
       <c r="D17" t="n">
-        <v>417.99</v>
+        <v>944.11</v>
       </c>
       <c r="E17" t="n">
-        <v>412.67</v>
+        <v>945.86</v>
       </c>
       <c r="F17" t="n">
-        <v>335.09</v>
+        <v>848.37</v>
       </c>
       <c r="G17" t="n">
-        <v>25.58</v>
+        <v>24.36</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1063,30 +1063,67 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>421.45</v>
+      </c>
+      <c r="D18" t="n">
+        <v>418.02</v>
+      </c>
+      <c r="E18" t="n">
+        <v>412.69</v>
+      </c>
+      <c r="F18" t="n">
+        <v>335.09</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25.77</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>07-09-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>3335.6</v>
-      </c>
-      <c r="D18" t="n">
-        <v>2995.71</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2914.5</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2645.04</v>
-      </c>
-      <c r="G18" t="n">
-        <v>26.11</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="C19" t="n">
+        <v>3330.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2995.53</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2914.39</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2645.01</v>
+      </c>
+      <c r="G19" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1147.9</v>
+        <v>589.15</v>
       </c>
       <c r="D2" t="n">
-        <v>1125.03</v>
+        <v>580.36</v>
       </c>
       <c r="E2" t="n">
-        <v>1090.57</v>
+        <v>560.29</v>
       </c>
       <c r="F2" t="n">
-        <v>1127.02</v>
+        <v>575.2</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>589.15</v>
+        <v>115.6</v>
       </c>
       <c r="D3" t="n">
-        <v>580.36</v>
+        <v>115.31</v>
       </c>
       <c r="E3" t="n">
-        <v>560.29</v>
+        <v>111.97</v>
       </c>
       <c r="F3" t="n">
-        <v>575.2</v>
+        <v>112.47</v>
       </c>
       <c r="G3" t="n">
-        <v>2.42</v>
+        <v>2.78</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>115.6</v>
+        <v>422.1</v>
       </c>
       <c r="D4" t="n">
-        <v>115.31</v>
+        <v>402.33</v>
       </c>
       <c r="E4" t="n">
-        <v>111.97</v>
+        <v>394.97</v>
       </c>
       <c r="F4" t="n">
-        <v>112.47</v>
+        <v>399.99</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78</v>
+        <v>5.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>290.95</v>
+        <v>487</v>
       </c>
       <c r="D5" t="n">
-        <v>285.77</v>
+        <v>468.22</v>
       </c>
       <c r="E5" t="n">
-        <v>281.97</v>
+        <v>454.19</v>
       </c>
       <c r="F5" t="n">
-        <v>278.05</v>
+        <v>452.73</v>
       </c>
       <c r="G5" t="n">
-        <v>4.64</v>
+        <v>7.57</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>422.1</v>
+        <v>186.04</v>
       </c>
       <c r="D6" t="n">
-        <v>402.33</v>
+        <v>182.54</v>
       </c>
       <c r="E6" t="n">
-        <v>394.97</v>
+        <v>176.53</v>
       </c>
       <c r="F6" t="n">
-        <v>399.99</v>
+        <v>168.61</v>
       </c>
       <c r="G6" t="n">
-        <v>5.53</v>
+        <v>10.34</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1414.9</v>
+        <v>2206.5</v>
       </c>
       <c r="D7" t="n">
-        <v>1362.93</v>
+        <v>2062.63</v>
       </c>
       <c r="E7" t="n">
-        <v>1361.82</v>
+        <v>1958.78</v>
       </c>
       <c r="F7" t="n">
-        <v>1332.17</v>
+        <v>1941.41</v>
       </c>
       <c r="G7" t="n">
-        <v>6.21</v>
+        <v>13.65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2210</v>
+        <v>187.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2184.78</v>
+        <v>179.44</v>
       </c>
       <c r="E8" t="n">
-        <v>2089.91</v>
+        <v>173.84</v>
       </c>
       <c r="F8" t="n">
-        <v>2058.16</v>
+        <v>164.9</v>
       </c>
       <c r="G8" t="n">
-        <v>7.38</v>
+        <v>13.95</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>487</v>
+        <v>1055</v>
       </c>
       <c r="D9" t="n">
-        <v>468.22</v>
+        <v>944.11</v>
       </c>
       <c r="E9" t="n">
-        <v>454.19</v>
+        <v>945.86</v>
       </c>
       <c r="F9" t="n">
-        <v>452.73</v>
+        <v>848.37</v>
       </c>
       <c r="G9" t="n">
-        <v>7.57</v>
+        <v>24.36</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>672.7</v>
+        <v>421.45</v>
       </c>
       <c r="D10" t="n">
-        <v>667.6900000000001</v>
+        <v>418.02</v>
       </c>
       <c r="E10" t="n">
-        <v>660.83</v>
+        <v>412.69</v>
       </c>
       <c r="F10" t="n">
-        <v>625.04</v>
+        <v>335.09</v>
       </c>
       <c r="G10" t="n">
-        <v>7.62</v>
+        <v>25.77</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>08-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1792</v>
+        <v>3330.2</v>
       </c>
       <c r="D11" t="n">
-        <v>1733.53</v>
+        <v>2995.53</v>
       </c>
       <c r="E11" t="n">
-        <v>1674.32</v>
+        <v>2914.39</v>
       </c>
       <c r="F11" t="n">
-        <v>1651.96</v>
+        <v>2645.01</v>
       </c>
       <c r="G11" t="n">
-        <v>8.48</v>
+        <v>25.9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -828,302 +828,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>186.04</v>
-      </c>
-      <c r="D12" t="n">
-        <v>182.54</v>
-      </c>
-      <c r="E12" t="n">
-        <v>176.53</v>
-      </c>
-      <c r="F12" t="n">
-        <v>168.61</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2215</v>
-      </c>
-      <c r="D13" t="n">
-        <v>2070.58</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1966.33</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1948.89</v>
-      </c>
-      <c r="G13" t="n">
-        <v>13.65</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>187.9</v>
-      </c>
-      <c r="D14" t="n">
-        <v>179.44</v>
-      </c>
-      <c r="E14" t="n">
-        <v>173.84</v>
-      </c>
-      <c r="F14" t="n">
-        <v>164.9</v>
-      </c>
-      <c r="G14" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>320.8</v>
-      </c>
-      <c r="D15" t="n">
-        <v>319.32</v>
-      </c>
-      <c r="E15" t="n">
-        <v>305.74</v>
-      </c>
-      <c r="F15" t="n">
-        <v>273.69</v>
-      </c>
-      <c r="G15" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NUVAMA</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1832.4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1750.23</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1806.18</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1498.22</v>
-      </c>
-      <c r="G16" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>1055</v>
-      </c>
-      <c r="D17" t="n">
-        <v>944.11</v>
-      </c>
-      <c r="E17" t="n">
-        <v>945.86</v>
-      </c>
-      <c r="F17" t="n">
-        <v>848.37</v>
-      </c>
-      <c r="G17" t="n">
-        <v>24.36</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>421.45</v>
-      </c>
-      <c r="D18" t="n">
-        <v>418.02</v>
-      </c>
-      <c r="E18" t="n">
-        <v>412.69</v>
-      </c>
-      <c r="F18" t="n">
-        <v>335.09</v>
-      </c>
-      <c r="G18" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>3330.2</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2995.53</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2914.39</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2645.01</v>
-      </c>
-      <c r="G19" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>589.15</v>
+        <v>1146.3</v>
       </c>
       <c r="D2" t="n">
-        <v>580.36</v>
+        <v>1124.97</v>
       </c>
       <c r="E2" t="n">
-        <v>560.29</v>
+        <v>1090.53</v>
       </c>
       <c r="F2" t="n">
-        <v>575.2</v>
+        <v>1127.01</v>
       </c>
       <c r="G2" t="n">
-        <v>2.42</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>115.6</v>
+        <v>286.35</v>
       </c>
       <c r="D3" t="n">
-        <v>115.31</v>
+        <v>285.62</v>
       </c>
       <c r="E3" t="n">
-        <v>111.97</v>
+        <v>281.88</v>
       </c>
       <c r="F3" t="n">
-        <v>112.47</v>
+        <v>278.03</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>422.1</v>
+        <v>116.3</v>
       </c>
       <c r="D4" t="n">
-        <v>402.33</v>
+        <v>115.47</v>
       </c>
       <c r="E4" t="n">
-        <v>394.97</v>
+        <v>112.16</v>
       </c>
       <c r="F4" t="n">
-        <v>399.99</v>
+        <v>112.46</v>
       </c>
       <c r="G4" t="n">
-        <v>5.53</v>
+        <v>3.41</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>487</v>
+        <v>604.1</v>
       </c>
       <c r="D5" t="n">
-        <v>468.22</v>
+        <v>582.9299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>454.19</v>
+        <v>561.71</v>
       </c>
       <c r="F5" t="n">
-        <v>452.73</v>
+        <v>575.97</v>
       </c>
       <c r="G5" t="n">
-        <v>7.57</v>
+        <v>4.88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>186.04</v>
+        <v>1399.3</v>
       </c>
       <c r="D6" t="n">
-        <v>182.54</v>
+        <v>1362.41</v>
       </c>
       <c r="E6" t="n">
-        <v>176.53</v>
+        <v>1361.51</v>
       </c>
       <c r="F6" t="n">
-        <v>168.61</v>
+        <v>1332.09</v>
       </c>
       <c r="G6" t="n">
-        <v>10.34</v>
+        <v>5.05</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2206.5</v>
+        <v>423.55</v>
       </c>
       <c r="D7" t="n">
-        <v>2062.63</v>
+        <v>403.61</v>
       </c>
       <c r="E7" t="n">
-        <v>1958.78</v>
+        <v>395.61</v>
       </c>
       <c r="F7" t="n">
-        <v>1941.41</v>
+        <v>400.02</v>
       </c>
       <c r="G7" t="n">
-        <v>13.65</v>
+        <v>5.88</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>187.9</v>
+        <v>485.25</v>
       </c>
       <c r="D8" t="n">
-        <v>179.44</v>
+        <v>469.6</v>
       </c>
       <c r="E8" t="n">
-        <v>173.84</v>
+        <v>455.57</v>
       </c>
       <c r="F8" t="n">
-        <v>164.9</v>
+        <v>453.07</v>
       </c>
       <c r="G8" t="n">
-        <v>13.95</v>
+        <v>7.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1055</v>
+        <v>672.25</v>
       </c>
       <c r="D9" t="n">
-        <v>944.11</v>
+        <v>667.67</v>
       </c>
       <c r="E9" t="n">
-        <v>945.86</v>
+        <v>660.8200000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>848.37</v>
+        <v>625.04</v>
       </c>
       <c r="G9" t="n">
-        <v>24.36</v>
+        <v>7.55</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>421.45</v>
+        <v>2214.7</v>
       </c>
       <c r="D10" t="n">
-        <v>418.02</v>
+        <v>2184.94</v>
       </c>
       <c r="E10" t="n">
-        <v>412.69</v>
+        <v>2090.01</v>
       </c>
       <c r="F10" t="n">
-        <v>335.09</v>
+        <v>2058.18</v>
       </c>
       <c r="G10" t="n">
-        <v>25.77</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,30 +804,326 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>184.3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>183.07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>176.87</v>
+      </c>
+      <c r="F11" t="n">
+        <v>168.79</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>POLICYBZR</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1814.8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1734.29</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1674.77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1652.08</v>
+      </c>
+      <c r="G12" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2169.2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2073.62</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1966.53</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1943.65</v>
+      </c>
+      <c r="G13" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>189.55</v>
+      </c>
+      <c r="D14" t="n">
+        <v>180.23</v>
+      </c>
+      <c r="E14" t="n">
+        <v>174.16</v>
+      </c>
+      <c r="F14" t="n">
+        <v>165.18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>322.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>319.38</v>
+      </c>
+      <c r="E15" t="n">
+        <v>305.77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>273.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NUVAMA</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1829.5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1750.13</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1806.12</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1498.21</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22.11</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1044</v>
+      </c>
+      <c r="D17" t="n">
+        <v>950.37</v>
+      </c>
+      <c r="E17" t="n">
+        <v>947.71</v>
+      </c>
+      <c r="F17" t="n">
+        <v>848.89</v>
+      </c>
+      <c r="G17" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>MCX</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>3330.2</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2995.53</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2914.39</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2645.01</v>
-      </c>
-      <c r="G11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="C18" t="n">
+        <v>3291.3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3015.02</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2923.62</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2651.81</v>
+      </c>
+      <c r="G18" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>08-09-2026</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>424.4</v>
+      </c>
+      <c r="D19" t="n">
+        <v>418.64</v>
+      </c>
+      <c r="E19" t="n">
+        <v>412.92</v>
+      </c>
+      <c r="F19" t="n">
+        <v>335.81</v>
+      </c>
+      <c r="G19" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1146.3</v>
+        <v>285.8</v>
       </c>
       <c r="D2" t="n">
-        <v>1124.97</v>
+        <v>285.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1090.53</v>
+        <v>281.87</v>
       </c>
       <c r="F2" t="n">
-        <v>1127.01</v>
+        <v>278.03</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>286.35</v>
+        <v>116</v>
       </c>
       <c r="D3" t="n">
-        <v>285.62</v>
+        <v>115.46</v>
       </c>
       <c r="E3" t="n">
-        <v>281.88</v>
+        <v>112.16</v>
       </c>
       <c r="F3" t="n">
-        <v>278.03</v>
+        <v>112.46</v>
       </c>
       <c r="G3" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116.3</v>
+        <v>595.5</v>
       </c>
       <c r="D4" t="n">
-        <v>115.47</v>
+        <v>582.64</v>
       </c>
       <c r="E4" t="n">
-        <v>112.16</v>
+        <v>561.54</v>
       </c>
       <c r="F4" t="n">
-        <v>112.46</v>
+        <v>575.9299999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>604.1</v>
+        <v>419.25</v>
       </c>
       <c r="D5" t="n">
-        <v>582.9299999999999</v>
+        <v>403.46</v>
       </c>
       <c r="E5" t="n">
-        <v>561.71</v>
+        <v>395.53</v>
       </c>
       <c r="F5" t="n">
-        <v>575.97</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>4.88</v>
+        <v>4.81</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1399.3</v>
+        <v>1400</v>
       </c>
       <c r="D6" t="n">
-        <v>1362.41</v>
+        <v>1362.43</v>
       </c>
       <c r="E6" t="n">
-        <v>1361.51</v>
+        <v>1361.53</v>
       </c>
       <c r="F6" t="n">
         <v>1332.09</v>
       </c>
       <c r="G6" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>423.55</v>
+        <v>2220</v>
       </c>
       <c r="D7" t="n">
-        <v>403.61</v>
+        <v>2192.68</v>
       </c>
       <c r="E7" t="n">
-        <v>395.61</v>
+        <v>2096.56</v>
       </c>
       <c r="F7" t="n">
-        <v>400.02</v>
+        <v>2057.69</v>
       </c>
       <c r="G7" t="n">
-        <v>5.88</v>
+        <v>7.89</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>485.25</v>
+        <v>675.1</v>
       </c>
       <c r="D8" t="n">
-        <v>469.6</v>
+        <v>667.77</v>
       </c>
       <c r="E8" t="n">
-        <v>455.57</v>
+        <v>660.88</v>
       </c>
       <c r="F8" t="n">
-        <v>453.07</v>
+        <v>625.05</v>
       </c>
       <c r="G8" t="n">
-        <v>7.1</v>
+        <v>8.01</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>672.25</v>
+        <v>183.22</v>
       </c>
       <c r="D9" t="n">
-        <v>667.67</v>
+        <v>183.03</v>
       </c>
       <c r="E9" t="n">
-        <v>660.8200000000001</v>
+        <v>176.85</v>
       </c>
       <c r="F9" t="n">
-        <v>625.04</v>
+        <v>168.79</v>
       </c>
       <c r="G9" t="n">
-        <v>7.55</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2214.7</v>
+        <v>495.4</v>
       </c>
       <c r="D10" t="n">
-        <v>2184.94</v>
+        <v>469.94</v>
       </c>
       <c r="E10" t="n">
-        <v>2090.01</v>
+        <v>455.78</v>
       </c>
       <c r="F10" t="n">
-        <v>2058.18</v>
+        <v>453.12</v>
       </c>
       <c r="G10" t="n">
-        <v>7.6</v>
+        <v>9.33</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>184.3</v>
+        <v>1826</v>
       </c>
       <c r="D11" t="n">
-        <v>183.07</v>
+        <v>1734.66</v>
       </c>
       <c r="E11" t="n">
-        <v>176.87</v>
+        <v>1675</v>
       </c>
       <c r="F11" t="n">
-        <v>168.79</v>
+        <v>1652.13</v>
       </c>
       <c r="G11" t="n">
-        <v>9.19</v>
+        <v>10.52</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1814.8</v>
+        <v>2185</v>
       </c>
       <c r="D12" t="n">
-        <v>1734.29</v>
+        <v>2074.14</v>
       </c>
       <c r="E12" t="n">
-        <v>1674.77</v>
+        <v>1966.84</v>
       </c>
       <c r="F12" t="n">
-        <v>1652.08</v>
+        <v>1943.73</v>
       </c>
       <c r="G12" t="n">
-        <v>9.85</v>
+        <v>12.41</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2169.2</v>
+        <v>186.1</v>
       </c>
       <c r="D13" t="n">
-        <v>2073.62</v>
+        <v>180.11</v>
       </c>
       <c r="E13" t="n">
-        <v>1966.53</v>
+        <v>174.09</v>
       </c>
       <c r="F13" t="n">
-        <v>1943.65</v>
+        <v>165.16</v>
       </c>
       <c r="G13" t="n">
-        <v>11.6</v>
+        <v>12.68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>189.55</v>
+        <v>321.6</v>
       </c>
       <c r="D14" t="n">
-        <v>180.23</v>
+        <v>319.34</v>
       </c>
       <c r="E14" t="n">
-        <v>174.16</v>
+        <v>305.75</v>
       </c>
       <c r="F14" t="n">
-        <v>165.18</v>
+        <v>273.7</v>
       </c>
       <c r="G14" t="n">
-        <v>14.75</v>
+        <v>17.5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -952,23 +952,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>NUVAMA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>322.6</v>
+        <v>1836.4</v>
       </c>
       <c r="D15" t="n">
-        <v>319.38</v>
+        <v>1750.36</v>
       </c>
       <c r="E15" t="n">
-        <v>305.77</v>
+        <v>1806.26</v>
       </c>
       <c r="F15" t="n">
-        <v>273.7</v>
+        <v>1498.24</v>
       </c>
       <c r="G15" t="n">
-        <v>17.87</v>
+        <v>22.57</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -989,23 +989,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1829.5</v>
+        <v>1051.5</v>
       </c>
       <c r="D16" t="n">
-        <v>1750.13</v>
+        <v>950.62</v>
       </c>
       <c r="E16" t="n">
-        <v>1806.12</v>
+        <v>947.86</v>
       </c>
       <c r="F16" t="n">
-        <v>1498.21</v>
+        <v>848.92</v>
       </c>
       <c r="G16" t="n">
-        <v>22.11</v>
+        <v>23.86</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1026,23 +1026,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1044</v>
+        <v>422.15</v>
       </c>
       <c r="D17" t="n">
-        <v>950.37</v>
+        <v>418.56</v>
       </c>
       <c r="E17" t="n">
-        <v>947.71</v>
+        <v>412.88</v>
       </c>
       <c r="F17" t="n">
-        <v>848.89</v>
+        <v>335.8</v>
       </c>
       <c r="G17" t="n">
-        <v>22.98</v>
+        <v>25.72</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1067,19 +1067,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3291.3</v>
+        <v>3342</v>
       </c>
       <c r="D18" t="n">
-        <v>3015.02</v>
+        <v>3016.71</v>
       </c>
       <c r="E18" t="n">
-        <v>2923.62</v>
+        <v>2924.63</v>
       </c>
       <c r="F18" t="n">
-        <v>2651.81</v>
+        <v>2652.06</v>
       </c>
       <c r="G18" t="n">
-        <v>24.12</v>
+        <v>26.02</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1087,43 +1087,6 @@
         </is>
       </c>
       <c r="I18" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>424.4</v>
-      </c>
-      <c r="D19" t="n">
-        <v>418.64</v>
-      </c>
-      <c r="E19" t="n">
-        <v>412.92</v>
-      </c>
-      <c r="F19" t="n">
-        <v>335.81</v>
-      </c>
-      <c r="G19" t="n">
-        <v>26.38</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -540,7 +540,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>419.25</v>
+        <v>1400</v>
       </c>
       <c r="D5" t="n">
-        <v>403.46</v>
+        <v>1362.43</v>
       </c>
       <c r="E5" t="n">
-        <v>395.53</v>
+        <v>1361.53</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>1332.09</v>
       </c>
       <c r="G5" t="n">
-        <v>4.81</v>
+        <v>5.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1400</v>
+        <v>2220</v>
       </c>
       <c r="D6" t="n">
-        <v>1362.43</v>
+        <v>2192.68</v>
       </c>
       <c r="E6" t="n">
-        <v>1361.53</v>
+        <v>2096.56</v>
       </c>
       <c r="F6" t="n">
-        <v>1332.09</v>
+        <v>2057.69</v>
       </c>
       <c r="G6" t="n">
-        <v>5.1</v>
+        <v>7.89</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>DLF</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2220</v>
+        <v>675.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2192.68</v>
+        <v>667.77</v>
       </c>
       <c r="E7" t="n">
-        <v>2096.56</v>
+        <v>660.88</v>
       </c>
       <c r="F7" t="n">
-        <v>2057.69</v>
+        <v>625.05</v>
       </c>
       <c r="G7" t="n">
-        <v>7.89</v>
+        <v>8.01</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>675.1</v>
+        <v>183.22</v>
       </c>
       <c r="D8" t="n">
-        <v>667.77</v>
+        <v>183.03</v>
       </c>
       <c r="E8" t="n">
-        <v>660.88</v>
+        <v>176.85</v>
       </c>
       <c r="F8" t="n">
-        <v>625.05</v>
+        <v>168.79</v>
       </c>
       <c r="G8" t="n">
-        <v>8.01</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>183.22</v>
+        <v>495.4</v>
       </c>
       <c r="D9" t="n">
-        <v>183.03</v>
+        <v>469.94</v>
       </c>
       <c r="E9" t="n">
-        <v>176.85</v>
+        <v>455.78</v>
       </c>
       <c r="F9" t="n">
-        <v>168.79</v>
+        <v>453.12</v>
       </c>
       <c r="G9" t="n">
-        <v>8.550000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>495.4</v>
+        <v>1826</v>
       </c>
       <c r="D10" t="n">
-        <v>469.94</v>
+        <v>1734.66</v>
       </c>
       <c r="E10" t="n">
-        <v>455.78</v>
+        <v>1675</v>
       </c>
       <c r="F10" t="n">
-        <v>453.12</v>
+        <v>1652.13</v>
       </c>
       <c r="G10" t="n">
-        <v>9.33</v>
+        <v>10.52</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1826</v>
+        <v>186.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1734.66</v>
+        <v>180.11</v>
       </c>
       <c r="E11" t="n">
-        <v>1675</v>
+        <v>174.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1652.13</v>
+        <v>165.16</v>
       </c>
       <c r="G11" t="n">
-        <v>10.52</v>
+        <v>12.68</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -836,28 +836,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2185</v>
+        <v>321.6</v>
       </c>
       <c r="D12" t="n">
-        <v>2074.14</v>
+        <v>319.34</v>
       </c>
       <c r="E12" t="n">
-        <v>1966.84</v>
+        <v>305.75</v>
       </c>
       <c r="F12" t="n">
-        <v>1943.73</v>
+        <v>273.7</v>
       </c>
       <c r="G12" t="n">
-        <v>12.41</v>
+        <v>17.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -873,28 +873,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>186.1</v>
+        <v>1051.5</v>
       </c>
       <c r="D13" t="n">
-        <v>180.11</v>
+        <v>950.62</v>
       </c>
       <c r="E13" t="n">
-        <v>174.09</v>
+        <v>947.86</v>
       </c>
       <c r="F13" t="n">
-        <v>165.16</v>
+        <v>848.92</v>
       </c>
       <c r="G13" t="n">
-        <v>12.68</v>
+        <v>23.86</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -910,28 +910,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>321.6</v>
+        <v>422.15</v>
       </c>
       <c r="D14" t="n">
-        <v>319.34</v>
+        <v>418.56</v>
       </c>
       <c r="E14" t="n">
-        <v>305.75</v>
+        <v>412.88</v>
       </c>
       <c r="F14" t="n">
-        <v>273.7</v>
+        <v>335.8</v>
       </c>
       <c r="G14" t="n">
-        <v>17.5</v>
+        <v>25.72</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -947,28 +947,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08-09-2026</t>
+          <t>09-09-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NUVAMA</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1836.4</v>
+        <v>3342</v>
       </c>
       <c r="D15" t="n">
-        <v>1750.36</v>
+        <v>3016.71</v>
       </c>
       <c r="E15" t="n">
-        <v>1806.26</v>
+        <v>2924.63</v>
       </c>
       <c r="F15" t="n">
-        <v>1498.24</v>
+        <v>2652.06</v>
       </c>
       <c r="G15" t="n">
-        <v>22.57</v>
+        <v>26.02</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -976,117 +976,6 @@
         </is>
       </c>
       <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1051.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>950.62</v>
-      </c>
-      <c r="E16" t="n">
-        <v>947.86</v>
-      </c>
-      <c r="F16" t="n">
-        <v>848.92</v>
-      </c>
-      <c r="G16" t="n">
-        <v>23.86</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>422.15</v>
-      </c>
-      <c r="D17" t="n">
-        <v>418.56</v>
-      </c>
-      <c r="E17" t="n">
-        <v>412.88</v>
-      </c>
-      <c r="F17" t="n">
-        <v>335.8</v>
-      </c>
-      <c r="G17" t="n">
-        <v>25.72</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>3342</v>
-      </c>
-      <c r="D18" t="n">
-        <v>3016.71</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2924.63</v>
-      </c>
-      <c r="F18" t="n">
-        <v>2652.06</v>
-      </c>
-      <c r="G18" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>285.8</v>
+        <v>1370.8</v>
       </c>
       <c r="D2" t="n">
-        <v>285.6</v>
+        <v>1363.29</v>
       </c>
       <c r="E2" t="n">
-        <v>281.87</v>
+        <v>1363.07</v>
       </c>
       <c r="F2" t="n">
-        <v>278.03</v>
+        <v>1330.97</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>2.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>116</v>
+        <v>287.3</v>
       </c>
       <c r="D3" t="n">
-        <v>115.46</v>
+        <v>285.92</v>
       </c>
       <c r="E3" t="n">
-        <v>112.16</v>
+        <v>282</v>
       </c>
       <c r="F3" t="n">
-        <v>112.46</v>
+        <v>278.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.15</v>
+        <v>3.31</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>595.5</v>
+        <v>414.2</v>
       </c>
       <c r="D4" t="n">
-        <v>582.64</v>
+        <v>403.3</v>
       </c>
       <c r="E4" t="n">
-        <v>561.54</v>
+        <v>395.43</v>
       </c>
       <c r="F4" t="n">
-        <v>575.9299999999999</v>
+        <v>399.97</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1400</v>
+        <v>116.6</v>
       </c>
       <c r="D5" t="n">
-        <v>1362.43</v>
+        <v>115.64</v>
       </c>
       <c r="E5" t="n">
-        <v>1361.53</v>
+        <v>112.34</v>
       </c>
       <c r="F5" t="n">
-        <v>1332.09</v>
+        <v>112.45</v>
       </c>
       <c r="G5" t="n">
-        <v>5.1</v>
+        <v>3.69</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2220</v>
+        <v>603.4</v>
       </c>
       <c r="D6" t="n">
-        <v>2192.68</v>
+        <v>584.87</v>
       </c>
       <c r="E6" t="n">
-        <v>2096.56</v>
+        <v>563.12</v>
       </c>
       <c r="F6" t="n">
-        <v>2057.69</v>
+        <v>576.72</v>
       </c>
       <c r="G6" t="n">
-        <v>7.89</v>
+        <v>4.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>675.1</v>
+        <v>670.1</v>
       </c>
       <c r="D7" t="n">
-        <v>667.77</v>
+        <v>668</v>
       </c>
       <c r="E7" t="n">
-        <v>660.88</v>
+        <v>662.03</v>
       </c>
       <c r="F7" t="n">
-        <v>625.05</v>
+        <v>624.8200000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>8.01</v>
+        <v>7.25</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>183.22</v>
+        <v>1805.2</v>
       </c>
       <c r="D8" t="n">
-        <v>183.03</v>
+        <v>1742.06</v>
       </c>
       <c r="E8" t="n">
-        <v>176.85</v>
+        <v>1678.53</v>
       </c>
       <c r="F8" t="n">
-        <v>168.79</v>
+        <v>1651.94</v>
       </c>
       <c r="G8" t="n">
-        <v>8.550000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>495.4</v>
+        <v>500.3</v>
       </c>
       <c r="D9" t="n">
-        <v>469.94</v>
+        <v>471.72</v>
       </c>
       <c r="E9" t="n">
-        <v>455.78</v>
+        <v>457.4</v>
       </c>
       <c r="F9" t="n">
-        <v>453.12</v>
+        <v>453.55</v>
       </c>
       <c r="G9" t="n">
-        <v>9.33</v>
+        <v>10.31</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1826</v>
+        <v>2183.2</v>
       </c>
       <c r="D10" t="n">
-        <v>1734.66</v>
+        <v>2074.08</v>
       </c>
       <c r="E10" t="n">
-        <v>1675</v>
+        <v>1966.81</v>
       </c>
       <c r="F10" t="n">
-        <v>1652.13</v>
+        <v>1943.72</v>
       </c>
       <c r="G10" t="n">
-        <v>10.52</v>
+        <v>12.32</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>186.1</v>
+        <v>187.84</v>
       </c>
       <c r="D11" t="n">
-        <v>180.11</v>
+        <v>180.68</v>
       </c>
       <c r="E11" t="n">
-        <v>174.09</v>
+        <v>174.49</v>
       </c>
       <c r="F11" t="n">
-        <v>165.16</v>
+        <v>165.44</v>
       </c>
       <c r="G11" t="n">
-        <v>12.68</v>
+        <v>13.54</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>321.6</v>
+        <v>1033.2</v>
       </c>
       <c r="D12" t="n">
-        <v>319.34</v>
+        <v>956.55</v>
       </c>
       <c r="E12" t="n">
-        <v>305.75</v>
+        <v>949.4</v>
       </c>
       <c r="F12" t="n">
-        <v>273.7</v>
+        <v>849.4</v>
       </c>
       <c r="G12" t="n">
-        <v>17.5</v>
+        <v>21.64</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1051.5</v>
+        <v>3366.7</v>
       </c>
       <c r="D13" t="n">
-        <v>950.62</v>
+        <v>3038.57</v>
       </c>
       <c r="E13" t="n">
-        <v>947.86</v>
+        <v>2932.87</v>
       </c>
       <c r="F13" t="n">
-        <v>848.92</v>
+        <v>2659.06</v>
       </c>
       <c r="G13" t="n">
-        <v>23.86</v>
+        <v>26.61</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -919,19 +919,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>422.15</v>
+        <v>427.15</v>
       </c>
       <c r="D14" t="n">
-        <v>418.56</v>
+        <v>419.3</v>
       </c>
       <c r="E14" t="n">
-        <v>412.88</v>
+        <v>413.17</v>
       </c>
       <c r="F14" t="n">
-        <v>335.8</v>
+        <v>336.55</v>
       </c>
       <c r="G14" t="n">
-        <v>25.72</v>
+        <v>26.92</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -939,43 +939,6 @@
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3342</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3016.71</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2924.63</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2652.06</v>
-      </c>
-      <c r="G15" t="n">
-        <v>26.02</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1370.8</v>
+        <v>115.61</v>
       </c>
       <c r="D2" t="n">
-        <v>1363.29</v>
+        <v>115.61</v>
       </c>
       <c r="E2" t="n">
-        <v>1363.07</v>
+        <v>112.32</v>
       </c>
       <c r="F2" t="n">
-        <v>1330.97</v>
+        <v>112.45</v>
       </c>
       <c r="G2" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>287.3</v>
+        <v>285.9</v>
       </c>
       <c r="D3" t="n">
-        <v>285.92</v>
+        <v>285.87</v>
       </c>
       <c r="E3" t="n">
-        <v>282</v>
+        <v>281.97</v>
       </c>
       <c r="F3" t="n">
         <v>278.1</v>
       </c>
       <c r="G3" t="n">
-        <v>3.31</v>
+        <v>2.81</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>414.2</v>
+        <v>1368.6</v>
       </c>
       <c r="D4" t="n">
-        <v>403.3</v>
+        <v>1363.22</v>
       </c>
       <c r="E4" t="n">
-        <v>395.43</v>
+        <v>1363.02</v>
       </c>
       <c r="F4" t="n">
-        <v>399.97</v>
+        <v>1330.96</v>
       </c>
       <c r="G4" t="n">
-        <v>3.56</v>
+        <v>2.83</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116.6</v>
+        <v>414</v>
       </c>
       <c r="D5" t="n">
-        <v>115.64</v>
+        <v>404.26</v>
       </c>
       <c r="E5" t="n">
-        <v>112.34</v>
+        <v>395.81</v>
       </c>
       <c r="F5" t="n">
-        <v>112.45</v>
+        <v>399.98</v>
       </c>
       <c r="G5" t="n">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>603.4</v>
+        <v>605.4</v>
       </c>
       <c r="D6" t="n">
-        <v>584.87</v>
+        <v>584.9299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>563.12</v>
+        <v>563.16</v>
       </c>
       <c r="F6" t="n">
-        <v>576.72</v>
+        <v>576.73</v>
       </c>
       <c r="G6" t="n">
-        <v>4.63</v>
+        <v>4.97</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DLF</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>670.1</v>
+        <v>555</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>515.03</v>
       </c>
       <c r="E7" t="n">
-        <v>662.03</v>
+        <v>523.33</v>
       </c>
       <c r="F7" t="n">
-        <v>624.8200000000001</v>
+        <v>523.27</v>
       </c>
       <c r="G7" t="n">
-        <v>7.25</v>
+        <v>6.06</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1805.2</v>
+        <v>183.89</v>
       </c>
       <c r="D8" t="n">
-        <v>1742.06</v>
+        <v>183.46</v>
       </c>
       <c r="E8" t="n">
-        <v>1678.53</v>
+        <v>177.13</v>
       </c>
       <c r="F8" t="n">
-        <v>1651.94</v>
+        <v>168.97</v>
       </c>
       <c r="G8" t="n">
-        <v>9.279999999999999</v>
+        <v>8.83</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>500.3</v>
+        <v>1800</v>
       </c>
       <c r="D9" t="n">
-        <v>471.72</v>
+        <v>1741.88</v>
       </c>
       <c r="E9" t="n">
-        <v>457.4</v>
+        <v>1678.42</v>
       </c>
       <c r="F9" t="n">
-        <v>453.55</v>
+        <v>1651.91</v>
       </c>
       <c r="G9" t="n">
-        <v>10.31</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2183.2</v>
+        <v>498.95</v>
       </c>
       <c r="D10" t="n">
-        <v>2074.08</v>
+        <v>471.67</v>
       </c>
       <c r="E10" t="n">
-        <v>1966.81</v>
+        <v>457.38</v>
       </c>
       <c r="F10" t="n">
-        <v>1943.72</v>
+        <v>453.55</v>
       </c>
       <c r="G10" t="n">
-        <v>12.32</v>
+        <v>10.01</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>187.84</v>
+        <v>2168</v>
       </c>
       <c r="D11" t="n">
-        <v>180.68</v>
+        <v>2084.32</v>
       </c>
       <c r="E11" t="n">
-        <v>174.49</v>
+        <v>1974.64</v>
       </c>
       <c r="F11" t="n">
-        <v>165.44</v>
+        <v>1946.02</v>
       </c>
       <c r="G11" t="n">
-        <v>13.54</v>
+        <v>11.41</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1033.2</v>
+        <v>186.4</v>
       </c>
       <c r="D12" t="n">
-        <v>956.55</v>
+        <v>180.63</v>
       </c>
       <c r="E12" t="n">
-        <v>949.4</v>
+        <v>174.46</v>
       </c>
       <c r="F12" t="n">
-        <v>849.4</v>
+        <v>165.43</v>
       </c>
       <c r="G12" t="n">
-        <v>21.64</v>
+        <v>12.67</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3366.7</v>
+        <v>320.6</v>
       </c>
       <c r="D13" t="n">
-        <v>3038.57</v>
+        <v>319.75</v>
       </c>
       <c r="E13" t="n">
-        <v>2932.87</v>
+        <v>306.87</v>
       </c>
       <c r="F13" t="n">
-        <v>2659.06</v>
+        <v>273.79</v>
       </c>
       <c r="G13" t="n">
-        <v>26.61</v>
+        <v>17.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,30 +915,104 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D14" t="n">
+        <v>956.28</v>
+      </c>
+      <c r="E14" t="n">
+        <v>949.24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>849.35</v>
+      </c>
+      <c r="G14" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>09-09-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3350</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3038.01</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2932.53</v>
+      </c>
+      <c r="F15" t="n">
+        <v>2658.97</v>
+      </c>
+      <c r="G15" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>09-09-2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>427.15</v>
-      </c>
-      <c r="D14" t="n">
-        <v>419.3</v>
-      </c>
-      <c r="E14" t="n">
-        <v>413.17</v>
-      </c>
-      <c r="F14" t="n">
-        <v>336.55</v>
-      </c>
-      <c r="G14" t="n">
-        <v>26.92</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="C16" t="n">
+        <v>433.7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>419.51</v>
+      </c>
+      <c r="E16" t="n">
+        <v>413.3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>336.58</v>
+      </c>
+      <c r="G16" t="n">
+        <v>28.86</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>285.9</v>
+        <v>1368.6</v>
       </c>
       <c r="D3" t="n">
-        <v>285.87</v>
+        <v>1363.22</v>
       </c>
       <c r="E3" t="n">
-        <v>281.97</v>
+        <v>1363.02</v>
       </c>
       <c r="F3" t="n">
-        <v>278.1</v>
+        <v>1330.96</v>
       </c>
       <c r="G3" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1368.6</v>
+        <v>605.4</v>
       </c>
       <c r="D4" t="n">
-        <v>1363.22</v>
+        <v>584.9299999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>1363.02</v>
+        <v>563.16</v>
       </c>
       <c r="F4" t="n">
-        <v>1330.96</v>
+        <v>576.73</v>
       </c>
       <c r="G4" t="n">
-        <v>2.83</v>
+        <v>4.97</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>414</v>
+        <v>555</v>
       </c>
       <c r="D5" t="n">
-        <v>404.26</v>
+        <v>515.03</v>
       </c>
       <c r="E5" t="n">
-        <v>395.81</v>
+        <v>523.33</v>
       </c>
       <c r="F5" t="n">
-        <v>399.98</v>
+        <v>523.27</v>
       </c>
       <c r="G5" t="n">
-        <v>3.5</v>
+        <v>6.06</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>605.4</v>
+        <v>498.95</v>
       </c>
       <c r="D6" t="n">
-        <v>584.9299999999999</v>
+        <v>471.67</v>
       </c>
       <c r="E6" t="n">
-        <v>563.16</v>
+        <v>457.38</v>
       </c>
       <c r="F6" t="n">
-        <v>576.73</v>
+        <v>453.55</v>
       </c>
       <c r="G6" t="n">
-        <v>4.97</v>
+        <v>10.01</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>555</v>
+        <v>186.4</v>
       </c>
       <c r="D7" t="n">
-        <v>515.03</v>
+        <v>180.63</v>
       </c>
       <c r="E7" t="n">
-        <v>523.33</v>
+        <v>174.46</v>
       </c>
       <c r="F7" t="n">
-        <v>523.27</v>
+        <v>165.43</v>
       </c>
       <c r="G7" t="n">
-        <v>6.06</v>
+        <v>12.67</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>183.89</v>
+        <v>320.6</v>
       </c>
       <c r="D8" t="n">
-        <v>183.46</v>
+        <v>319.75</v>
       </c>
       <c r="E8" t="n">
-        <v>177.13</v>
+        <v>306.87</v>
       </c>
       <c r="F8" t="n">
-        <v>168.97</v>
+        <v>273.79</v>
       </c>
       <c r="G8" t="n">
-        <v>8.83</v>
+        <v>17.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1800</v>
+        <v>1025</v>
       </c>
       <c r="D9" t="n">
-        <v>1741.88</v>
+        <v>956.28</v>
       </c>
       <c r="E9" t="n">
-        <v>1678.42</v>
+        <v>949.24</v>
       </c>
       <c r="F9" t="n">
-        <v>1651.91</v>
+        <v>849.35</v>
       </c>
       <c r="G9" t="n">
-        <v>8.960000000000001</v>
+        <v>20.68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>498.95</v>
+        <v>3350</v>
       </c>
       <c r="D10" t="n">
-        <v>471.67</v>
+        <v>3038.01</v>
       </c>
       <c r="E10" t="n">
-        <v>457.38</v>
+        <v>2932.53</v>
       </c>
       <c r="F10" t="n">
-        <v>453.55</v>
+        <v>2658.97</v>
       </c>
       <c r="G10" t="n">
-        <v>10.01</v>
+        <v>25.99</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>09-09-2026</t>
+          <t>10-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2168</v>
+        <v>433.7</v>
       </c>
       <c r="D11" t="n">
-        <v>2084.32</v>
+        <v>419.51</v>
       </c>
       <c r="E11" t="n">
-        <v>1974.64</v>
+        <v>413.3</v>
       </c>
       <c r="F11" t="n">
-        <v>1946.02</v>
+        <v>336.58</v>
       </c>
       <c r="G11" t="n">
-        <v>11.41</v>
+        <v>28.86</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -828,191 +828,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="D12" t="n">
-        <v>180.63</v>
-      </c>
-      <c r="E12" t="n">
-        <v>174.46</v>
-      </c>
-      <c r="F12" t="n">
-        <v>165.43</v>
-      </c>
-      <c r="G12" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>320.6</v>
-      </c>
-      <c r="D13" t="n">
-        <v>319.75</v>
-      </c>
-      <c r="E13" t="n">
-        <v>306.87</v>
-      </c>
-      <c r="F13" t="n">
-        <v>273.79</v>
-      </c>
-      <c r="G13" t="n">
-        <v>17.1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1025</v>
-      </c>
-      <c r="D14" t="n">
-        <v>956.28</v>
-      </c>
-      <c r="E14" t="n">
-        <v>949.24</v>
-      </c>
-      <c r="F14" t="n">
-        <v>849.35</v>
-      </c>
-      <c r="G14" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>3350</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3038.01</v>
-      </c>
-      <c r="E15" t="n">
-        <v>2932.53</v>
-      </c>
-      <c r="F15" t="n">
-        <v>2658.97</v>
-      </c>
-      <c r="G15" t="n">
-        <v>25.99</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>09-09-2026</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>433.7</v>
-      </c>
-      <c r="D16" t="n">
-        <v>419.51</v>
-      </c>
-      <c r="E16" t="n">
-        <v>413.3</v>
-      </c>
-      <c r="F16" t="n">
-        <v>336.58</v>
-      </c>
-      <c r="G16" t="n">
-        <v>28.86</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>115.61</v>
+        <v>414.3</v>
       </c>
       <c r="D2" t="n">
-        <v>115.61</v>
+        <v>404.27</v>
       </c>
       <c r="E2" t="n">
-        <v>112.32</v>
+        <v>395.82</v>
       </c>
       <c r="F2" t="n">
-        <v>112.45</v>
+        <v>399.99</v>
       </c>
       <c r="G2" t="n">
-        <v>2.81</v>
+        <v>3.58</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1368.6</v>
+        <v>290.05</v>
       </c>
       <c r="D3" t="n">
-        <v>1363.22</v>
+        <v>286.01</v>
       </c>
       <c r="E3" t="n">
-        <v>1363.02</v>
+        <v>282.05</v>
       </c>
       <c r="F3" t="n">
-        <v>1330.96</v>
+        <v>278.12</v>
       </c>
       <c r="G3" t="n">
-        <v>2.83</v>
+        <v>4.29</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -549,19 +549,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>605.4</v>
+        <v>604.2</v>
       </c>
       <c r="D4" t="n">
-        <v>584.9299999999999</v>
+        <v>587.21</v>
       </c>
       <c r="E4" t="n">
-        <v>563.16</v>
+        <v>564.67</v>
       </c>
       <c r="F4" t="n">
-        <v>576.73</v>
+        <v>577.48</v>
       </c>
       <c r="G4" t="n">
-        <v>4.97</v>
+        <v>4.63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>555</v>
+        <v>117.75</v>
       </c>
       <c r="D5" t="n">
-        <v>515.03</v>
+        <v>115.81</v>
       </c>
       <c r="E5" t="n">
-        <v>523.33</v>
+        <v>112.53</v>
       </c>
       <c r="F5" t="n">
-        <v>523.27</v>
+        <v>112.44</v>
       </c>
       <c r="G5" t="n">
-        <v>6.06</v>
+        <v>4.72</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>498.95</v>
+        <v>550.55</v>
       </c>
       <c r="D6" t="n">
-        <v>471.67</v>
+        <v>515.29</v>
       </c>
       <c r="E6" t="n">
-        <v>457.38</v>
+        <v>523.47</v>
       </c>
       <c r="F6" t="n">
-        <v>453.55</v>
+        <v>523.35</v>
       </c>
       <c r="G6" t="n">
-        <v>10.01</v>
+        <v>5.2</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>186.4</v>
+        <v>2212.6</v>
       </c>
       <c r="D7" t="n">
-        <v>180.63</v>
+        <v>2200.63</v>
       </c>
       <c r="E7" t="n">
-        <v>174.46</v>
+        <v>2102.81</v>
       </c>
       <c r="F7" t="n">
-        <v>165.43</v>
+        <v>2057.34</v>
       </c>
       <c r="G7" t="n">
-        <v>12.67</v>
+        <v>7.55</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>320.6</v>
+        <v>1790.5</v>
       </c>
       <c r="D8" t="n">
-        <v>319.75</v>
+        <v>1741.57</v>
       </c>
       <c r="E8" t="n">
-        <v>306.87</v>
+        <v>1678.23</v>
       </c>
       <c r="F8" t="n">
-        <v>273.79</v>
+        <v>1651.87</v>
       </c>
       <c r="G8" t="n">
-        <v>17.1</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1025</v>
+        <v>184.88</v>
       </c>
       <c r="D9" t="n">
-        <v>956.28</v>
+        <v>181.16</v>
       </c>
       <c r="E9" t="n">
-        <v>949.24</v>
+        <v>174.79</v>
       </c>
       <c r="F9" t="n">
-        <v>849.35</v>
+        <v>165.7</v>
       </c>
       <c r="G9" t="n">
-        <v>20.68</v>
+        <v>11.58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3350</v>
+        <v>507.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3038.01</v>
+        <v>473.38</v>
       </c>
       <c r="E10" t="n">
-        <v>2932.53</v>
+        <v>459.13</v>
       </c>
       <c r="F10" t="n">
-        <v>2658.97</v>
+        <v>454.01</v>
       </c>
       <c r="G10" t="n">
-        <v>25.99</v>
+        <v>11.69</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,30 +804,178 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2174</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2084.52</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1974.76</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1946.05</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>320.3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="E12" t="n">
+        <v>307.69</v>
+      </c>
+      <c r="F12" t="n">
+        <v>273.89</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16.95</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1015.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>962.23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>950.42</v>
+      </c>
+      <c r="F13" t="n">
+        <v>849.74</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3292.6</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3058.75</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2940.07</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2665.59</v>
+      </c>
+      <c r="G14" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10-09-2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>433.7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>419.51</v>
-      </c>
-      <c r="E11" t="n">
-        <v>413.3</v>
-      </c>
-      <c r="F11" t="n">
-        <v>336.58</v>
-      </c>
-      <c r="G11" t="n">
-        <v>28.86</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="C15" t="n">
+        <v>432.1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>420.48</v>
+      </c>
+      <c r="E15" t="n">
+        <v>413.93</v>
+      </c>
+      <c r="F15" t="n">
+        <v>337.33</v>
+      </c>
+      <c r="G15" t="n">
+        <v>28.09</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>414.3</v>
+        <v>593.6</v>
       </c>
       <c r="D2" t="n">
-        <v>404.27</v>
+        <v>586.86</v>
       </c>
       <c r="E2" t="n">
-        <v>395.82</v>
+        <v>564.45</v>
       </c>
       <c r="F2" t="n">
-        <v>399.99</v>
+        <v>577.4299999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>3.58</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -512,19 +512,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>290.05</v>
+        <v>288.7</v>
       </c>
       <c r="D3" t="n">
-        <v>286.01</v>
+        <v>286.26</v>
       </c>
       <c r="E3" t="n">
-        <v>282.05</v>
+        <v>282.16</v>
       </c>
       <c r="F3" t="n">
-        <v>278.12</v>
+        <v>278.2</v>
       </c>
       <c r="G3" t="n">
-        <v>4.29</v>
+        <v>3.77</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>604.2</v>
+        <v>116.85</v>
       </c>
       <c r="D4" t="n">
-        <v>587.21</v>
+        <v>115.78</v>
       </c>
       <c r="E4" t="n">
-        <v>564.67</v>
+        <v>112.52</v>
       </c>
       <c r="F4" t="n">
-        <v>577.48</v>
+        <v>112.43</v>
       </c>
       <c r="G4" t="n">
-        <v>4.63</v>
+        <v>3.93</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>117.75</v>
+        <v>416.55</v>
       </c>
       <c r="D5" t="n">
-        <v>115.81</v>
+        <v>405.16</v>
       </c>
       <c r="E5" t="n">
-        <v>112.53</v>
+        <v>396.17</v>
       </c>
       <c r="F5" t="n">
-        <v>112.44</v>
+        <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>4.72</v>
+        <v>4.14</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -623,19 +623,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>550.55</v>
+        <v>552.3</v>
       </c>
       <c r="D6" t="n">
-        <v>515.29</v>
+        <v>515.35</v>
       </c>
       <c r="E6" t="n">
-        <v>523.47</v>
+        <v>523.51</v>
       </c>
       <c r="F6" t="n">
-        <v>523.35</v>
+        <v>523.36</v>
       </c>
       <c r="G6" t="n">
-        <v>5.2</v>
+        <v>5.53</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2212.6</v>
+        <v>1800</v>
       </c>
       <c r="D7" t="n">
-        <v>2200.63</v>
+        <v>1748.18</v>
       </c>
       <c r="E7" t="n">
-        <v>2102.81</v>
+        <v>1680.74</v>
       </c>
       <c r="F7" t="n">
-        <v>2057.34</v>
+        <v>1651.86</v>
       </c>
       <c r="G7" t="n">
-        <v>7.55</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1790.5</v>
+        <v>500.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1741.57</v>
+        <v>473.15</v>
       </c>
       <c r="E8" t="n">
-        <v>1678.23</v>
+        <v>459</v>
       </c>
       <c r="F8" t="n">
-        <v>1651.87</v>
+        <v>453.98</v>
       </c>
       <c r="G8" t="n">
-        <v>8.390000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>184.88</v>
+        <v>183.75</v>
       </c>
       <c r="D9" t="n">
-        <v>181.16</v>
+        <v>181.12</v>
       </c>
       <c r="E9" t="n">
-        <v>174.79</v>
+        <v>174.77</v>
       </c>
       <c r="F9" t="n">
-        <v>165.7</v>
+        <v>165.69</v>
       </c>
       <c r="G9" t="n">
-        <v>11.58</v>
+        <v>10.9</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>507.1</v>
+        <v>2194.8</v>
       </c>
       <c r="D10" t="n">
-        <v>473.38</v>
+        <v>2094.62</v>
       </c>
       <c r="E10" t="n">
-        <v>459.13</v>
+        <v>1982.91</v>
       </c>
       <c r="F10" t="n">
-        <v>454.01</v>
+        <v>1948.54</v>
       </c>
       <c r="G10" t="n">
-        <v>11.69</v>
+        <v>12.64</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,23 +804,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2174</v>
+        <v>322.1</v>
       </c>
       <c r="D11" t="n">
-        <v>2084.52</v>
+        <v>320.1</v>
       </c>
       <c r="E11" t="n">
-        <v>1974.76</v>
+        <v>307.72</v>
       </c>
       <c r="F11" t="n">
-        <v>1946.05</v>
+        <v>273.9</v>
       </c>
       <c r="G11" t="n">
-        <v>11.71</v>
+        <v>17.6</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -841,23 +841,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>320.3</v>
+        <v>1015</v>
       </c>
       <c r="D12" t="n">
-        <v>320.04</v>
+        <v>962.21</v>
       </c>
       <c r="E12" t="n">
-        <v>307.69</v>
+        <v>950.4</v>
       </c>
       <c r="F12" t="n">
-        <v>273.89</v>
+        <v>849.74</v>
       </c>
       <c r="G12" t="n">
-        <v>16.95</v>
+        <v>19.45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -878,23 +878,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1015.6</v>
+        <v>3300</v>
       </c>
       <c r="D13" t="n">
-        <v>962.23</v>
+        <v>3059</v>
       </c>
       <c r="E13" t="n">
-        <v>950.42</v>
+        <v>2940.21</v>
       </c>
       <c r="F13" t="n">
-        <v>849.74</v>
+        <v>2665.63</v>
       </c>
       <c r="G13" t="n">
-        <v>19.52</v>
+        <v>23.8</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -915,23 +915,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3292.6</v>
+        <v>429.5</v>
       </c>
       <c r="D14" t="n">
-        <v>3058.75</v>
+        <v>420.4</v>
       </c>
       <c r="E14" t="n">
-        <v>2940.07</v>
+        <v>413.87</v>
       </c>
       <c r="F14" t="n">
-        <v>2665.59</v>
+        <v>337.32</v>
       </c>
       <c r="G14" t="n">
-        <v>23.52</v>
+        <v>27.33</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -939,43 +939,6 @@
         </is>
       </c>
       <c r="I14" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>10-09-2026</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>432.1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>420.48</v>
-      </c>
-      <c r="E15" t="n">
-        <v>413.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>337.33</v>
-      </c>
-      <c r="G15" t="n">
-        <v>28.09</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>288.7</v>
+        <v>116.85</v>
       </c>
       <c r="D3" t="n">
-        <v>286.26</v>
+        <v>115.78</v>
       </c>
       <c r="E3" t="n">
-        <v>282.16</v>
+        <v>112.52</v>
       </c>
       <c r="F3" t="n">
-        <v>278.2</v>
+        <v>112.43</v>
       </c>
       <c r="G3" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>116.85</v>
+        <v>416.55</v>
       </c>
       <c r="D4" t="n">
-        <v>115.78</v>
+        <v>405.16</v>
       </c>
       <c r="E4" t="n">
-        <v>112.52</v>
+        <v>396.17</v>
       </c>
       <c r="F4" t="n">
-        <v>112.43</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>3.93</v>
+        <v>4.14</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>416.55</v>
+        <v>552.3</v>
       </c>
       <c r="D5" t="n">
-        <v>405.16</v>
+        <v>515.35</v>
       </c>
       <c r="E5" t="n">
-        <v>396.17</v>
+        <v>523.51</v>
       </c>
       <c r="F5" t="n">
-        <v>400</v>
+        <v>523.36</v>
       </c>
       <c r="G5" t="n">
-        <v>4.14</v>
+        <v>5.53</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>552.3</v>
+        <v>183.75</v>
       </c>
       <c r="D6" t="n">
-        <v>515.35</v>
+        <v>181.12</v>
       </c>
       <c r="E6" t="n">
-        <v>523.51</v>
+        <v>174.77</v>
       </c>
       <c r="F6" t="n">
-        <v>523.36</v>
+        <v>165.69</v>
       </c>
       <c r="G6" t="n">
-        <v>5.53</v>
+        <v>10.9</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1800</v>
+        <v>2194.8</v>
       </c>
       <c r="D7" t="n">
-        <v>1748.18</v>
+        <v>2094.62</v>
       </c>
       <c r="E7" t="n">
-        <v>1680.74</v>
+        <v>1982.91</v>
       </c>
       <c r="F7" t="n">
-        <v>1651.86</v>
+        <v>1948.54</v>
       </c>
       <c r="G7" t="n">
-        <v>8.970000000000001</v>
+        <v>12.64</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>500.3</v>
+        <v>322.1</v>
       </c>
       <c r="D8" t="n">
-        <v>473.15</v>
+        <v>320.1</v>
       </c>
       <c r="E8" t="n">
-        <v>459</v>
+        <v>307.72</v>
       </c>
       <c r="F8" t="n">
-        <v>453.98</v>
+        <v>273.9</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2</v>
+        <v>17.6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -725,28 +725,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>183.75</v>
+        <v>1015</v>
       </c>
       <c r="D9" t="n">
-        <v>181.12</v>
+        <v>962.21</v>
       </c>
       <c r="E9" t="n">
-        <v>174.77</v>
+        <v>950.4</v>
       </c>
       <c r="F9" t="n">
-        <v>165.69</v>
+        <v>849.74</v>
       </c>
       <c r="G9" t="n">
-        <v>10.9</v>
+        <v>19.45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -762,28 +762,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2194.8</v>
+        <v>3300</v>
       </c>
       <c r="D10" t="n">
-        <v>2094.62</v>
+        <v>3059</v>
       </c>
       <c r="E10" t="n">
-        <v>1982.91</v>
+        <v>2940.21</v>
       </c>
       <c r="F10" t="n">
-        <v>1948.54</v>
+        <v>2665.63</v>
       </c>
       <c r="G10" t="n">
-        <v>12.64</v>
+        <v>23.8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -799,28 +799,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10-09-2026</t>
+          <t>11-09-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>322.1</v>
+        <v>429.5</v>
       </c>
       <c r="D11" t="n">
-        <v>320.1</v>
+        <v>420.4</v>
       </c>
       <c r="E11" t="n">
-        <v>307.72</v>
+        <v>413.87</v>
       </c>
       <c r="F11" t="n">
-        <v>273.9</v>
+        <v>337.32</v>
       </c>
       <c r="G11" t="n">
-        <v>17.6</v>
+        <v>27.33</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -828,117 +828,6 @@
         </is>
       </c>
       <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10-09-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>1015</v>
-      </c>
-      <c r="D12" t="n">
-        <v>962.21</v>
-      </c>
-      <c r="E12" t="n">
-        <v>950.4</v>
-      </c>
-      <c r="F12" t="n">
-        <v>849.74</v>
-      </c>
-      <c r="G12" t="n">
-        <v>19.45</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>10-09-2026</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3059</v>
-      </c>
-      <c r="E13" t="n">
-        <v>2940.21</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2665.63</v>
-      </c>
-      <c r="G13" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>10-09-2026</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>429.5</v>
-      </c>
-      <c r="D14" t="n">
-        <v>420.4</v>
-      </c>
-      <c r="E14" t="n">
-        <v>413.87</v>
-      </c>
-      <c r="F14" t="n">
-        <v>337.32</v>
-      </c>
-      <c r="G14" t="n">
-        <v>27.33</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>593.6</v>
+        <v>116.44</v>
       </c>
       <c r="D2" t="n">
-        <v>586.86</v>
+        <v>115.91</v>
       </c>
       <c r="E2" t="n">
-        <v>564.45</v>
+        <v>112.74</v>
       </c>
       <c r="F2" t="n">
-        <v>577.4299999999999</v>
+        <v>112.41</v>
       </c>
       <c r="G2" t="n">
-        <v>2.8</v>
+        <v>3.59</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>116.85</v>
+        <v>416.1</v>
       </c>
       <c r="D3" t="n">
-        <v>115.78</v>
+        <v>406.02</v>
       </c>
       <c r="E3" t="n">
-        <v>112.52</v>
+        <v>396.57</v>
       </c>
       <c r="F3" t="n">
-        <v>112.43</v>
+        <v>399.98</v>
       </c>
       <c r="G3" t="n">
-        <v>3.93</v>
+        <v>4.03</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>416.55</v>
+        <v>562.75</v>
       </c>
       <c r="D4" t="n">
-        <v>405.16</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>396.17</v>
+        <v>523.92</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>523.49</v>
       </c>
       <c r="G4" t="n">
-        <v>4.14</v>
+        <v>7.5</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>552.3</v>
+        <v>496.45</v>
       </c>
       <c r="D5" t="n">
-        <v>515.35</v>
+        <v>473.02</v>
       </c>
       <c r="E5" t="n">
-        <v>523.51</v>
+        <v>458.92</v>
       </c>
       <c r="F5" t="n">
-        <v>523.36</v>
+        <v>453.96</v>
       </c>
       <c r="G5" t="n">
-        <v>5.53</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>183.75</v>
+        <v>1806.5</v>
       </c>
       <c r="D6" t="n">
-        <v>181.12</v>
+        <v>1748.39</v>
       </c>
       <c r="E6" t="n">
-        <v>174.77</v>
+        <v>1680.87</v>
       </c>
       <c r="F6" t="n">
-        <v>165.69</v>
+        <v>1651.89</v>
       </c>
       <c r="G6" t="n">
-        <v>10.9</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -660,19 +660,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2194.8</v>
+        <v>2151.2</v>
       </c>
       <c r="D7" t="n">
-        <v>2094.62</v>
+        <v>2105.91</v>
       </c>
       <c r="E7" t="n">
-        <v>1982.91</v>
+        <v>1990.31</v>
       </c>
       <c r="F7" t="n">
-        <v>1948.54</v>
+        <v>1950.66</v>
       </c>
       <c r="G7" t="n">
-        <v>12.64</v>
+        <v>10.28</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -697,19 +697,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>322.1</v>
+        <v>323.25</v>
       </c>
       <c r="D8" t="n">
-        <v>320.1</v>
+        <v>320.52</v>
       </c>
       <c r="E8" t="n">
-        <v>307.72</v>
+        <v>308.59</v>
       </c>
       <c r="F8" t="n">
-        <v>273.9</v>
+        <v>274</v>
       </c>
       <c r="G8" t="n">
-        <v>17.6</v>
+        <v>17.97</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -734,19 +734,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1015</v>
+        <v>1004.2</v>
       </c>
       <c r="D9" t="n">
-        <v>962.21</v>
+        <v>967.29</v>
       </c>
       <c r="E9" t="n">
-        <v>950.4</v>
+        <v>951.12</v>
       </c>
       <c r="F9" t="n">
-        <v>849.74</v>
+        <v>850</v>
       </c>
       <c r="G9" t="n">
-        <v>19.45</v>
+        <v>18.14</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -771,19 +771,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3300</v>
+        <v>3287</v>
       </c>
       <c r="D10" t="n">
-        <v>3059</v>
+        <v>3079.04</v>
       </c>
       <c r="E10" t="n">
-        <v>2940.21</v>
+        <v>2949.81</v>
       </c>
       <c r="F10" t="n">
-        <v>2665.63</v>
+        <v>2671.81</v>
       </c>
       <c r="G10" t="n">
-        <v>23.8</v>
+        <v>23.03</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -808,19 +808,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>429.5</v>
+        <v>424.65</v>
       </c>
       <c r="D11" t="n">
-        <v>420.4</v>
+        <v>420.99</v>
       </c>
       <c r="E11" t="n">
-        <v>413.87</v>
+        <v>414.72</v>
       </c>
       <c r="F11" t="n">
-        <v>337.32</v>
+        <v>338</v>
       </c>
       <c r="G11" t="n">
-        <v>27.33</v>
+        <v>25.64</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.44</v>
+        <v>287.2</v>
       </c>
       <c r="D2" t="n">
-        <v>115.91</v>
+        <v>286.53</v>
       </c>
       <c r="E2" t="n">
-        <v>112.74</v>
+        <v>282.4</v>
       </c>
       <c r="F2" t="n">
-        <v>112.41</v>
+        <v>278.29</v>
       </c>
       <c r="G2" t="n">
-        <v>3.59</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>416.1</v>
+        <v>116.75</v>
       </c>
       <c r="D3" t="n">
-        <v>406.02</v>
+        <v>115.92</v>
       </c>
       <c r="E3" t="n">
-        <v>396.57</v>
+        <v>112.74</v>
       </c>
       <c r="F3" t="n">
-        <v>399.98</v>
+        <v>112.41</v>
       </c>
       <c r="G3" t="n">
-        <v>4.03</v>
+        <v>3.86</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>562.75</v>
+        <v>419</v>
       </c>
       <c r="D4" t="n">
-        <v>516.4400000000001</v>
+        <v>406.12</v>
       </c>
       <c r="E4" t="n">
-        <v>523.92</v>
+        <v>396.63</v>
       </c>
       <c r="F4" t="n">
-        <v>523.49</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>7.5</v>
+        <v>4.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>496.45</v>
+        <v>562.9</v>
       </c>
       <c r="D5" t="n">
-        <v>473.02</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>458.92</v>
+        <v>523.9299999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>453.96</v>
+        <v>523.49</v>
       </c>
       <c r="G5" t="n">
-        <v>9.359999999999999</v>
+        <v>7.53</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1806.5</v>
+        <v>489.8</v>
       </c>
       <c r="D6" t="n">
-        <v>1748.39</v>
+        <v>474.22</v>
       </c>
       <c r="E6" t="n">
-        <v>1680.87</v>
+        <v>460.37</v>
       </c>
       <c r="F6" t="n">
-        <v>1651.89</v>
+        <v>454.35</v>
       </c>
       <c r="G6" t="n">
-        <v>9.359999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2151.2</v>
+        <v>1797.3</v>
       </c>
       <c r="D7" t="n">
-        <v>2105.91</v>
+        <v>1754.97</v>
       </c>
       <c r="E7" t="n">
-        <v>1990.31</v>
+        <v>1683.04</v>
       </c>
       <c r="F7" t="n">
-        <v>1950.66</v>
+        <v>1651.94</v>
       </c>
       <c r="G7" t="n">
-        <v>10.28</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,23 +693,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>323.25</v>
+        <v>2153.5</v>
       </c>
       <c r="D8" t="n">
-        <v>320.52</v>
+        <v>2105.99</v>
       </c>
       <c r="E8" t="n">
-        <v>308.59</v>
+        <v>1990.35</v>
       </c>
       <c r="F8" t="n">
-        <v>274</v>
+        <v>1950.67</v>
       </c>
       <c r="G8" t="n">
-        <v>17.97</v>
+        <v>10.4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -730,23 +730,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1004.2</v>
+        <v>323.5</v>
       </c>
       <c r="D9" t="n">
-        <v>967.29</v>
+        <v>320.52</v>
       </c>
       <c r="E9" t="n">
-        <v>951.12</v>
+        <v>308.6</v>
       </c>
       <c r="F9" t="n">
-        <v>850</v>
+        <v>274</v>
       </c>
       <c r="G9" t="n">
-        <v>18.14</v>
+        <v>18.06</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -767,23 +767,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3287</v>
+        <v>1026.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3079.04</v>
+        <v>968.03</v>
       </c>
       <c r="E10" t="n">
-        <v>2949.81</v>
+        <v>951.5700000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>2671.81</v>
+        <v>850.11</v>
       </c>
       <c r="G10" t="n">
-        <v>23.03</v>
+        <v>20.75</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -804,30 +804,67 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3276</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3078.68</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2949.59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2671.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>424.65</v>
-      </c>
-      <c r="D11" t="n">
-        <v>420.99</v>
-      </c>
-      <c r="E11" t="n">
-        <v>414.72</v>
-      </c>
-      <c r="F11" t="n">
-        <v>338</v>
-      </c>
-      <c r="G11" t="n">
-        <v>25.64</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="C12" t="n">
+        <v>431</v>
+      </c>
+      <c r="D12" t="n">
+        <v>421.2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>414.85</v>
+      </c>
+      <c r="F12" t="n">
+        <v>338.03</v>
+      </c>
+      <c r="G12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,28 +466,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>287.2</v>
+        <v>116.75</v>
       </c>
       <c r="D2" t="n">
-        <v>286.53</v>
+        <v>115.92</v>
       </c>
       <c r="E2" t="n">
-        <v>282.4</v>
+        <v>112.74</v>
       </c>
       <c r="F2" t="n">
-        <v>278.29</v>
+        <v>112.41</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3.86</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -503,28 +503,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>116.75</v>
+        <v>419</v>
       </c>
       <c r="D3" t="n">
-        <v>115.92</v>
+        <v>406.12</v>
       </c>
       <c r="E3" t="n">
-        <v>112.74</v>
+        <v>396.63</v>
       </c>
       <c r="F3" t="n">
-        <v>112.41</v>
+        <v>400</v>
       </c>
       <c r="G3" t="n">
-        <v>3.86</v>
+        <v>4.75</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -540,28 +540,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>419</v>
+        <v>562.9</v>
       </c>
       <c r="D4" t="n">
-        <v>406.12</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>396.63</v>
+        <v>523.9299999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>400</v>
+        <v>523.49</v>
       </c>
       <c r="G4" t="n">
-        <v>4.75</v>
+        <v>7.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -577,28 +577,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>562.9</v>
+        <v>489.8</v>
       </c>
       <c r="D5" t="n">
-        <v>516.4400000000001</v>
+        <v>474.22</v>
       </c>
       <c r="E5" t="n">
-        <v>523.9299999999999</v>
+        <v>460.37</v>
       </c>
       <c r="F5" t="n">
-        <v>523.49</v>
+        <v>454.35</v>
       </c>
       <c r="G5" t="n">
-        <v>7.53</v>
+        <v>7.8</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -614,28 +614,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>489.8</v>
+        <v>323.5</v>
       </c>
       <c r="D6" t="n">
-        <v>474.22</v>
+        <v>320.52</v>
       </c>
       <c r="E6" t="n">
-        <v>460.37</v>
+        <v>308.6</v>
       </c>
       <c r="F6" t="n">
-        <v>454.35</v>
+        <v>274</v>
       </c>
       <c r="G6" t="n">
-        <v>7.8</v>
+        <v>18.06</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -651,28 +651,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1797.3</v>
+        <v>3276</v>
       </c>
       <c r="D7" t="n">
-        <v>1754.97</v>
+        <v>3078.68</v>
       </c>
       <c r="E7" t="n">
-        <v>1683.04</v>
+        <v>2949.59</v>
       </c>
       <c r="F7" t="n">
-        <v>1651.94</v>
+        <v>2671.75</v>
       </c>
       <c r="G7" t="n">
-        <v>8.800000000000001</v>
+        <v>22.62</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -688,28 +688,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11-09-2026</t>
+          <t>12-09-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2153.5</v>
+        <v>431</v>
       </c>
       <c r="D8" t="n">
-        <v>2105.99</v>
+        <v>421.2</v>
       </c>
       <c r="E8" t="n">
-        <v>1990.35</v>
+        <v>414.85</v>
       </c>
       <c r="F8" t="n">
-        <v>1950.67</v>
+        <v>338.03</v>
       </c>
       <c r="G8" t="n">
-        <v>10.4</v>
+        <v>27.5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -717,154 +717,6 @@
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>323.5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>320.52</v>
-      </c>
-      <c r="E9" t="n">
-        <v>308.6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>274</v>
-      </c>
-      <c r="G9" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>1026.5</v>
-      </c>
-      <c r="D10" t="n">
-        <v>968.03</v>
-      </c>
-      <c r="E10" t="n">
-        <v>951.5700000000001</v>
-      </c>
-      <c r="F10" t="n">
-        <v>850.11</v>
-      </c>
-      <c r="G10" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>MCX</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3276</v>
-      </c>
-      <c r="D11" t="n">
-        <v>3078.68</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2949.59</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2671.75</v>
-      </c>
-      <c r="G11" t="n">
-        <v>22.62</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>🟢 Positive Breakout</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>11-09-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>431</v>
-      </c>
-      <c r="D12" t="n">
-        <v>421.2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>414.85</v>
-      </c>
-      <c r="F12" t="n">
-        <v>338.03</v>
-      </c>
-      <c r="G12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>

--- a/Final_Breakout_List.xlsx
+++ b/Final_Breakout_List.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,23 +471,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>116.75</v>
+        <v>287.2</v>
       </c>
       <c r="D2" t="n">
-        <v>115.92</v>
+        <v>286.53</v>
       </c>
       <c r="E2" t="n">
-        <v>112.74</v>
+        <v>282.4</v>
       </c>
       <c r="F2" t="n">
-        <v>112.41</v>
+        <v>278.29</v>
       </c>
       <c r="G2" t="n">
-        <v>3.86</v>
+        <v>3.2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -508,23 +508,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>419</v>
+        <v>116.75</v>
       </c>
       <c r="D3" t="n">
-        <v>406.12</v>
+        <v>115.92</v>
       </c>
       <c r="E3" t="n">
-        <v>396.63</v>
+        <v>112.74</v>
       </c>
       <c r="F3" t="n">
-        <v>400</v>
+        <v>112.41</v>
       </c>
       <c r="G3" t="n">
-        <v>4.75</v>
+        <v>3.86</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -545,23 +545,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>562.9</v>
+        <v>419</v>
       </c>
       <c r="D4" t="n">
-        <v>516.4400000000001</v>
+        <v>406.12</v>
       </c>
       <c r="E4" t="n">
-        <v>523.9299999999999</v>
+        <v>396.63</v>
       </c>
       <c r="F4" t="n">
-        <v>523.49</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>7.53</v>
+        <v>4.75</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -582,23 +582,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>489.8</v>
+        <v>562.9</v>
       </c>
       <c r="D5" t="n">
-        <v>474.22</v>
+        <v>516.4400000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>460.37</v>
+        <v>523.9299999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>454.35</v>
+        <v>523.49</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>7.53</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -619,23 +619,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>323.5</v>
+        <v>489.8</v>
       </c>
       <c r="D6" t="n">
-        <v>320.52</v>
+        <v>474.22</v>
       </c>
       <c r="E6" t="n">
-        <v>308.6</v>
+        <v>460.37</v>
       </c>
       <c r="F6" t="n">
-        <v>274</v>
+        <v>454.35</v>
       </c>
       <c r="G6" t="n">
-        <v>18.06</v>
+        <v>7.8</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -656,23 +656,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3276</v>
+        <v>1797.3</v>
       </c>
       <c r="D7" t="n">
-        <v>3078.68</v>
+        <v>1754.97</v>
       </c>
       <c r="E7" t="n">
-        <v>2949.59</v>
+        <v>1683.04</v>
       </c>
       <c r="F7" t="n">
-        <v>2671.75</v>
+        <v>1651.94</v>
       </c>
       <c r="G7" t="n">
-        <v>22.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -693,30 +693,178 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2153.5</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2105.99</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1990.35</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1950.67</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>320.52</v>
+      </c>
+      <c r="E9" t="n">
+        <v>308.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>274</v>
+      </c>
+      <c r="G9" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1026.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>968.03</v>
+      </c>
+      <c r="E10" t="n">
+        <v>951.5700000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>850.11</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MCX</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3276</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3078.68</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2949.59</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2671.75</v>
+      </c>
+      <c r="G11" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>🟢 Positive Breakout</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>BHEL</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C12" t="n">
         <v>431</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D12" t="n">
         <v>421.2</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E12" t="n">
         <v>414.85</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F12" t="n">
         <v>338.03</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G12" t="n">
         <v>27.5</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>🟢 Positive Breakout</t>
         </is>
